--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 36.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 36.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,16 +526,14 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -545,7 +543,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -557,6 +555,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-143.6700000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3.21875e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-50.825</v>
+      </c>
+      <c r="F2" t="n">
+        <v/>
+      </c>
+      <c r="G2" t="n">
+        <v/>
+      </c>
+      <c r="H2" t="n">
+        <v/>
+      </c>
+      <c r="I2" t="n">
+        <v/>
+      </c>
+      <c r="J2" t="n">
+        <v>23.50819051819527</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.64734640804066</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>y = 13.138x + -30005.753</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-30005.75286025774</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.288885276243789e-10</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>143.6700000000001</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000000104e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8220353692950022</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-125.48</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3.33289e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-52.548</v>
+      </c>
+      <c r="F3" t="n">
+        <v/>
+      </c>
+      <c r="G3" t="n">
+        <v/>
+      </c>
+      <c r="H3" t="n">
+        <v/>
+      </c>
+      <c r="I3" t="n">
+        <v/>
+      </c>
+      <c r="J3" t="n">
+        <v>25.38407689878018</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.77810386746992</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>y = 13.547x + -29591.617</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-29591.61726137361</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>4.038184347860714e-10</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>125.48</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000000025e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8230149902873902</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-110.5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3.37632e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-53.344</v>
+      </c>
+      <c r="F4" t="n">
+        <v/>
+      </c>
+      <c r="G4" t="n">
+        <v/>
+      </c>
+      <c r="H4" t="n">
+        <v/>
+      </c>
+      <c r="I4" t="n">
+        <v/>
+      </c>
+      <c r="J4" t="n">
+        <v>26.44943764494086</v>
+      </c>
+      <c r="K4" t="n">
+        <v>85.95154901116902</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>y = 14.129x + -30378.455</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-30378.4553114298</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.636065939816327e-09</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>110.6999999999998</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.00000000000067e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.823396817960149</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-104.4099999999999</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3.41131e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-53.944</v>
+      </c>
+      <c r="F5" t="n">
+        <v/>
+      </c>
+      <c r="G5" t="n">
+        <v/>
+      </c>
+      <c r="H5" t="n">
+        <v/>
+      </c>
+      <c r="I5" t="n">
+        <v/>
+      </c>
+      <c r="J5" t="n">
+        <v>25.12163405170091</v>
+      </c>
+      <c r="K5" t="n">
+        <v>85.9639341652811</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>y = 14.172x + -30022.533</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-30022.53268889376</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>4.660672964029683e-09</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>109.9700000000003</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000000014e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8238277432532697</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-106.3499999999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3.44068e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-54.467</v>
+      </c>
+      <c r="F6" t="n">
+        <v/>
+      </c>
+      <c r="G6" t="n">
+        <v/>
+      </c>
+      <c r="H6" t="n">
+        <v/>
+      </c>
+      <c r="I6" t="n">
+        <v/>
+      </c>
+      <c r="J6" t="n">
+        <v>20.37922166693785</v>
+      </c>
+      <c r="K6" t="n">
+        <v>85.5311086830211</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>y = 12.795x + -26648.468</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-26648.46776713715</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>9.443867881205971e-11</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>115.9300000000003</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000000059e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8241800051206308</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-97.43000000000029</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3.47512e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-55.02</v>
+      </c>
+      <c r="F7" t="n">
+        <v/>
+      </c>
+      <c r="G7" t="n">
+        <v/>
+      </c>
+      <c r="H7" t="n">
+        <v/>
+      </c>
+      <c r="I7" t="n">
+        <v/>
+      </c>
+      <c r="J7" t="n">
+        <v>19.09617276326737</v>
+      </c>
+      <c r="K7" t="n">
+        <v>85.55717016970785</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>y = 12.870x + -26433.480</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-26433.47969658138</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>8.82816451659133e-10</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>112.54</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000013293e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8246520731325662</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-92.49000000000024</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3.50007e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-55.467</v>
+      </c>
+      <c r="F8" t="n">
+        <v/>
+      </c>
+      <c r="G8" t="n">
+        <v/>
+      </c>
+      <c r="H8" t="n">
+        <v/>
+      </c>
+      <c r="I8" t="n">
+        <v/>
+      </c>
+      <c r="J8" t="n">
+        <v>18.57042870385614</v>
+      </c>
+      <c r="K8" t="n">
+        <v>85.55650137490484</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>y = 12.868x + -26106.723</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-26106.72336765886</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>3.539659406776374e-10</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>109.6799999999998</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.00000000000003e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8250918689372405</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-87.17000000000007</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.52865e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-55.902</v>
+      </c>
+      <c r="F9" t="n">
+        <v/>
+      </c>
+      <c r="G9" t="n">
+        <v/>
+      </c>
+      <c r="H9" t="n">
+        <v/>
+      </c>
+      <c r="I9" t="n">
+        <v/>
+      </c>
+      <c r="J9" t="n">
+        <v>17.67260199782607</v>
+      </c>
+      <c r="K9" t="n">
+        <v>85.53386345187783</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>y = 12.803x + -25655.123</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-25655.12322408354</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.878325676382569e-10</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>107.0499999999997</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.00000000000045e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8255544971559319</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-84.57999999999993</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3.55368e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-56.329</v>
+      </c>
+      <c r="F10" t="n">
+        <v/>
+      </c>
+      <c r="G10" t="n">
+        <v/>
+      </c>
+      <c r="H10" t="n">
+        <v/>
+      </c>
+      <c r="I10" t="n">
+        <v/>
+      </c>
+      <c r="J10" t="n">
+        <v>16.70472601548688</v>
+      </c>
+      <c r="K10" t="n">
+        <v>85.50959463695597</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>y = 12.733x + -25182.419</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-25182.41937332417</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>5.928004529350924e-10</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>106.23</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8260728795718459</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-84.43999999999983</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3.57908e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-56.714</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.03138138138137649</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.5012278308321236</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.968312757201658</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.384741144414158</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>85.10441995810237</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>y = 11.675x + -22770.765</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-22770.76496777428</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.041348318209447e-11</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>108.9100000000001</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.00000000000002e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8265402066269282</v>
       </c>
     </row>
   </sheetData>
@@ -570,7 +1088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -674,16 +1192,14 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -693,7 +1209,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -705,6 +1221,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-147.8499999999999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3.50084e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-61.977</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1772397094430852</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.7795572916666338</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.421179302045696</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.777639344262239</v>
+      </c>
+      <c r="J2" t="n">
+        <v>17.85262538132501</v>
+      </c>
+      <c r="K2" t="n">
+        <v>84.15726188596206</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>y = 9.772x + -17015.433</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-17015.43293009196</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>5.078255915022336e-09</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>168.1699999999998</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8267167429692154</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-119.97</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3.64831e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-63.364</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.3508177570093708</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.388055130168467</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.053706111833499</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.490704070407043</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>84.82174617823858</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>y = 11.035x + -17987.868</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-17987.86788757323</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>7.02470719264075e-12</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>144.75</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8273802921156419</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-117.75</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3.68465e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-63.85</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.5441696113074458</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.3812307692307739</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.394678217821834</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.101371951219499</v>
+      </c>
+      <c r="J4" t="n">
+        <v>14.33007810820176</v>
+      </c>
+      <c r="K4" t="n">
+        <v>84.64552725877967</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>y = 10.669x + -16970.612</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-16970.61181723978</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>3.514883384618697e-12</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>143.9200000000001</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8276142146253896</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-117.5999999999999</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3.70409e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-64.23099999999999</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.02038043478261347</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.209090909090921</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.8908616187989684</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.450120870265968</v>
+      </c>
+      <c r="J5" t="n">
+        <v>14.88228165027338</v>
+      </c>
+      <c r="K5" t="n">
+        <v>84.40234898269946</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>y = 10.203x + -15954.478</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-15954.47778077594</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>4.780424302601326e-11</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>146.0599999999999</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.827788539465369</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-117.8099999999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3.71536e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-64.538</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1767584097859319</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.3065708418891312</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.6573793103448126</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.261358811040396</v>
+      </c>
+      <c r="J6" t="n">
+        <v>14.19285092928548</v>
+      </c>
+      <c r="K6" t="n">
+        <v>84.14928176602405</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>y = 9.759x + -15063.353</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-15063.35333011143</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>3.537786588235589e-09</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>148.5899999999999</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.00000000000001e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8280178828800255</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-111.8699999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3.72856e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-64.81999999999999</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.2288640595903332</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.4527363184080048</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.078364779874308</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.56942148760332</v>
+      </c>
+      <c r="J7" t="n">
+        <v>13.64862167789395</v>
+      </c>
+      <c r="K7" t="n">
+        <v>84.41322827390229</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>y = 10.223x + -15644.677</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-15644.67735598397</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>9.417652825247201e-12</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>143.0599999999999</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8282691527004641</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-110.8500000000001</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3.74415e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-65.13500000000001</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.1970085470085128</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.1734999999999949</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.6999999999999998</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.300166666666741</v>
+      </c>
+      <c r="J8" t="n">
+        <v>13.4199996376029</v>
+      </c>
+      <c r="K8" t="n">
+        <v>84.14667144194296</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>y = 9.755x + -14710.897</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-14710.89724905403</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>3.794007527303487e-10</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>144.6500000000001</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8285524028515685</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-108.1799999999998</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.75922e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-65.443</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1494522691705863</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.4786046511628182</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.325192307692328</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.725596816976154</v>
+      </c>
+      <c r="J9" t="n">
+        <v>12.42720796277315</v>
+      </c>
+      <c r="K9" t="n">
+        <v>84.13055082820483</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>y = 9.728x + -14498.221</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-14498.22070462981</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>8.694514854141747e-10</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>144.48</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.00000000000001e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8288695539065057</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-98.48000000000002</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3.77394e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-65.733</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.04395604395604338</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.6840236686390722</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.30755627009645</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.507154213036602</v>
+      </c>
+      <c r="J10" t="n">
+        <v>9.895827623414803</v>
+      </c>
+      <c r="K10" t="n">
+        <v>84.35986172357947</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>y = 10.126x + -14950.917</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-14950.91672660913</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>8.155609730440974e-11</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>135.3600000000001</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.829204368396678</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-97.95999999999981</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3.7891e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-66.05800000000001</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.4490153172866617</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.4681069958848001</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.016145833333231</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.804115853658517</v>
+      </c>
+      <c r="J11" t="n">
+        <v>10.19214685588772</v>
+      </c>
+      <c r="K11" t="n">
+        <v>83.96894711286227</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>y = 9.465x + -13765.050</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-13765.04988246847</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.22834557659326e-08</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>138.99</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.00000000000012e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8295666008595675</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-88.23000000000002</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3.80504e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-66.336</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.4557894736842675</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.199757281553413</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.129485396383898</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.925560975609695</v>
+      </c>
+      <c r="J12" t="n">
+        <v>4.971492849267263</v>
+      </c>
+      <c r="K12" t="n">
+        <v>84.15566797095875</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>y = 9.770x + -14076.702</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-14076.70171652841</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>3.469974662060197e-08</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>130.78</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.000000000000875e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8299365425505235</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-85.86999999999989</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3.81827e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-66.628</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.2451704545454759</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.8814732142856925</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.314577259475294</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.671514543630914</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.749463182120563</v>
+      </c>
+      <c r="K13" t="n">
+        <v>83.97978427177917</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>y = 9.482x + -13489.607</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-13489.6073187469</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>3.271293927605402e-10</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>131.46</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.000000000000727e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8303279715955958</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-85.06000000000017</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3.83316e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-66.899</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.0808259587020501</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.4786666666667301</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.9040579710144514</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.022670375521478</v>
+      </c>
+      <c r="J14" t="n">
+        <v>6.281280071470497</v>
+      </c>
+      <c r="K14" t="n">
+        <v>83.63784420144287</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>y = 8.969x + -12575.630</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-12575.63001602633</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>4.147818104728947e-10</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>132.6300000000001</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.000000000000242e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8307235729535724</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-79.33999999999992</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3.84765e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-67.218</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.1796721311475469</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.2934354485776941</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.5199213630406117</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.355986696230574</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.283029918440783</v>
+      </c>
+      <c r="K15" t="n">
+        <v>83.29991164472642</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>y = 8.512x + -11781.296</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-11781.29576294632</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.420342748467271e-10</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>130.95</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.000000000000402e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8311395019231349</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-80.6400000000001</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3.85963e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-67.48</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.04051767762398824</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.4305132751383817</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.560132086084758</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.452152241944754</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>83.14660460730367</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>y = 8.320x + -11364.999</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-11364.99916730823</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>3.087387867397427e-08</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>133.3299999999999</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.000000000002781e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8315541560369971</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-70.63000000000011</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3.87442e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-67.748</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.603937007874693</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.07665289256198038</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.8987261146498073</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.570870113492997</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.3751499724847109</v>
+      </c>
+      <c r="K17" t="n">
+        <v>82.97218045826641</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>y = 8.112x + -10949.683</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-10949.68281148155</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>2.798315625394458e-08</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>125.6400000000001</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.000000000005385e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8319803920677162</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-64.16999999999985</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3.88796e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-68.038</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.2303303303303584</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.9777292576418939</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.195612708018148</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.132894736842174</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>82.62237828107673</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>y = 7.723x + -10281.778</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-10281.77806303802</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.8818470196258528</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>121.74</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.669899940135306e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.79501592205168</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-59.45000000000005</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3.89977e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-68.301</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.6694835680751694</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.589969604863239</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.227838258164906</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.699704433497526</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>82.2367987790237</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>y = 7.335x + -9629.455</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-9629.454571360633</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>3.086157898744619e-13</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>118.74</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8328563482705436</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-63.85000000000014</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3.91183e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-68.59</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.2893630337410727</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.6674130663856573</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.399912310493249</v>
+      </c>
+      <c r="I20" t="n">
+        <v>155.728650377143</v>
+      </c>
+      <c r="J20" t="n">
+        <v>6.500568358078487</v>
+      </c>
+      <c r="K20" t="n">
+        <v>81.75990489710814</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>y = 6.905x + -8927.526</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-8927.526278065347</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>3.316908048150845e-10</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>125.49</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.000000000000003e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.833299599175079</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-56.13000000000011</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3.92731e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-68.875</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.5140700093249601</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.5680966415857508</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.791614224706498</v>
+      </c>
+      <c r="I21" t="n">
+        <v>121.9464316596788</v>
+      </c>
+      <c r="J21" t="n">
+        <v>6.580861691306702</v>
+      </c>
+      <c r="K21" t="n">
+        <v>81.08546369845592</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>y = 6.375x + -8109.956</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-8109.955938307442</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>2.183882676503599e-09</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>120.8099999999999</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.000000000001101e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.833754606305494</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-51.16999999999985</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3.93865e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-69.149</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.04195121951233</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.609354838709598</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.302150537634419</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.799421128798766</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>80.11546595980685</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>y = 5.739x + -7160.385</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-7160.385382407118</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>5.190226086266899e-10</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>118.0999999999999</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.000000000000021e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8342102281061093</v>
       </c>
     </row>
   </sheetData>
@@ -718,7 +2326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -822,16 +2430,14 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -841,7 +2447,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -853,6 +2459,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-146.52</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3.42798e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-53.004</v>
+      </c>
+      <c r="F2" t="n">
+        <v/>
+      </c>
+      <c r="G2" t="n">
+        <v/>
+      </c>
+      <c r="H2" t="n">
+        <v/>
+      </c>
+      <c r="I2" t="n">
+        <v/>
+      </c>
+      <c r="J2" t="n">
+        <v>19.71343064952844</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.43829387511607</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>y = 12.534x + -26214.443</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-26214.44258555676</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>5.541298658147226e-09</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>146.52</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000003183e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8225065740333724</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-121.27</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3.54276e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-54.831</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1477453580901716</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.5744803695150319</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.663030303030276</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.14095878889816</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.3846080067192</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>y = 12.387x + -24758.821</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-24758.82138059601</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>3.812023470129079e-11</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>121.5799999999999</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8229630447503807</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-108.3199999999999</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3.57814e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-55.537</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.16572164948454</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.8999999999999132</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.43159509202457</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.099876644736819</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>85.37456612357062</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>y = 12.360x + -24325.726</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-24325.7259433379</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>6.808290655865747e-10</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>117.4599999999998</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000000043e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8233357022393375</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-96.56000000000017</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3.6039e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-56.04</v>
+      </c>
+      <c r="F5" t="n">
+        <v/>
+      </c>
+      <c r="G5" t="n">
+        <v/>
+      </c>
+      <c r="H5" t="n">
+        <v/>
+      </c>
+      <c r="I5" t="n">
+        <v/>
+      </c>
+      <c r="J5" t="n">
+        <v>19.61729010513972</v>
+      </c>
+      <c r="K5" t="n">
+        <v>85.70559847180388</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>y = 13.317x + -25977.778</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-25977.77842972598</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.540732805980894e-10</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>110.0999999999999</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.823675887328453</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-89.77999999999997</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3.63083e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-56.484</v>
+      </c>
+      <c r="F6" t="n">
+        <v/>
+      </c>
+      <c r="G6" t="n">
+        <v/>
+      </c>
+      <c r="H6" t="n">
+        <v/>
+      </c>
+      <c r="I6" t="n">
+        <v/>
+      </c>
+      <c r="J6" t="n">
+        <v>18.65952497497768</v>
+      </c>
+      <c r="K6" t="n">
+        <v>85.63825527665279</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>y = 13.111x + -25258.808</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-25258.80810553961</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.227799825251502e-11</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>107.1399999999999</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000001834e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8239646086605117</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-92.33999999999992</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3.65282e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-56.898</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.080913348946136</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.528904847396861</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.964970645792476</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.215358361774638</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>85.32604517599174</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>y = 12.231x + -23245.160</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-23245.16000230626</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>3.800168648515154e-13</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>112.8099999999999</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8242499916326076</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-80.06999999999994</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3.67409e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-57.278</v>
+      </c>
+      <c r="F8" t="n">
+        <v/>
+      </c>
+      <c r="G8" t="n">
+        <v/>
+      </c>
+      <c r="H8" t="n">
+        <v/>
+      </c>
+      <c r="I8" t="n">
+        <v/>
+      </c>
+      <c r="J8" t="n">
+        <v>15.63948427037806</v>
+      </c>
+      <c r="K8" t="n">
+        <v>85.47432271066397</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>y = 12.634x + -23804.865</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-23804.86509309887</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.099531431124705e-10</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>103.8699999999999</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000000081e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8245862782282972</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-82</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.69758e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-57.632</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.05148148148148767</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.8073550212163488</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.814019520851761</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.350581915846059</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>85.12585822455783</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>y = 11.727x + -21804.109</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-21804.10890993775</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.046865820866358e-09</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>108.79</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000001189e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8249583368294882</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-78.88000000000011</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3.71604e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-57.955</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.2517307692307522</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.619925742574302</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.028626692456536</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.556556986170798</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>85.03653081940523</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>y = 11.515x + -21190.063</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-21190.06294064082</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>4.025590510433788e-10</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>106.95</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8253120335653574</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-69.8599999999999</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3.73813e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-58.296</v>
+      </c>
+      <c r="F11" t="n">
+        <v/>
+      </c>
+      <c r="G11" t="n">
+        <v/>
+      </c>
+      <c r="H11" t="n">
+        <v/>
+      </c>
+      <c r="I11" t="n">
+        <v/>
+      </c>
+      <c r="J11" t="n">
+        <v>11.37329456554101</v>
+      </c>
+      <c r="K11" t="n">
+        <v>85.26673206274738</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>y = 12.077x + -22025.435</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-22025.43501170534</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.196517491302546e-10</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>99.42000000000007</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8256951017135238</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-65.13000000000011</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3.76013e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-58.604</v>
+      </c>
+      <c r="F12" t="n">
+        <v/>
+      </c>
+      <c r="G12" t="n">
+        <v/>
+      </c>
+      <c r="H12" t="n">
+        <v/>
+      </c>
+      <c r="I12" t="n">
+        <v/>
+      </c>
+      <c r="J12" t="n">
+        <v>7.841791312716895</v>
+      </c>
+      <c r="K12" t="n">
+        <v>85.01765938439033</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>y = 11.471x + -20698.133</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-20698.13310447288</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>4.797252980949783e-10</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>98.35000000000014</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.000000000000296e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8260742225357488</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-60.26999999999998</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3.77787e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-58.922</v>
+      </c>
+      <c r="F13" t="n">
+        <v/>
+      </c>
+      <c r="G13" t="n">
+        <v/>
+      </c>
+      <c r="H13" t="n">
+        <v/>
+      </c>
+      <c r="I13" t="n">
+        <v/>
+      </c>
+      <c r="J13" t="n">
+        <v>5.186029911891853</v>
+      </c>
+      <c r="K13" t="n">
+        <v>84.75612030995326</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>y = 10.896x + -19445.368</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-19445.36752758491</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>6.374504475335359e-10</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>95.68000000000006</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8264435291272435</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-63.88000000000011</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3.79782e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-59.199</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.1277108433734979</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.040674955595003</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.920330739299603</v>
+      </c>
+      <c r="I14" t="n">
+        <v>209.3868852459078</v>
+      </c>
+      <c r="J14" t="n">
+        <v>7.128377908996096</v>
+      </c>
+      <c r="K14" t="n">
+        <v>84.64922985880173</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>y = 10.677x + -18845.873</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-18845.87304426603</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.614136944123934e-10</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>99.58000000000015</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.000000000000005e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8268357757718611</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-56.87000000000012</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3.81492e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-59.501</v>
+      </c>
+      <c r="F15" t="n">
+        <v/>
+      </c>
+      <c r="G15" t="n">
+        <v/>
+      </c>
+      <c r="H15" t="n">
+        <v/>
+      </c>
+      <c r="I15" t="n">
+        <v/>
+      </c>
+      <c r="J15" t="n">
+        <v>2.834550189885208</v>
+      </c>
+      <c r="K15" t="n">
+        <v>84.5964145509308</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>y = 10.572x + -18479.296</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-18479.29582233515</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>3.227074115855774e-09</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>93.59999999999991</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.000000000000436e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8272286976949332</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-57.3599999999999</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3.83809e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-59.847</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.2510101010100745</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.7450349650349404</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.847736976942892</v>
+      </c>
+      <c r="I16" t="n">
+        <v>526.3167910447532</v>
+      </c>
+      <c r="J16" t="n">
+        <v>7.739901477832682</v>
+      </c>
+      <c r="K16" t="n">
+        <v>83.8873259842145</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>y = 9.338x + -16080.876</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-16080.87588875104</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.543672370184439e-10</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>98.02999999999997</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.000000000000143e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.827645713622947</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-52.52999999999997</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3.85732e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-60.142</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.2927835051546179</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.346588693957132</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.769415807560104</v>
+      </c>
+      <c r="I17" t="n">
+        <v>669.3191943127331</v>
+      </c>
+      <c r="J17" t="n">
+        <v>7.911368909512697</v>
+      </c>
+      <c r="K17" t="n">
+        <v>83.84950143556108</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>y = 9.280x + -15817.825</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-15817.82457141673</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>8.487538027545064e-12</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>93.6099999999999</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.000000000000003e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8281011956147474</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-49.8599999999999</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3.87449e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-60.412</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.2045614035087634</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.137337192474646</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.151304347826123</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>8.168038353975263</v>
+      </c>
+      <c r="K18" t="n">
+        <v>83.03150958013086</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>y = 8.182x + -13761.671</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-13761.67120707656</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.91260812370299e-08</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>94.37999999999988</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.000000000000507e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8285358283569312</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-45.97999999999979</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3.89213e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-60.687</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.5530120481928154</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.153514376996758</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.654231119199382</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>8.684304551254741</v>
+      </c>
+      <c r="K19" t="n">
+        <v>82.77435677241263</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>y = 7.887x + -13120.676</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-13120.67620608886</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>8.548719048641945e-09</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>90.7199999999998</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.00000000000151e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8289594362779041</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-50.63999999999987</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3.90892e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-60.925</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.273921971252559</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.2238938053097252</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.246821392532797</v>
+      </c>
+      <c r="I20" t="n">
+        <v>273.0250950570233</v>
+      </c>
+      <c r="J20" t="n">
+        <v>6.754679243697739</v>
+      </c>
+      <c r="K20" t="n">
+        <v>82.73382390880052</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>y = 7.843x + -12929.071</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-12929.07100717827</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>2.025638953728457e-08</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>95.67999999999984</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.000000000000195e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8294069796176506</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-47.6400000000001</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3.92624e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-61.223</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.1561624649859986</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.557309941520447</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.266279069767455</v>
+      </c>
+      <c r="I21" t="n">
+        <v>419.6310495627191</v>
+      </c>
+      <c r="J21" t="n">
+        <v>7.07559643093564</v>
+      </c>
+      <c r="K21" t="n">
+        <v>81.93453877658332</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>y = 7.057x + -11470.572</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-11470.57186577493</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.752050007909983e-08</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>95.16000000000008</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.000000000000456e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.829831926004313</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-43.4699999999998</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3.94348e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-61.501</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.07575757575757334</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.5641089108910526</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.468669527897076</v>
+      </c>
+      <c r="I22" t="n">
+        <v>667.2289351851733</v>
+      </c>
+      <c r="J22" t="n">
+        <v>7.108552881401914</v>
+      </c>
+      <c r="K22" t="n">
+        <v>81.02447070953967</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>y = 6.331x + -10139.899</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-10139.89883350505</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>5.821268237732372e-09</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>93.57999999999993</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.000000000000031e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8302774363535452</v>
       </c>
     </row>
   </sheetData>
@@ -866,7 +3564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -970,16 +3668,14 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -989,7 +3685,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -1001,6 +3697,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-293.3000000000002</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3.26362e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-48.614</v>
+      </c>
+      <c r="F2" t="n">
+        <v/>
+      </c>
+      <c r="G2" t="n">
+        <v/>
+      </c>
+      <c r="H2" t="n">
+        <v/>
+      </c>
+      <c r="I2" t="n">
+        <v/>
+      </c>
+      <c r="J2" t="n">
+        <v>10.04293692076986</v>
+      </c>
+      <c r="K2" t="n">
+        <v>82.87246204251296</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>y = 7.997x + -17035.165</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-17035.16492583882</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.43552925947184e-09</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>293.3000000000002</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000000019e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8266837363685654</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-227.8900000000001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3.50995e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-51.585</v>
+      </c>
+      <c r="F3" t="n">
+        <v/>
+      </c>
+      <c r="G3" t="n">
+        <v/>
+      </c>
+      <c r="H3" t="n">
+        <v/>
+      </c>
+      <c r="I3" t="n">
+        <v/>
+      </c>
+      <c r="J3" t="n">
+        <v>13.23688585896683</v>
+      </c>
+      <c r="K3" t="n">
+        <v>84.29810912628179</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>y = 10.015x + -19903.461</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-19903.46052767711</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>9.229892964243688e-10</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>227.8900000000001</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000001121e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8273785291472333</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-211.7599999999998</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3.5845e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-52.828</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.18052805280527</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.022495894909689</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.760033726812839</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.833603082851622</v>
+      </c>
+      <c r="J4" t="n">
+        <v>29.84174166225471</v>
+      </c>
+      <c r="K4" t="n">
+        <v>84.47525403802632</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>y = 10.339x + -20017.323</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-20017.32349947653</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>6.958771555508287e-09</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>211.7599999999998</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000001104e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8276890499240875</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-188.9400000000001</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3.62271e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-53.561</v>
+      </c>
+      <c r="F5" t="n">
+        <v/>
+      </c>
+      <c r="G5" t="n">
+        <v/>
+      </c>
+      <c r="H5" t="n">
+        <v/>
+      </c>
+      <c r="I5" t="n">
+        <v/>
+      </c>
+      <c r="J5" t="n">
+        <v>16.09407295805488</v>
+      </c>
+      <c r="K5" t="n">
+        <v>85.08080360645602</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>y = 11.619x + -22291.095</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-22291.09534960582</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>7.072475311902202e-10</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>188.9400000000001</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000001934e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8279820818544708</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-179.23</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3.65422e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-54.167</v>
+      </c>
+      <c r="F6" t="n">
+        <v/>
+      </c>
+      <c r="G6" t="n">
+        <v/>
+      </c>
+      <c r="H6" t="n">
+        <v/>
+      </c>
+      <c r="I6" t="n">
+        <v/>
+      </c>
+      <c r="J6" t="n">
+        <v>16.96308812353972</v>
+      </c>
+      <c r="K6" t="n">
+        <v>85.23320703257785</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>y = 11.992x + -22726.896</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-22726.89571323263</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>6.243939984793676e-12</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>179.23</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000000042e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8282968464883121</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-177.27</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3.68586e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-54.696</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.2501901140684187</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.9626220362621808</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.058834951456245</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.845380434782664</v>
+      </c>
+      <c r="J7" t="n">
+        <v>43.90265856437524</v>
+      </c>
+      <c r="K7" t="n">
+        <v>85.13928882704994</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>y = 11.759x + -21966.103</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-21966.10306427179</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>5.783910471788046e-10</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>177.27</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000000097e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.828662381842392</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-166.8199999999999</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3.71476e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-55.183</v>
+      </c>
+      <c r="F8" t="n">
+        <v/>
+      </c>
+      <c r="G8" t="n">
+        <v/>
+      </c>
+      <c r="H8" t="n">
+        <v/>
+      </c>
+      <c r="I8" t="n">
+        <v/>
+      </c>
+      <c r="J8" t="n">
+        <v>18.62414649420217</v>
+      </c>
+      <c r="K8" t="n">
+        <v>85.50323347619953</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>y = 12.715x + -23546.807</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-23546.80736587457</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>8.963737035817436e-11</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>166.8199999999999</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000000196e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8290488156660615</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-163.8099999999999</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.74348e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-55.595</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.09807460890493576</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.927534246575372</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.711515664690904</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.044092219020165</v>
+      </c>
+      <c r="J9" t="n">
+        <v>54.98396604574329</v>
+      </c>
+      <c r="K9" t="n">
+        <v>85.40079520789749</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>y = 12.431x + -22713.018</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-22713.01822669869</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.981859031213007e-10</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>163.8099999999999</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000000013e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8294575281000326</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-151.5999999999999</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3.77123e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-56.006</v>
+      </c>
+      <c r="F10" t="n">
+        <v/>
+      </c>
+      <c r="G10" t="n">
+        <v/>
+      </c>
+      <c r="H10" t="n">
+        <v/>
+      </c>
+      <c r="I10" t="n">
+        <v/>
+      </c>
+      <c r="J10" t="n">
+        <v>20.1917131174878</v>
+      </c>
+      <c r="K10" t="n">
+        <v>85.7844482803424</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>y = 13.567x + -24584.774</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-24584.77447526265</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>5.474393743273697e-09</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>151.5999999999999</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000000467e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8298920214506248</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-151.0999999999999</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3.7933e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-56.336</v>
+      </c>
+      <c r="F11" t="n">
+        <v/>
+      </c>
+      <c r="G11" t="n">
+        <v/>
+      </c>
+      <c r="H11" t="n">
+        <v/>
+      </c>
+      <c r="I11" t="n">
+        <v/>
+      </c>
+      <c r="J11" t="n">
+        <v>20.06663439230603</v>
+      </c>
+      <c r="K11" t="n">
+        <v>85.78032281468909</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>y = 13.554x + -24296.189</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-24296.18936322996</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>4.011318450530509e-10</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>151.0999999999999</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000000037e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8303127365707181</v>
       </c>
     </row>
   </sheetData>
@@ -1014,7 +4230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1118,16 +4334,14 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -1137,7 +4351,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -1149,6 +4363,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-212.8</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4.23414e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-58.246</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.8875949367089176</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.9277419354838548</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.503529411764728</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.451873767258388</v>
+      </c>
+      <c r="J2" t="n">
+        <v>19.95946851888533</v>
+      </c>
+      <c r="K2" t="n">
+        <v>84.29157986772481</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>y = 10.004x + -14794.510</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-14794.51045243109</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.195289892865387e-12</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>212.8</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8321077831733287</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-171.9299999999998</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4.3275e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-60.751</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.2821522309711143</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.416560509554228</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.760196905766502</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.742947903430725</v>
+      </c>
+      <c r="J3" t="n">
+        <v>19.36522839351223</v>
+      </c>
+      <c r="K3" t="n">
+        <v>84.76359292678485</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>y = 10.911x + -15334.959</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-15334.95902045895</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.365301058043345e-11</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>171.9299999999998</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8324967839821114</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-153.8199999999999</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4.35951e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-61.788</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2.261971830985526</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.3104308390022535</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.7678657074341251</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.212359550561808</v>
+      </c>
+      <c r="J4" t="n">
+        <v>18.47272800731751</v>
+      </c>
+      <c r="K4" t="n">
+        <v>84.81592564277415</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>y = 11.022x + -15152.563</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-15152.5633894038</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.535576153115226e-09</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>153.8199999999999</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000000383e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8329038413179529</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-144.47</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4.38116e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-62.488</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.1949999999999439</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.5015037593984536</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.471428571428488</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.217322834645704</v>
+      </c>
+      <c r="J5" t="n">
+        <v>19.09993825200998</v>
+      </c>
+      <c r="K5" t="n">
+        <v>84.92344506142399</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>y = 11.257x + -15206.828</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-15206.82816016236</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>4.434136425764144e-13</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>144.47</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8334844306000366</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-135.5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.40232e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-63.058</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.7859154929577603</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.127598566308095</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.085694249649361</v>
+      </c>
+      <c r="J6" t="n">
+        <v>23.22126879201184</v>
+      </c>
+      <c r="K6" t="n">
+        <v>85.28020782147409</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>y = 12.112x + -16132.011</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-16132.01103357115</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>3.277163233124847e-09</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>135.5</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000002174e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8340083973848813</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-127.9300000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4.42322e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-63.542</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.2932114882507049</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.8414698162729236</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.474242424242364</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.627355623100359</v>
+      </c>
+      <c r="J7" t="n">
+        <v>29.57202562288776</v>
+      </c>
+      <c r="K7" t="n">
+        <v>85.52805428366283</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>y = 12.786x + -16828.888</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-16828.88792932818</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.443577533704001e-08</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>127.9300000000001</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000001083e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8344343892557708</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-126.1000000000001</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4.44305e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-63.966</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.1460526315789201</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.4932862190812675</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.752820512820413</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.621997874601445</v>
+      </c>
+      <c r="J8" t="n">
+        <v>23.85590927826167</v>
+      </c>
+      <c r="K8" t="n">
+        <v>85.33464182375577</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>y = 12.254x + -15859.379</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-15859.37896803688</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>4.650962941173963e-10</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>126.1000000000001</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000000239e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8348737990609221</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-125.48</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4.45998e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-64.34699999999999</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.156037151702802</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.08296146044625062</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.45431578947368</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.195102040816012</v>
+      </c>
+      <c r="J9" t="n">
+        <v>20.9688700112818</v>
+      </c>
+      <c r="K9" t="n">
+        <v>85.25920610367623</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>y = 12.058x + -15374.365</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-15374.36538035429</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.625280022033863e-08</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>125.48</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000001981e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8359678274860433</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-117.8200000000002</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4.50525e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-65.081</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.6262376237623983</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.8122186495177489</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.386295503211945</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.670728793309423</v>
+      </c>
+      <c r="J10" t="n">
+        <v>24.99286650874291</v>
+      </c>
+      <c r="K10" t="n">
+        <v>85.51287642381136</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>y = 12.743x + -15795.456</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-15795.45562874301</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.362036821396672e-08</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>117.8200000000002</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000002207e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.836941258026506</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-119.74</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4.52218e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-65.41500000000001</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.2400327381973486</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.4854925414063918</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.58730002659417</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.550248110077668</v>
+      </c>
+      <c r="J11" t="n">
+        <v>47.0744364867566</v>
+      </c>
+      <c r="K11" t="n">
+        <v>85.13160294092722</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>y = 11.741x + -14297.148</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-14297.14802215251</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>5.397444398910247e-10</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>119.74</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000000186e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8373959246190945</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-116.8899999999999</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4.53792e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-65.751</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.1261221828733325</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.5013407862531229</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.519097170651178</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.815182623530424</v>
+      </c>
+      <c r="J12" t="n">
+        <v>44.18815138896286</v>
+      </c>
+      <c r="K12" t="n">
+        <v>85.16390910288288</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>y = 11.819x + -14220.389</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-14220.3889639639</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.646039073902291</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>116.8899999999999</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.11296106566074e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8301202655219043</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-112.8599999999999</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4.55112e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-66.081</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.08728489781672054</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.9125130736155846</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.88783189296646</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.852161434378508</v>
+      </c>
+      <c r="J13" t="n">
+        <v>47.41960431019216</v>
+      </c>
+      <c r="K13" t="n">
+        <v>85.27032811850945</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>y = 12.087x + -14372.857</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-14372.85713044984</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.044162985223539e-08</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>112.8599999999999</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.00000000000037e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8383400912304341</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-108.29</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4.56581e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-66.371</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.3328671328671466</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.5071078431372531</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.10395604395602</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.194921875000048</v>
+      </c>
+      <c r="J14" t="n">
+        <v>21.96787808658928</v>
+      </c>
+      <c r="K14" t="n">
+        <v>85.43648124167997</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>y = 12.529x + -14752.010</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-14752.00982808087</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.955972353526669e-09</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>109.5899999999999</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.000000000000008e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8388012164334024</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-106.5999999999999</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4.58282e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-66.672</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.1378811086042951</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.6977622439447728</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.709449109781569</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.753867862908704</v>
+      </c>
+      <c r="J15" t="n">
+        <v>42.19845363341759</v>
+      </c>
+      <c r="K15" t="n">
+        <v>85.35199058660156</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>y = 12.300x + -14282.752</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-14282.7519702549</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>6.946933965987063e-09</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>109.74</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.000000000000044e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8393101945971007</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-104.8900000000001</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4.59592e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-66.971</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.2982800888684479</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.8429199155084094</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.792057239721545</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.611013103612479</v>
+      </c>
+      <c r="J16" t="n">
+        <v>41.76446205969599</v>
+      </c>
+      <c r="K16" t="n">
+        <v>85.36703815480016</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>y = 12.340x + -14163.213</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-14163.21347150649</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.317777510507496e-12</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>108.9300000000001</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8397868574760489</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-107.1700000000001</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4.61087e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-67.261</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.04966584997506734</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.2213307910433163</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.975105197437993</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.712809522370996</v>
+      </c>
+      <c r="J17" t="n">
+        <v>25.72104463456168</v>
+      </c>
+      <c r="K17" t="n">
+        <v>85.02808390379695</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>y = 11.495x + -12979.630</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-12979.62958242628</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>3.773369718771121e-11</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>112.8700000000001</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8402883893917831</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-93.49000000000001</v>
+      </c>
+      <c r="D18" t="n">
+        <v>4.62663e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-67.56399999999999</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.6528089887640606</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.7471153846154235</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.418402777777863</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.160793465577637</v>
+      </c>
+      <c r="J18" t="n">
+        <v>24.98987117065673</v>
+      </c>
+      <c r="K18" t="n">
+        <v>85.74503766977601</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>y = 13.441x + -15118.415</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-15118.41544456057</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>6.718298736843242e-09</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>101.47</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.000000000000173e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8407914392213998</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-90.69999999999982</v>
+      </c>
+      <c r="D19" t="n">
+        <v>4.64176e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-67.84399999999999</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.392337164750732</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.3510729613734014</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.21411935953422</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.001702610669688</v>
+      </c>
+      <c r="J19" t="n">
+        <v>24.89573249037776</v>
+      </c>
+      <c r="K19" t="n">
+        <v>85.7597954527312</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>y = 13.488x + -14985.982</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-14985.98171521551</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>2.396165538541654e-08</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>99.83999999999992</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.00000000000009e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8412945433784456</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-95.86000000000013</v>
+      </c>
+      <c r="D20" t="n">
+        <v>4.65548e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-68.121</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.3704297909920484</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.5717856008035495</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.004194206607812</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.444802431856331</v>
+      </c>
+      <c r="J20" t="n">
+        <v>28.45831503359108</v>
+      </c>
+      <c r="K20" t="n">
+        <v>85.26109577660421</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>y = 12.063x + -13152.696</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-13152.69576382672</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.631463280094322e-10</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>105.5700000000002</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8418198223054431</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-89.47000000000003</v>
+      </c>
+      <c r="D21" t="n">
+        <v>4.66994e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-68.43300000000001</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.3572397520006366</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.080586108610235</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.90478664853881</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.853529042604027</v>
+      </c>
+      <c r="J21" t="n">
+        <v>10.90406168021083</v>
+      </c>
+      <c r="K21" t="n">
+        <v>85.44933411728937</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>y = 12.564x + -13556.250</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-13556.25032917496</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>2.07358855129548e-11</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>101.8100000000002</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.842349213806347</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-86.62999999999988</v>
+      </c>
+      <c r="D22" t="n">
+        <v>4.68552e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-68.718</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.4457353332360831</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.7378880632915988</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.774215108682587</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3.124725781107508</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2.399510270709893</v>
+      </c>
+      <c r="K22" t="n">
+        <v>85.47404457713796</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>y = 12.633x + -13463.887</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-13463.88744921737</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>9.705506530223433e-12</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>100.01</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.842883274437631</v>
       </c>
     </row>
   </sheetData>
@@ -1162,7 +5468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1266,16 +5572,14 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -1285,7 +5589,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -1297,6 +5601,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-248.9300000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4.24516e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-56.793</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.4389021479714156</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.730769230769181</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.281444759206768</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.575904486251795</v>
+      </c>
+      <c r="J2" t="n">
+        <v>13.38475750765249</v>
+      </c>
+      <c r="K2" t="n">
+        <v>83.29187978546906</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>y = 8.502x + -12557.057</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-12557.0569811854</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.857120419133815e-10</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>248.9300000000001</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8329929119116914</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-206.79</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4.3251e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-58.699</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.6029032258065347</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4.145999999999344</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.814307004471065</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.915798045602605</v>
+      </c>
+      <c r="J3" t="n">
+        <v>17.05408389641397</v>
+      </c>
+      <c r="K3" t="n">
+        <v>84.15644170843692</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>y = 9.771x + -14015.678</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-14015.6778187673</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>3.578574811151836e-12</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>206.79</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8332372655986989</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-190.76</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4.35569e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-59.731</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.009859154929575547</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.3017716535433421</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.645244956772156</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.497611630321974</v>
+      </c>
+      <c r="J4" t="n">
+        <v>16.47358831974366</v>
+      </c>
+      <c r="K4" t="n">
+        <v>84.33490526499038</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>y = 10.081x + -14183.873</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-14183.87339017491</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.569572412145782e-11</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>190.76</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8334817869172857</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-180.3699999999999</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4.3794e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-60.5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.1333333333333077</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.584943181818164</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.125121951219435</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.781469298245574</v>
+      </c>
+      <c r="J5" t="n">
+        <v>17.50734696948017</v>
+      </c>
+      <c r="K5" t="n">
+        <v>84.50140570356353</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>y = 10.388x + -14387.354</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-14387.35384990727</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.241585259746103e-12</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>180.3699999999999</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.833799035812953</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-175.7</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.40335e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-61.103</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1234042553191611</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.01333333333333857</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.6645454545454504</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.842955326460339</v>
+      </c>
+      <c r="J6" t="n">
+        <v>16.13921346509225</v>
+      </c>
+      <c r="K6" t="n">
+        <v>84.46374403670583</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>y = 10.317x + -14038.855</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-14038.85517380458</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.750223480252316e-11</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>175.7</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8342937424826312</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-157.26</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4.44043e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-61.73</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.818380062305196</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.7654676258993085</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.606504065040689</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.369515839808762</v>
+      </c>
+      <c r="J7" t="n">
+        <v>30.91630218200714</v>
+      </c>
+      <c r="K7" t="n">
+        <v>85.2113548665366</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>y = 11.937x + -16069.931</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-16069.93145612055</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.996394218619561e-09</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>157.26</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000000147e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8347660144063926</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-158</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4.46692e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-62.253</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.9744360902253231</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.280726256983201</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.121014492753639</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.736442516269007</v>
+      </c>
+      <c r="J8" t="n">
+        <v>19.69227215590608</v>
+      </c>
+      <c r="K8" t="n">
+        <v>84.91994308826736</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>y = 11.249x + -14829.492</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-14829.49186189311</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.202655218792861e-10</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>158</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000000054e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8350573690958482</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-152.9100000000001</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4.49304e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-62.734</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.6155172413792549</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.8594654788418399</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.40054794520522</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.444965104685971</v>
+      </c>
+      <c r="J9" t="n">
+        <v>20.45718987837393</v>
+      </c>
+      <c r="K9" t="n">
+        <v>85.00364251023134</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>y = 11.438x + -14851.658</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-14851.65772171988</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>3.533504427906842e-10</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>152.9100000000001</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8350383188528258</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-148.1300000000001</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4.5171e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-63.161</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.067944250871142</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.4464527027027063</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.241337386018242</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.956617647058906</v>
+      </c>
+      <c r="J10" t="n">
+        <v>21.18666575845444</v>
+      </c>
+      <c r="K10" t="n">
+        <v>85.07494422047473</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>y = 11.605x + -14844.997</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-14844.99680820529</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.344228692442649e-09</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>148.1300000000001</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000001497e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8354669955290038</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-147.0600000000002</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4.54192e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-63.571</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.7470852017936435</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.3737896494157039</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.894354838709672</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.286217457886645</v>
+      </c>
+      <c r="J11" t="n">
+        <v>18.67590530554978</v>
+      </c>
+      <c r="K11" t="n">
+        <v>84.97518770845778</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>y = 11.373x + -14297.770</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-14297.77010131324</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>8.206331235602397e-10</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>147.0600000000002</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000000713e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8359167128145656</v>
       </c>
     </row>
   </sheetData>
@@ -1310,7 +6134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1414,16 +6238,14 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -1433,7 +6255,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -1445,6 +6267,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-186.6799999999998</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4.37132e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-59.585</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.239095744680856</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.980515759312291</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.334017595307888</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.363323262840057</v>
+      </c>
+      <c r="J2" t="n">
+        <v>23.82595615524672</v>
+      </c>
+      <c r="K2" t="n">
+        <v>84.69957835180981</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>y = 10.779x + -15220.491</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-15220.49099597104</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>5.720515138620531e-10</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>186.6799999999998</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8325931877394172</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-149</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4.39257e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-61.209</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.425882352941161</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.8982339955849531</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.696547619047595</v>
+      </c>
+      <c r="J3" t="n">
+        <v>20.91324940953918</v>
+      </c>
+      <c r="K3" t="n">
+        <v>84.96440355693494</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>y = 11.349x + -15759.772</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-15759.77187096125</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.405020186175405e-11</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>149</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8320871781901723</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-134.4300000000001</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4.42755e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-62.137</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.04719101123595645</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.6905999999999675</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.9785123966941569</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.087645348837366</v>
+      </c>
+      <c r="J4" t="n">
+        <v>22.60308904714875</v>
+      </c>
+      <c r="K4" t="n">
+        <v>85.06970479274403</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>y = 11.592x + -15743.345</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-15743.34464358955</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>3.849068832980438e-12</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>134.4300000000001</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.832484552392343</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-126.1799999999998</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4.44808e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-62.644</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.527188940092435</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.8564154786151337</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.858105646630206</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.51448551448552</v>
+      </c>
+      <c r="J5" t="n">
+        <v>28.13137864428654</v>
+      </c>
+      <c r="K5" t="n">
+        <v>85.41196432998279</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>y = 12.461x + -16705.191</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-16705.190842766</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>3.972725382163073e-08</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>126.1799999999998</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000000082e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8335082663071087</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-123.9000000000001</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.49283e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-63.4</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.2080952380952536</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.518644067796547</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.7889929742388265</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.975459317585316</v>
+      </c>
+      <c r="J6" t="n">
+        <v>23.20274917771795</v>
+      </c>
+      <c r="K6" t="n">
+        <v>85.29685877639768</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>y = 12.155x + -15810.281</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-15810.28106044284</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.432665748083905e-08</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>123.9000000000001</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000002293e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8338717127474594</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-125.5899999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4.51206e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-63.796</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.2292207792207749</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.1060000000000045</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.7062271062271</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.083333333333269</v>
+      </c>
+      <c r="J7" t="n">
+        <v>19.89093419738325</v>
+      </c>
+      <c r="K7" t="n">
+        <v>84.99323427216088</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>y = 11.415x + -14598.390</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-14598.38951733558</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>5.669064314104212e-10</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>125.5899999999999</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000000391e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8343117487425564</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-122.3699999999999</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4.53291e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-64.19499999999999</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.1110903837185272</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.6501104785506829</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.090462591821676</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.615754127975166</v>
+      </c>
+      <c r="J8" t="n">
+        <v>42.99223780040595</v>
+      </c>
+      <c r="K8" t="n">
+        <v>84.95593288638126</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>y = 11.330x + -14273.137</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-14273.13733194418</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>6.033836778576327e-10</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>122.3699999999999</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000000033e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8347827323162988</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-115.8899999999999</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4.55235e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-64.556</v>
+      </c>
+      <c r="F9" t="n">
+        <v>41.84999999956538</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.03312883435580984</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.084412470023971</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.272423025435136</v>
+      </c>
+      <c r="J9" t="n">
+        <v>20.12970626298159</v>
+      </c>
+      <c r="K9" t="n">
+        <v>85.1665127896344</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>y = 11.826x + -14724.142</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-14724.14165709195</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>9.654838727229941e-10</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>115.8899999999999</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000000043e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8352437186803376</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-112.21</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4.57109e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-64.892</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.5553097345132646</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.292178770949652</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.83633217993051</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.306085753803526</v>
+      </c>
+      <c r="J10" t="n">
+        <v>21.02973245681488</v>
+      </c>
+      <c r="K10" t="n">
+        <v>85.2853650046402</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>y = 12.125x + -14923.198</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-14923.19798881167</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>4.148303916280517e-14</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>112.21</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8357672395960193</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-108.9400000000001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4.59292e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-65.282</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.8298113207547476</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.1738341968911918</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.6802180685358307</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.36928895612703</v>
+      </c>
+      <c r="J11" t="n">
+        <v>20.43210742181096</v>
+      </c>
+      <c r="K11" t="n">
+        <v>85.26118134802077</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>y = 12.063x + -14624.646</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-14624.64625254544</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>5.927648706203283e-11</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>111.6800000000001</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.836339673968898</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-104.6299999999999</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4.61286e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-65.65000000000001</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.8781818181818274</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.9632218844984357</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.9481481481481612</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.549621785173983</v>
+      </c>
+      <c r="J12" t="n">
+        <v>20.67610247526614</v>
+      </c>
+      <c r="K12" t="n">
+        <v>85.27067498680989</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>y = 12.087x + -14455.317</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-14455.31715333279</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>4.257795657508232e-08</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>110.3599999999999</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.000000000000044e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8368885419044735</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-102.04</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4.63177e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-65.985</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.6273927392739019</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.6871052631578985</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.31825192802073</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.491134020618358</v>
+      </c>
+      <c r="J13" t="n">
+        <v>20.64423150311537</v>
+      </c>
+      <c r="K13" t="n">
+        <v>85.30855357734916</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>y = 12.186x + -14379.489</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-14379.48901530511</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>3.881021092753764e-09</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>108.78</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.000000000000032e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8374412808543498</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-100.8</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4.64722e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-66.291</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.06221042471042554</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.9053924219027367</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.802517307076914</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.732774568555258</v>
+      </c>
+      <c r="J14" t="n">
+        <v>28.47249060432522</v>
+      </c>
+      <c r="K14" t="n">
+        <v>85.16346003264717</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>y = 11.818x + -13745.311</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-13745.31108476702</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.975839838410178e-08</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>109.24</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.000000000000244e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8379153493642926</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-95.30999999999995</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4.66419e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-66.623</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.363636363636083</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.975603217158205</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.9120614035087621</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.887393526405316</v>
+      </c>
+      <c r="J15" t="n">
+        <v>19.98301213925421</v>
+      </c>
+      <c r="K15" t="n">
+        <v>85.3217718766406</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>y = 12.220x + -14063.416</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-14063.41627469487</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.029298790741381e-12</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>106.3999999999999</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8384121433308739</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-91.97999999999979</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4.68247e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-66.90600000000001</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.7519999999999284</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.8403225806453644</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.6641237113402442</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.98424242424255</v>
+      </c>
+      <c r="J16" t="n">
+        <v>20.36897692555258</v>
+      </c>
+      <c r="K16" t="n">
+        <v>85.34911493268234</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>y = 12.292x + -13981.306</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-13981.30618522348</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>4.162083300514258e-10</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.000000000000015e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8389165976775568</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-88.74000000000001</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4.69891e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-67.21599999999999</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.345238095237668</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.7062068965517407</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.503960396039302</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.06439522998302</v>
+      </c>
+      <c r="J17" t="n">
+        <v>19.93755735879732</v>
+      </c>
+      <c r="K17" t="n">
+        <v>85.35152114097437</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>y = 12.299x + -13817.133</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-13817.13317467756</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>2.684064584578977e-08</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>103.1200000000001</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8393764144437562</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-89.25999999999999</v>
+      </c>
+      <c r="D18" t="n">
+        <v>4.70976e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-67.452</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.07493603070524234</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.868964219963118</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.643585122944768</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.78240037620215</v>
+      </c>
+      <c r="J18" t="n">
+        <v>6.088107995850057</v>
+      </c>
+      <c r="K18" t="n">
+        <v>85.27729633485104</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>y = 12.104x + -13435.470</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-13435.46996480902</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.119223745646828e-08</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>103.1700000000001</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.000000000000048e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8398377001424042</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-89.37999999999988</v>
+      </c>
+      <c r="D19" t="n">
+        <v>4.72749e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-67.76300000000001</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.2278271944468502</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.477131128716333</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.626405353728462</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.314555442044038</v>
+      </c>
+      <c r="J19" t="n">
+        <v>17.87258339835366</v>
+      </c>
+      <c r="K19" t="n">
+        <v>84.98131933645425</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>y = 11.387x + -12450.898</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-12450.89787332109</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>8.147913167944852e-09</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>106.6899999999998</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.000000000000141e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8403785040264899</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-85.54999999999995</v>
+      </c>
+      <c r="D20" t="n">
+        <v>4.7425e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-68.051</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.1821360558120402</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.032047320135243</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.525146576019675</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.31600785040188</v>
+      </c>
+      <c r="J20" t="n">
+        <v>16.34433479455846</v>
+      </c>
+      <c r="K20" t="n">
+        <v>85.06418096498804</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>y = 11.579x + -12505.158</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-12505.15815299472</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>3.575284539399535e-08</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>103.71</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.000000000000781e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8413357784211097</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-78.90999999999985</v>
+      </c>
+      <c r="D21" t="n">
+        <v>4.76944e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-68.502</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.7413897280966428</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.4712296983758784</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.341602067183499</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.054945054945096</v>
+      </c>
+      <c r="J21" t="n">
+        <v>18.04630672300943</v>
+      </c>
+      <c r="K21" t="n">
+        <v>85.36916721598409</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>y = 12.346x + -13102.684</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-13102.68398428272</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.091914501195043e-08</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>98.70999999999981</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8424216063489984</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-82.31999999999994</v>
+      </c>
+      <c r="D22" t="n">
+        <v>4.80279e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-69.06699999999999</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.3217473287241148</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.8247663237173271</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.921941640963257</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.463549019585859</v>
+      </c>
+      <c r="J22" t="n">
+        <v>17.27696044348651</v>
+      </c>
+      <c r="K22" t="n">
+        <v>84.96948788281516</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>y = 11.360x + -11653.613</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-11653.612686609</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.694152859371714e-08</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>102.48</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.000000000000003e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8433912690254576</v>
       </c>
     </row>
   </sheetData>
@@ -1458,7 +7372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1562,16 +7476,14 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -1581,7 +7493,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -1593,6 +7505,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-278.21</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3.91163e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-53.475</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.7454545454545591</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.6358048780487715</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.818844221105524</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.424547548535715</v>
+      </c>
+      <c r="J2" t="n">
+        <v>16.31668625146886</v>
+      </c>
+      <c r="K2" t="n">
+        <v>82.81292236651709</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>y = 7.930x + -13281.791</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-13281.79072917973</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>9.200561400212982e-09</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>278.21</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000000006e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8284031854164853</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-199.6800000000001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4.20174e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-57.547</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.270408163265389</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.355570469798548</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.840672782874595</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.766314199395766</v>
+      </c>
+      <c r="J3" t="n">
+        <v>30.69924737290529</v>
+      </c>
+      <c r="K3" t="n">
+        <v>84.50869731979265</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>y = 10.402x + -15851.703</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-15851.70328379813</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>4.065936168913495e-09</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>199.6800000000001</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000004021e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8289223470162235</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-176.9300000000001</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4.27276e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-59.203</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.4534954407294752</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.7906921241050239</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.317207334273595</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.670312499999969</v>
+      </c>
+      <c r="J4" t="n">
+        <v>20.97188886248135</v>
+      </c>
+      <c r="K4" t="n">
+        <v>84.63548831530643</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>y = 10.649x + -15655.107</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-15655.10664406893</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>3.86677482297048e-10</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>176.9300000000001</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8291880611169845</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-162.6900000000001</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4.314e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-60.2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.05317220543806224</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.5406746031746239</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.059033078880185</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.871480144404231</v>
+      </c>
+      <c r="J5" t="n">
+        <v>19.28513144261598</v>
+      </c>
+      <c r="K5" t="n">
+        <v>84.60891718908613</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>y = 10.596x + -15220.945</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-15220.94529272925</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>6.561498959134325e-12</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>162.6900000000001</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8294413702267376</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-151.6099999999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.34637e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-60.958</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.2520000000000011</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.5253554502370354</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.662051282051197</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.523755186722007</v>
+      </c>
+      <c r="J6" t="n">
+        <v>20.14885447202583</v>
+      </c>
+      <c r="K6" t="n">
+        <v>84.80183513301951</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>y = 10.992x + -15517.042</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-15517.04222311667</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>4.353083679553433e-11</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>151.6099999999999</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.829710660250638</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-141.5799999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4.37929e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-61.586</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1382352941176513</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.453649635036595</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.140368509212706</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.48141086749289</v>
+      </c>
+      <c r="J7" t="n">
+        <v>20.76489733801327</v>
+      </c>
+      <c r="K7" t="n">
+        <v>84.89752450767745</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>y = 11.199x + -15534.455</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-15534.4546766757</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.581603528249857e-09</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>141.5799999999999</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000000048e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8300354402130599</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-132.71</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4.41101e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-62.13</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.6645569620253631</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.9781645569619466</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.408559498955994</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.974384236453142</v>
+      </c>
+      <c r="J8" t="n">
+        <v>21.65651067143481</v>
+      </c>
+      <c r="K8" t="n">
+        <v>85.02603763945039</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>y = 11.490x + -15673.253</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-15673.25322399462</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.857311217561788e-08</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>132.71</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000000331e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8303925869631766</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-123.9300000000001</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4.44239e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-62.642</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.9382550335569928</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.183053691275155</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.404393939394043</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.166814551907726</v>
+      </c>
+      <c r="J9" t="n">
+        <v>27.5688320828623</v>
+      </c>
+      <c r="K9" t="n">
+        <v>85.29281186330189</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>y = 12.145x + -16328.198</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-16328.19756850009</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.978407653209302e-08</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>123.9300000000001</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000003297e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8307646042557969</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-127.3800000000001</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4.4712e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-63.094</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.8490322491451618</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.513431283803345</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.555102795831937</v>
+      </c>
+      <c r="J10" t="n">
+        <v>40.17568204186471</v>
+      </c>
+      <c r="K10" t="n">
+        <v>84.71981144865391</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>y = 10.820x + -14216.450</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-14216.45014198157</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>8.491653452779986e-10</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>127.3800000000001</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000000552e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8311487213264482</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-122.73</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4.49771e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-63.513</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.05945945945945714</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.7222627737226754</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.6947619047619104</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.969176882661902</v>
+      </c>
+      <c r="J11" t="n">
+        <v>19.08251706481992</v>
+      </c>
+      <c r="K11" t="n">
+        <v>84.92702167297365</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>y = 11.265x + -14604.093</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-14604.09283335973</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>4.621049876732005e-10</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>122.73</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000000025e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8315389482098392</v>
       </c>
     </row>
   </sheetData>
@@ -1606,7 +8038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1710,16 +8142,14 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -1729,7 +8159,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -1741,6 +8171,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-194.4300000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4.31391e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-59.531</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.3729542302357828</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.01237410071943078</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.01242484969938</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.681694915254219</v>
+      </c>
+      <c r="J2" t="n">
+        <v>16.84482306421697</v>
+      </c>
+      <c r="K2" t="n">
+        <v>84.17884112240792</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>y = 9.809x + -14025.882</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-14025.88224767315</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.27196624550196e-11</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>194.4300000000001</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8300167163308894</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-152.99</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4.40301e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-61.818</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.6607287449392242</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.6020080321285322</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.043583535108876</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.208421052631563</v>
+      </c>
+      <c r="J3" t="n">
+        <v>17.89853968774645</v>
+      </c>
+      <c r="K3" t="n">
+        <v>84.71783366981693</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>y = 10.816x + -14704.948</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-14704.94776391744</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.08838873926891e-12</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>152.99</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8303059415707552</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-139.45</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4.42917e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-62.535</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.0803468208092456</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.3881453154875469</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.8029023746701648</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.501080246913556</v>
+      </c>
+      <c r="J4" t="n">
+        <v>21.71478279751009</v>
+      </c>
+      <c r="K4" t="n">
+        <v>84.99731831245673</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>y = 11.424x + -15295.272</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-15295.2724659305</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>5.342138618469332e-10</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>139.45</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000000031e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8304992596469074</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-133.49</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4.4482e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-62.977</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.4779005524862077</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.7511383537652727</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.320843672456632</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.952305825242832</v>
+      </c>
+      <c r="J5" t="n">
+        <v>22.05487035432486</v>
+      </c>
+      <c r="K5" t="n">
+        <v>85.10076522835156</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>y = 11.666x + -15427.874</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-15427.87373519644</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.862011069255058e-08</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>133.49</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000003143e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8307662655285678</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-129.0599999999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.464e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-63.37</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.2385026737967876</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.794736842105481</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.683693045563587</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.339237057220706</v>
+      </c>
+      <c r="J6" t="n">
+        <v>22.66860832030125</v>
+      </c>
+      <c r="K6" t="n">
+        <v>85.17445459739281</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>y = 11.845x + -15479.413</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-15479.41308114051</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>5.888687977710606e-09</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>129.0599999999999</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000000148e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.831079933509654</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-129.8599999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4.48057e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-63.711</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.3026011560693581</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.014900662251685</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.462889518413593</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.653756260433965</v>
+      </c>
+      <c r="J7" t="n">
+        <v>19.63312384001986</v>
+      </c>
+      <c r="K7" t="n">
+        <v>84.97736917416218</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>y = 11.378x + -14655.405</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-14655.40463624706</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>7.729415954565923e-11</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>129.8599999999999</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8314204096666354</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-118.8099999999999</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4.49997e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-64.059</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.9942652329749699</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.7861367837338074</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.65007363770251</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.082857142857144</v>
+      </c>
+      <c r="J8" t="n">
+        <v>28.86037771684565</v>
+      </c>
+      <c r="K8" t="n">
+        <v>85.46998644276681</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>y = 12.622x + -16151.193</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-16151.19265390456</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>8.419406680258176e-14</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>118.8099999999999</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8318144207924617</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-122.8399999999999</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4.51829e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-64.401</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1920378057503442</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.833853234528754</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.238893268107457</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.481245105043041</v>
+      </c>
+      <c r="J9" t="n">
+        <v>42.78520824174625</v>
+      </c>
+      <c r="K9" t="n">
+        <v>84.91003985232454</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>y = 11.227x + -14092.428</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-14092.42771567705</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.525030701132558e-11</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>122.8399999999999</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000001317e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8322144141010407</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-116.51</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4.53622e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-64.711</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.4387559808613274</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.2831481481481596</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.068999999999959</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.635197368421106</v>
+      </c>
+      <c r="J10" t="n">
+        <v>20.16213179664474</v>
+      </c>
+      <c r="K10" t="n">
+        <v>85.16621755379342</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>y = 11.825x + -14710.905</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-14710.90490501782</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>4.782729252109054e-11</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>116.51</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8325963459740516</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-114.3799999999999</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4.55476e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-65.02</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.2861471861471886</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.4825737265415453</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.772870662460241</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.442966360856256</v>
+      </c>
+      <c r="J11" t="n">
+        <v>20.47736623949968</v>
+      </c>
+      <c r="K11" t="n">
+        <v>85.15250549842341</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>y = 11.791x + -14504.058</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-14504.05841288523</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.91677281693671e-08</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>116.04</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000000034e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8329994601735757</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-109.53</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4.57073e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-65.31399999999999</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.09839572192512704</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.286227544910314</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.09407744874719</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.014917127071719</v>
+      </c>
+      <c r="J12" t="n">
+        <v>20.25625930435349</v>
+      </c>
+      <c r="K12" t="n">
+        <v>85.2212811840911</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>y = 11.962x + -14552.665</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-14552.66473296584</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>3.180452003584913e-09</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>112.3500000000001</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.000000000000003e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8334056593467165</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-103.96</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4.58828e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-65.62</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.181249999999945</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.9119842829076278</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.323005565862668</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.130316091953885</v>
+      </c>
+      <c r="J13" t="n">
+        <v>23.24862057931246</v>
+      </c>
+      <c r="K13" t="n">
+        <v>85.41877434052572</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>y = 12.480x + -15045.939</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-15045.93913038232</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.275423215382914e-09</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>109.73</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.000000000000078e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8338248196596109</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-105.23</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4.60394e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-65.905</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.3720095693780042</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.122155777190177</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.659365397298413</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.766965838000641</v>
+      </c>
+      <c r="J14" t="n">
+        <v>32.65969620253188</v>
+      </c>
+      <c r="K14" t="n">
+        <v>85.07401703520414</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>y = 11.603x + -13777.008</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-13777.00809800909</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>6.322043780405196e-09</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>112.23</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.000000000000171e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8342537658259238</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-102.99</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4.6214e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-66.20099999999999</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.67687704723382</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.6032434399715112</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.472247455703861</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.78376754829137</v>
+      </c>
+      <c r="J15" t="n">
+        <v>25.4240100242232</v>
+      </c>
+      <c r="K15" t="n">
+        <v>85.05343488771216</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>y = 11.554x + -13556.950</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-13556.95033914214</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.624561494765244e-10</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>112.48</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8346901559036031</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-95.98000000000002</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4.63978e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-66.502</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.8430693069305298</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.8702127659573708</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.801005025125543</v>
+      </c>
+      <c r="J16" t="n">
+        <v>19.67539403564603</v>
+      </c>
+      <c r="K16" t="n">
+        <v>85.18410989860938</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>y = 11.869x + -13791.093</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-13791.09269012721</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>7.108295698050464e-11</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>108.3199999999999</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8351238211759799</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-100.78</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4.65652e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-66.773</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.4712657712658155</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.7040077021100273</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.6063234903741286</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.954908715377978</v>
+      </c>
+      <c r="J17" t="n">
+        <v>19.51201810419492</v>
+      </c>
+      <c r="K17" t="n">
+        <v>84.62129534688206</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>y = 10.621x + -12114.955</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-12114.95481458074</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.384184944204951e-09</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>113.73</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8355662219531531</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-94.6099999999999</v>
+      </c>
+      <c r="D18" t="n">
+        <v>4.67156e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-67.05</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.6880705894974548</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.7912295884234384</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.570389473952497</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.892066472090487</v>
+      </c>
+      <c r="J18" t="n">
+        <v>7.467353394552998</v>
+      </c>
+      <c r="K18" t="n">
+        <v>85.1099176869902</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>y = 11.688x + -13244.152</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-13244.15151782749</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>7.980224748905889e-12</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>108.3099999999999</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8359988410809432</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-87.28999999999996</v>
+      </c>
+      <c r="D19" t="n">
+        <v>4.69099e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-67.354</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.206024096385668</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.2457420924574034</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.9860406091370371</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.900176056337989</v>
+      </c>
+      <c r="J19" t="n">
+        <v>18.40174427863388</v>
+      </c>
+      <c r="K19" t="n">
+        <v>85.22997130373646</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>y = 11.984x + -13431.368</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-13431.36814650586</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>2.919678243613795e-09</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>103.95</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8364540256777742</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-85.26999999999998</v>
+      </c>
+      <c r="D20" t="n">
+        <v>4.70661e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-67.621</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.726046511628043</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.9042857142856076</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.9712830957229582</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.497441860464951</v>
+      </c>
+      <c r="J20" t="n">
+        <v>19.17480637916633</v>
+      </c>
+      <c r="K20" t="n">
+        <v>85.32974306621261</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>y = 12.241x + -13563.153</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-13563.15286952507</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>2.983169149554645e-08</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>101.95</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.000000000000037e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8369004121880459</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-80.13999999999987</v>
+      </c>
+      <c r="D21" t="n">
+        <v>4.72531e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-67.929</v>
+      </c>
+      <c r="F21" t="n">
+        <v>6.089583333335669</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.5324808184143263</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.507808564231701</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.675921908893697</v>
+      </c>
+      <c r="J21" t="n">
+        <v>18.05679882031519</v>
+      </c>
+      <c r="K21" t="n">
+        <v>85.26851256380095</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>y = 12.082x + -13210.893</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-13210.89265957081</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.655998173363553e-08</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>99.16000000000008</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8373681415220726</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-81.86000000000013</v>
+      </c>
+      <c r="D22" t="n">
+        <v>4.74299e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-68.20099999999999</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.2973384788081177</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.7345885745662486</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.673662794417919</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.357975477350953</v>
+      </c>
+      <c r="J22" t="n">
+        <v>10.89948957310489</v>
+      </c>
+      <c r="K22" t="n">
+        <v>84.95704401492692</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>y = 11.332x + -12189.992</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-12189.99184383551</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.334879530913401e-08</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>102.2700000000002</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.000000000000018e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8378569494704342</v>
       </c>
     </row>
   </sheetData>
@@ -1754,7 +9276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1858,16 +9380,14 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -1877,7 +9397,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -1889,6 +9409,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-208.6299999999999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4.51846e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-60.94</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.7376404494381527</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.6620915032679756</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.02399425287359</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.566666666666626</v>
+      </c>
+      <c r="J2" t="n">
+        <v>15.59733288311291</v>
+      </c>
+      <c r="K2" t="n">
+        <v>84.18378291574035</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>y = 9.817x + -12737.640</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-12737.63958463638</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.869656676034459e-08</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>208.6299999999999</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000000982e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8319789203211562</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-148.5699999999999</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4.66674e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-64.833</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.05116809277189791</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.4741520002765883</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.213726047648821</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.202898614834687</v>
+      </c>
+      <c r="J3" t="n">
+        <v>29.05123986674472</v>
+      </c>
+      <c r="K3" t="n">
+        <v>84.93799595836562</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>y = 11.289x + -13245.038</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-13245.03810169215</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>8.108928582058926e-10</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>148.5699999999999</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000000003e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8323125432047137</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-125.01</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4.6716e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-66.04000000000001</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.4224094649249371</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.7330957864454616</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.970781877833805</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.743928954267056</v>
+      </c>
+      <c r="J4" t="n">
+        <v>49.99083641701312</v>
+      </c>
+      <c r="K4" t="n">
+        <v>85.37416272287376</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>y = 12.359x + -14172.608</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-14172.60819647558</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.900937840576138e-11</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>125.01</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8324771989517259</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-115.9399999999998</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4.67022e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-66.717</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.5130701296414133</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.8541903661457602</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.721826030128872</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.824414084164798</v>
+      </c>
+      <c r="J5" t="n">
+        <v>54.13847522499942</v>
+      </c>
+      <c r="K5" t="n">
+        <v>85.45124352320212</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>y = 12.569x + -14182.592</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-14182.59212932005</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.346681399974671e-08</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>115.9399999999998</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8326966992689748</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-112.4000000000001</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.67225e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-67.209</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.4725976581180024</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.075625970623147</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.10372332135491</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.825157797240739</v>
+      </c>
+      <c r="J6" t="n">
+        <v>54.94102559160388</v>
+      </c>
+      <c r="K6" t="n">
+        <v>85.52715115959077</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>y = 12.784x + -14216.795</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-14216.79492881361</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>5.292420589213277e-12</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>112.4000000000001</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8329860328488268</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-107.3200000000002</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4.68074e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-67.607</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.6179954441912824</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.8672097759674261</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.8335302806499133</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.670938897168394</v>
+      </c>
+      <c r="J7" t="n">
+        <v>24.07162065564544</v>
+      </c>
+      <c r="K7" t="n">
+        <v>85.74056446904169</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>y = 13.427x + -14753.176</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-14753.17619692637</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>3.494730951868302e-12</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>107.3200000000002</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.833340525675825</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-109.8100000000002</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4.69062e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-67.997</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.1649680511182404</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.7280163425118001</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.042557025115498</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.656671067791302</v>
+      </c>
+      <c r="J8" t="n">
+        <v>24.01456330974726</v>
+      </c>
+      <c r="K8" t="n">
+        <v>85.16273897873488</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>y = 11.817x + -12697.974</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-12697.97441281812</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.539227863482646e-09</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>109.8100000000002</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8337176306061557</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-108.4200000000001</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4.70189e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-68.35599999999999</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.03890393440158307</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.1340777434343667</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.148836712913629</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.622559957075926</v>
+      </c>
+      <c r="J9" t="n">
+        <v>21.59716346479664</v>
+      </c>
+      <c r="K9" t="n">
+        <v>85.10010118566932</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>y = 11.665x + -12339.301</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-12339.30102183179</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>7.123585102941405e-12</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>108.4200000000001</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8341304710465119</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-103.4300000000001</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4.71574e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-68.681</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.161245193329616</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.5857733146096377</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.283249964747706</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.13487202009813</v>
+      </c>
+      <c r="J10" t="n">
+        <v>29.97583159916922</v>
+      </c>
+      <c r="K10" t="n">
+        <v>85.42325054749543</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>y = 12.492x + -13073.631</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-13073.63139279546</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>9.078463945277714e-10</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>104.4400000000001</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8346108953997701</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-100.54</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4.72768e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-68.98099999999999</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.4504338876803785</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.6973292985284389</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.214186034513914</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.965843712635973</v>
+      </c>
+      <c r="J11" t="n">
+        <v>29.69119835096446</v>
+      </c>
+      <c r="K11" t="n">
+        <v>85.44698449543256</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>y = 12.558x + -12978.063</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-12978.06331141998</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>4.149259456054139e-12</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>102.9400000000001</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8350318826856246</v>
       </c>
     </row>
   </sheetData>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 36.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 36.xlsx
@@ -528,12 +528,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -588,10 +588,8 @@
       <c r="K2" t="n">
         <v>85.64734640804066</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 13.138x + -30005.753</t>
-        </is>
+      <c r="W2" t="n">
+        <v>13.13808114540886</v>
       </c>
       <c r="X2" t="n">
         <v>-30005.75286025774</v>
@@ -600,7 +598,7 @@
         <v>2.288885276243789e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>143.6700000000001</v>
+        <v>2615.739406248856</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000104e-08</v>
@@ -640,10 +638,8 @@
       <c r="K3" t="n">
         <v>85.77810386746992</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 13.547x + -29591.617</t>
-        </is>
+      <c r="W3" t="n">
+        <v>13.54653027123325</v>
       </c>
       <c r="X3" t="n">
         <v>-29591.61726137361</v>
@@ -652,7 +648,7 @@
         <v>4.038184347860714e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>125.48</v>
+        <v>2504.001632047016</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000025e-08</v>
@@ -692,10 +688,8 @@
       <c r="K4" t="n">
         <v>85.95154901116902</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 14.129x + -30378.455</t>
-        </is>
+      <c r="W4" t="n">
+        <v>14.12895821703982</v>
       </c>
       <c r="X4" t="n">
         <v>-30378.4553114298</v>
@@ -704,7 +698,7 @@
         <v>1.636065939816327e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>110.6999999999998</v>
+        <v>2461.853418078507</v>
       </c>
       <c r="AA4" t="n">
         <v>1.00000000000067e-08</v>
@@ -744,10 +738,8 @@
       <c r="K5" t="n">
         <v>85.9639341652811</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 14.172x + -30022.533</t>
-        </is>
+      <c r="W5" t="n">
+        <v>14.17245905177188</v>
       </c>
       <c r="X5" t="n">
         <v>-30022.53268889376</v>
@@ -756,7 +748,7 @@
         <v>4.660672964029683e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>109.9700000000003</v>
+        <v>2423.106427508083</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000014e-08</v>
@@ -796,10 +788,8 @@
       <c r="K6" t="n">
         <v>85.5311086830211</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 12.795x + -26648.468</t>
-        </is>
+      <c r="W6" t="n">
+        <v>12.79501822728133</v>
       </c>
       <c r="X6" t="n">
         <v>-26648.46776713715</v>
@@ -808,7 +798,7 @@
         <v>9.443867881205971e-11</v>
       </c>
       <c r="Z6" t="n">
-        <v>115.9300000000003</v>
+        <v>2390.549441454362</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000059e-08</v>
@@ -848,10 +838,8 @@
       <c r="K7" t="n">
         <v>85.55717016970785</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 12.870x + -26433.480</t>
-        </is>
+      <c r="W7" t="n">
+        <v>12.87037773732172</v>
       </c>
       <c r="X7" t="n">
         <v>-26433.47969658138</v>
@@ -860,7 +848,7 @@
         <v>8.82816451659133e-10</v>
       </c>
       <c r="Z7" t="n">
-        <v>112.54</v>
+        <v>2356.006004572259</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000013293e-08</v>
@@ -900,10 +888,8 @@
       <c r="K8" t="n">
         <v>85.55650137490484</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 12.868x + -26106.723</t>
-        </is>
+      <c r="W8" t="n">
+        <v>12.86843281824995</v>
       </c>
       <c r="X8" t="n">
         <v>-26106.72336765886</v>
@@ -912,7 +898,7 @@
         <v>3.539659406776374e-10</v>
       </c>
       <c r="Z8" t="n">
-        <v>109.6799999999998</v>
+        <v>2324.577024620783</v>
       </c>
       <c r="AA8" t="n">
         <v>1.00000000000003e-08</v>
@@ -952,10 +938,8 @@
       <c r="K9" t="n">
         <v>85.53386345187783</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 12.803x + -25655.123</t>
-        </is>
+      <c r="W9" t="n">
+        <v>12.80294244357264</v>
       </c>
       <c r="X9" t="n">
         <v>-25655.12322408354</v>
@@ -964,7 +948,7 @@
         <v>1.878325676382569e-10</v>
       </c>
       <c r="Z9" t="n">
-        <v>107.0499999999997</v>
+        <v>2295.067218311654</v>
       </c>
       <c r="AA9" t="n">
         <v>1.00000000000045e-08</v>
@@ -1004,10 +988,8 @@
       <c r="K10" t="n">
         <v>85.50959463695597</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 12.733x + -25182.419</t>
-        </is>
+      <c r="W10" t="n">
+        <v>12.7334658991018</v>
       </c>
       <c r="X10" t="n">
         <v>-25182.41937332417</v>
@@ -1016,7 +998,7 @@
         <v>5.928004529350924e-10</v>
       </c>
       <c r="Z10" t="n">
-        <v>106.23</v>
+        <v>2264.48755042764</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000002e-08</v>
@@ -1056,10 +1038,8 @@
       <c r="K11" t="n">
         <v>85.10441995810237</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 11.675x + -22770.765</t>
-        </is>
+      <c r="W11" t="n">
+        <v>11.67507802581874</v>
       </c>
       <c r="X11" t="n">
         <v>-22770.76496777428</v>
@@ -1068,7 +1048,7 @@
         <v>2.041348318209447e-11</v>
       </c>
       <c r="Z11" t="n">
-        <v>108.9100000000001</v>
+        <v>2238.891502218598</v>
       </c>
       <c r="AA11" t="n">
         <v>1.00000000000002e-08</v>
@@ -1194,12 +1174,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -1254,10 +1234,8 @@
       <c r="K2" t="n">
         <v>84.15726188596206</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 9.772x + -17015.433</t>
-        </is>
+      <c r="W2" t="n">
+        <v>9.772308143420897</v>
       </c>
       <c r="X2" t="n">
         <v>-17015.43293009196</v>
@@ -1266,7 +1244,7 @@
         <v>5.078255915022336e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>168.1699999999998</v>
+        <v>1943.788660361249</v>
       </c>
       <c r="AA2" t="n">
         <v>1e-08</v>
@@ -1306,10 +1284,8 @@
       <c r="K3" t="n">
         <v>84.82174617823858</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 11.035x + -17987.868</t>
-        </is>
+      <c r="W3" t="n">
+        <v>11.03454892679072</v>
       </c>
       <c r="X3" t="n">
         <v>-17987.86788757323</v>
@@ -1318,7 +1294,7 @@
         <v>7.02470719264075e-12</v>
       </c>
       <c r="Z3" t="n">
-        <v>144.75</v>
+        <v>1835.944548685289</v>
       </c>
       <c r="AA3" t="n">
         <v>1e-08</v>
@@ -1358,10 +1334,8 @@
       <c r="K4" t="n">
         <v>84.64552725877967</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 10.669x + -16970.612</t>
-        </is>
+      <c r="W4" t="n">
+        <v>10.66937634727152</v>
       </c>
       <c r="X4" t="n">
         <v>-16970.61181723978</v>
@@ -1370,7 +1344,7 @@
         <v>3.514883384618697e-12</v>
       </c>
       <c r="Z4" t="n">
-        <v>143.9200000000001</v>
+        <v>1799.099779385603</v>
       </c>
       <c r="AA4" t="n">
         <v>1e-08</v>
@@ -1410,10 +1384,8 @@
       <c r="K5" t="n">
         <v>84.40234898269946</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 10.203x + -15954.478</t>
-        </is>
+      <c r="W5" t="n">
+        <v>10.2030961158081</v>
       </c>
       <c r="X5" t="n">
         <v>-15954.47778077594</v>
@@ -1422,7 +1394,7 @@
         <v>4.780424302601326e-11</v>
       </c>
       <c r="Z5" t="n">
-        <v>146.0599999999999</v>
+        <v>1774.928220215958</v>
       </c>
       <c r="AA5" t="n">
         <v>1e-08</v>
@@ -1462,10 +1434,8 @@
       <c r="K6" t="n">
         <v>84.14928176602405</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 9.759x + -15063.353</t>
-        </is>
+      <c r="W6" t="n">
+        <v>9.758886230328484</v>
       </c>
       <c r="X6" t="n">
         <v>-15063.35333011143</v>
@@ -1474,7 +1444,7 @@
         <v>3.537786588235589e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>148.5899999999999</v>
+        <v>1755.614259668295</v>
       </c>
       <c r="AA6" t="n">
         <v>1.00000000000001e-08</v>
@@ -1514,10 +1484,8 @@
       <c r="K7" t="n">
         <v>84.41322827390229</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 10.223x + -15644.677</t>
-        </is>
+      <c r="W7" t="n">
+        <v>10.22309178719359</v>
       </c>
       <c r="X7" t="n">
         <v>-15644.67735598397</v>
@@ -1526,7 +1494,7 @@
         <v>9.417652825247201e-12</v>
       </c>
       <c r="Z7" t="n">
-        <v>143.0599999999999</v>
+        <v>1734.989738670846</v>
       </c>
       <c r="AA7" t="n">
         <v>1e-08</v>
@@ -1566,10 +1534,8 @@
       <c r="K8" t="n">
         <v>84.14667144194296</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 9.755x + -14710.897</t>
-        </is>
+      <c r="W8" t="n">
+        <v>9.754503793284201</v>
       </c>
       <c r="X8" t="n">
         <v>-14710.89724905403</v>
@@ -1578,7 +1544,7 @@
         <v>3.794007527303487e-10</v>
       </c>
       <c r="Z8" t="n">
-        <v>144.6500000000001</v>
+        <v>1713.457686446511</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000002e-08</v>
@@ -1618,10 +1584,8 @@
       <c r="K9" t="n">
         <v>84.13055082820483</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 9.728x + -14498.221</t>
-        </is>
+      <c r="W9" t="n">
+        <v>9.727525187412287</v>
       </c>
       <c r="X9" t="n">
         <v>-14498.22070462981</v>
@@ -1630,7 +1594,7 @@
         <v>8.694514854141747e-10</v>
       </c>
       <c r="Z9" t="n">
-        <v>144.48</v>
+        <v>1692.441826545994</v>
       </c>
       <c r="AA9" t="n">
         <v>1.00000000000001e-08</v>
@@ -1670,10 +1634,8 @@
       <c r="K10" t="n">
         <v>84.35986172357947</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 10.126x + -14950.917</t>
-        </is>
+      <c r="W10" t="n">
+        <v>10.12574288430962</v>
       </c>
       <c r="X10" t="n">
         <v>-14950.91672660913</v>
@@ -1682,7 +1644,7 @@
         <v>8.155609730440974e-11</v>
       </c>
       <c r="Z10" t="n">
-        <v>135.3600000000001</v>
+        <v>1672.185272462108</v>
       </c>
       <c r="AA10" t="n">
         <v>1e-08</v>
@@ -1722,10 +1684,8 @@
       <c r="K11" t="n">
         <v>83.96894711286227</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 9.465x + -13765.050</t>
-        </is>
+      <c r="W11" t="n">
+        <v>9.465015658719462</v>
       </c>
       <c r="X11" t="n">
         <v>-13765.04988246847</v>
@@ -1734,7 +1694,7 @@
         <v>1.22834557659326e-08</v>
       </c>
       <c r="Z11" t="n">
-        <v>138.99</v>
+        <v>1651.982173117055</v>
       </c>
       <c r="AA11" t="n">
         <v>1.00000000000012e-08</v>
@@ -1774,10 +1734,8 @@
       <c r="K12" t="n">
         <v>84.15566797095875</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 9.770x + -14076.702</t>
-        </is>
+      <c r="W12" t="n">
+        <v>9.769624388721313</v>
       </c>
       <c r="X12" t="n">
         <v>-14076.70171652841</v>
@@ -1786,7 +1744,7 @@
         <v>3.469974662060197e-08</v>
       </c>
       <c r="Z12" t="n">
-        <v>130.78</v>
+        <v>1632.532912182233</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000000875e-08</v>
@@ -1826,10 +1784,8 @@
       <c r="K13" t="n">
         <v>83.97978427177917</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 9.482x + -13489.607</t>
-        </is>
+      <c r="W13" t="n">
+        <v>9.482180294434437</v>
       </c>
       <c r="X13" t="n">
         <v>-13489.6073187469</v>
@@ -1838,7 +1794,7 @@
         <v>3.271293927605402e-10</v>
       </c>
       <c r="Z13" t="n">
-        <v>131.46</v>
+        <v>1613.364482158759</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000727e-08</v>
@@ -1878,10 +1834,8 @@
       <c r="K14" t="n">
         <v>83.63784420144287</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 8.969x + -12575.630</t>
-        </is>
+      <c r="W14" t="n">
+        <v>8.968673784275518</v>
       </c>
       <c r="X14" t="n">
         <v>-12575.63001602633</v>
@@ -1890,7 +1844,7 @@
         <v>4.147818104728947e-10</v>
       </c>
       <c r="Z14" t="n">
-        <v>132.6300000000001</v>
+        <v>1594.484557164249</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000242e-08</v>
@@ -1930,10 +1884,8 @@
       <c r="K15" t="n">
         <v>83.29991164472642</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 8.512x + -11781.296</t>
-        </is>
+      <c r="W15" t="n">
+        <v>8.5124809952092</v>
       </c>
       <c r="X15" t="n">
         <v>-11781.29576294632</v>
@@ -1942,7 +1894,7 @@
         <v>2.420342748467271e-10</v>
       </c>
       <c r="Z15" t="n">
-        <v>130.95</v>
+        <v>1575.951107119047</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000000402e-08</v>
@@ -1982,10 +1934,8 @@
       <c r="K16" t="n">
         <v>83.14660460730367</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 8.320x + -11364.999</t>
-        </is>
+      <c r="W16" t="n">
+        <v>8.320293886217215</v>
       </c>
       <c r="X16" t="n">
         <v>-11364.99916730823</v>
@@ -1994,7 +1944,7 @@
         <v>3.087387867397427e-08</v>
       </c>
       <c r="Z16" t="n">
-        <v>133.3299999999999</v>
+        <v>1557.81152168727</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000002781e-08</v>
@@ -2034,10 +1984,8 @@
       <c r="K17" t="n">
         <v>82.97218045826641</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 8.112x + -10949.683</t>
-        </is>
+      <c r="W17" t="n">
+        <v>8.111783426305024</v>
       </c>
       <c r="X17" t="n">
         <v>-10949.68281148155</v>
@@ -2046,7 +1994,7 @@
         <v>2.798315625394458e-08</v>
       </c>
       <c r="Z17" t="n">
-        <v>125.6400000000001</v>
+        <v>1539.531680938524</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000005385e-08</v>
@@ -2086,10 +2034,8 @@
       <c r="K18" t="n">
         <v>82.62237828107673</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 7.723x + -10281.778</t>
-        </is>
+      <c r="W18" t="n">
+        <v>7.723189704221721</v>
       </c>
       <c r="X18" t="n">
         <v>-10281.77806303802</v>
@@ -2098,7 +2044,7 @@
         <v>0.8818470196258528</v>
       </c>
       <c r="Z18" t="n">
-        <v>121.74</v>
+        <v>1639.648233897678</v>
       </c>
       <c r="AA18" t="n">
         <v>1.669899940135306e-08</v>
@@ -2138,10 +2084,8 @@
       <c r="K19" t="n">
         <v>82.2367987790237</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 7.335x + -9629.455</t>
-        </is>
+      <c r="W19" t="n">
+        <v>7.335212255506595</v>
       </c>
       <c r="X19" t="n">
         <v>-9629.454571360633</v>
@@ -2150,7 +2094,7 @@
         <v>3.086157898744619e-13</v>
       </c>
       <c r="Z19" t="n">
-        <v>118.74</v>
+        <v>1503.412154771458</v>
       </c>
       <c r="AA19" t="n">
         <v>1e-08</v>
@@ -2190,10 +2134,8 @@
       <c r="K20" t="n">
         <v>81.75990489710814</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 6.905x + -8927.526</t>
-        </is>
+      <c r="W20" t="n">
+        <v>6.905285885128736</v>
       </c>
       <c r="X20" t="n">
         <v>-8927.526278065347</v>
@@ -2202,7 +2144,7 @@
         <v>3.316908048150845e-10</v>
       </c>
       <c r="Z20" t="n">
-        <v>125.49</v>
+        <v>1485.335957251127</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000003e-08</v>
@@ -2242,10 +2184,8 @@
       <c r="K21" t="n">
         <v>81.08546369845592</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 6.375x + -8109.956</t>
-        </is>
+      <c r="W21" t="n">
+        <v>6.375283927555249</v>
       </c>
       <c r="X21" t="n">
         <v>-8109.955938307442</v>
@@ -2254,7 +2194,7 @@
         <v>2.183882676503599e-09</v>
       </c>
       <c r="Z21" t="n">
-        <v>120.8099999999999</v>
+        <v>1466.963421712221</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000001101e-08</v>
@@ -2294,10 +2234,8 @@
       <c r="K22" t="n">
         <v>80.11546595980685</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 5.739x + -7160.385</t>
-        </is>
+      <c r="W22" t="n">
+        <v>5.738887572902948</v>
       </c>
       <c r="X22" t="n">
         <v>-7160.385382407118</v>
@@ -2306,7 +2244,7 @@
         <v>5.190226086266899e-10</v>
       </c>
       <c r="Z22" t="n">
-        <v>118.0999999999999</v>
+        <v>1448.996689381289</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000000021e-08</v>
@@ -2432,12 +2370,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -2492,10 +2430,8 @@
       <c r="K2" t="n">
         <v>85.43829387511607</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 12.534x + -26214.443</t>
-        </is>
+      <c r="W2" t="n">
+        <v>12.53361438801531</v>
       </c>
       <c r="X2" t="n">
         <v>-26214.44258555676</v>
@@ -2504,7 +2440,7 @@
         <v>5.541298658147226e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>146.52</v>
+        <v>2379.358443471029</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000003183e-08</v>
@@ -2544,10 +2480,8 @@
       <c r="K3" t="n">
         <v>85.3846080067192</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 12.387x + -24758.821</t>
-        </is>
+      <c r="W3" t="n">
+        <v>12.38720283166858</v>
       </c>
       <c r="X3" t="n">
         <v>-24758.82138059601</v>
@@ -2556,7 +2490,7 @@
         <v>3.812023470129079e-11</v>
       </c>
       <c r="Z3" t="n">
-        <v>121.5799999999999</v>
+        <v>2298.686712933061</v>
       </c>
       <c r="AA3" t="n">
         <v>1e-08</v>
@@ -2596,10 +2530,8 @@
       <c r="K4" t="n">
         <v>85.37456612357062</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 12.360x + -24325.726</t>
-        </is>
+      <c r="W4" t="n">
+        <v>12.3601932199479</v>
       </c>
       <c r="X4" t="n">
         <v>-24325.7259433379</v>
@@ -2608,7 +2540,7 @@
         <v>6.808290655865747e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>117.4599999999998</v>
+        <v>2264.08941764979</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000043e-08</v>
@@ -2648,10 +2580,8 @@
       <c r="K5" t="n">
         <v>85.70559847180388</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 13.317x + -25977.778</t>
-        </is>
+      <c r="W5" t="n">
+        <v>13.31697755772579</v>
       </c>
       <c r="X5" t="n">
         <v>-25977.77842972598</v>
@@ -2660,7 +2590,7 @@
         <v>1.540732805980894e-10</v>
       </c>
       <c r="Z5" t="n">
-        <v>110.0999999999999</v>
+        <v>2236.62994468916</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000001e-08</v>
@@ -2700,10 +2630,8 @@
       <c r="K6" t="n">
         <v>85.63825527665279</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 13.111x + -25258.808</t>
-        </is>
+      <c r="W6" t="n">
+        <v>13.11059185151038</v>
       </c>
       <c r="X6" t="n">
         <v>-25258.80810553961</v>
@@ -2712,7 +2640,7 @@
         <v>2.227799825251502e-11</v>
       </c>
       <c r="Z6" t="n">
-        <v>107.1399999999999</v>
+        <v>2209.588793247175</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000001834e-08</v>
@@ -2752,10 +2680,8 @@
       <c r="K7" t="n">
         <v>85.32604517599174</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 12.231x + -23245.160</t>
-        </is>
+      <c r="W7" t="n">
+        <v>12.23131827771866</v>
       </c>
       <c r="X7" t="n">
         <v>-23245.16000230626</v>
@@ -2764,7 +2690,7 @@
         <v>3.800168648515154e-13</v>
       </c>
       <c r="Z7" t="n">
-        <v>112.8099999999999</v>
+        <v>2184.383669229311</v>
       </c>
       <c r="AA7" t="n">
         <v>1e-08</v>
@@ -2804,10 +2730,8 @@
       <c r="K8" t="n">
         <v>85.47432271066397</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 12.634x + -23804.865</t>
-        </is>
+      <c r="W8" t="n">
+        <v>12.63381550331409</v>
       </c>
       <c r="X8" t="n">
         <v>-23804.86509309887</v>
@@ -2816,7 +2740,7 @@
         <v>1.099531431124705e-10</v>
       </c>
       <c r="Z8" t="n">
-        <v>103.8699999999999</v>
+        <v>2161.343787670391</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000081e-08</v>
@@ -2856,10 +2780,8 @@
       <c r="K9" t="n">
         <v>85.12585822455783</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 11.727x + -21804.109</t>
-        </is>
+      <c r="W9" t="n">
+        <v>11.72667954547315</v>
       </c>
       <c r="X9" t="n">
         <v>-21804.10890993775</v>
@@ -2868,7 +2790,7 @@
         <v>2.046865820866358e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>108.79</v>
+        <v>2138.103073593617</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000001189e-08</v>
@@ -2908,10 +2830,8 @@
       <c r="K10" t="n">
         <v>85.03653081940523</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 11.515x + -21190.063</t>
-        </is>
+      <c r="W10" t="n">
+        <v>11.51460381523546</v>
       </c>
       <c r="X10" t="n">
         <v>-21190.06294064082</v>
@@ -2920,7 +2840,7 @@
         <v>4.025590510433788e-10</v>
       </c>
       <c r="Z10" t="n">
-        <v>106.95</v>
+        <v>2115.760414333809</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000001e-08</v>
@@ -2960,10 +2880,8 @@
       <c r="K11" t="n">
         <v>85.26673206274738</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 12.077x + -22025.435</t>
-        </is>
+      <c r="W11" t="n">
+        <v>12.07735981958195</v>
       </c>
       <c r="X11" t="n">
         <v>-22025.43501170534</v>
@@ -2972,7 +2890,7 @@
         <v>2.196517491302546e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>99.42000000000007</v>
+        <v>2093.084988747466</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000001e-08</v>
@@ -3012,10 +2930,8 @@
       <c r="K12" t="n">
         <v>85.01765938439033</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 11.471x + -20698.133</t>
-        </is>
+      <c r="W12" t="n">
+        <v>11.47077097471103</v>
       </c>
       <c r="X12" t="n">
         <v>-20698.13310447288</v>
@@ -3024,7 +2940,7 @@
         <v>4.797252980949783e-10</v>
       </c>
       <c r="Z12" t="n">
-        <v>98.35000000000014</v>
+        <v>2071.993436691035</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000000296e-08</v>
@@ -3064,10 +2980,8 @@
       <c r="K13" t="n">
         <v>84.75612030995326</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 10.896x + -19445.368</t>
-        </is>
+      <c r="W13" t="n">
+        <v>10.89569460163166</v>
       </c>
       <c r="X13" t="n">
         <v>-19445.36752758491</v>
@@ -3076,7 +2990,7 @@
         <v>6.374504475335359e-10</v>
       </c>
       <c r="Z13" t="n">
-        <v>95.68000000000006</v>
+        <v>2051.959127575353</v>
       </c>
       <c r="AA13" t="n">
         <v>1e-08</v>
@@ -3116,10 +3030,8 @@
       <c r="K14" t="n">
         <v>84.64922985880173</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 10.677x + -18845.873</t>
-        </is>
+      <c r="W14" t="n">
+        <v>10.67680243749723</v>
       </c>
       <c r="X14" t="n">
         <v>-18845.87304426603</v>
@@ -3128,7 +3040,7 @@
         <v>1.614136944123934e-10</v>
       </c>
       <c r="Z14" t="n">
-        <v>99.58000000000015</v>
+        <v>2030.984346180971</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000005e-08</v>
@@ -3168,10 +3080,8 @@
       <c r="K15" t="n">
         <v>84.5964145509308</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 10.572x + -18479.296</t>
-        </is>
+      <c r="W15" t="n">
+        <v>10.5718338092747</v>
       </c>
       <c r="X15" t="n">
         <v>-18479.29582233515</v>
@@ -3180,7 +3090,7 @@
         <v>3.227074115855774e-09</v>
       </c>
       <c r="Z15" t="n">
-        <v>93.59999999999991</v>
+        <v>2010.325514160533</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000000436e-08</v>
@@ -3220,10 +3130,8 @@
       <c r="K16" t="n">
         <v>83.8873259842145</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 9.338x + -16080.876</t>
-        </is>
+      <c r="W16" t="n">
+        <v>9.337686704726467</v>
       </c>
       <c r="X16" t="n">
         <v>-16080.87588875104</v>
@@ -3232,7 +3140,7 @@
         <v>1.543672370184439e-10</v>
       </c>
       <c r="Z16" t="n">
-        <v>98.02999999999997</v>
+        <v>1988.750459253557</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000000143e-08</v>
@@ -3272,10 +3180,8 @@
       <c r="K17" t="n">
         <v>83.84950143556108</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 9.280x + -15817.825</t>
-        </is>
+      <c r="W17" t="n">
+        <v>9.27982204989377</v>
       </c>
       <c r="X17" t="n">
         <v>-15817.82457141673</v>
@@ -3284,7 +3190,7 @@
         <v>8.487538027545064e-12</v>
       </c>
       <c r="Z17" t="n">
-        <v>93.6099999999999</v>
+        <v>1968.855056994121</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000000003e-08</v>
@@ -3324,10 +3230,8 @@
       <c r="K18" t="n">
         <v>83.03150958013086</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 8.182x + -13761.671</t>
-        </is>
+      <c r="W18" t="n">
+        <v>8.181541091792829</v>
       </c>
       <c r="X18" t="n">
         <v>-13761.67120707656</v>
@@ -3336,7 +3240,7 @@
         <v>1.91260812370299e-08</v>
       </c>
       <c r="Z18" t="n">
-        <v>94.37999999999988</v>
+        <v>1951.54936457166</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000000507e-08</v>
@@ -3376,10 +3280,8 @@
       <c r="K19" t="n">
         <v>82.77435677241263</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 7.887x + -13120.676</t>
-        </is>
+      <c r="W19" t="n">
+        <v>7.887424022376358</v>
       </c>
       <c r="X19" t="n">
         <v>-13120.67620608886</v>
@@ -3388,7 +3290,7 @@
         <v>8.548719048641945e-09</v>
       </c>
       <c r="Z19" t="n">
-        <v>90.7199999999998</v>
+        <v>1932.428859428727</v>
       </c>
       <c r="AA19" t="n">
         <v>1.00000000000151e-08</v>
@@ -3428,10 +3330,8 @@
       <c r="K20" t="n">
         <v>82.73382390880052</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 7.843x + -12929.071</t>
-        </is>
+      <c r="W20" t="n">
+        <v>7.842954344332018</v>
       </c>
       <c r="X20" t="n">
         <v>-12929.07100717827</v>
@@ -3440,7 +3340,7 @@
         <v>2.025638953728457e-08</v>
       </c>
       <c r="Z20" t="n">
-        <v>95.67999999999984</v>
+        <v>1914.083541807276</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000195e-08</v>
@@ -3480,10 +3380,8 @@
       <c r="K21" t="n">
         <v>81.93453877658332</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 7.057x + -11470.572</t>
-        </is>
+      <c r="W21" t="n">
+        <v>7.05685909151844</v>
       </c>
       <c r="X21" t="n">
         <v>-11470.57186577493</v>
@@ -3492,7 +3390,7 @@
         <v>1.752050007909983e-08</v>
       </c>
       <c r="Z21" t="n">
-        <v>95.16000000000008</v>
+        <v>1895.709493056404</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000000456e-08</v>
@@ -3532,10 +3430,8 @@
       <c r="K22" t="n">
         <v>81.02447070953967</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 6.331x + -10139.899</t>
-        </is>
+      <c r="W22" t="n">
+        <v>6.33125126127253</v>
       </c>
       <c r="X22" t="n">
         <v>-10139.89883350505</v>
@@ -3544,7 +3440,7 @@
         <v>5.821268237732372e-09</v>
       </c>
       <c r="Z22" t="n">
-        <v>93.57999999999993</v>
+        <v>1878.08991469867</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000000031e-08</v>
@@ -3670,12 +3566,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -3730,10 +3626,8 @@
       <c r="K2" t="n">
         <v>82.87246204251296</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 7.997x + -17035.165</t>
-        </is>
+      <c r="W2" t="n">
+        <v>7.997140332641517</v>
       </c>
       <c r="X2" t="n">
         <v>-17035.16492583882</v>
@@ -3742,7 +3636,7 @@
         <v>1.43552925947184e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>293.3000000000002</v>
+        <v>2414.184672349003</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000019e-08</v>
@@ -3782,10 +3676,8 @@
       <c r="K3" t="n">
         <v>84.29810912628179</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 10.015x + -19903.461</t>
-        </is>
+      <c r="W3" t="n">
+        <v>10.01536353342914</v>
       </c>
       <c r="X3" t="n">
         <v>-19903.46052767711</v>
@@ -3794,7 +3686,7 @@
         <v>9.229892964243688e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>227.8900000000001</v>
+        <v>2269.65944353937</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000001121e-08</v>
@@ -3834,10 +3726,8 @@
       <c r="K4" t="n">
         <v>84.47525403802632</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 10.339x + -20017.323</t>
-        </is>
+      <c r="W4" t="n">
+        <v>10.33859206957012</v>
       </c>
       <c r="X4" t="n">
         <v>-20017.32349947653</v>
@@ -3846,7 +3736,7 @@
         <v>6.958771555508287e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>211.7599999999998</v>
+        <v>2220.428780864845</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000001104e-08</v>
@@ -3886,10 +3776,8 @@
       <c r="K5" t="n">
         <v>85.08080360645602</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 11.619x + -22291.095</t>
-        </is>
+      <c r="W5" t="n">
+        <v>11.61875326434367</v>
       </c>
       <c r="X5" t="n">
         <v>-22291.09534960582</v>
@@ -3898,7 +3786,7 @@
         <v>7.072475311902202e-10</v>
       </c>
       <c r="Z5" t="n">
-        <v>188.9400000000001</v>
+        <v>2190.12682626144</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000001934e-08</v>
@@ -3938,10 +3826,8 @@
       <c r="K6" t="n">
         <v>85.23320703257785</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 11.992x + -22726.896</t>
-        </is>
+      <c r="W6" t="n">
+        <v>11.9920302377218</v>
       </c>
       <c r="X6" t="n">
         <v>-22726.89571323263</v>
@@ -3950,7 +3836,7 @@
         <v>6.243939984793676e-12</v>
       </c>
       <c r="Z6" t="n">
-        <v>179.23</v>
+        <v>2161.898799835519</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000042e-08</v>
@@ -3990,10 +3876,8 @@
       <c r="K7" t="n">
         <v>85.13928882704994</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 11.759x + -21966.103</t>
-        </is>
+      <c r="W7" t="n">
+        <v>11.75923810363861</v>
       </c>
       <c r="X7" t="n">
         <v>-21966.10306427179</v>
@@ -4002,7 +3886,7 @@
         <v>5.783910471788046e-10</v>
       </c>
       <c r="Z7" t="n">
-        <v>177.27</v>
+        <v>2134.599167013088</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000097e-08</v>
@@ -4042,10 +3926,8 @@
       <c r="K8" t="n">
         <v>85.50323347619953</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 12.715x + -23546.807</t>
-        </is>
+      <c r="W8" t="n">
+        <v>12.71537901578058</v>
       </c>
       <c r="X8" t="n">
         <v>-23546.80736587457</v>
@@ -4054,7 +3936,7 @@
         <v>8.963737035817436e-11</v>
       </c>
       <c r="Z8" t="n">
-        <v>166.8199999999999</v>
+        <v>2108.106949011164</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000196e-08</v>
@@ -4094,10 +3976,8 @@
       <c r="K9" t="n">
         <v>85.40079520789749</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 12.431x + -22713.018</t>
-        </is>
+      <c r="W9" t="n">
+        <v>12.43098924070793</v>
       </c>
       <c r="X9" t="n">
         <v>-22713.01822669869</v>
@@ -4106,7 +3986,7 @@
         <v>1.981859031213007e-10</v>
       </c>
       <c r="Z9" t="n">
-        <v>163.8099999999999</v>
+        <v>2082.409191383807</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000013e-08</v>
@@ -4146,10 +4026,8 @@
       <c r="K10" t="n">
         <v>85.7844482803424</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 13.567x + -24584.774</t>
-        </is>
+      <c r="W10" t="n">
+        <v>13.56699175309253</v>
       </c>
       <c r="X10" t="n">
         <v>-24584.77447526265</v>
@@ -4158,7 +4036,7 @@
         <v>5.474393743273697e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>151.5999999999999</v>
+        <v>2058.209139504361</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000467e-08</v>
@@ -4198,10 +4076,8 @@
       <c r="K11" t="n">
         <v>85.78032281468909</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 13.554x + -24296.189</t>
-        </is>
+      <c r="W11" t="n">
+        <v>13.55367965450652</v>
       </c>
       <c r="X11" t="n">
         <v>-24296.18936322996</v>
@@ -4210,7 +4086,7 @@
         <v>4.011318450530509e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>151.0999999999999</v>
+        <v>2034.459712771494</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000037e-08</v>
@@ -4336,12 +4212,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -4396,10 +4272,8 @@
       <c r="K2" t="n">
         <v>84.29157986772481</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 10.004x + -14794.510</t>
-        </is>
+      <c r="W2" t="n">
+        <v>10.00383198900444</v>
       </c>
       <c r="X2" t="n">
         <v>-14794.51045243109</v>
@@ -4408,7 +4282,7 @@
         <v>2.195289892865387e-12</v>
       </c>
       <c r="Z2" t="n">
-        <v>212.8</v>
+        <v>1628.089489807075</v>
       </c>
       <c r="AA2" t="n">
         <v>1e-08</v>
@@ -4448,10 +4322,8 @@
       <c r="K3" t="n">
         <v>84.76359292678485</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 10.911x + -15334.959</t>
-        </is>
+      <c r="W3" t="n">
+        <v>10.91133041405952</v>
       </c>
       <c r="X3" t="n">
         <v>-15334.95902045895</v>
@@ -4460,7 +4332,7 @@
         <v>2.365301058043345e-11</v>
       </c>
       <c r="Z3" t="n">
-        <v>171.9299999999998</v>
+        <v>1566.524190175706</v>
       </c>
       <c r="AA3" t="n">
         <v>1e-08</v>
@@ -4500,10 +4372,8 @@
       <c r="K4" t="n">
         <v>84.81592564277415</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 11.022x + -15152.563</t>
-        </is>
+      <c r="W4" t="n">
+        <v>11.02209187924315</v>
       </c>
       <c r="X4" t="n">
         <v>-15152.5633894038</v>
@@ -4512,7 +4382,7 @@
         <v>1.535576153115226e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>153.8199999999999</v>
+        <v>1536.346467996142</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000383e-08</v>
@@ -4552,10 +4422,8 @@
       <c r="K5" t="n">
         <v>84.92344506142399</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 11.257x + -15206.828</t>
-        </is>
+      <c r="W5" t="n">
+        <v>11.25680105724169</v>
       </c>
       <c r="X5" t="n">
         <v>-15206.82816016236</v>
@@ -4564,7 +4432,7 @@
         <v>4.434136425764144e-13</v>
       </c>
       <c r="Z5" t="n">
-        <v>144.47</v>
+        <v>1507.939512535982</v>
       </c>
       <c r="AA5" t="n">
         <v>1e-08</v>
@@ -4604,10 +4472,8 @@
       <c r="K6" t="n">
         <v>85.28020782147409</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 12.112x + -16132.011</t>
-        </is>
+      <c r="W6" t="n">
+        <v>12.11199977031418</v>
       </c>
       <c r="X6" t="n">
         <v>-16132.01103357115</v>
@@ -4616,7 +4482,7 @@
         <v>3.277163233124847e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>135.5</v>
+        <v>1481.633125818683</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000002174e-08</v>
@@ -4656,10 +4522,8 @@
       <c r="K7" t="n">
         <v>85.52805428366283</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 12.786x + -16828.888</t>
-        </is>
+      <c r="W7" t="n">
+        <v>12.78624350064413</v>
       </c>
       <c r="X7" t="n">
         <v>-16828.88792932818</v>
@@ -4668,7 +4532,7 @@
         <v>1.443577533704001e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>127.9300000000001</v>
+        <v>1459.276569040487</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000001083e-08</v>
@@ -4708,10 +4572,8 @@
       <c r="K8" t="n">
         <v>85.33464182375577</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 12.254x + -15859.379</t>
-        </is>
+      <c r="W8" t="n">
+        <v>12.25395659070184</v>
       </c>
       <c r="X8" t="n">
         <v>-15859.37896803688</v>
@@ -4720,7 +4582,7 @@
         <v>4.650962941173963e-10</v>
       </c>
       <c r="Z8" t="n">
-        <v>126.1000000000001</v>
+        <v>1438.460456695073</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000239e-08</v>
@@ -4760,10 +4622,8 @@
       <c r="K9" t="n">
         <v>85.25920610367623</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 12.058x + -15374.365</t>
-        </is>
+      <c r="W9" t="n">
+        <v>12.05809956257537</v>
       </c>
       <c r="X9" t="n">
         <v>-15374.36538035429</v>
@@ -4772,7 +4632,7 @@
         <v>2.625280022033863e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>125.48</v>
+        <v>1413.222041036442</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000001981e-08</v>
@@ -4812,10 +4672,8 @@
       <c r="K10" t="n">
         <v>85.51287642381136</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 12.743x + -15795.456</t>
-        </is>
+      <c r="W10" t="n">
+        <v>12.74281711611629</v>
       </c>
       <c r="X10" t="n">
         <v>-15795.45562874301</v>
@@ -4824,7 +4682,7 @@
         <v>2.362036821396672e-08</v>
       </c>
       <c r="Z10" t="n">
-        <v>117.8200000000002</v>
+        <v>1372.236703505263</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000002207e-08</v>
@@ -4864,10 +4722,8 @@
       <c r="K11" t="n">
         <v>85.13160294092722</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 11.741x + -14297.148</t>
-        </is>
+      <c r="W11" t="n">
+        <v>11.74058399299445</v>
       </c>
       <c r="X11" t="n">
         <v>-14297.14802215251</v>
@@ -4876,7 +4732,7 @@
         <v>5.397444398910247e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>119.74</v>
+        <v>1354.01641079458</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000186e-08</v>
@@ -4916,10 +4772,8 @@
       <c r="K12" t="n">
         <v>85.16390910288288</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 11.819x + -14220.389</t>
-        </is>
+      <c r="W12" t="n">
+        <v>11.81939121911365</v>
       </c>
       <c r="X12" t="n">
         <v>-14220.3889639639</v>
@@ -4928,7 +4782,7 @@
         <v>2.646039073902291</v>
       </c>
       <c r="Z12" t="n">
-        <v>116.8899999999999</v>
+        <v>1374.412059626735</v>
       </c>
       <c r="AA12" t="n">
         <v>1.11296106566074e-08</v>
@@ -4968,10 +4822,8 @@
       <c r="K13" t="n">
         <v>85.27032811850945</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 12.087x + -14372.857</t>
-        </is>
+      <c r="W13" t="n">
+        <v>12.08658435245719</v>
       </c>
       <c r="X13" t="n">
         <v>-14372.85713044984</v>
@@ -4980,7 +4832,7 @@
         <v>2.044162985223539e-08</v>
       </c>
       <c r="Z13" t="n">
-        <v>112.8599999999999</v>
+        <v>1319.653545226634</v>
       </c>
       <c r="AA13" t="n">
         <v>1.00000000000037e-08</v>
@@ -5020,10 +4872,8 @@
       <c r="K14" t="n">
         <v>85.43648124167997</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 12.529x + -14752.010</t>
-        </is>
+      <c r="W14" t="n">
+        <v>12.52861492137982</v>
       </c>
       <c r="X14" t="n">
         <v>-14752.00982808087</v>
@@ -5032,7 +4882,7 @@
         <v>1.955972353526669e-09</v>
       </c>
       <c r="Z14" t="n">
-        <v>109.5899999999999</v>
+        <v>1303.037974414169</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000008e-08</v>
@@ -5072,10 +4922,8 @@
       <c r="K15" t="n">
         <v>85.35199058660156</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 12.300x + -14282.752</t>
-        </is>
+      <c r="W15" t="n">
+        <v>12.29989707922384</v>
       </c>
       <c r="X15" t="n">
         <v>-14282.7519702549</v>
@@ -5084,7 +4932,7 @@
         <v>6.946933965987063e-09</v>
       </c>
       <c r="Z15" t="n">
-        <v>109.74</v>
+        <v>1286.607047277894</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000000044e-08</v>
@@ -5124,10 +4972,8 @@
       <c r="K16" t="n">
         <v>85.36703815480016</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 12.340x + -14163.213</t>
-        </is>
+      <c r="W16" t="n">
+        <v>12.34002189431738</v>
       </c>
       <c r="X16" t="n">
         <v>-14163.21347150649</v>
@@ -5136,7 +4982,7 @@
         <v>1.317777510507496e-12</v>
       </c>
       <c r="Z16" t="n">
-        <v>108.9300000000001</v>
+        <v>1270.552012661203</v>
       </c>
       <c r="AA16" t="n">
         <v>1e-08</v>
@@ -5176,10 +5022,8 @@
       <c r="K17" t="n">
         <v>85.02808390379695</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 11.495x + -12979.630</t>
-        </is>
+      <c r="W17" t="n">
+        <v>11.49494306050369</v>
       </c>
       <c r="X17" t="n">
         <v>-12979.62958242628</v>
@@ -5188,7 +5032,7 @@
         <v>3.773369718771121e-11</v>
       </c>
       <c r="Z17" t="n">
-        <v>112.8700000000001</v>
+        <v>1254.713551795002</v>
       </c>
       <c r="AA17" t="n">
         <v>1e-08</v>
@@ -5228,10 +5072,8 @@
       <c r="K18" t="n">
         <v>85.74503766977601</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 13.441x + -15118.415</t>
-        </is>
+      <c r="W18" t="n">
+        <v>13.44087383798877</v>
       </c>
       <c r="X18" t="n">
         <v>-15118.41544456057</v>
@@ -5240,7 +5082,7 @@
         <v>6.718298736843242e-09</v>
       </c>
       <c r="Z18" t="n">
-        <v>101.47</v>
+        <v>1238.755925526981</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000000173e-08</v>
@@ -5280,10 +5122,8 @@
       <c r="K19" t="n">
         <v>85.7597954527312</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 13.488x + -14985.982</t>
-        </is>
+      <c r="W19" t="n">
+        <v>13.48782614974743</v>
       </c>
       <c r="X19" t="n">
         <v>-14985.98171521551</v>
@@ -5292,7 +5132,7 @@
         <v>2.396165538541654e-08</v>
       </c>
       <c r="Z19" t="n">
-        <v>99.83999999999992</v>
+        <v>1223.036752604663</v>
       </c>
       <c r="AA19" t="n">
         <v>1.00000000000009e-08</v>
@@ -5332,10 +5172,8 @@
       <c r="K20" t="n">
         <v>85.26109577660421</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 12.063x + -13152.696</t>
-        </is>
+      <c r="W20" t="n">
+        <v>12.06292983031289</v>
       </c>
       <c r="X20" t="n">
         <v>-13152.69576382672</v>
@@ -5344,7 +5182,7 @@
         <v>1.631463280094322e-10</v>
       </c>
       <c r="Z20" t="n">
-        <v>105.5700000000002</v>
+        <v>1207.145201132615</v>
       </c>
       <c r="AA20" t="n">
         <v>1e-08</v>
@@ -5384,10 +5222,8 @@
       <c r="K21" t="n">
         <v>85.44933411728937</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 12.564x + -13556.250</t>
-        </is>
+      <c r="W21" t="n">
+        <v>12.56415055985919</v>
       </c>
       <c r="X21" t="n">
         <v>-13556.25032917496</v>
@@ -5396,7 +5232,7 @@
         <v>2.07358855129548e-11</v>
       </c>
       <c r="Z21" t="n">
-        <v>101.8100000000002</v>
+        <v>1191.151566546085</v>
       </c>
       <c r="AA21" t="n">
         <v>1e-08</v>
@@ -5436,10 +5272,8 @@
       <c r="K22" t="n">
         <v>85.47404457713796</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 12.633x + -13463.887</t>
-        </is>
+      <c r="W22" t="n">
+        <v>12.63303587865937</v>
       </c>
       <c r="X22" t="n">
         <v>-13463.88744921737</v>
@@ -5448,7 +5282,7 @@
         <v>9.705506530223433e-12</v>
       </c>
       <c r="Z22" t="n">
-        <v>100.01</v>
+        <v>1175.537807625076</v>
       </c>
       <c r="AA22" t="n">
         <v>1e-08</v>
@@ -5574,12 +5408,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -5634,10 +5468,8 @@
       <c r="K2" t="n">
         <v>83.29187978546906</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 8.502x + -12557.057</t>
-        </is>
+      <c r="W2" t="n">
+        <v>8.502195143941647</v>
       </c>
       <c r="X2" t="n">
         <v>-12557.0569811854</v>
@@ -5646,7 +5478,7 @@
         <v>2.857120419133815e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>248.9300000000001</v>
+        <v>1643.215844494769</v>
       </c>
       <c r="AA2" t="n">
         <v>1e-08</v>
@@ -5686,10 +5518,8 @@
       <c r="K3" t="n">
         <v>84.15644170843692</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 9.771x + -14015.678</t>
-        </is>
+      <c r="W3" t="n">
+        <v>9.77092698713358</v>
       </c>
       <c r="X3" t="n">
         <v>-14015.6778187673</v>
@@ -5698,7 +5528,7 @@
         <v>3.578574811151836e-12</v>
       </c>
       <c r="Z3" t="n">
-        <v>206.79</v>
+        <v>1598.382999802017</v>
       </c>
       <c r="AA3" t="n">
         <v>1e-08</v>
@@ -5738,10 +5568,8 @@
       <c r="K4" t="n">
         <v>84.33490526499038</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 10.081x + -14183.873</t>
-        </is>
+      <c r="W4" t="n">
+        <v>10.08084580072607</v>
       </c>
       <c r="X4" t="n">
         <v>-14183.87339017491</v>
@@ -5750,7 +5578,7 @@
         <v>1.569572412145782e-11</v>
       </c>
       <c r="Z4" t="n">
-        <v>190.76</v>
+        <v>1570.636705029124</v>
       </c>
       <c r="AA4" t="n">
         <v>1e-08</v>
@@ -5790,10 +5618,8 @@
       <c r="K5" t="n">
         <v>84.50140570356353</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 10.388x + -14387.354</t>
-        </is>
+      <c r="W5" t="n">
+        <v>10.38806846242153</v>
       </c>
       <c r="X5" t="n">
         <v>-14387.35384990727</v>
@@ -5802,7 +5628,7 @@
         <v>1.241585259746103e-12</v>
       </c>
       <c r="Z5" t="n">
-        <v>180.3699999999999</v>
+        <v>1544.736492937587</v>
       </c>
       <c r="AA5" t="n">
         <v>1e-08</v>
@@ -5842,10 +5668,8 @@
       <c r="K6" t="n">
         <v>84.46374403670583</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 10.317x + -14038.855</t>
-        </is>
+      <c r="W6" t="n">
+        <v>10.3169639507533</v>
       </c>
       <c r="X6" t="n">
         <v>-14038.85517380458</v>
@@ -5854,7 +5678,7 @@
         <v>1.750223480252316e-11</v>
       </c>
       <c r="Z6" t="n">
-        <v>175.7</v>
+        <v>1518.661451730663</v>
       </c>
       <c r="AA6" t="n">
         <v>1e-08</v>
@@ -5894,10 +5718,8 @@
       <c r="K7" t="n">
         <v>85.2113548665366</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 11.937x + -16069.931</t>
-        </is>
+      <c r="W7" t="n">
+        <v>11.93705273448915</v>
       </c>
       <c r="X7" t="n">
         <v>-16069.93145612055</v>
@@ -5906,7 +5728,7 @@
         <v>1.996394218619561e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>157.26</v>
+        <v>1489.075362164951</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000147e-08</v>
@@ -5946,10 +5768,8 @@
       <c r="K8" t="n">
         <v>84.91994308826736</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 11.249x + -14829.492</t>
-        </is>
+      <c r="W8" t="n">
+        <v>11.24900032585141</v>
       </c>
       <c r="X8" t="n">
         <v>-14829.49186189311</v>
@@ -5958,7 +5778,7 @@
         <v>2.202655218792861e-10</v>
       </c>
       <c r="Z8" t="n">
-        <v>158</v>
+        <v>1464.84296172248</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000054e-08</v>
@@ -5998,10 +5818,8 @@
       <c r="K9" t="n">
         <v>85.00364251023134</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 11.438x + -14851.658</t>
-        </is>
+      <c r="W9" t="n">
+        <v>11.43842763082429</v>
       </c>
       <c r="X9" t="n">
         <v>-14851.65772171988</v>
@@ -6010,7 +5828,7 @@
         <v>3.533504427906842e-10</v>
       </c>
       <c r="Z9" t="n">
-        <v>152.9100000000001</v>
+        <v>1441.857485825023</v>
       </c>
       <c r="AA9" t="n">
         <v>1e-08</v>
@@ -6050,10 +5868,8 @@
       <c r="K10" t="n">
         <v>85.07494422047473</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 11.605x + -14844.997</t>
-        </is>
+      <c r="W10" t="n">
+        <v>11.60486211880897</v>
       </c>
       <c r="X10" t="n">
         <v>-14844.99680820529</v>
@@ -6062,7 +5878,7 @@
         <v>2.344228692442649e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>148.1300000000001</v>
+        <v>1419.028734077478</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000001497e-08</v>
@@ -6102,10 +5918,8 @@
       <c r="K11" t="n">
         <v>84.97518770845778</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 11.373x + -14297.770</t>
-        </is>
+      <c r="W11" t="n">
+        <v>11.37332294569194</v>
       </c>
       <c r="X11" t="n">
         <v>-14297.77010131324</v>
@@ -6114,7 +5928,7 @@
         <v>8.206331235602397e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>147.0600000000002</v>
+        <v>1396.888355884578</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000713e-08</v>
@@ -6240,12 +6054,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -6300,10 +6114,8 @@
       <c r="K2" t="n">
         <v>84.69957835180981</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 10.779x + -15220.491</t>
-        </is>
+      <c r="W2" t="n">
+        <v>10.77881024896596</v>
       </c>
       <c r="X2" t="n">
         <v>-15220.49099597104</v>
@@ -6312,7 +6124,7 @@
         <v>5.720515138620531e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>186.6799999999998</v>
+        <v>1561.134085333618</v>
       </c>
       <c r="AA2" t="n">
         <v>1e-08</v>
@@ -6352,10 +6164,8 @@
       <c r="K3" t="n">
         <v>84.96440355693494</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 11.349x + -15759.772</t>
-        </is>
+      <c r="W3" t="n">
+        <v>11.34884054817086</v>
       </c>
       <c r="X3" t="n">
         <v>-15759.77187096125</v>
@@ -6364,7 +6174,7 @@
         <v>1.405020186175405e-11</v>
       </c>
       <c r="Z3" t="n">
-        <v>149</v>
+        <v>1551.139027118607</v>
       </c>
       <c r="AA3" t="n">
         <v>1e-08</v>
@@ -6404,10 +6214,8 @@
       <c r="K4" t="n">
         <v>85.06970479274403</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 11.592x + -15743.345</t>
-        </is>
+      <c r="W4" t="n">
+        <v>11.59246863346858</v>
       </c>
       <c r="X4" t="n">
         <v>-15743.34464358955</v>
@@ -6416,7 +6224,7 @@
         <v>3.849068832980438e-12</v>
       </c>
       <c r="Z4" t="n">
-        <v>134.4300000000001</v>
+        <v>1518.087734658738</v>
       </c>
       <c r="AA4" t="n">
         <v>1e-08</v>
@@ -6456,10 +6264,8 @@
       <c r="K5" t="n">
         <v>85.41196432998279</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 12.461x + -16705.191</t>
-        </is>
+      <c r="W5" t="n">
+        <v>12.46138149116811</v>
       </c>
       <c r="X5" t="n">
         <v>-16705.190842766</v>
@@ -6468,7 +6274,7 @@
         <v>3.972725382163073e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>126.1799999999998</v>
+        <v>1475.56739157723</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000082e-08</v>
@@ -6508,10 +6314,8 @@
       <c r="K6" t="n">
         <v>85.29685877639768</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 12.155x + -15810.281</t>
-        </is>
+      <c r="W6" t="n">
+        <v>12.15507523593054</v>
       </c>
       <c r="X6" t="n">
         <v>-15810.28106044284</v>
@@ -6520,7 +6324,7 @@
         <v>1.432665748083905e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>123.9000000000001</v>
+        <v>1448.98698330561</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000002293e-08</v>
@@ -6560,10 +6364,8 @@
       <c r="K7" t="n">
         <v>84.99323427216088</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 11.415x + -14598.390</t>
-        </is>
+      <c r="W7" t="n">
+        <v>11.41452792862191</v>
       </c>
       <c r="X7" t="n">
         <v>-14598.38951733558</v>
@@ -6572,7 +6374,7 @@
         <v>5.669064314104212e-10</v>
       </c>
       <c r="Z7" t="n">
-        <v>125.5899999999999</v>
+        <v>1427.972103037568</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000391e-08</v>
@@ -6612,10 +6414,8 @@
       <c r="K8" t="n">
         <v>84.95593288638126</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 11.330x + -14273.137</t>
-        </is>
+      <c r="W8" t="n">
+        <v>11.32968348111185</v>
       </c>
       <c r="X8" t="n">
         <v>-14273.13733194418</v>
@@ -6624,7 +6424,7 @@
         <v>6.033836778576327e-10</v>
       </c>
       <c r="Z8" t="n">
-        <v>122.3699999999999</v>
+        <v>1407.744060034204</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000033e-08</v>
@@ -6664,10 +6464,8 @@
       <c r="K9" t="n">
         <v>85.1665127896344</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 11.826x + -14724.142</t>
-        </is>
+      <c r="W9" t="n">
+        <v>11.82578838154075</v>
       </c>
       <c r="X9" t="n">
         <v>-14724.14165709195</v>
@@ -6676,7 +6474,7 @@
         <v>9.654838727229941e-10</v>
       </c>
       <c r="Z9" t="n">
-        <v>115.8899999999999</v>
+        <v>1388.279453831081</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000043e-08</v>
@@ -6716,10 +6514,8 @@
       <c r="K10" t="n">
         <v>85.2853650046402</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 12.125x + -14923.198</t>
-        </is>
+      <c r="W10" t="n">
+        <v>12.12530877963914</v>
       </c>
       <c r="X10" t="n">
         <v>-14923.19798881167</v>
@@ -6728,7 +6524,7 @@
         <v>4.148303916280517e-14</v>
       </c>
       <c r="Z10" t="n">
-        <v>112.21</v>
+        <v>1369.4863788943</v>
       </c>
       <c r="AA10" t="n">
         <v>1e-08</v>
@@ -6768,10 +6564,8 @@
       <c r="K11" t="n">
         <v>85.26118134802077</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 12.063x + -14624.646</t>
-        </is>
+      <c r="W11" t="n">
+        <v>12.06314865376089</v>
       </c>
       <c r="X11" t="n">
         <v>-14624.64625254544</v>
@@ -6780,7 +6574,7 @@
         <v>5.927648706203283e-11</v>
       </c>
       <c r="Z11" t="n">
-        <v>111.6800000000001</v>
+        <v>1348.577299168596</v>
       </c>
       <c r="AA11" t="n">
         <v>1e-08</v>
@@ -6820,10 +6614,8 @@
       <c r="K12" t="n">
         <v>85.27067498680989</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 12.087x + -14455.317</t>
-        </is>
+      <c r="W12" t="n">
+        <v>12.0874748724692</v>
       </c>
       <c r="X12" t="n">
         <v>-14455.31715333279</v>
@@ -6832,7 +6624,7 @@
         <v>4.257795657508232e-08</v>
       </c>
       <c r="Z12" t="n">
-        <v>110.3599999999999</v>
+        <v>1329.114153146811</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000000044e-08</v>
@@ -6872,10 +6664,8 @@
       <c r="K13" t="n">
         <v>85.30855357734916</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 12.186x + -14379.489</t>
-        </is>
+      <c r="W13" t="n">
+        <v>12.18551167942328</v>
       </c>
       <c r="X13" t="n">
         <v>-14379.48901530511</v>
@@ -6884,7 +6674,7 @@
         <v>3.881021092753764e-09</v>
       </c>
       <c r="Z13" t="n">
-        <v>108.78</v>
+        <v>1310.494918396676</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000032e-08</v>
@@ -6924,10 +6714,8 @@
       <c r="K14" t="n">
         <v>85.16346003264717</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 11.818x + -13745.311</t>
-        </is>
+      <c r="W14" t="n">
+        <v>11.81828856485341</v>
       </c>
       <c r="X14" t="n">
         <v>-13745.31108476702</v>
@@ -6936,7 +6724,7 @@
         <v>1.975839838410178e-08</v>
       </c>
       <c r="Z14" t="n">
-        <v>109.24</v>
+        <v>1293.970002298678</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000244e-08</v>
@@ -6976,10 +6764,8 @@
       <c r="K15" t="n">
         <v>85.3217718766406</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 12.220x + -14063.416</t>
-        </is>
+      <c r="W15" t="n">
+        <v>12.22009591001306</v>
       </c>
       <c r="X15" t="n">
         <v>-14063.41627469487</v>
@@ -6988,7 +6774,7 @@
         <v>2.029298790741381e-12</v>
       </c>
       <c r="Z15" t="n">
-        <v>106.3999999999999</v>
+        <v>1277.592410583077</v>
       </c>
       <c r="AA15" t="n">
         <v>1e-08</v>
@@ -7028,10 +6814,8 @@
       <c r="K16" t="n">
         <v>85.34911493268234</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 12.292x + -13981.306</t>
-        </is>
+      <c r="W16" t="n">
+        <v>12.29225854315993</v>
       </c>
       <c r="X16" t="n">
         <v>-13981.30618522348</v>
@@ -7040,7 +6824,7 @@
         <v>4.162083300514258e-10</v>
       </c>
       <c r="Z16" t="n">
-        <v>103.8</v>
+        <v>1261.494779866881</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000000015e-08</v>
@@ -7080,10 +6864,8 @@
       <c r="K17" t="n">
         <v>85.35152114097437</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 12.299x + -13817.133</t>
-        </is>
+      <c r="W17" t="n">
+        <v>12.29864945710096</v>
       </c>
       <c r="X17" t="n">
         <v>-13817.13317467756</v>
@@ -7092,7 +6874,7 @@
         <v>2.684064584578977e-08</v>
       </c>
       <c r="Z17" t="n">
-        <v>103.1200000000001</v>
+        <v>1246.467035942742</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000000001e-08</v>
@@ -7132,10 +6914,8 @@
       <c r="K18" t="n">
         <v>85.27729633485104</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 12.104x + -13435.470</t>
-        </is>
+      <c r="W18" t="n">
+        <v>12.1044989798793</v>
       </c>
       <c r="X18" t="n">
         <v>-13435.46996480902</v>
@@ -7144,7 +6924,7 @@
         <v>1.119223745646828e-08</v>
       </c>
       <c r="Z18" t="n">
-        <v>103.1700000000001</v>
+        <v>1231.861757013885</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000000048e-08</v>
@@ -7184,10 +6964,8 @@
       <c r="K19" t="n">
         <v>84.98131933645425</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 11.387x + -12450.898</t>
-        </is>
+      <c r="W19" t="n">
+        <v>11.38728988891936</v>
       </c>
       <c r="X19" t="n">
         <v>-12450.89787332109</v>
@@ -7196,7 +6974,7 @@
         <v>8.147913167944852e-09</v>
       </c>
       <c r="Z19" t="n">
-        <v>106.6899999999998</v>
+        <v>1215.763524037895</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000000141e-08</v>
@@ -7236,10 +7014,8 @@
       <c r="K20" t="n">
         <v>85.06418096498804</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 11.579x + -12505.158</t>
-        </is>
+      <c r="W20" t="n">
+        <v>11.57943084299711</v>
       </c>
       <c r="X20" t="n">
         <v>-12505.15815299472</v>
@@ -7248,7 +7024,7 @@
         <v>3.575284539399535e-08</v>
       </c>
       <c r="Z20" t="n">
-        <v>103.71</v>
+        <v>1190.827821894881</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000781e-08</v>
@@ -7288,10 +7064,8 @@
       <c r="K21" t="n">
         <v>85.36916721598409</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 12.346x + -13102.684</t>
-        </is>
+      <c r="W21" t="n">
+        <v>12.34572011487032</v>
       </c>
       <c r="X21" t="n">
         <v>-13102.68398428272</v>
@@ -7300,7 +7074,7 @@
         <v>1.091914501195043e-08</v>
       </c>
       <c r="Z21" t="n">
-        <v>98.70999999999981</v>
+        <v>1168.959373694144</v>
       </c>
       <c r="AA21" t="n">
         <v>1e-08</v>
@@ -7340,10 +7114,8 @@
       <c r="K22" t="n">
         <v>84.96948788281516</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 11.360x + -11653.613</t>
-        </is>
+      <c r="W22" t="n">
+        <v>11.36037004230211</v>
       </c>
       <c r="X22" t="n">
         <v>-11653.612686609</v>
@@ -7352,7 +7124,7 @@
         <v>2.694152859371714e-08</v>
       </c>
       <c r="Z22" t="n">
-        <v>102.48</v>
+        <v>1137.195400226974</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000000003e-08</v>
@@ -7478,12 +7250,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -7538,10 +7310,8 @@
       <c r="K2" t="n">
         <v>82.81292236651709</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 7.930x + -13281.791</t>
-        </is>
+      <c r="W2" t="n">
+        <v>7.930198535607936</v>
       </c>
       <c r="X2" t="n">
         <v>-13281.79072917973</v>
@@ -7550,7 +7320,7 @@
         <v>9.200561400212982e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>278.21</v>
+        <v>1830.049929466298</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000006e-08</v>
@@ -7590,10 +7360,8 @@
       <c r="K3" t="n">
         <v>84.50869731979265</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 10.402x + -15851.703</t>
-        </is>
+      <c r="W3" t="n">
+        <v>10.40194724253539</v>
       </c>
       <c r="X3" t="n">
         <v>-15851.70328379813</v>
@@ -7602,7 +7370,7 @@
         <v>4.065936168913495e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>199.6800000000001</v>
+        <v>1689.575864067239</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000004021e-08</v>
@@ -7642,10 +7410,8 @@
       <c r="K4" t="n">
         <v>84.63548831530643</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 10.649x + -15655.107</t>
-        </is>
+      <c r="W4" t="n">
+        <v>10.64929324606391</v>
       </c>
       <c r="X4" t="n">
         <v>-15655.10664406893</v>
@@ -7654,7 +7420,7 @@
         <v>3.86677482297048e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>176.9300000000001</v>
+        <v>1641.579977125335</v>
       </c>
       <c r="AA4" t="n">
         <v>1e-08</v>
@@ -7694,10 +7460,8 @@
       <c r="K5" t="n">
         <v>84.60891718908613</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 10.596x + -15220.945</t>
-        </is>
+      <c r="W5" t="n">
+        <v>10.59649711416417</v>
       </c>
       <c r="X5" t="n">
         <v>-15220.94529272925</v>
@@ -7706,7 +7470,7 @@
         <v>6.561498959134325e-12</v>
       </c>
       <c r="Z5" t="n">
-        <v>162.6900000000001</v>
+        <v>1608.530501502305</v>
       </c>
       <c r="AA5" t="n">
         <v>1e-08</v>
@@ -7746,10 +7510,8 @@
       <c r="K6" t="n">
         <v>84.80183513301951</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 10.992x + -15517.042</t>
-        </is>
+      <c r="W6" t="n">
+        <v>10.99205071730707</v>
       </c>
       <c r="X6" t="n">
         <v>-15517.04222311667</v>
@@ -7758,7 +7520,7 @@
         <v>4.353083679553433e-11</v>
       </c>
       <c r="Z6" t="n">
-        <v>151.6099999999999</v>
+        <v>1578.911717433993</v>
       </c>
       <c r="AA6" t="n">
         <v>1e-08</v>
@@ -7798,10 +7560,8 @@
       <c r="K7" t="n">
         <v>84.89752450767745</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 11.199x + -15534.455</t>
-        </is>
+      <c r="W7" t="n">
+        <v>11.19931540573011</v>
       </c>
       <c r="X7" t="n">
         <v>-15534.4546766757</v>
@@ -7810,7 +7570,7 @@
         <v>1.581603528249857e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>141.5799999999999</v>
+        <v>1550.379064830883</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000048e-08</v>
@@ -7850,10 +7610,8 @@
       <c r="K8" t="n">
         <v>85.02603763945039</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 11.490x + -15673.253</t>
-        </is>
+      <c r="W8" t="n">
+        <v>11.49019026745334</v>
       </c>
       <c r="X8" t="n">
         <v>-15673.25322399462</v>
@@ -7862,7 +7620,7 @@
         <v>1.857311217561788e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>132.71</v>
+        <v>1522.112183208116</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000331e-08</v>
@@ -7902,10 +7660,8 @@
       <c r="K9" t="n">
         <v>85.29281186330189</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 12.145x + -16328.198</t>
-        </is>
+      <c r="W9" t="n">
+        <v>12.14457803722284</v>
       </c>
       <c r="X9" t="n">
         <v>-16328.19756850009</v>
@@ -7914,7 +7670,7 @@
         <v>1.978407653209302e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>123.9300000000001</v>
+        <v>1495.690982409313</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000003297e-08</v>
@@ -7954,10 +7710,8 @@
       <c r="K10" t="n">
         <v>84.71981144865391</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 10.820x + -14216.450</t>
-        </is>
+      <c r="W10" t="n">
+        <v>10.82034959652196</v>
       </c>
       <c r="X10" t="n">
         <v>-14216.45014198157</v>
@@ -7966,7 +7720,7 @@
         <v>8.491653452779986e-10</v>
       </c>
       <c r="Z10" t="n">
-        <v>127.3800000000001</v>
+        <v>1470.951771926578</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000552e-08</v>
@@ -8006,10 +7760,8 @@
       <c r="K11" t="n">
         <v>84.92702167297365</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 11.265x + -14604.093</t>
-        </is>
+      <c r="W11" t="n">
+        <v>11.26477913511042</v>
       </c>
       <c r="X11" t="n">
         <v>-14604.09283335973</v>
@@ -8018,7 +7770,7 @@
         <v>4.621049876732005e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>122.73</v>
+        <v>1447.456958989253</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000025e-08</v>
@@ -8144,12 +7896,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -8204,10 +7956,8 @@
       <c r="K2" t="n">
         <v>84.17884112240792</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 9.809x + -14025.882</t>
-        </is>
+      <c r="W2" t="n">
+        <v>9.808786325496181</v>
       </c>
       <c r="X2" t="n">
         <v>-14025.88224767315</v>
@@ -8216,7 +7966,7 @@
         <v>1.27196624550196e-11</v>
       </c>
       <c r="Z2" t="n">
-        <v>194.4300000000001</v>
+        <v>1578.690383320698</v>
       </c>
       <c r="AA2" t="n">
         <v>1e-08</v>
@@ -8256,10 +8006,8 @@
       <c r="K3" t="n">
         <v>84.71783366981693</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 10.816x + -14704.948</t>
-        </is>
+      <c r="W3" t="n">
+        <v>10.81627514523796</v>
       </c>
       <c r="X3" t="n">
         <v>-14704.94776391744</v>
@@ -8268,7 +8016,7 @@
         <v>1.08838873926891e-12</v>
       </c>
       <c r="Z3" t="n">
-        <v>152.99</v>
+        <v>1517.532787080726</v>
       </c>
       <c r="AA3" t="n">
         <v>1e-08</v>
@@ -8308,10 +8056,8 @@
       <c r="K4" t="n">
         <v>84.99731831245673</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 11.424x + -15295.272</t>
-        </is>
+      <c r="W4" t="n">
+        <v>11.42389399695365</v>
       </c>
       <c r="X4" t="n">
         <v>-15295.2724659305</v>
@@ -8320,7 +8066,7 @@
         <v>5.342138618469332e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>139.45</v>
+        <v>1493.052936686385</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000031e-08</v>
@@ -8360,10 +8106,8 @@
       <c r="K5" t="n">
         <v>85.10076522835156</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 11.666x + -15427.874</t>
-        </is>
+      <c r="W5" t="n">
+        <v>11.66632610415554</v>
       </c>
       <c r="X5" t="n">
         <v>-15427.87373519644</v>
@@ -8372,7 +8116,7 @@
         <v>2.862011069255058e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>133.49</v>
+        <v>1473.692805584746</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000003143e-08</v>
@@ -8412,10 +8156,8 @@
       <c r="K6" t="n">
         <v>85.17445459739281</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 11.845x + -15479.413</t>
-        </is>
+      <c r="W6" t="n">
+        <v>11.84534365146112</v>
       </c>
       <c r="X6" t="n">
         <v>-15479.41308114051</v>
@@ -8424,7 +8166,7 @@
         <v>5.888687977710606e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>129.0599999999999</v>
+        <v>1455.06074743676</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000148e-08</v>
@@ -8464,10 +8206,8 @@
       <c r="K7" t="n">
         <v>84.97736917416218</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 11.378x + -14655.405</t>
-        </is>
+      <c r="W7" t="n">
+        <v>11.37828810445258</v>
       </c>
       <c r="X7" t="n">
         <v>-14655.40463624706</v>
@@ -8476,7 +8216,7 @@
         <v>7.729415954565923e-11</v>
       </c>
       <c r="Z7" t="n">
-        <v>129.8599999999999</v>
+        <v>1437.008184830983</v>
       </c>
       <c r="AA7" t="n">
         <v>1e-08</v>
@@ -8516,10 +8256,8 @@
       <c r="K8" t="n">
         <v>85.46998644276681</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 12.622x + -16151.193</t>
-        </is>
+      <c r="W8" t="n">
+        <v>12.62167155502846</v>
       </c>
       <c r="X8" t="n">
         <v>-16151.19265390456</v>
@@ -8528,7 +8266,7 @@
         <v>8.419406680258176e-14</v>
       </c>
       <c r="Z8" t="n">
-        <v>118.8099999999999</v>
+        <v>1419.177120355056</v>
       </c>
       <c r="AA8" t="n">
         <v>1e-08</v>
@@ -8568,10 +8306,8 @@
       <c r="K9" t="n">
         <v>84.91003985232454</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 11.227x + -14092.428</t>
-        </is>
+      <c r="W9" t="n">
+        <v>11.22699856954115</v>
       </c>
       <c r="X9" t="n">
         <v>-14092.42771567705</v>
@@ -8580,7 +8316,7 @@
         <v>1.525030701132558e-11</v>
       </c>
       <c r="Z9" t="n">
-        <v>122.8399999999999</v>
+        <v>1401.265498985481</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000001317e-08</v>
@@ -8620,10 +8356,8 @@
       <c r="K10" t="n">
         <v>85.16621755379342</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 11.825x + -14710.905</t>
-        </is>
+      <c r="W10" t="n">
+        <v>11.82506265236012</v>
       </c>
       <c r="X10" t="n">
         <v>-14710.90490501782</v>
@@ -8632,7 +8366,7 @@
         <v>4.782729252109054e-11</v>
       </c>
       <c r="Z10" t="n">
-        <v>116.51</v>
+        <v>1384.601825518677</v>
       </c>
       <c r="AA10" t="n">
         <v>1e-08</v>
@@ -8672,10 +8406,8 @@
       <c r="K11" t="n">
         <v>85.15250549842341</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 11.791x + -14504.058</t>
-        </is>
+      <c r="W11" t="n">
+        <v>11.79145375214653</v>
       </c>
       <c r="X11" t="n">
         <v>-14504.05841288523</v>
@@ -8684,7 +8416,7 @@
         <v>2.91677281693671e-08</v>
       </c>
       <c r="Z11" t="n">
-        <v>116.04</v>
+        <v>1368.390390971445</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000034e-08</v>
@@ -8724,10 +8456,8 @@
       <c r="K12" t="n">
         <v>85.2212811840911</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 11.962x + -14552.665</t>
-        </is>
+      <c r="W12" t="n">
+        <v>11.9619640130516</v>
       </c>
       <c r="X12" t="n">
         <v>-14552.66473296584</v>
@@ -8736,7 +8466,7 @@
         <v>3.180452003584913e-09</v>
       </c>
       <c r="Z12" t="n">
-        <v>112.3500000000001</v>
+        <v>1352.357036463741</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000000003e-08</v>
@@ -8776,10 +8506,8 @@
       <c r="K13" t="n">
         <v>85.41877434052572</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 12.480x + -15045.939</t>
-        </is>
+      <c r="W13" t="n">
+        <v>12.47998475007076</v>
       </c>
       <c r="X13" t="n">
         <v>-15045.93913038232</v>
@@ -8788,7 +8516,7 @@
         <v>2.275423215382914e-09</v>
       </c>
       <c r="Z13" t="n">
-        <v>109.73</v>
+        <v>1336.665934289909</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000078e-08</v>
@@ -8828,10 +8556,8 @@
       <c r="K14" t="n">
         <v>85.07401703520414</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 11.603x + -13777.008</t>
-        </is>
+      <c r="W14" t="n">
+        <v>11.60266701426827</v>
       </c>
       <c r="X14" t="n">
         <v>-13777.00809800909</v>
@@ -8840,7 +8566,7 @@
         <v>6.322043780405196e-09</v>
       </c>
       <c r="Z14" t="n">
-        <v>112.23</v>
+        <v>1321.064042952145</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000171e-08</v>
@@ -8880,10 +8606,8 @@
       <c r="K15" t="n">
         <v>85.05343488771216</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 11.554x + -13556.950</t>
-        </is>
+      <c r="W15" t="n">
+        <v>11.55415029024188</v>
       </c>
       <c r="X15" t="n">
         <v>-13556.95033914214</v>
@@ -8892,7 +8616,7 @@
         <v>1.624561494765244e-10</v>
       </c>
       <c r="Z15" t="n">
-        <v>112.48</v>
+        <v>1305.248307885294</v>
       </c>
       <c r="AA15" t="n">
         <v>1e-08</v>
@@ -8932,10 +8656,8 @@
       <c r="K16" t="n">
         <v>85.18410989860938</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 11.869x + -13791.093</t>
-        </is>
+      <c r="W16" t="n">
+        <v>11.86920475533394</v>
       </c>
       <c r="X16" t="n">
         <v>-13791.09269012721</v>
@@ -8944,7 +8666,7 @@
         <v>7.108295698050464e-11</v>
       </c>
       <c r="Z16" t="n">
-        <v>108.3199999999999</v>
+        <v>1289.512726259253</v>
       </c>
       <c r="AA16" t="n">
         <v>1e-08</v>
@@ -8984,10 +8706,8 @@
       <c r="K17" t="n">
         <v>84.62129534688206</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 10.621x + -12114.955</t>
-        </is>
+      <c r="W17" t="n">
+        <v>10.62102748036397</v>
       </c>
       <c r="X17" t="n">
         <v>-12114.95481458074</v>
@@ -8996,7 +8716,7 @@
         <v>1.384184944204951e-09</v>
       </c>
       <c r="Z17" t="n">
-        <v>113.73</v>
+        <v>1273.785316868221</v>
       </c>
       <c r="AA17" t="n">
         <v>1e-08</v>
@@ -9036,10 +8756,8 @@
       <c r="K18" t="n">
         <v>85.1099176869902</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 11.688x + -13244.152</t>
-        </is>
+      <c r="W18" t="n">
+        <v>11.68826792808816</v>
       </c>
       <c r="X18" t="n">
         <v>-13244.15151782749</v>
@@ -9048,7 +8766,7 @@
         <v>7.980224748905889e-12</v>
       </c>
       <c r="Z18" t="n">
-        <v>108.3099999999999</v>
+        <v>1257.905590422531</v>
       </c>
       <c r="AA18" t="n">
         <v>1e-08</v>
@@ -9088,10 +8806,8 @@
       <c r="K19" t="n">
         <v>85.22997130373646</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 11.984x + -13431.368</t>
-        </is>
+      <c r="W19" t="n">
+        <v>11.98385782316719</v>
       </c>
       <c r="X19" t="n">
         <v>-13431.36814650586</v>
@@ -9100,7 +8816,7 @@
         <v>2.919678243613795e-09</v>
       </c>
       <c r="Z19" t="n">
-        <v>103.95</v>
+        <v>1241.799825405904</v>
       </c>
       <c r="AA19" t="n">
         <v>1e-08</v>
@@ -9140,10 +8856,8 @@
       <c r="K20" t="n">
         <v>85.32974306621261</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 12.241x + -13563.153</t>
-        </is>
+      <c r="W20" t="n">
+        <v>12.24104606733497</v>
       </c>
       <c r="X20" t="n">
         <v>-13563.15286952507</v>
@@ -9152,7 +8866,7 @@
         <v>2.983169149554645e-08</v>
       </c>
       <c r="Z20" t="n">
-        <v>101.95</v>
+        <v>1225.882886725404</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000037e-08</v>
@@ -9192,10 +8906,8 @@
       <c r="K21" t="n">
         <v>85.26851256380095</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 12.082x + -13210.893</t>
-        </is>
+      <c r="W21" t="n">
+        <v>12.08192537796969</v>
       </c>
       <c r="X21" t="n">
         <v>-13210.89265957081</v>
@@ -9204,7 +8916,7 @@
         <v>1.655998173363553e-08</v>
       </c>
       <c r="Z21" t="n">
-        <v>99.16000000000008</v>
+        <v>1209.790388678459</v>
       </c>
       <c r="AA21" t="n">
         <v>1e-08</v>
@@ -9244,10 +8956,8 @@
       <c r="K22" t="n">
         <v>84.95704401492692</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 11.332x + -12189.992</t>
-        </is>
+      <c r="W22" t="n">
+        <v>11.33219272521159</v>
       </c>
       <c r="X22" t="n">
         <v>-12189.99184383551</v>
@@ -9256,7 +8966,7 @@
         <v>1.334879530913401e-08</v>
       </c>
       <c r="Z22" t="n">
-        <v>102.2700000000002</v>
+        <v>1193.504918833813</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000000018e-08</v>
@@ -9382,12 +9092,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -9442,10 +9152,8 @@
       <c r="K2" t="n">
         <v>84.18378291574035</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 9.817x + -12737.640</t>
-        </is>
+      <c r="W2" t="n">
+        <v>9.817178039847603</v>
       </c>
       <c r="X2" t="n">
         <v>-12737.63958463638</v>
@@ -9454,7 +9162,7 @@
         <v>1.869656676034459e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>208.6299999999999</v>
+        <v>1391.609393157072</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000982e-08</v>
@@ -9494,10 +9202,8 @@
       <c r="K3" t="n">
         <v>84.93799595836562</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 11.289x + -13245.038</t>
-        </is>
+      <c r="W3" t="n">
+        <v>11.28932882962558</v>
       </c>
       <c r="X3" t="n">
         <v>-13245.03810169215</v>
@@ -9506,7 +9212,7 @@
         <v>8.108928582058926e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>148.5699999999999</v>
+        <v>1295.417361774248</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000003e-08</v>
@@ -9546,10 +9252,8 @@
       <c r="K4" t="n">
         <v>85.37416272287376</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 12.359x + -14172.608</t>
-        </is>
+      <c r="W4" t="n">
+        <v>12.35911063946338</v>
       </c>
       <c r="X4" t="n">
         <v>-14172.60819647558</v>
@@ -9558,7 +9262,7 @@
         <v>2.900937840576138e-11</v>
       </c>
       <c r="Z4" t="n">
-        <v>125.01</v>
+        <v>1266.111630016187</v>
       </c>
       <c r="AA4" t="n">
         <v>1e-08</v>
@@ -9598,10 +9302,8 @@
       <c r="K5" t="n">
         <v>85.45124352320212</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 12.569x + -14182.592</t>
-        </is>
+      <c r="W5" t="n">
+        <v>12.56944678295664</v>
       </c>
       <c r="X5" t="n">
         <v>-14182.59212932005</v>
@@ -9610,7 +9312,7 @@
         <v>2.346681399974671e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>115.9399999999998</v>
+        <v>1245.857993000636</v>
       </c>
       <c r="AA5" t="n">
         <v>1e-08</v>
@@ -9650,10 +9352,8 @@
       <c r="K6" t="n">
         <v>85.52715115959077</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 12.784x + -14216.795</t>
-        </is>
+      <c r="W6" t="n">
+        <v>12.78365128250039</v>
       </c>
       <c r="X6" t="n">
         <v>-14216.79492881361</v>
@@ -9662,7 +9362,7 @@
         <v>5.292420589213277e-12</v>
       </c>
       <c r="Z6" t="n">
-        <v>112.4000000000001</v>
+        <v>1226.774437129283</v>
       </c>
       <c r="AA6" t="n">
         <v>1e-08</v>
@@ -9702,10 +9402,8 @@
       <c r="K7" t="n">
         <v>85.74056446904169</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 13.427x + -14753.176</t>
-        </is>
+      <c r="W7" t="n">
+        <v>13.42670635771172</v>
       </c>
       <c r="X7" t="n">
         <v>-14753.17619692637</v>
@@ -9714,7 +9412,7 @@
         <v>3.494730951868302e-12</v>
       </c>
       <c r="Z7" t="n">
-        <v>107.3200000000002</v>
+        <v>1208.181963510594</v>
       </c>
       <c r="AA7" t="n">
         <v>1e-08</v>
@@ -9754,10 +9452,8 @@
       <c r="K8" t="n">
         <v>85.16273897873488</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 11.817x + -12697.974</t>
-        </is>
+      <c r="W8" t="n">
+        <v>11.81651850477065</v>
       </c>
       <c r="X8" t="n">
         <v>-12697.97441281812</v>
@@ -9766,7 +9462,7 @@
         <v>1.539227863482646e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>109.8100000000002</v>
+        <v>1190.016728613844</v>
       </c>
       <c r="AA8" t="n">
         <v>1e-08</v>
@@ -9806,10 +9502,8 @@
       <c r="K9" t="n">
         <v>85.10010118566932</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 11.665x + -12339.301</t>
-        </is>
+      <c r="W9" t="n">
+        <v>11.66473733014953</v>
       </c>
       <c r="X9" t="n">
         <v>-12339.30102183179</v>
@@ -9818,7 +9512,7 @@
         <v>7.123585102941405e-12</v>
       </c>
       <c r="Z9" t="n">
-        <v>108.4200000000001</v>
+        <v>1171.80634583206</v>
       </c>
       <c r="AA9" t="n">
         <v>1e-08</v>
@@ -9858,10 +9552,8 @@
       <c r="K10" t="n">
         <v>85.42325054749543</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 12.492x + -13073.631</t>
-        </is>
+      <c r="W10" t="n">
+        <v>12.49224272620482</v>
       </c>
       <c r="X10" t="n">
         <v>-13073.63139279546</v>
@@ -9870,7 +9562,7 @@
         <v>9.078463945277714e-10</v>
       </c>
       <c r="Z10" t="n">
-        <v>104.4400000000001</v>
+        <v>1154.342603242539</v>
       </c>
       <c r="AA10" t="n">
         <v>1e-08</v>
@@ -9910,10 +9602,8 @@
       <c r="K11" t="n">
         <v>85.44698449543256</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 12.558x + -12978.063</t>
-        </is>
+      <c r="W11" t="n">
+        <v>12.55763936947451</v>
       </c>
       <c r="X11" t="n">
         <v>-12978.06331141998</v>
@@ -9922,7 +9612,7 @@
         <v>4.149259456054139e-12</v>
       </c>
       <c r="Z11" t="n">
-        <v>102.9400000000001</v>
+        <v>1139.994134631766</v>
       </c>
       <c r="AA11" t="n">
         <v>1e-08</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 36.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 36.xlsx
@@ -428,7 +428,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -559,7 +559,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-143.6700000000001</v>
@@ -609,7 +609,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-125.48</v>
@@ -659,7 +659,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-110.5</v>
@@ -709,7 +709,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-104.4099999999999</v>
@@ -759,7 +759,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-106.3499999999999</v>
@@ -809,7 +809,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-97.43000000000029</v>
@@ -859,7 +859,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-92.49000000000024</v>
@@ -909,7 +909,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-87.17000000000007</v>
@@ -959,7 +959,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-84.57999999999993</v>
@@ -1009,7 +1009,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-84.43999999999983</v>
@@ -1074,7 +1074,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -2270,7 +2270,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -3466,7 +3466,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -3597,7 +3597,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-293.3000000000002</v>
@@ -3647,7 +3647,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-227.8900000000001</v>
@@ -3697,7 +3697,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-211.7599999999998</v>
@@ -3747,7 +3747,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-188.9400000000001</v>
@@ -3797,7 +3797,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-179.23</v>
@@ -3847,7 +3847,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-177.27</v>
@@ -3897,7 +3897,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-166.8199999999999</v>
@@ -3947,7 +3947,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-163.8099999999999</v>
@@ -3997,7 +3997,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-151.5999999999999</v>
@@ -4047,7 +4047,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-151.0999999999999</v>
@@ -4112,7 +4112,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -5308,7 +5308,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -5439,7 +5439,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-248.9300000000001</v>
@@ -5489,7 +5489,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-206.79</v>
@@ -5539,7 +5539,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-190.76</v>
@@ -5589,7 +5589,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-180.3699999999999</v>
@@ -5639,7 +5639,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-175.7</v>
@@ -5689,7 +5689,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-157.26</v>
@@ -5739,7 +5739,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-158</v>
@@ -5789,7 +5789,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-152.9100000000001</v>
@@ -5839,7 +5839,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-148.1300000000001</v>
@@ -5889,7 +5889,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-147.0600000000002</v>
@@ -5954,7 +5954,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -7150,7 +7150,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -7281,7 +7281,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-278.21</v>
@@ -7331,7 +7331,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-199.6800000000001</v>
@@ -7381,7 +7381,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-176.9300000000001</v>
@@ -7431,7 +7431,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-162.6900000000001</v>
@@ -7481,7 +7481,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-151.6099999999999</v>
@@ -7531,7 +7531,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-141.5799999999999</v>
@@ -7581,7 +7581,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-132.71</v>
@@ -7631,7 +7631,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-123.9300000000001</v>
@@ -7681,7 +7681,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-127.3800000000001</v>
@@ -7731,7 +7731,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-122.73</v>
@@ -7796,7 +7796,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -8992,7 +8992,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -9123,7 +9123,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-208.6299999999999</v>
@@ -9173,7 +9173,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-148.5699999999999</v>
@@ -9223,7 +9223,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-125.01</v>
@@ -9273,7 +9273,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-115.9399999999998</v>
@@ -9323,7 +9323,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-112.4000000000001</v>
@@ -9373,7 +9373,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-107.3200000000002</v>
@@ -9423,7 +9423,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-109.8100000000002</v>
@@ -9473,7 +9473,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-108.4200000000001</v>
@@ -9523,7 +9523,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-103.4300000000001</v>
@@ -9573,7 +9573,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-100.54</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 36.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 36.xlsx
@@ -562,7 +562,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-143.6700000000001</v>
+        <v>1930.794</v>
       </c>
       <c r="D2" t="n">
         <v>3.21875e-07</v>
@@ -612,7 +612,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-125.48</v>
+        <v>1830.712</v>
       </c>
       <c r="D3" t="n">
         <v>3.33289e-07</v>
@@ -662,7 +662,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-110.5</v>
+        <v>1796.852</v>
       </c>
       <c r="D4" t="n">
         <v>3.37632e-07</v>
@@ -712,7 +712,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-104.4099999999999</v>
+        <v>1764.29</v>
       </c>
       <c r="D5" t="n">
         <v>3.41131e-07</v>
@@ -762,7 +762,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-106.3499999999999</v>
+        <v>1729.522</v>
       </c>
       <c r="D6" t="n">
         <v>3.44068e-07</v>
@@ -812,7 +812,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-97.43000000000029</v>
+        <v>1701.958</v>
       </c>
       <c r="D7" t="n">
         <v>3.47512e-07</v>
@@ -862,7 +862,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-92.49000000000024</v>
+        <v>1683.699</v>
       </c>
       <c r="D8" t="n">
         <v>3.50007e-07</v>
@@ -912,7 +912,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-87.17000000000007</v>
+        <v>1659.309</v>
       </c>
       <c r="D9" t="n">
         <v>3.52865e-07</v>
@@ -962,7 +962,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-84.57999999999993</v>
+        <v>1636.784</v>
       </c>
       <c r="D10" t="n">
         <v>3.55368e-07</v>
@@ -1012,7 +1012,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-84.43999999999983</v>
+        <v>1609.728</v>
       </c>
       <c r="D11" t="n">
         <v>3.57908e-07</v>
@@ -1208,7 +1208,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-147.8499999999999</v>
+        <v>1354.546</v>
       </c>
       <c r="D2" t="n">
         <v>3.50084e-07</v>
@@ -1258,7 +1258,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-119.97</v>
+        <v>1244.023</v>
       </c>
       <c r="D3" t="n">
         <v>3.64831e-07</v>
@@ -1308,7 +1308,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-117.75</v>
+        <v>1205.615</v>
       </c>
       <c r="D4" t="n">
         <v>3.68465e-07</v>
@@ -1358,7 +1358,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-117.5999999999999</v>
+        <v>1179.377</v>
       </c>
       <c r="D5" t="n">
         <v>3.70409e-07</v>
@@ -1408,7 +1408,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-117.8099999999999</v>
+        <v>1158.48</v>
       </c>
       <c r="D6" t="n">
         <v>3.71536e-07</v>
@@ -1458,7 +1458,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-111.8699999999999</v>
+        <v>1144.563</v>
       </c>
       <c r="D7" t="n">
         <v>3.72856e-07</v>
@@ -1508,7 +1508,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-110.8500000000001</v>
+        <v>1123.976</v>
       </c>
       <c r="D8" t="n">
         <v>3.74415e-07</v>
@@ -1558,7 +1558,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-108.1799999999998</v>
+        <v>1105.091</v>
       </c>
       <c r="D9" t="n">
         <v>3.75922e-07</v>
@@ -1608,7 +1608,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-98.48000000000002</v>
+        <v>1097.122</v>
       </c>
       <c r="D10" t="n">
         <v>3.77394e-07</v>
@@ -1658,7 +1658,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-97.95999999999981</v>
+        <v>1076.179</v>
       </c>
       <c r="D11" t="n">
         <v>3.7891e-07</v>
@@ -1708,7 +1708,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-88.23000000000002</v>
+        <v>1065.261</v>
       </c>
       <c r="D12" t="n">
         <v>3.80504e-07</v>
@@ -1758,7 +1758,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-85.86999999999989</v>
+        <v>1048.456</v>
       </c>
       <c r="D13" t="n">
         <v>3.81827e-07</v>
@@ -1808,7 +1808,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-85.06000000000017</v>
+        <v>1030.135</v>
       </c>
       <c r="D14" t="n">
         <v>3.83316e-07</v>
@@ -1858,7 +1858,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-79.33999999999992</v>
+        <v>1016.373</v>
       </c>
       <c r="D15" t="n">
         <v>3.84765e-07</v>
@@ -1908,7 +1908,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-80.6400000000001</v>
+        <v>999.289</v>
       </c>
       <c r="D16" t="n">
         <v>3.85963e-07</v>
@@ -1958,7 +1958,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-70.63000000000011</v>
+        <v>990.212</v>
       </c>
       <c r="D17" t="n">
         <v>3.87442e-07</v>
@@ -2008,7 +2008,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-64.16999999999985</v>
+        <v>979.1770000000001</v>
       </c>
       <c r="D18" t="n">
         <v>3.88796e-07</v>
@@ -2058,7 +2058,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-59.45000000000005</v>
+        <v>966.704</v>
       </c>
       <c r="D19" t="n">
         <v>3.89977e-07</v>
@@ -2108,7 +2108,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-63.85000000000014</v>
+        <v>944.8869999999999</v>
       </c>
       <c r="D20" t="n">
         <v>3.91183e-07</v>
@@ -2158,7 +2158,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-56.13000000000011</v>
+        <v>932.79</v>
       </c>
       <c r="D21" t="n">
         <v>3.92731e-07</v>
@@ -2208,7 +2208,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-51.16999999999985</v>
+        <v>922.5360000000001</v>
       </c>
       <c r="D22" t="n">
         <v>3.93865e-07</v>
@@ -2404,7 +2404,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-146.52</v>
+        <v>1723.042</v>
       </c>
       <c r="D2" t="n">
         <v>3.42798e-07</v>
@@ -2454,7 +2454,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-121.27</v>
+        <v>1630.375</v>
       </c>
       <c r="D3" t="n">
         <v>3.54276e-07</v>
@@ -2504,7 +2504,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-108.3199999999999</v>
+        <v>1602.884</v>
       </c>
       <c r="D4" t="n">
         <v>3.57814e-07</v>
@@ -2554,7 +2554,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-96.56000000000017</v>
+        <v>1584.398</v>
       </c>
       <c r="D5" t="n">
         <v>3.6039e-07</v>
@@ -2604,7 +2604,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-89.77999999999997</v>
+        <v>1563.037</v>
       </c>
       <c r="D6" t="n">
         <v>3.63083e-07</v>
@@ -2654,7 +2654,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-92.33999999999992</v>
+        <v>1540.405</v>
       </c>
       <c r="D7" t="n">
         <v>3.65282e-07</v>
@@ -2704,7 +2704,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-80.06999999999994</v>
+        <v>1527.777</v>
       </c>
       <c r="D8" t="n">
         <v>3.67409e-07</v>
@@ -2754,7 +2754,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-82</v>
+        <v>1504.661</v>
       </c>
       <c r="D9" t="n">
         <v>3.69758e-07</v>
@@ -2804,7 +2804,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-78.88000000000011</v>
+        <v>1487.335</v>
       </c>
       <c r="D10" t="n">
         <v>3.71604e-07</v>
@@ -2854,7 +2854,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-69.8599999999999</v>
+        <v>1474.421</v>
       </c>
       <c r="D11" t="n">
         <v>3.73813e-07</v>
@@ -2904,7 +2904,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-65.13000000000011</v>
+        <v>1459.115</v>
       </c>
       <c r="D12" t="n">
         <v>3.76013e-07</v>
@@ -2954,7 +2954,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-60.26999999999998</v>
+        <v>1444.263</v>
       </c>
       <c r="D13" t="n">
         <v>3.77787e-07</v>
@@ -3004,7 +3004,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-63.88000000000011</v>
+        <v>1421.302</v>
       </c>
       <c r="D14" t="n">
         <v>3.79782e-07</v>
@@ -3054,7 +3054,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-56.87000000000012</v>
+        <v>1410.956</v>
       </c>
       <c r="D15" t="n">
         <v>3.81492e-07</v>
@@ -3104,7 +3104,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-57.3599999999999</v>
+        <v>1388.711</v>
       </c>
       <c r="D16" t="n">
         <v>3.83809e-07</v>
@@ -3154,7 +3154,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-52.52999999999997</v>
+        <v>1374.654</v>
       </c>
       <c r="D17" t="n">
         <v>3.85732e-07</v>
@@ -3204,7 +3204,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-49.8599999999999</v>
+        <v>1359.802</v>
       </c>
       <c r="D18" t="n">
         <v>3.87449e-07</v>
@@ -3254,7 +3254,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-45.97999999999979</v>
+        <v>1348.519</v>
       </c>
       <c r="D19" t="n">
         <v>3.89213e-07</v>
@@ -3304,7 +3304,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-50.63999999999987</v>
+        <v>1326.99</v>
       </c>
       <c r="D20" t="n">
         <v>3.90892e-07</v>
@@ -3354,7 +3354,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-47.6400000000001</v>
+        <v>1313.218</v>
       </c>
       <c r="D21" t="n">
         <v>3.92624e-07</v>
@@ -3404,7 +3404,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-43.4699999999998</v>
+        <v>1303.231</v>
       </c>
       <c r="D22" t="n">
         <v>3.94348e-07</v>
@@ -3600,7 +3600,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-293.3000000000002</v>
+        <v>1799.67</v>
       </c>
       <c r="D2" t="n">
         <v>3.26362e-07</v>
@@ -3650,7 +3650,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-227.8900000000001</v>
+        <v>1651.82</v>
       </c>
       <c r="D3" t="n">
         <v>3.50995e-07</v>
@@ -3700,7 +3700,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-211.7599999999998</v>
+        <v>1596.015</v>
       </c>
       <c r="D4" t="n">
         <v>3.5845e-07</v>
@@ -3750,7 +3750,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-188.9400000000001</v>
+        <v>1579</v>
       </c>
       <c r="D5" t="n">
         <v>3.62271e-07</v>
@@ -3800,7 +3800,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-179.23</v>
+        <v>1557.156</v>
       </c>
       <c r="D6" t="n">
         <v>3.65422e-07</v>
@@ -3850,7 +3850,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-177.27</v>
+        <v>1527.902</v>
       </c>
       <c r="D7" t="n">
         <v>3.68586e-07</v>
@@ -3900,7 +3900,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-166.8199999999999</v>
+        <v>1510.324</v>
       </c>
       <c r="D8" t="n">
         <v>3.71476e-07</v>
@@ -3950,7 +3950,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-163.8099999999999</v>
+        <v>1487.341</v>
       </c>
       <c r="D9" t="n">
         <v>3.74348e-07</v>
@@ -4000,7 +4000,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-151.5999999999999</v>
+        <v>1474.733</v>
       </c>
       <c r="D10" t="n">
         <v>3.77123e-07</v>
@@ -4050,7 +4050,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-151.0999999999999</v>
+        <v>1457.247</v>
       </c>
       <c r="D11" t="n">
         <v>3.7933e-07</v>
@@ -4246,7 +4246,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-212.8</v>
+        <v>1097.688</v>
       </c>
       <c r="D2" t="n">
         <v>4.23414e-07</v>
@@ -4296,7 +4296,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-171.9299999999998</v>
+        <v>1022.422</v>
       </c>
       <c r="D3" t="n">
         <v>4.3275e-07</v>
@@ -4346,7 +4346,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-153.8199999999999</v>
+        <v>995.0419999999999</v>
       </c>
       <c r="D4" t="n">
         <v>4.35951e-07</v>
@@ -4396,7 +4396,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-144.47</v>
+        <v>972.7489999999999</v>
       </c>
       <c r="D5" t="n">
         <v>4.38116e-07</v>
@@ -4446,7 +4446,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-135.5</v>
+        <v>953.058</v>
       </c>
       <c r="D6" t="n">
         <v>4.40232e-07</v>
@@ -4496,7 +4496,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-127.9300000000001</v>
+        <v>937.2249999999999</v>
       </c>
       <c r="D7" t="n">
         <v>4.42322e-07</v>
@@ -4546,7 +4546,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-126.1000000000001</v>
+        <v>917.6209999999999</v>
       </c>
       <c r="D8" t="n">
         <v>4.44305e-07</v>
@@ -4596,7 +4596,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-125.48</v>
+        <v>903.425</v>
       </c>
       <c r="D9" t="n">
         <v>4.45998e-07</v>
@@ -4646,7 +4646,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-117.8200000000002</v>
+        <v>869.933</v>
       </c>
       <c r="D10" t="n">
         <v>4.50525e-07</v>
@@ -4696,7 +4696,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-119.74</v>
+        <v>850.2719999999999</v>
       </c>
       <c r="D11" t="n">
         <v>4.52218e-07</v>
@@ -4746,7 +4746,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-116.8899999999999</v>
+        <v>836.0520000000001</v>
       </c>
       <c r="D12" t="n">
         <v>4.53792e-07</v>
@@ -4796,7 +4796,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-112.8599999999999</v>
+        <v>825.3199999999999</v>
       </c>
       <c r="D13" t="n">
         <v>4.55112e-07</v>
@@ -4846,7 +4846,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-108.29</v>
+        <v>815.347</v>
       </c>
       <c r="D14" t="n">
         <v>4.56581e-07</v>
@@ -4896,7 +4896,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-106.5999999999999</v>
+        <v>803.2450000000001</v>
       </c>
       <c r="D15" t="n">
         <v>4.58282e-07</v>
@@ -4946,7 +4946,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-104.8900000000001</v>
+        <v>789.414</v>
       </c>
       <c r="D16" t="n">
         <v>4.59592e-07</v>
@@ -4996,7 +4996,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-107.1700000000001</v>
+        <v>772.1279999999999</v>
       </c>
       <c r="D17" t="n">
         <v>4.61087e-07</v>
@@ -5046,7 +5046,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-93.49000000000001</v>
+        <v>771.028</v>
       </c>
       <c r="D18" t="n">
         <v>4.62663e-07</v>
@@ -5096,7 +5096,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-90.69999999999982</v>
+        <v>759.961</v>
       </c>
       <c r="D19" t="n">
         <v>4.64176e-07</v>
@@ -5146,7 +5146,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-95.86000000000013</v>
+        <v>741.038</v>
       </c>
       <c r="D20" t="n">
         <v>4.65548e-07</v>
@@ -5196,7 +5196,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-89.47000000000003</v>
+        <v>730.3839999999999</v>
       </c>
       <c r="D21" t="n">
         <v>4.66994e-07</v>
@@ -5246,7 +5246,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-86.62999999999988</v>
+        <v>721.009</v>
       </c>
       <c r="D22" t="n">
         <v>4.68552e-07</v>
@@ -5442,7 +5442,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-248.9300000000001</v>
+        <v>1103.268</v>
       </c>
       <c r="D2" t="n">
         <v>4.24516e-07</v>
@@ -5492,7 +5492,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-206.79</v>
+        <v>1060.644</v>
       </c>
       <c r="D3" t="n">
         <v>4.3251e-07</v>
@@ -5542,7 +5542,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-190.76</v>
+        <v>1033.375</v>
       </c>
       <c r="D4" t="n">
         <v>4.35569e-07</v>
@@ -5592,7 +5592,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-180.3699999999999</v>
+        <v>1009.235</v>
       </c>
       <c r="D5" t="n">
         <v>4.3794e-07</v>
@@ -5642,7 +5642,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-175.7</v>
+        <v>987.1590000000001</v>
       </c>
       <c r="D6" t="n">
         <v>4.40335e-07</v>
@@ -5692,7 +5692,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-157.26</v>
+        <v>971.6859999999999</v>
       </c>
       <c r="D7" t="n">
         <v>4.44043e-07</v>
@@ -5742,7 +5742,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-158</v>
+        <v>942.199</v>
       </c>
       <c r="D8" t="n">
         <v>4.46692e-07</v>
@@ -5792,7 +5792,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-152.9100000000001</v>
+        <v>923.4749999999999</v>
       </c>
       <c r="D9" t="n">
         <v>4.49304e-07</v>
@@ -5842,7 +5842,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-148.1300000000001</v>
+        <v>905.785</v>
       </c>
       <c r="D10" t="n">
         <v>4.5171e-07</v>
@@ -5892,7 +5892,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-147.0600000000002</v>
+        <v>884.502</v>
       </c>
       <c r="D11" t="n">
         <v>4.54192e-07</v>
@@ -6088,7 +6088,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-186.6799999999998</v>
+        <v>1030.872</v>
       </c>
       <c r="D2" t="n">
         <v>4.37132e-07</v>
@@ -6138,7 +6138,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-149</v>
+        <v>1006.711</v>
       </c>
       <c r="D3" t="n">
         <v>4.39257e-07</v>
@@ -6188,7 +6188,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-134.4300000000001</v>
+        <v>976.9299999999999</v>
       </c>
       <c r="D4" t="n">
         <v>4.42755e-07</v>
@@ -6238,7 +6238,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-126.1799999999998</v>
+        <v>961.5530000000001</v>
       </c>
       <c r="D5" t="n">
         <v>4.44808e-07</v>
@@ -6288,7 +6288,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-123.9000000000001</v>
+        <v>924.0379999999999</v>
       </c>
       <c r="D6" t="n">
         <v>4.49283e-07</v>
@@ -6338,7 +6338,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-125.5899999999999</v>
+        <v>900.8800000000001</v>
       </c>
       <c r="D7" t="n">
         <v>4.51206e-07</v>
@@ -6388,7 +6388,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-122.3699999999999</v>
+        <v>884.3800000000001</v>
       </c>
       <c r="D8" t="n">
         <v>4.53291e-07</v>
@@ -6438,7 +6438,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-115.8899999999999</v>
+        <v>873.403</v>
       </c>
       <c r="D9" t="n">
         <v>4.55235e-07</v>
@@ -6488,7 +6488,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-112.21</v>
+        <v>858.8789999999999</v>
       </c>
       <c r="D10" t="n">
         <v>4.57109e-07</v>
@@ -6538,7 +6538,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-108.9400000000001</v>
+        <v>841.515</v>
       </c>
       <c r="D11" t="n">
         <v>4.59292e-07</v>
@@ -6588,7 +6588,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-104.6299999999999</v>
+        <v>830.0150000000001</v>
       </c>
       <c r="D12" t="n">
         <v>4.61286e-07</v>
@@ -6638,7 +6638,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-102.04</v>
+        <v>814.2909999999999</v>
       </c>
       <c r="D13" t="n">
         <v>4.63177e-07</v>
@@ -6688,7 +6688,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-100.8</v>
+        <v>801.577</v>
       </c>
       <c r="D14" t="n">
         <v>4.64722e-07</v>
@@ -6738,7 +6738,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-95.30999999999995</v>
+        <v>789.8200000000001</v>
       </c>
       <c r="D15" t="n">
         <v>4.66419e-07</v>
@@ -6788,7 +6788,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-91.97999999999979</v>
+        <v>779.105</v>
       </c>
       <c r="D16" t="n">
         <v>4.68247e-07</v>
@@ -6838,7 +6838,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-88.74000000000001</v>
+        <v>767.2379999999999</v>
       </c>
       <c r="D17" t="n">
         <v>4.69891e-07</v>
@@ -6888,7 +6888,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-89.25999999999999</v>
+        <v>754.0160000000001</v>
       </c>
       <c r="D18" t="n">
         <v>4.70976e-07</v>
@@ -6938,7 +6938,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-89.37999999999988</v>
+        <v>739.6190000000001</v>
       </c>
       <c r="D19" t="n">
         <v>4.72749e-07</v>
@@ -6988,7 +6988,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-85.54999999999995</v>
+        <v>729.491</v>
       </c>
       <c r="D20" t="n">
         <v>4.7425e-07</v>
@@ -7038,7 +7038,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-78.90999999999985</v>
+        <v>715.3940000000001</v>
       </c>
       <c r="D21" t="n">
         <v>4.76944e-07</v>
@@ -7088,7 +7088,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-82.31999999999994</v>
+        <v>682.413</v>
       </c>
       <c r="D22" t="n">
         <v>4.80279e-07</v>
@@ -7284,7 +7284,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-278.21</v>
+        <v>1285.113</v>
       </c>
       <c r="D2" t="n">
         <v>3.91163e-07</v>
@@ -7334,7 +7334,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-199.6800000000001</v>
+        <v>1127.67</v>
       </c>
       <c r="D3" t="n">
         <v>4.20174e-07</v>
@@ -7384,7 +7384,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-176.9300000000001</v>
+        <v>1072.181</v>
       </c>
       <c r="D4" t="n">
         <v>4.27276e-07</v>
@@ -7434,7 +7434,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-162.6900000000001</v>
+        <v>1038.584</v>
       </c>
       <c r="D5" t="n">
         <v>4.314e-07</v>
@@ -7484,7 +7484,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-151.6099999999999</v>
+        <v>1011.139</v>
       </c>
       <c r="D6" t="n">
         <v>4.34637e-07</v>
@@ -7534,7 +7534,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-141.5799999999999</v>
+        <v>988.9290000000001</v>
       </c>
       <c r="D7" t="n">
         <v>4.37929e-07</v>
@@ -7584,7 +7584,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-132.71</v>
+        <v>967.7239999999999</v>
       </c>
       <c r="D8" t="n">
         <v>4.41101e-07</v>
@@ -7634,7 +7634,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-123.9300000000001</v>
+        <v>947.5649999999999</v>
       </c>
       <c r="D9" t="n">
         <v>4.44239e-07</v>
@@ -7684,7 +7684,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-127.3800000000001</v>
+        <v>917.337</v>
       </c>
       <c r="D10" t="n">
         <v>4.4712e-07</v>
@@ -7734,7 +7734,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-122.73</v>
+        <v>899.665</v>
       </c>
       <c r="D11" t="n">
         <v>4.49771e-07</v>
@@ -7930,7 +7930,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-194.4300000000001</v>
+        <v>1025.941</v>
       </c>
       <c r="D2" t="n">
         <v>4.31391e-07</v>
@@ -7980,7 +7980,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-152.99</v>
+        <v>958.264</v>
       </c>
       <c r="D3" t="n">
         <v>4.40301e-07</v>
@@ -8030,7 +8030,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-139.45</v>
+        <v>939.049</v>
       </c>
       <c r="D4" t="n">
         <v>4.42917e-07</v>
@@ -8080,7 +8080,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-133.49</v>
+        <v>921.4680000000001</v>
       </c>
       <c r="D5" t="n">
         <v>4.4482e-07</v>
@@ -8130,7 +8130,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-129.0599999999999</v>
+        <v>905.664</v>
       </c>
       <c r="D6" t="n">
         <v>4.464e-07</v>
@@ -8180,7 +8180,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-129.8599999999999</v>
+        <v>889.5640000000001</v>
       </c>
       <c r="D7" t="n">
         <v>4.48057e-07</v>
@@ -8230,7 +8230,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-118.8099999999999</v>
+        <v>880.3820000000001</v>
       </c>
       <c r="D8" t="n">
         <v>4.49997e-07</v>
@@ -8280,7 +8280,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-122.8399999999999</v>
+        <v>861.3890000000001</v>
       </c>
       <c r="D9" t="n">
         <v>4.51829e-07</v>
@@ -8330,7 +8330,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-116.51</v>
+        <v>849.6870000000001</v>
       </c>
       <c r="D10" t="n">
         <v>4.53622e-07</v>
@@ -8380,7 +8380,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-114.3799999999999</v>
+        <v>835.6020000000001</v>
       </c>
       <c r="D11" t="n">
         <v>4.55476e-07</v>
@@ -8430,7 +8430,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-109.53</v>
+        <v>826.7269999999999</v>
       </c>
       <c r="D12" t="n">
         <v>4.57073e-07</v>
@@ -8480,7 +8480,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-103.96</v>
+        <v>815.9640000000001</v>
       </c>
       <c r="D13" t="n">
         <v>4.58828e-07</v>
@@ -8530,7 +8530,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-105.23</v>
+        <v>799.6709999999999</v>
       </c>
       <c r="D14" t="n">
         <v>4.60394e-07</v>
@@ -8580,7 +8580,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-102.99</v>
+        <v>787.1419999999999</v>
       </c>
       <c r="D15" t="n">
         <v>4.6214e-07</v>
@@ -8630,7 +8630,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-95.98000000000002</v>
+        <v>778.432</v>
       </c>
       <c r="D16" t="n">
         <v>4.63978e-07</v>
@@ -8680,7 +8680,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-100.78</v>
+        <v>759.7130000000001</v>
       </c>
       <c r="D17" t="n">
         <v>4.65652e-07</v>
@@ -8730,7 +8730,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-94.6099999999999</v>
+        <v>753.1580000000001</v>
       </c>
       <c r="D18" t="n">
         <v>4.67156e-07</v>
@@ -8780,7 +8780,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-87.28999999999996</v>
+        <v>743.519</v>
       </c>
       <c r="D19" t="n">
         <v>4.69099e-07</v>
@@ -8830,7 +8830,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-85.26999999999998</v>
+        <v>733.282</v>
       </c>
       <c r="D20" t="n">
         <v>4.70661e-07</v>
@@ -8880,7 +8880,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-80.13999999999987</v>
+        <v>720.221</v>
       </c>
       <c r="D21" t="n">
         <v>4.72531e-07</v>
@@ -8930,7 +8930,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-81.86000000000013</v>
+        <v>705.5419999999999</v>
       </c>
       <c r="D22" t="n">
         <v>4.74299e-07</v>
@@ -9126,7 +9126,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-208.6299999999999</v>
+        <v>888.883</v>
       </c>
       <c r="D2" t="n">
         <v>4.51846e-07</v>
@@ -9176,7 +9176,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-148.5699999999999</v>
+        <v>764.0119999999999</v>
       </c>
       <c r="D3" t="n">
         <v>4.66674e-07</v>
@@ -9226,7 +9226,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-125.01</v>
+        <v>738.019</v>
       </c>
       <c r="D4" t="n">
         <v>4.6716e-07</v>
@@ -9276,7 +9276,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-115.9399999999998</v>
+        <v>720.3130000000001</v>
       </c>
       <c r="D5" t="n">
         <v>4.67022e-07</v>
@@ -9326,7 +9326,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-112.4000000000001</v>
+        <v>703.7619999999999</v>
       </c>
       <c r="D6" t="n">
         <v>4.67225e-07</v>
@@ -9376,7 +9376,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-107.3200000000002</v>
+        <v>691.2249999999999</v>
       </c>
       <c r="D7" t="n">
         <v>4.68074e-07</v>
@@ -9426,7 +9426,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-109.8100000000002</v>
+        <v>670.2239999999999</v>
       </c>
       <c r="D8" t="n">
         <v>4.69062e-07</v>
@@ -9476,7 +9476,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-108.4200000000001</v>
+        <v>655.4949999999999</v>
       </c>
       <c r="D9" t="n">
         <v>4.70189e-07</v>
@@ -9526,7 +9526,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-103.4300000000001</v>
+        <v>643.347</v>
       </c>
       <c r="D10" t="n">
         <v>4.71574e-07</v>
@@ -9576,7 +9576,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-100.54</v>
+        <v>632.314</v>
       </c>
       <c r="D11" t="n">
         <v>4.72768e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 36.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 36.xlsx
@@ -438,7 +438,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -564,6 +564,9 @@
       <c r="B2" t="n">
         <v>1930.794</v>
       </c>
+      <c r="C2" t="n">
+        <v>2268.126181417028</v>
+      </c>
       <c r="D2" t="n">
         <v>3.21875e-07</v>
       </c>
@@ -614,6 +617,9 @@
       <c r="B3" t="n">
         <v>1830.712</v>
       </c>
+      <c r="C3" t="n">
+        <v>2171.630105350745</v>
+      </c>
       <c r="D3" t="n">
         <v>3.33289e-07</v>
       </c>
@@ -664,6 +670,9 @@
       <c r="B4" t="n">
         <v>1796.852</v>
       </c>
+      <c r="C4" t="n">
+        <v>2138.143295587891</v>
+      </c>
       <c r="D4" t="n">
         <v>3.37632e-07</v>
       </c>
@@ -714,6 +723,9 @@
       <c r="B5" t="n">
         <v>1764.29</v>
       </c>
+      <c r="C5" t="n">
+        <v>2112.767757304954</v>
+      </c>
       <c r="D5" t="n">
         <v>3.41131e-07</v>
       </c>
@@ -764,6 +776,9 @@
       <c r="B6" t="n">
         <v>1729.522</v>
       </c>
+      <c r="C6" t="n">
+        <v>2081.367713907285</v>
+      </c>
       <c r="D6" t="n">
         <v>3.44068e-07</v>
       </c>
@@ -814,6 +829,9 @@
       <c r="B7" t="n">
         <v>1701.958</v>
       </c>
+      <c r="C7" t="n">
+        <v>2054.720610115364</v>
+      </c>
       <c r="D7" t="n">
         <v>3.47512e-07</v>
       </c>
@@ -864,6 +882,9 @@
       <c r="B8" t="n">
         <v>1683.699</v>
       </c>
+      <c r="C8" t="n">
+        <v>2032.963606923738</v>
+      </c>
       <c r="D8" t="n">
         <v>3.50007e-07</v>
       </c>
@@ -914,6 +935,9 @@
       <c r="B9" t="n">
         <v>1659.309</v>
       </c>
+      <c r="C9" t="n">
+        <v>2009.080633040748</v>
+      </c>
       <c r="D9" t="n">
         <v>3.52865e-07</v>
       </c>
@@ -964,6 +988,9 @@
       <c r="B10" t="n">
         <v>1636.784</v>
       </c>
+      <c r="C10" t="n">
+        <v>1985.599158023935</v>
+      </c>
       <c r="D10" t="n">
         <v>3.55368e-07</v>
       </c>
@@ -1013,6 +1040,9 @@
       </c>
       <c r="B11" t="n">
         <v>1609.728</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1962.117647621546</v>
       </c>
       <c r="D11" t="n">
         <v>3.57908e-07</v>
@@ -1084,7 +1114,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -1210,6 +1240,9 @@
       <c r="B2" t="n">
         <v>1354.546</v>
       </c>
+      <c r="C2" t="n">
+        <v>1810.023459554588</v>
+      </c>
       <c r="D2" t="n">
         <v>3.50084e-07</v>
       </c>
@@ -1260,6 +1293,9 @@
       <c r="B3" t="n">
         <v>1244.023</v>
       </c>
+      <c r="C3" t="n">
+        <v>1657.436375332882</v>
+      </c>
       <c r="D3" t="n">
         <v>3.64831e-07</v>
       </c>
@@ -1310,6 +1346,9 @@
       <c r="B4" t="n">
         <v>1205.615</v>
       </c>
+      <c r="C4" t="n">
+        <v>1614.664208835687</v>
+      </c>
       <c r="D4" t="n">
         <v>3.68465e-07</v>
       </c>
@@ -1360,6 +1399,9 @@
       <c r="B5" t="n">
         <v>1179.377</v>
       </c>
+      <c r="C5" t="n">
+        <v>1589.722295890937</v>
+      </c>
       <c r="D5" t="n">
         <v>3.70409e-07</v>
       </c>
@@ -1410,6 +1452,9 @@
       <c r="B6" t="n">
         <v>1158.48</v>
       </c>
+      <c r="C6" t="n">
+        <v>1572.435767681853</v>
+      </c>
       <c r="D6" t="n">
         <v>3.71536e-07</v>
       </c>
@@ -1460,6 +1505,9 @@
       <c r="B7" t="n">
         <v>1144.563</v>
       </c>
+      <c r="C7" t="n">
+        <v>1560.118040426775</v>
+      </c>
       <c r="D7" t="n">
         <v>3.72856e-07</v>
       </c>
@@ -1510,6 +1558,9 @@
       <c r="B8" t="n">
         <v>1123.976</v>
       </c>
+      <c r="C8" t="n">
+        <v>1542.341260504835</v>
+      </c>
       <c r="D8" t="n">
         <v>3.74415e-07</v>
       </c>
@@ -1560,6 +1611,9 @@
       <c r="B9" t="n">
         <v>1105.091</v>
       </c>
+      <c r="C9" t="n">
+        <v>1523.341553091965</v>
+      </c>
       <c r="D9" t="n">
         <v>3.75922e-07</v>
       </c>
@@ -1610,6 +1664,9 @@
       <c r="B10" t="n">
         <v>1097.122</v>
       </c>
+      <c r="C10" t="n">
+        <v>1510.895520695873</v>
+      </c>
       <c r="D10" t="n">
         <v>3.77394e-07</v>
       </c>
@@ -1660,6 +1717,9 @@
       <c r="B11" t="n">
         <v>1076.179</v>
       </c>
+      <c r="C11" t="n">
+        <v>1493.535796842517</v>
+      </c>
       <c r="D11" t="n">
         <v>3.7891e-07</v>
       </c>
@@ -1710,6 +1770,9 @@
       <c r="B12" t="n">
         <v>1065.261</v>
       </c>
+      <c r="C12" t="n">
+        <v>1481.74458956301</v>
+      </c>
       <c r="D12" t="n">
         <v>3.80504e-07</v>
       </c>
@@ -1760,6 +1823,9 @@
       <c r="B13" t="n">
         <v>1048.456</v>
       </c>
+      <c r="C13" t="n">
+        <v>1464.99529645375</v>
+      </c>
       <c r="D13" t="n">
         <v>3.81827e-07</v>
       </c>
@@ -1810,6 +1876,9 @@
       <c r="B14" t="n">
         <v>1030.135</v>
       </c>
+      <c r="C14" t="n">
+        <v>1449.12654276467</v>
+      </c>
       <c r="D14" t="n">
         <v>3.83316e-07</v>
       </c>
@@ -1860,6 +1929,9 @@
       <c r="B15" t="n">
         <v>1016.373</v>
       </c>
+      <c r="C15" t="n">
+        <v>1434.142923002567</v>
+      </c>
       <c r="D15" t="n">
         <v>3.84765e-07</v>
       </c>
@@ -1910,6 +1982,9 @@
       <c r="B16" t="n">
         <v>999.289</v>
       </c>
+      <c r="C16" t="n">
+        <v>1417.347555101051</v>
+      </c>
       <c r="D16" t="n">
         <v>3.85963e-07</v>
       </c>
@@ -1960,6 +2035,9 @@
       <c r="B17" t="n">
         <v>990.212</v>
       </c>
+      <c r="C17" t="n">
+        <v>1405.532711646474</v>
+      </c>
       <c r="D17" t="n">
         <v>3.87442e-07</v>
       </c>
@@ -2010,6 +2088,9 @@
       <c r="B18" t="n">
         <v>979.1770000000001</v>
       </c>
+      <c r="C18" t="n">
+        <v>1393.959875018377</v>
+      </c>
       <c r="D18" t="n">
         <v>3.88796e-07</v>
       </c>
@@ -2060,6 +2141,9 @@
       <c r="B19" t="n">
         <v>966.704</v>
       </c>
+      <c r="C19" t="n">
+        <v>1382.23737671459</v>
+      </c>
       <c r="D19" t="n">
         <v>3.89977e-07</v>
       </c>
@@ -2110,6 +2194,9 @@
       <c r="B20" t="n">
         <v>944.8869999999999</v>
       </c>
+      <c r="C20" t="n">
+        <v>1360.679640580912</v>
+      </c>
       <c r="D20" t="n">
         <v>3.91183e-07</v>
       </c>
@@ -2160,6 +2247,9 @@
       <c r="B21" t="n">
         <v>932.79</v>
       </c>
+      <c r="C21" t="n">
+        <v>1345.637757482641</v>
+      </c>
       <c r="D21" t="n">
         <v>3.92731e-07</v>
       </c>
@@ -2209,6 +2299,9 @@
       </c>
       <c r="B22" t="n">
         <v>922.5360000000001</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1334.625936410205</v>
       </c>
       <c r="D22" t="n">
         <v>3.93865e-07</v>
@@ -2280,7 +2373,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -2406,6 +2499,9 @@
       <c r="B2" t="n">
         <v>1723.042</v>
       </c>
+      <c r="C2" t="n">
+        <v>2094.534712989729</v>
+      </c>
       <c r="D2" t="n">
         <v>3.42798e-07</v>
       </c>
@@ -2456,6 +2552,9 @@
       <c r="B3" t="n">
         <v>1630.375</v>
       </c>
+      <c r="C3" t="n">
+        <v>1992.451850867281</v>
+      </c>
       <c r="D3" t="n">
         <v>3.54276e-07</v>
       </c>
@@ -2506,6 +2605,9 @@
       <c r="B4" t="n">
         <v>1602.884</v>
       </c>
+      <c r="C4" t="n">
+        <v>1962.484897894658</v>
+      </c>
       <c r="D4" t="n">
         <v>3.57814e-07</v>
       </c>
@@ -2556,6 +2658,9 @@
       <c r="B5" t="n">
         <v>1584.398</v>
       </c>
+      <c r="C5" t="n">
+        <v>1945.200645155621</v>
+      </c>
       <c r="D5" t="n">
         <v>3.6039e-07</v>
       </c>
@@ -2606,6 +2711,9 @@
       <c r="B6" t="n">
         <v>1563.037</v>
       </c>
+      <c r="C6" t="n">
+        <v>1922.682427035942</v>
+      </c>
       <c r="D6" t="n">
         <v>3.63083e-07</v>
       </c>
@@ -2656,6 +2764,9 @@
       <c r="B7" t="n">
         <v>1540.405</v>
       </c>
+      <c r="C7" t="n">
+        <v>1900.4739349992</v>
+      </c>
       <c r="D7" t="n">
         <v>3.65282e-07</v>
       </c>
@@ -2706,6 +2817,9 @@
       <c r="B8" t="n">
         <v>1527.777</v>
       </c>
+      <c r="C8" t="n">
+        <v>1887.054747237192</v>
+      </c>
       <c r="D8" t="n">
         <v>3.67409e-07</v>
       </c>
@@ -2756,6 +2870,9 @@
       <c r="B9" t="n">
         <v>1504.661</v>
       </c>
+      <c r="C9" t="n">
+        <v>1867.22220442995</v>
+      </c>
       <c r="D9" t="n">
         <v>3.69758e-07</v>
       </c>
@@ -2806,6 +2923,9 @@
       <c r="B10" t="n">
         <v>1487.335</v>
       </c>
+      <c r="C10" t="n">
+        <v>1849.809382143937</v>
+      </c>
       <c r="D10" t="n">
         <v>3.71604e-07</v>
       </c>
@@ -2856,6 +2976,9 @@
       <c r="B11" t="n">
         <v>1474.421</v>
       </c>
+      <c r="C11" t="n">
+        <v>1833.594078761014</v>
+      </c>
       <c r="D11" t="n">
         <v>3.73813e-07</v>
       </c>
@@ -2906,6 +3029,9 @@
       <c r="B12" t="n">
         <v>1459.115</v>
       </c>
+      <c r="C12" t="n">
+        <v>1820.567636385785</v>
+      </c>
       <c r="D12" t="n">
         <v>3.76013e-07</v>
       </c>
@@ -2956,6 +3082,9 @@
       <c r="B13" t="n">
         <v>1444.263</v>
       </c>
+      <c r="C13" t="n">
+        <v>1808.005014798475</v>
+      </c>
       <c r="D13" t="n">
         <v>3.77787e-07</v>
       </c>
@@ -3006,6 +3135,9 @@
       <c r="B14" t="n">
         <v>1421.302</v>
       </c>
+      <c r="C14" t="n">
+        <v>1787.808088355597</v>
+      </c>
       <c r="D14" t="n">
         <v>3.79782e-07</v>
       </c>
@@ -3056,6 +3188,9 @@
       <c r="B15" t="n">
         <v>1410.956</v>
       </c>
+      <c r="C15" t="n">
+        <v>1774.806189642046</v>
+      </c>
       <c r="D15" t="n">
         <v>3.81492e-07</v>
       </c>
@@ -3106,6 +3241,9 @@
       <c r="B16" t="n">
         <v>1388.711</v>
       </c>
+      <c r="C16" t="n">
+        <v>1755.640584499156</v>
+      </c>
       <c r="D16" t="n">
         <v>3.83809e-07</v>
       </c>
@@ -3156,6 +3294,9 @@
       <c r="B17" t="n">
         <v>1374.654</v>
       </c>
+      <c r="C17" t="n">
+        <v>1739.37196557861</v>
+      </c>
       <c r="D17" t="n">
         <v>3.85732e-07</v>
       </c>
@@ -3206,6 +3347,9 @@
       <c r="B18" t="n">
         <v>1359.802</v>
       </c>
+      <c r="C18" t="n">
+        <v>1726.802778376697</v>
+      </c>
       <c r="D18" t="n">
         <v>3.87449e-07</v>
       </c>
@@ -3256,6 +3400,9 @@
       <c r="B19" t="n">
         <v>1348.519</v>
       </c>
+      <c r="C19" t="n">
+        <v>1713.902298346405</v>
+      </c>
       <c r="D19" t="n">
         <v>3.89213e-07</v>
       </c>
@@ -3306,6 +3453,9 @@
       <c r="B20" t="n">
         <v>1326.99</v>
       </c>
+      <c r="C20" t="n">
+        <v>1697.740888694918</v>
+      </c>
       <c r="D20" t="n">
         <v>3.90892e-07</v>
       </c>
@@ -3356,6 +3506,9 @@
       <c r="B21" t="n">
         <v>1313.218</v>
       </c>
+      <c r="C21" t="n">
+        <v>1681.075913893635</v>
+      </c>
       <c r="D21" t="n">
         <v>3.92624e-07</v>
       </c>
@@ -3405,6 +3558,9 @@
       </c>
       <c r="B22" t="n">
         <v>1303.231</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1669.245099415437</v>
       </c>
       <c r="D22" t="n">
         <v>3.94348e-07</v>
@@ -3476,7 +3632,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -3602,6 +3758,9 @@
       <c r="B2" t="n">
         <v>1799.67</v>
       </c>
+      <c r="C2" t="n">
+        <v>2147.285807801437</v>
+      </c>
       <c r="D2" t="n">
         <v>3.26362e-07</v>
       </c>
@@ -3652,6 +3811,9 @@
       <c r="B3" t="n">
         <v>1651.82</v>
       </c>
+      <c r="C3" t="n">
+        <v>1975.397389433182</v>
+      </c>
       <c r="D3" t="n">
         <v>3.50995e-07</v>
       </c>
@@ -3702,6 +3864,9 @@
       <c r="B4" t="n">
         <v>1596.015</v>
       </c>
+      <c r="C4" t="n">
+        <v>1926.838235194174</v>
+      </c>
       <c r="D4" t="n">
         <v>3.5845e-07</v>
       </c>
@@ -3752,6 +3917,9 @@
       <c r="B5" t="n">
         <v>1579</v>
       </c>
+      <c r="C5" t="n">
+        <v>1904.022547217711</v>
+      </c>
       <c r="D5" t="n">
         <v>3.62271e-07</v>
       </c>
@@ -3802,6 +3970,9 @@
       <c r="B6" t="n">
         <v>1557.156</v>
       </c>
+      <c r="C6" t="n">
+        <v>1881.769254769199</v>
+      </c>
       <c r="D6" t="n">
         <v>3.65422e-07</v>
       </c>
@@ -3852,6 +4023,9 @@
       <c r="B7" t="n">
         <v>1527.902</v>
       </c>
+      <c r="C7" t="n">
+        <v>1858.17083633283</v>
+      </c>
       <c r="D7" t="n">
         <v>3.68586e-07</v>
       </c>
@@ -3902,6 +4076,9 @@
       <c r="B8" t="n">
         <v>1510.324</v>
       </c>
+      <c r="C8" t="n">
+        <v>1841.912975942348</v>
+      </c>
       <c r="D8" t="n">
         <v>3.71476e-07</v>
       </c>
@@ -3952,6 +4129,9 @@
       <c r="B9" t="n">
         <v>1487.341</v>
       </c>
+      <c r="C9" t="n">
+        <v>1820.229816884357</v>
+      </c>
       <c r="D9" t="n">
         <v>3.74348e-07</v>
       </c>
@@ -4002,6 +4182,9 @@
       <c r="B10" t="n">
         <v>1474.733</v>
       </c>
+      <c r="C10" t="n">
+        <v>1802.781229795612</v>
+      </c>
       <c r="D10" t="n">
         <v>3.77123e-07</v>
       </c>
@@ -4051,6 +4234,9 @@
       </c>
       <c r="B11" t="n">
         <v>1457.247</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1785.688415451813</v>
       </c>
       <c r="D11" t="n">
         <v>3.7933e-07</v>
@@ -4122,7 +4308,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -4248,6 +4434,9 @@
       <c r="B2" t="n">
         <v>1097.688</v>
       </c>
+      <c r="C2" t="n">
+        <v>1523.270593476137</v>
+      </c>
       <c r="D2" t="n">
         <v>4.23414e-07</v>
       </c>
@@ -4298,6 +4487,9 @@
       <c r="B3" t="n">
         <v>1022.422</v>
       </c>
+      <c r="C3" t="n">
+        <v>1430.556168926691</v>
+      </c>
       <c r="D3" t="n">
         <v>4.3275e-07</v>
       </c>
@@ -4348,6 +4540,9 @@
       <c r="B4" t="n">
         <v>995.0419999999999</v>
       </c>
+      <c r="C4" t="n">
+        <v>1398.245285654846</v>
+      </c>
       <c r="D4" t="n">
         <v>4.35951e-07</v>
       </c>
@@ -4398,6 +4593,9 @@
       <c r="B5" t="n">
         <v>972.7489999999999</v>
       </c>
+      <c r="C5" t="n">
+        <v>1376.137489740064</v>
+      </c>
       <c r="D5" t="n">
         <v>4.38116e-07</v>
       </c>
@@ -4448,6 +4646,9 @@
       <c r="B6" t="n">
         <v>953.058</v>
       </c>
+      <c r="C6" t="n">
+        <v>1358.440868475107</v>
+      </c>
       <c r="D6" t="n">
         <v>4.40232e-07</v>
       </c>
@@ -4498,6 +4699,9 @@
       <c r="B7" t="n">
         <v>937.2249999999999</v>
       </c>
+      <c r="C7" t="n">
+        <v>1340.204541359324</v>
+      </c>
       <c r="D7" t="n">
         <v>4.42322e-07</v>
       </c>
@@ -4548,6 +4752,9 @@
       <c r="B8" t="n">
         <v>917.6209999999999</v>
       </c>
+      <c r="C8" t="n">
+        <v>1321.502497689098</v>
+      </c>
       <c r="D8" t="n">
         <v>4.44305e-07</v>
       </c>
@@ -4598,6 +4805,9 @@
       <c r="B9" t="n">
         <v>903.425</v>
       </c>
+      <c r="C9" t="n">
+        <v>1285.113884230718</v>
+      </c>
       <c r="D9" t="n">
         <v>4.45998e-07</v>
       </c>
@@ -4648,6 +4858,9 @@
       <c r="B10" t="n">
         <v>869.933</v>
       </c>
+      <c r="C10" t="n">
+        <v>1265.622653800745</v>
+      </c>
       <c r="D10" t="n">
         <v>4.50525e-07</v>
       </c>
@@ -4698,6 +4911,9 @@
       <c r="B11" t="n">
         <v>850.2719999999999</v>
       </c>
+      <c r="C11" t="n">
+        <v>1246.823010844561</v>
+      </c>
       <c r="D11" t="n">
         <v>4.52218e-07</v>
       </c>
@@ -4748,6 +4964,9 @@
       <c r="B12" t="n">
         <v>836.0520000000001</v>
       </c>
+      <c r="C12" t="n">
+        <v>1231.539165158899</v>
+      </c>
       <c r="D12" t="n">
         <v>4.53792e-07</v>
       </c>
@@ -4798,6 +5017,9 @@
       <c r="B13" t="n">
         <v>825.3199999999999</v>
       </c>
+      <c r="C13" t="n">
+        <v>1217.824533050761</v>
+      </c>
       <c r="D13" t="n">
         <v>4.55112e-07</v>
       </c>
@@ -4848,6 +5070,9 @@
       <c r="B14" t="n">
         <v>815.347</v>
       </c>
+      <c r="C14" t="n">
+        <v>1205.432775690289</v>
+      </c>
       <c r="D14" t="n">
         <v>4.56581e-07</v>
       </c>
@@ -4898,6 +5123,9 @@
       <c r="B15" t="n">
         <v>803.2450000000001</v>
       </c>
+      <c r="C15" t="n">
+        <v>1189.515827218494</v>
+      </c>
       <c r="D15" t="n">
         <v>4.58282e-07</v>
       </c>
@@ -4948,6 +5176,9 @@
       <c r="B16" t="n">
         <v>789.414</v>
       </c>
+      <c r="C16" t="n">
+        <v>1175.355302685921</v>
+      </c>
       <c r="D16" t="n">
         <v>4.59592e-07</v>
       </c>
@@ -4998,6 +5229,9 @@
       <c r="B17" t="n">
         <v>772.1279999999999</v>
       </c>
+      <c r="C17" t="n">
+        <v>1158.208669292641</v>
+      </c>
       <c r="D17" t="n">
         <v>4.61087e-07</v>
       </c>
@@ -5048,6 +5282,9 @@
       <c r="B18" t="n">
         <v>771.028</v>
       </c>
+      <c r="C18" t="n">
+        <v>1154.607872273115</v>
+      </c>
       <c r="D18" t="n">
         <v>4.62663e-07</v>
       </c>
@@ -5098,6 +5335,9 @@
       <c r="B19" t="n">
         <v>759.961</v>
       </c>
+      <c r="C19" t="n">
+        <v>1138.080696627848</v>
+      </c>
       <c r="D19" t="n">
         <v>4.64176e-07</v>
       </c>
@@ -5148,6 +5388,9 @@
       <c r="B20" t="n">
         <v>741.038</v>
       </c>
+      <c r="C20" t="n">
+        <v>1120.827389988081</v>
+      </c>
       <c r="D20" t="n">
         <v>4.65548e-07</v>
       </c>
@@ -5198,6 +5441,9 @@
       <c r="B21" t="n">
         <v>730.3839999999999</v>
       </c>
+      <c r="C21" t="n">
+        <v>1109.715556344335</v>
+      </c>
       <c r="D21" t="n">
         <v>4.66994e-07</v>
       </c>
@@ -5247,6 +5493,9 @@
       </c>
       <c r="B22" t="n">
         <v>721.009</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1093.464197620228</v>
       </c>
       <c r="D22" t="n">
         <v>4.68552e-07</v>
@@ -5318,7 +5567,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -5444,6 +5693,9 @@
       <c r="B2" t="n">
         <v>1103.268</v>
       </c>
+      <c r="C2" t="n">
+        <v>1502.779276547776</v>
+      </c>
       <c r="D2" t="n">
         <v>4.24516e-07</v>
       </c>
@@ -5494,6 +5746,9 @@
       <c r="B3" t="n">
         <v>1060.644</v>
       </c>
+      <c r="C3" t="n">
+        <v>1450.018808845394</v>
+      </c>
       <c r="D3" t="n">
         <v>4.3251e-07</v>
       </c>
@@ -5544,6 +5799,9 @@
       <c r="B4" t="n">
         <v>1033.375</v>
       </c>
+      <c r="C4" t="n">
+        <v>1423.464630649422</v>
+      </c>
       <c r="D4" t="n">
         <v>4.35569e-07</v>
       </c>
@@ -5594,6 +5852,9 @@
       <c r="B5" t="n">
         <v>1009.235</v>
       </c>
+      <c r="C5" t="n">
+        <v>1402.918049986543</v>
+      </c>
       <c r="D5" t="n">
         <v>4.3794e-07</v>
       </c>
@@ -5644,6 +5905,9 @@
       <c r="B6" t="n">
         <v>987.1590000000001</v>
       </c>
+      <c r="C6" t="n">
+        <v>1377.575235031508</v>
+      </c>
       <c r="D6" t="n">
         <v>4.40335e-07</v>
       </c>
@@ -5694,6 +5958,9 @@
       <c r="B7" t="n">
         <v>971.6859999999999</v>
       </c>
+      <c r="C7" t="n">
+        <v>1363.630012511125</v>
+      </c>
       <c r="D7" t="n">
         <v>4.44043e-07</v>
       </c>
@@ -5744,6 +6011,9 @@
       <c r="B8" t="n">
         <v>942.199</v>
       </c>
+      <c r="C8" t="n">
+        <v>1351.233919406838</v>
+      </c>
       <c r="D8" t="n">
         <v>4.46692e-07</v>
       </c>
@@ -5794,6 +6064,9 @@
       <c r="B9" t="n">
         <v>923.4749999999999</v>
       </c>
+      <c r="C9" t="n">
+        <v>1320.093377382473</v>
+      </c>
       <c r="D9" t="n">
         <v>4.49304e-07</v>
       </c>
@@ -5844,6 +6117,9 @@
       <c r="B10" t="n">
         <v>905.785</v>
       </c>
+      <c r="C10" t="n">
+        <v>1301.633756100767</v>
+      </c>
       <c r="D10" t="n">
         <v>4.5171e-07</v>
       </c>
@@ -5893,6 +6169,9 @@
       </c>
       <c r="B11" t="n">
         <v>884.502</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1281.948187934509</v>
       </c>
       <c r="D11" t="n">
         <v>4.54192e-07</v>
@@ -5964,7 +6243,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -6090,6 +6369,9 @@
       <c r="B2" t="n">
         <v>1030.872</v>
       </c>
+      <c r="C2" t="n">
+        <v>1507.215422820027</v>
+      </c>
       <c r="D2" t="n">
         <v>4.37132e-07</v>
       </c>
@@ -6140,6 +6422,9 @@
       <c r="B3" t="n">
         <v>1006.711</v>
       </c>
+      <c r="C3" t="n">
+        <v>1408.661345283361</v>
+      </c>
       <c r="D3" t="n">
         <v>4.39257e-07</v>
       </c>
@@ -6190,6 +6475,9 @@
       <c r="B4" t="n">
         <v>976.9299999999999</v>
       </c>
+      <c r="C4" t="n">
+        <v>1385.183531593908</v>
+      </c>
       <c r="D4" t="n">
         <v>4.42755e-07</v>
       </c>
@@ -6240,6 +6528,9 @@
       <c r="B5" t="n">
         <v>961.5530000000001</v>
       </c>
+      <c r="C5" t="n">
+        <v>1396.011596236439</v>
+      </c>
       <c r="D5" t="n">
         <v>4.44808e-07</v>
       </c>
@@ -6290,6 +6581,9 @@
       <c r="B6" t="n">
         <v>924.0379999999999</v>
       </c>
+      <c r="C6" t="n">
+        <v>1329.448200224221</v>
+      </c>
       <c r="D6" t="n">
         <v>4.49283e-07</v>
       </c>
@@ -6340,6 +6634,9 @@
       <c r="B7" t="n">
         <v>900.8800000000001</v>
       </c>
+      <c r="C7" t="n">
+        <v>1309.863724958478</v>
+      </c>
       <c r="D7" t="n">
         <v>4.51206e-07</v>
       </c>
@@ -6390,6 +6687,9 @@
       <c r="B8" t="n">
         <v>884.3800000000001</v>
       </c>
+      <c r="C8" t="n">
+        <v>1291.406171382699</v>
+      </c>
       <c r="D8" t="n">
         <v>4.53291e-07</v>
       </c>
@@ -6440,6 +6740,9 @@
       <c r="B9" t="n">
         <v>873.403</v>
       </c>
+      <c r="C9" t="n">
+        <v>1278.194412869387</v>
+      </c>
       <c r="D9" t="n">
         <v>4.55235e-07</v>
       </c>
@@ -6490,6 +6793,9 @@
       <c r="B10" t="n">
         <v>858.8789999999999</v>
       </c>
+      <c r="C10" t="n">
+        <v>1256.600404026334</v>
+      </c>
       <c r="D10" t="n">
         <v>4.57109e-07</v>
       </c>
@@ -6540,6 +6846,9 @@
       <c r="B11" t="n">
         <v>841.515</v>
       </c>
+      <c r="C11" t="n">
+        <v>1242.971667753642</v>
+      </c>
       <c r="D11" t="n">
         <v>4.59292e-07</v>
       </c>
@@ -6590,6 +6899,9 @@
       <c r="B12" t="n">
         <v>830.0150000000001</v>
       </c>
+      <c r="C12" t="n">
+        <v>1228.233549895886</v>
+      </c>
       <c r="D12" t="n">
         <v>4.61286e-07</v>
       </c>
@@ -6640,6 +6952,9 @@
       <c r="B13" t="n">
         <v>814.2909999999999</v>
       </c>
+      <c r="C13" t="n">
+        <v>1213.866011765583</v>
+      </c>
       <c r="D13" t="n">
         <v>4.63177e-07</v>
       </c>
@@ -6690,6 +7005,9 @@
       <c r="B14" t="n">
         <v>801.577</v>
       </c>
+      <c r="C14" t="n">
+        <v>1195.827250747904</v>
+      </c>
       <c r="D14" t="n">
         <v>4.64722e-07</v>
       </c>
@@ -6740,6 +7058,9 @@
       <c r="B15" t="n">
         <v>789.8200000000001</v>
       </c>
+      <c r="C15" t="n">
+        <v>1183.398634711001</v>
+      </c>
       <c r="D15" t="n">
         <v>4.66419e-07</v>
       </c>
@@ -6790,6 +7111,9 @@
       <c r="B16" t="n">
         <v>779.105</v>
       </c>
+      <c r="C16" t="n">
+        <v>1171.12945782568</v>
+      </c>
       <c r="D16" t="n">
         <v>4.68247e-07</v>
       </c>
@@ -6840,6 +7164,9 @@
       <c r="B17" t="n">
         <v>767.2379999999999</v>
       </c>
+      <c r="C17" t="n">
+        <v>1158.436186574346</v>
+      </c>
       <c r="D17" t="n">
         <v>4.69891e-07</v>
       </c>
@@ -6890,6 +7217,9 @@
       <c r="B18" t="n">
         <v>754.0160000000001</v>
       </c>
+      <c r="C18" t="n">
+        <v>1141.150140988081</v>
+      </c>
       <c r="D18" t="n">
         <v>4.70976e-07</v>
       </c>
@@ -6940,6 +7270,9 @@
       <c r="B19" t="n">
         <v>739.6190000000001</v>
       </c>
+      <c r="C19" t="n">
+        <v>1127.370888081084</v>
+      </c>
       <c r="D19" t="n">
         <v>4.72749e-07</v>
       </c>
@@ -6990,6 +7323,9 @@
       <c r="B20" t="n">
         <v>729.491</v>
       </c>
+      <c r="C20" t="n">
+        <v>1108.440848540964</v>
+      </c>
       <c r="D20" t="n">
         <v>4.7425e-07</v>
       </c>
@@ -7040,6 +7376,9 @@
       <c r="B21" t="n">
         <v>715.3940000000001</v>
       </c>
+      <c r="C21" t="n">
+        <v>1075.965097882781</v>
+      </c>
       <c r="D21" t="n">
         <v>4.76944e-07</v>
       </c>
@@ -7089,6 +7428,9 @@
       </c>
       <c r="B22" t="n">
         <v>682.413</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1054.336552539145</v>
       </c>
       <c r="D22" t="n">
         <v>4.80279e-07</v>
@@ -7160,7 +7502,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -7286,6 +7628,9 @@
       <c r="B2" t="n">
         <v>1285.113</v>
       </c>
+      <c r="C2" t="n">
+        <v>1746.288290084989</v>
+      </c>
       <c r="D2" t="n">
         <v>3.91163e-07</v>
       </c>
@@ -7336,6 +7681,9 @@
       <c r="B3" t="n">
         <v>1127.67</v>
       </c>
+      <c r="C3" t="n">
+        <v>1542.132214923713</v>
+      </c>
       <c r="D3" t="n">
         <v>4.20174e-07</v>
       </c>
@@ -7386,6 +7734,9 @@
       <c r="B4" t="n">
         <v>1072.181</v>
       </c>
+      <c r="C4" t="n">
+        <v>1484.611337762111</v>
+      </c>
       <c r="D4" t="n">
         <v>4.27276e-07</v>
       </c>
@@ -7436,6 +7787,9 @@
       <c r="B5" t="n">
         <v>1038.584</v>
       </c>
+      <c r="C5" t="n">
+        <v>1454.026771458737</v>
+      </c>
       <c r="D5" t="n">
         <v>4.314e-07</v>
       </c>
@@ -7486,6 +7840,9 @@
       <c r="B6" t="n">
         <v>1011.139</v>
       </c>
+      <c r="C6" t="n">
+        <v>1431.678880070765</v>
+      </c>
       <c r="D6" t="n">
         <v>4.34637e-07</v>
       </c>
@@ -7536,6 +7893,9 @@
       <c r="B7" t="n">
         <v>988.9290000000001</v>
       </c>
+      <c r="C7" t="n">
+        <v>1405.52891378237</v>
+      </c>
       <c r="D7" t="n">
         <v>4.37929e-07</v>
       </c>
@@ -7586,6 +7946,9 @@
       <c r="B8" t="n">
         <v>967.7239999999999</v>
       </c>
+      <c r="C8" t="n">
+        <v>1387.247335842548</v>
+      </c>
       <c r="D8" t="n">
         <v>4.41101e-07</v>
       </c>
@@ -7636,6 +7999,9 @@
       <c r="B9" t="n">
         <v>947.5649999999999</v>
       </c>
+      <c r="C9" t="n">
+        <v>1369.530998141567</v>
+      </c>
       <c r="D9" t="n">
         <v>4.44239e-07</v>
       </c>
@@ -7686,6 +8052,9 @@
       <c r="B10" t="n">
         <v>917.337</v>
       </c>
+      <c r="C10" t="n">
+        <v>1344.448213564349</v>
+      </c>
       <c r="D10" t="n">
         <v>4.4712e-07</v>
       </c>
@@ -7735,6 +8104,9 @@
       </c>
       <c r="B11" t="n">
         <v>899.665</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1327.25603136718</v>
       </c>
       <c r="D11" t="n">
         <v>4.49771e-07</v>
@@ -7806,7 +8178,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -7932,6 +8304,9 @@
       <c r="B2" t="n">
         <v>1025.941</v>
       </c>
+      <c r="C2" t="n">
+        <v>1482.916591821896</v>
+      </c>
       <c r="D2" t="n">
         <v>4.31391e-07</v>
       </c>
@@ -7982,6 +8357,9 @@
       <c r="B3" t="n">
         <v>958.264</v>
       </c>
+      <c r="C3" t="n">
+        <v>1386.574651067633</v>
+      </c>
       <c r="D3" t="n">
         <v>4.40301e-07</v>
       </c>
@@ -8032,6 +8410,9 @@
       <c r="B4" t="n">
         <v>939.049</v>
       </c>
+      <c r="C4" t="n">
+        <v>1364.961173030417</v>
+      </c>
       <c r="D4" t="n">
         <v>4.42917e-07</v>
       </c>
@@ -8082,6 +8463,9 @@
       <c r="B5" t="n">
         <v>921.4680000000001</v>
       </c>
+      <c r="C5" t="n">
+        <v>1349.457558432359</v>
+      </c>
       <c r="D5" t="n">
         <v>4.4482e-07</v>
       </c>
@@ -8132,6 +8516,9 @@
       <c r="B6" t="n">
         <v>905.664</v>
       </c>
+      <c r="C6" t="n">
+        <v>1334.719866641705</v>
+      </c>
       <c r="D6" t="n">
         <v>4.464e-07</v>
       </c>
@@ -8182,6 +8569,9 @@
       <c r="B7" t="n">
         <v>889.5640000000001</v>
       </c>
+      <c r="C7" t="n">
+        <v>1318.262209091663</v>
+      </c>
       <c r="D7" t="n">
         <v>4.48057e-07</v>
       </c>
@@ -8232,6 +8622,9 @@
       <c r="B8" t="n">
         <v>880.3820000000001</v>
       </c>
+      <c r="C8" t="n">
+        <v>1308.658129521323</v>
+      </c>
       <c r="D8" t="n">
         <v>4.49997e-07</v>
       </c>
@@ -8282,6 +8675,9 @@
       <c r="B9" t="n">
         <v>861.3890000000001</v>
       </c>
+      <c r="C9" t="n">
+        <v>1288.547915456701</v>
+      </c>
       <c r="D9" t="n">
         <v>4.51829e-07</v>
       </c>
@@ -8332,6 +8728,9 @@
       <c r="B10" t="n">
         <v>849.6870000000001</v>
       </c>
+      <c r="C10" t="n">
+        <v>1277.674637191294</v>
+      </c>
       <c r="D10" t="n">
         <v>4.53622e-07</v>
       </c>
@@ -8382,6 +8781,9 @@
       <c r="B11" t="n">
         <v>835.6020000000001</v>
       </c>
+      <c r="C11" t="n">
+        <v>1263.974557229638</v>
+      </c>
       <c r="D11" t="n">
         <v>4.55476e-07</v>
       </c>
@@ -8432,6 +8834,9 @@
       <c r="B12" t="n">
         <v>826.7269999999999</v>
       </c>
+      <c r="C12" t="n">
+        <v>1249.268957051645</v>
+      </c>
       <c r="D12" t="n">
         <v>4.57073e-07</v>
       </c>
@@ -8482,6 +8887,9 @@
       <c r="B13" t="n">
         <v>815.9640000000001</v>
       </c>
+      <c r="C13" t="n">
+        <v>1241.031162769922</v>
+      </c>
       <c r="D13" t="n">
         <v>4.58828e-07</v>
       </c>
@@ -8532,6 +8940,9 @@
       <c r="B14" t="n">
         <v>799.6709999999999</v>
       </c>
+      <c r="C14" t="n">
+        <v>1222.187665998255</v>
+      </c>
       <c r="D14" t="n">
         <v>4.60394e-07</v>
       </c>
@@ -8582,6 +8993,9 @@
       <c r="B15" t="n">
         <v>787.1419999999999</v>
       </c>
+      <c r="C15" t="n">
+        <v>1210.613011028484</v>
+      </c>
       <c r="D15" t="n">
         <v>4.6214e-07</v>
       </c>
@@ -8632,6 +9046,9 @@
       <c r="B16" t="n">
         <v>778.432</v>
       </c>
+      <c r="C16" t="n">
+        <v>1198.676164732769</v>
+      </c>
       <c r="D16" t="n">
         <v>4.63978e-07</v>
       </c>
@@ -8682,6 +9099,9 @@
       <c r="B17" t="n">
         <v>759.7130000000001</v>
       </c>
+      <c r="C17" t="n">
+        <v>1179.421343705392</v>
+      </c>
       <c r="D17" t="n">
         <v>4.65652e-07</v>
       </c>
@@ -8732,6 +9152,9 @@
       <c r="B18" t="n">
         <v>753.1580000000001</v>
       </c>
+      <c r="C18" t="n">
+        <v>1172.078035414172</v>
+      </c>
       <c r="D18" t="n">
         <v>4.67156e-07</v>
       </c>
@@ -8782,6 +9205,9 @@
       <c r="B19" t="n">
         <v>743.519</v>
       </c>
+      <c r="C19" t="n">
+        <v>1159.9168653835</v>
+      </c>
       <c r="D19" t="n">
         <v>4.69099e-07</v>
       </c>
@@ -8832,6 +9258,9 @@
       <c r="B20" t="n">
         <v>733.282</v>
       </c>
+      <c r="C20" t="n">
+        <v>1145.711573004148</v>
+      </c>
       <c r="D20" t="n">
         <v>4.70661e-07</v>
       </c>
@@ -8882,6 +9311,9 @@
       <c r="B21" t="n">
         <v>720.221</v>
       </c>
+      <c r="C21" t="n">
+        <v>1131.732877875347</v>
+      </c>
       <c r="D21" t="n">
         <v>4.72531e-07</v>
       </c>
@@ -8931,6 +9363,9 @@
       </c>
       <c r="B22" t="n">
         <v>705.5419999999999</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1113.601024614723</v>
       </c>
       <c r="D22" t="n">
         <v>4.74299e-07</v>
@@ -9002,7 +9437,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -9128,6 +9563,9 @@
       <c r="B2" t="n">
         <v>888.883</v>
       </c>
+      <c r="C2" t="n">
+        <v>1418.961381800347</v>
+      </c>
       <c r="D2" t="n">
         <v>4.51846e-07</v>
       </c>
@@ -9178,6 +9616,9 @@
       <c r="B3" t="n">
         <v>764.0119999999999</v>
       </c>
+      <c r="C3" t="n">
+        <v>1224.275610306775</v>
+      </c>
       <c r="D3" t="n">
         <v>4.66674e-07</v>
       </c>
@@ -9228,6 +9669,9 @@
       <c r="B4" t="n">
         <v>738.019</v>
       </c>
+      <c r="C4" t="n">
+        <v>1189.286982893059</v>
+      </c>
       <c r="D4" t="n">
         <v>4.6716e-07</v>
       </c>
@@ -9278,6 +9722,9 @@
       <c r="B5" t="n">
         <v>720.3130000000001</v>
       </c>
+      <c r="C5" t="n">
+        <v>1173.38174357279</v>
+      </c>
       <c r="D5" t="n">
         <v>4.67022e-07</v>
       </c>
@@ -9328,6 +9775,9 @@
       <c r="B6" t="n">
         <v>703.7619999999999</v>
       </c>
+      <c r="C6" t="n">
+        <v>1156.89564038517</v>
+      </c>
       <c r="D6" t="n">
         <v>4.67225e-07</v>
       </c>
@@ -9378,6 +9828,9 @@
       <c r="B7" t="n">
         <v>691.2249999999999</v>
       </c>
+      <c r="C7" t="n">
+        <v>1142.653270691916</v>
+      </c>
       <c r="D7" t="n">
         <v>4.68074e-07</v>
       </c>
@@ -9428,6 +9881,9 @@
       <c r="B8" t="n">
         <v>670.2239999999999</v>
       </c>
+      <c r="C8" t="n">
+        <v>1122.390572507551</v>
+      </c>
       <c r="D8" t="n">
         <v>4.69062e-07</v>
       </c>
@@ -9478,6 +9934,9 @@
       <c r="B9" t="n">
         <v>655.4949999999999</v>
       </c>
+      <c r="C9" t="n">
+        <v>1103.755808274577</v>
+      </c>
       <c r="D9" t="n">
         <v>4.70189e-07</v>
       </c>
@@ -9528,6 +9987,9 @@
       <c r="B10" t="n">
         <v>643.347</v>
       </c>
+      <c r="C10" t="n">
+        <v>1094.317038281651</v>
+      </c>
       <c r="D10" t="n">
         <v>4.71574e-07</v>
       </c>
@@ -9577,6 +10039,9 @@
       </c>
       <c r="B11" t="n">
         <v>632.314</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1077.469719916296</v>
       </c>
       <c r="D11" t="n">
         <v>4.72768e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 36.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 36.xlsx
@@ -565,7 +565,7 @@
         <v>1930.794</v>
       </c>
       <c r="C2" t="n">
-        <v>2268.126181417028</v>
+        <v>12669.47118789076</v>
       </c>
       <c r="D2" t="n">
         <v>3.21875e-07</v>
@@ -598,10 +598,7 @@
         <v>-30005.75286025774</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.288885276243789e-10</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2615.739406248856</v>
+        <v>-10145.3223780786</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000104e-08</v>
@@ -618,7 +615,7 @@
         <v>1830.712</v>
       </c>
       <c r="C3" t="n">
-        <v>2171.630105350745</v>
+        <v>13437.03086126353</v>
       </c>
       <c r="D3" t="n">
         <v>3.33289e-07</v>
@@ -651,10 +648,7 @@
         <v>-29591.61726137361</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.038184347860714e-10</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2504.001632047016</v>
+        <v>-11025.12442176415</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000025e-08</v>
@@ -671,7 +665,7 @@
         <v>1796.852</v>
       </c>
       <c r="C4" t="n">
-        <v>2138.143295587891</v>
+        <v>14472.17450124447</v>
       </c>
       <c r="D4" t="n">
         <v>3.37632e-07</v>
@@ -704,10 +698,7 @@
         <v>-30378.4553114298</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.636065939816327e-09</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2461.853418078507</v>
+        <v>-12109.5534566185</v>
       </c>
       <c r="AA4" t="n">
         <v>1.00000000000067e-08</v>
@@ -724,7 +715,7 @@
         <v>1764.29</v>
       </c>
       <c r="C5" t="n">
-        <v>2112.767757304954</v>
+        <v>12680.93507705993</v>
       </c>
       <c r="D5" t="n">
         <v>3.41131e-07</v>
@@ -757,10 +748,7 @@
         <v>-30022.53268889376</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.660672964029683e-09</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2423.106427508083</v>
+        <v>-10335.89086020842</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000014e-08</v>
@@ -777,7 +765,7 @@
         <v>1729.522</v>
       </c>
       <c r="C6" t="n">
-        <v>2081.367713907285</v>
+        <v>12909.55883876931</v>
       </c>
       <c r="D6" t="n">
         <v>3.44068e-07</v>
@@ -810,10 +798,7 @@
         <v>-26648.46776713715</v>
       </c>
       <c r="Y6" t="n">
-        <v>9.443867881205971e-11</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2390.549441454362</v>
+        <v>-10595.50316724251</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000059e-08</v>
@@ -830,7 +815,7 @@
         <v>1701.958</v>
       </c>
       <c r="C7" t="n">
-        <v>2054.720610115364</v>
+        <v>13393.49690164525</v>
       </c>
       <c r="D7" t="n">
         <v>3.47512e-07</v>
@@ -863,10 +848,7 @@
         <v>-26433.47969658138</v>
       </c>
       <c r="Y7" t="n">
-        <v>8.82816451659133e-10</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2356.006004572259</v>
+        <v>-11116.3611738374</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000013293e-08</v>
@@ -883,7 +865,7 @@
         <v>1683.699</v>
       </c>
       <c r="C8" t="n">
-        <v>2032.963606923738</v>
+        <v>15550.94003534199</v>
       </c>
       <c r="D8" t="n">
         <v>3.50007e-07</v>
@@ -916,10 +898,7 @@
         <v>-26106.72336765886</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.539659406776374e-10</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2324.577024620783</v>
+        <v>-13316.59090876033</v>
       </c>
       <c r="AA8" t="n">
         <v>1.00000000000003e-08</v>
@@ -936,7 +915,7 @@
         <v>1659.309</v>
       </c>
       <c r="C9" t="n">
-        <v>2009.080633040748</v>
+        <v>14396.50283481048</v>
       </c>
       <c r="D9" t="n">
         <v>3.52865e-07</v>
@@ -969,10 +948,7 @@
         <v>-25655.12322408354</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.878325676382569e-10</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2295.067218311654</v>
+        <v>-12180.85157859302</v>
       </c>
       <c r="AA9" t="n">
         <v>1.00000000000045e-08</v>
@@ -989,7 +965,7 @@
         <v>1636.784</v>
       </c>
       <c r="C10" t="n">
-        <v>1985.599158023935</v>
+        <v>14072.8224464425</v>
       </c>
       <c r="D10" t="n">
         <v>3.55368e-07</v>
@@ -1022,10 +998,7 @@
         <v>-25182.41937332417</v>
       </c>
       <c r="Y10" t="n">
-        <v>5.928004529350924e-10</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2264.48755042764</v>
+        <v>-11879.94653189032</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000002e-08</v>
@@ -1042,7 +1015,7 @@
         <v>1609.728</v>
       </c>
       <c r="C11" t="n">
-        <v>1962.117647621546</v>
+        <v>15174.46578337903</v>
       </c>
       <c r="D11" t="n">
         <v>3.57908e-07</v>
@@ -1075,10 +1048,7 @@
         <v>-22770.76496777428</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.041348318209447e-11</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2238.891502218598</v>
+        <v>-13014.47474454595</v>
       </c>
       <c r="AA11" t="n">
         <v>1.00000000000002e-08</v>
@@ -1241,7 +1211,7 @@
         <v>1354.546</v>
       </c>
       <c r="C2" t="n">
-        <v>1810.023459554588</v>
+        <v>13510.72293562273</v>
       </c>
       <c r="D2" t="n">
         <v>3.50084e-07</v>
@@ -1274,10 +1244,7 @@
         <v>-17015.43293009196</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.078255915022336e-09</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1943.788660361249</v>
+        <v>-11459.78939829737</v>
       </c>
       <c r="AA2" t="n">
         <v>1e-08</v>
@@ -1294,7 +1261,7 @@
         <v>1244.023</v>
       </c>
       <c r="C3" t="n">
-        <v>1657.436375332882</v>
+        <v>1244.023</v>
       </c>
       <c r="D3" t="n">
         <v>3.64831e-07</v>
@@ -1326,11 +1293,10 @@
       <c r="X3" t="n">
         <v>-17987.86788757323</v>
       </c>
-      <c r="Y3" t="n">
-        <v>7.02470719264075e-12</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1835.944548685289</v>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA3" t="n">
         <v>1e-08</v>
@@ -1347,7 +1313,7 @@
         <v>1205.615</v>
       </c>
       <c r="C4" t="n">
-        <v>1614.664208835687</v>
+        <v>561.5455563951309</v>
       </c>
       <c r="D4" t="n">
         <v>3.68465e-07</v>
@@ -1380,16 +1346,13 @@
         <v>-16970.61181723978</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.514883384618697e-12</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1799.099779385603</v>
+        <v>497.8025221276222</v>
       </c>
       <c r="AA4" t="n">
-        <v>1e-08</v>
+        <v>1.957811910732713e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8276142146253896</v>
+        <v>0.9787628619610076</v>
       </c>
     </row>
     <row r="5">
@@ -1400,7 +1363,7 @@
         <v>1179.377</v>
       </c>
       <c r="C5" t="n">
-        <v>1589.722295890937</v>
+        <v>563.2929408132808</v>
       </c>
       <c r="D5" t="n">
         <v>3.70409e-07</v>
@@ -1433,16 +1396,13 @@
         <v>-15954.47778077594</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.780424302601326e-11</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1774.928220215958</v>
+        <v>488.6307936616606</v>
       </c>
       <c r="AA5" t="n">
-        <v>1e-08</v>
+        <v>2.119928970431093e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.827788539465369</v>
+        <v>0.9716690013148229</v>
       </c>
     </row>
     <row r="6">
@@ -1453,7 +1413,7 @@
         <v>1158.48</v>
       </c>
       <c r="C6" t="n">
-        <v>1572.435767681853</v>
+        <v>565.2835920581981</v>
       </c>
       <c r="D6" t="n">
         <v>3.71536e-07</v>
@@ -1486,16 +1446,13 @@
         <v>-15063.35333011143</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.537786588235589e-09</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1755.614259668295</v>
+        <v>468.1469640204562</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.00000000000001e-08</v>
+        <v>1.550786464623745e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8280178828800255</v>
+        <v>0.992092870035409</v>
       </c>
     </row>
     <row r="7">
@@ -1506,7 +1463,7 @@
         <v>1144.563</v>
       </c>
       <c r="C7" t="n">
-        <v>1560.118040426775</v>
+        <v>565.8732383241513</v>
       </c>
       <c r="D7" t="n">
         <v>3.72856e-07</v>
@@ -1539,16 +1496,13 @@
         <v>-15644.67735598397</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.417652825247201e-12</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1734.989738670846</v>
+        <v>449.0453665965581</v>
       </c>
       <c r="AA7" t="n">
-        <v>1e-08</v>
+        <v>1.255490289717591e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8282691527004641</v>
+        <v>0.9996480467621021</v>
       </c>
     </row>
     <row r="8">
@@ -1559,7 +1513,7 @@
         <v>1123.976</v>
       </c>
       <c r="C8" t="n">
-        <v>1542.341260504835</v>
+        <v>567.3488303851581</v>
       </c>
       <c r="D8" t="n">
         <v>3.74415e-07</v>
@@ -1592,16 +1546,13 @@
         <v>-14710.89724905403</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.794007527303487e-10</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1713.457686446511</v>
+        <v>434.2308452297979</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000000000002e-08</v>
+        <v>1.2177355367963e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8285524028515685</v>
+        <v>0.9999021800676144</v>
       </c>
     </row>
     <row r="9">
@@ -1612,7 +1563,7 @@
         <v>1105.091</v>
       </c>
       <c r="C9" t="n">
-        <v>1523.341553091965</v>
+        <v>568.0288874095802</v>
       </c>
       <c r="D9" t="n">
         <v>3.75922e-07</v>
@@ -1645,16 +1596,13 @@
         <v>-14498.22070462981</v>
       </c>
       <c r="Y9" t="n">
-        <v>8.694514854141747e-10</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1692.441826545994</v>
+        <v>427.1774307610445</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.00000000000001e-08</v>
+        <v>1.346172371093917e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8288695539065057</v>
+        <v>0.9953091061446696</v>
       </c>
     </row>
     <row r="10">
@@ -1665,7 +1613,7 @@
         <v>1097.122</v>
       </c>
       <c r="C10" t="n">
-        <v>1510.895520695873</v>
+        <v>1026.251147103912</v>
       </c>
       <c r="D10" t="n">
         <v>3.77394e-07</v>
@@ -1698,16 +1646,13 @@
         <v>-14950.91672660913</v>
       </c>
       <c r="Y10" t="n">
-        <v>8.155609730440974e-11</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1672.185272462108</v>
+        <v>16.41727443684206</v>
       </c>
       <c r="AA10" t="n">
-        <v>1e-08</v>
+        <v>2.385516483231562e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.829204368396678</v>
+        <v>0.8906794598957126</v>
       </c>
     </row>
     <row r="11">
@@ -1718,7 +1663,7 @@
         <v>1076.179</v>
       </c>
       <c r="C11" t="n">
-        <v>1493.535796842517</v>
+        <v>928.8941732993472</v>
       </c>
       <c r="D11" t="n">
         <v>3.7891e-07</v>
@@ -1751,16 +1696,13 @@
         <v>-13765.04988246847</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.22834557659326e-08</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1651.982173117055</v>
+        <v>91.84101388889826</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.00000000000012e-08</v>
+        <v>2.039492791660817e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8295666008595675</v>
+        <v>0.9116202936211121</v>
       </c>
     </row>
     <row r="12">
@@ -1771,7 +1713,7 @@
         <v>1065.261</v>
       </c>
       <c r="C12" t="n">
-        <v>1481.74458956301</v>
+        <v>924.6690953720745</v>
       </c>
       <c r="D12" t="n">
         <v>3.80504e-07</v>
@@ -1804,16 +1746,13 @@
         <v>-14076.70171652841</v>
       </c>
       <c r="Y12" t="n">
-        <v>3.469974662060197e-08</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1632.532912182233</v>
+        <v>88.96631355916243</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.000000000000875e-08</v>
+        <v>2.111247838944852e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.8299365425505235</v>
+        <v>0.9107695192705672</v>
       </c>
     </row>
     <row r="13">
@@ -1824,7 +1763,7 @@
         <v>1048.456</v>
       </c>
       <c r="C13" t="n">
-        <v>1464.99529645375</v>
+        <v>948.3300676557117</v>
       </c>
       <c r="D13" t="n">
         <v>3.81827e-07</v>
@@ -1857,16 +1796,13 @@
         <v>-13489.6073187469</v>
       </c>
       <c r="Y13" t="n">
-        <v>3.271293927605402e-10</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1613.364482158759</v>
+        <v>59.34365180320191</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.000000000000727e-08</v>
+        <v>2.247981019031424e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.8303279715955958</v>
+        <v>0.9016656650832867</v>
       </c>
     </row>
     <row r="14">
@@ -1877,7 +1813,7 @@
         <v>1030.135</v>
       </c>
       <c r="C14" t="n">
-        <v>1449.12654276467</v>
+        <v>909.6938409276839</v>
       </c>
       <c r="D14" t="n">
         <v>3.83316e-07</v>
@@ -1910,16 +1846,13 @@
         <v>-12575.63001602633</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.147818104728947e-10</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1594.484557164249</v>
+        <v>87.60556979733599</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.000000000000242e-08</v>
+        <v>2.212167921759433e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.8307235729535724</v>
+        <v>0.9056134937596948</v>
       </c>
     </row>
     <row r="15">
@@ -1930,7 +1863,7 @@
         <v>1016.373</v>
       </c>
       <c r="C15" t="n">
-        <v>1434.142923002567</v>
+        <v>901.3454176943502</v>
       </c>
       <c r="D15" t="n">
         <v>3.84765e-07</v>
@@ -1963,16 +1896,13 @@
         <v>-11781.29576294632</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.420342748467271e-10</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1575.951107119047</v>
+        <v>87.87818460886281</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.000000000000402e-08</v>
+        <v>2.237400201246977e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.8311395019231349</v>
+        <v>0.9065826962155309</v>
       </c>
     </row>
     <row r="16">
@@ -1983,7 +1913,7 @@
         <v>999.289</v>
       </c>
       <c r="C16" t="n">
-        <v>1417.347555101051</v>
+        <v>926.6471649393848</v>
       </c>
       <c r="D16" t="n">
         <v>3.85963e-07</v>
@@ -2016,16 +1946,13 @@
         <v>-11364.99916730823</v>
       </c>
       <c r="Y16" t="n">
-        <v>3.087387867397427e-08</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1557.81152168727</v>
+        <v>56.85340367296322</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.000000000002781e-08</v>
+        <v>2.309782379898025e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.8315541560369971</v>
+        <v>0.899434368300055</v>
       </c>
     </row>
     <row r="17">
@@ -2036,7 +1963,7 @@
         <v>990.212</v>
       </c>
       <c r="C17" t="n">
-        <v>1405.532711646474</v>
+        <v>900.1234126772853</v>
       </c>
       <c r="D17" t="n">
         <v>3.87442e-07</v>
@@ -2069,16 +1996,13 @@
         <v>-10949.68281148155</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.798315625394458e-08</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1539.531680938524</v>
+        <v>74.9037927540376</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.000000000005385e-08</v>
+        <v>2.412409653499665e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.8319803920677162</v>
+        <v>0.9010560679063451</v>
       </c>
     </row>
     <row r="18">
@@ -2089,7 +2013,7 @@
         <v>979.1770000000001</v>
       </c>
       <c r="C18" t="n">
-        <v>1393.959875018377</v>
+        <v>889.3259989450008</v>
       </c>
       <c r="D18" t="n">
         <v>3.88796e-07</v>
@@ -2122,16 +2046,13 @@
         <v>-10281.77806303802</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.8818470196258528</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1639.648233897678</v>
+        <v>76.47884294596933</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.669899940135306e-08</v>
+        <v>2.312943951252964e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.79501592205168</v>
+        <v>0.9043394068968025</v>
       </c>
     </row>
     <row r="19">
@@ -2142,7 +2063,7 @@
         <v>966.704</v>
       </c>
       <c r="C19" t="n">
-        <v>1382.23737671459</v>
+        <v>2735.243727014276</v>
       </c>
       <c r="D19" t="n">
         <v>3.89977e-07</v>
@@ -2175,10 +2096,7 @@
         <v>-9629.454571360633</v>
       </c>
       <c r="Y19" t="n">
-        <v>3.086157898744619e-13</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1503.412154771458</v>
+        <v>-1272.884396785436</v>
       </c>
       <c r="AA19" t="n">
         <v>1e-08</v>
@@ -2195,7 +2113,7 @@
         <v>944.8869999999999</v>
       </c>
       <c r="C20" t="n">
-        <v>1360.679640580912</v>
+        <v>2541.172975196666</v>
       </c>
       <c r="D20" t="n">
         <v>3.91183e-07</v>
@@ -2228,10 +2146,7 @@
         <v>-8927.526278065347</v>
       </c>
       <c r="Y20" t="n">
-        <v>3.316908048150845e-10</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1485.335957251127</v>
+        <v>-1096.409019284516</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000003e-08</v>
@@ -2248,7 +2163,7 @@
         <v>932.79</v>
       </c>
       <c r="C21" t="n">
-        <v>1345.637757482641</v>
+        <v>873.5966514368132</v>
       </c>
       <c r="D21" t="n">
         <v>3.92731e-07</v>
@@ -2281,16 +2196,13 @@
         <v>-8109.955938307442</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.183882676503599e-09</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1466.963421712221</v>
+        <v>69.52079329611936</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.000000000001101e-08</v>
+        <v>2.566924837672894e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.833754606305494</v>
+        <v>0.8981418989396236</v>
       </c>
     </row>
     <row r="22">
@@ -2301,7 +2213,7 @@
         <v>922.5360000000001</v>
       </c>
       <c r="C22" t="n">
-        <v>1334.625936410205</v>
+        <v>861.5954788353714</v>
       </c>
       <c r="D22" t="n">
         <v>3.93865e-07</v>
@@ -2334,16 +2246,13 @@
         <v>-7160.385382407118</v>
       </c>
       <c r="Y22" t="n">
-        <v>5.190226086266899e-10</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1448.996689381289</v>
+        <v>70.24980602967948</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.000000000000021e-08</v>
+        <v>2.394387285234654e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.8342102281061093</v>
+        <v>0.9015548603264887</v>
       </c>
     </row>
   </sheetData>
@@ -2500,7 +2409,7 @@
         <v>1723.042</v>
       </c>
       <c r="C2" t="n">
-        <v>2094.534712989729</v>
+        <v>12869.80742950002</v>
       </c>
       <c r="D2" t="n">
         <v>3.42798e-07</v>
@@ -2533,10 +2442,7 @@
         <v>-26214.44258555676</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.541298658147226e-09</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2379.358443471029</v>
+        <v>-10537.44998115703</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000003183e-08</v>
@@ -2553,7 +2459,7 @@
         <v>1630.375</v>
       </c>
       <c r="C3" t="n">
-        <v>1992.451850867281</v>
+        <v>14272.07690254696</v>
       </c>
       <c r="D3" t="n">
         <v>3.54276e-07</v>
@@ -2586,10 +2492,7 @@
         <v>-24758.82138059601</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.812023470129079e-11</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2298.686712933061</v>
+        <v>-12052.36158618802</v>
       </c>
       <c r="AA3" t="n">
         <v>1e-08</v>
@@ -2606,7 +2509,7 @@
         <v>1602.884</v>
       </c>
       <c r="C4" t="n">
-        <v>1962.484897894658</v>
+        <v>12631.82361570787</v>
       </c>
       <c r="D4" t="n">
         <v>3.57814e-07</v>
@@ -2639,10 +2542,7 @@
         <v>-24325.7259433379</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.808290655865747e-10</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2264.08941764979</v>
+        <v>-10430.95778445083</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000043e-08</v>
@@ -2659,7 +2559,7 @@
         <v>1584.398</v>
       </c>
       <c r="C5" t="n">
-        <v>1945.200645155621</v>
+        <v>13381.22048938438</v>
       </c>
       <c r="D5" t="n">
         <v>3.6039e-07</v>
@@ -2692,10 +2592,7 @@
         <v>-25977.77842972598</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.540732805980894e-10</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2236.62994468916</v>
+        <v>-11212.75840569265</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000001e-08</v>
@@ -2712,7 +2609,7 @@
         <v>1563.037</v>
       </c>
       <c r="C6" t="n">
-        <v>1922.682427035942</v>
+        <v>15598.95905162799</v>
       </c>
       <c r="D6" t="n">
         <v>3.63083e-07</v>
@@ -2745,10 +2642,7 @@
         <v>-25258.80810553961</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.227799825251502e-11</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2209.588793247175</v>
+        <v>-13473.0313724089</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000001834e-08</v>
@@ -2765,7 +2659,7 @@
         <v>1540.405</v>
       </c>
       <c r="C7" t="n">
-        <v>1900.4739349992</v>
+        <v>15740.82269675673</v>
       </c>
       <c r="D7" t="n">
         <v>3.65282e-07</v>
@@ -2798,10 +2692,7 @@
         <v>-23245.16000230626</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.800168648515154e-13</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2184.383669229311</v>
+        <v>-13637.89406401474</v>
       </c>
       <c r="AA7" t="n">
         <v>1e-08</v>
@@ -2818,7 +2709,7 @@
         <v>1527.777</v>
       </c>
       <c r="C8" t="n">
-        <v>1887.054747237192</v>
+        <v>13994.13526200676</v>
       </c>
       <c r="D8" t="n">
         <v>3.67409e-07</v>
@@ -2851,10 +2742,7 @@
         <v>-23804.86509309887</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.099531431124705e-10</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2161.343787670391</v>
+        <v>-11898.79893483955</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000081e-08</v>
@@ -2871,7 +2759,7 @@
         <v>1504.661</v>
       </c>
       <c r="C9" t="n">
-        <v>1867.22220442995</v>
+        <v>702.0557847026847</v>
       </c>
       <c r="D9" t="n">
         <v>3.69758e-07</v>
@@ -2904,16 +2792,13 @@
         <v>-21804.10890993775</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.046865820866358e-09</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2138.103073593617</v>
+        <v>449.4584181410891</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.000000000001189e-08</v>
+        <v>1.145754885882149e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8249583368294882</v>
+        <v>0.9921115347424388</v>
       </c>
     </row>
     <row r="10">
@@ -2924,7 +2809,7 @@
         <v>1487.335</v>
       </c>
       <c r="C10" t="n">
-        <v>1849.809382143937</v>
+        <v>14747.11536457412</v>
       </c>
       <c r="D10" t="n">
         <v>3.71604e-07</v>
@@ -2957,10 +2842,7 @@
         <v>-21190.06294064082</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.025590510433788e-10</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2115.760414333809</v>
+        <v>-12698.07640971625</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000001e-08</v>
@@ -2977,7 +2859,7 @@
         <v>1474.421</v>
       </c>
       <c r="C11" t="n">
-        <v>1833.594078761014</v>
+        <v>1186.909234801189</v>
       </c>
       <c r="D11" t="n">
         <v>3.73813e-07</v>
@@ -3010,16 +2892,13 @@
         <v>-22025.43501170534</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.196517491302546e-10</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2093.084988747466</v>
+        <v>5.636956091842487</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.000000000000001e-08</v>
+        <v>2.365863841805377e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8256951017135238</v>
+        <v>0.8853944985956463</v>
       </c>
     </row>
     <row r="12">
@@ -3030,7 +2909,7 @@
         <v>1459.115</v>
       </c>
       <c r="C12" t="n">
-        <v>1820.567636385785</v>
+        <v>1183.971793172768</v>
       </c>
       <c r="D12" t="n">
         <v>3.76013e-07</v>
@@ -3063,16 +2942,13 @@
         <v>-20698.13310447288</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.797252980949783e-10</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2071.993436691035</v>
+        <v>3.538588363979929</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.000000000000296e-08</v>
+        <v>2.539536119098589e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.8260742225357488</v>
+        <v>0.8811809317722449</v>
       </c>
     </row>
     <row r="13">
@@ -3083,7 +2959,7 @@
         <v>1444.263</v>
       </c>
       <c r="C13" t="n">
-        <v>1808.005014798475</v>
+        <v>13879.24858935119</v>
       </c>
       <c r="D13" t="n">
         <v>3.77787e-07</v>
@@ -3116,10 +2992,7 @@
         <v>-19445.36752758491</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.374504475335359e-10</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2051.959127575353</v>
+        <v>-11880.79986373651</v>
       </c>
       <c r="AA13" t="n">
         <v>1e-08</v>
@@ -3136,7 +3009,7 @@
         <v>1421.302</v>
       </c>
       <c r="C14" t="n">
-        <v>1787.808088355597</v>
+        <v>14107.61117113743</v>
       </c>
       <c r="D14" t="n">
         <v>3.79782e-07</v>
@@ -3169,10 +3042,7 @@
         <v>-18845.87304426603</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.614136944123934e-10</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2030.984346180971</v>
+        <v>-12130.09179742741</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000005e-08</v>
@@ -3189,7 +3059,7 @@
         <v>1410.956</v>
       </c>
       <c r="C15" t="n">
-        <v>1774.806189642046</v>
+        <v>14138.11695022208</v>
       </c>
       <c r="D15" t="n">
         <v>3.81492e-07</v>
@@ -3222,10 +3092,7 @@
         <v>-18479.29582233515</v>
       </c>
       <c r="Y15" t="n">
-        <v>3.227074115855774e-09</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2010.325514160533</v>
+        <v>-12178.2360158983</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000000436e-08</v>
@@ -3242,7 +3109,7 @@
         <v>1388.711</v>
       </c>
       <c r="C16" t="n">
-        <v>1755.640584499156</v>
+        <v>14543.32964399587</v>
       </c>
       <c r="D16" t="n">
         <v>3.83809e-07</v>
@@ -3275,10 +3142,7 @@
         <v>-16080.87588875104</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.543672370184439e-10</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1988.750459253557</v>
+        <v>-12607.48488466543</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000000143e-08</v>
@@ -3295,7 +3159,7 @@
         <v>1374.654</v>
       </c>
       <c r="C17" t="n">
-        <v>1739.37196557861</v>
+        <v>550.9771256336103</v>
       </c>
       <c r="D17" t="n">
         <v>3.85732e-07</v>
@@ -3328,16 +3192,13 @@
         <v>-15817.82457141673</v>
       </c>
       <c r="Y17" t="n">
-        <v>8.487538027545064e-12</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1968.855056994121</v>
+        <v>536.2909053170177</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.000000000000003e-08</v>
+        <v>1.845075415698149e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.8281011956147474</v>
+        <v>0.990100881368786</v>
       </c>
     </row>
     <row r="18">
@@ -3348,7 +3209,7 @@
         <v>1359.802</v>
       </c>
       <c r="C18" t="n">
-        <v>1726.802778376697</v>
+        <v>13737.65430935425</v>
       </c>
       <c r="D18" t="n">
         <v>3.87449e-07</v>
@@ -3381,10 +3242,7 @@
         <v>-13761.67120707656</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.91260812370299e-08</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1951.54936457166</v>
+        <v>-11828.70151119797</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000000507e-08</v>
@@ -3401,7 +3259,7 @@
         <v>1348.519</v>
       </c>
       <c r="C19" t="n">
-        <v>1713.902298346405</v>
+        <v>14076.58746654036</v>
       </c>
       <c r="D19" t="n">
         <v>3.89213e-07</v>
@@ -3434,10 +3292,7 @@
         <v>-13120.67620608886</v>
       </c>
       <c r="Y19" t="n">
-        <v>8.548719048641945e-09</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1932.428859428727</v>
+        <v>-12188.13532601613</v>
       </c>
       <c r="AA19" t="n">
         <v>1.00000000000151e-08</v>
@@ -3454,7 +3309,7 @@
         <v>1326.99</v>
       </c>
       <c r="C20" t="n">
-        <v>1697.740888694918</v>
+        <v>549.467754992781</v>
       </c>
       <c r="D20" t="n">
         <v>3.90892e-07</v>
@@ -3487,16 +3342,13 @@
         <v>-12929.07100717827</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.025638953728457e-08</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1914.083541807276</v>
+        <v>533.6201497289497</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.000000000000195e-08</v>
+        <v>2.065919882224198e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.8294069796176506</v>
+        <v>0.9819118353121626</v>
       </c>
     </row>
     <row r="21">
@@ -3507,7 +3359,7 @@
         <v>1313.218</v>
       </c>
       <c r="C21" t="n">
-        <v>1681.075913893635</v>
+        <v>548.5259037267442</v>
       </c>
       <c r="D21" t="n">
         <v>3.92624e-07</v>
@@ -3540,16 +3392,13 @@
         <v>-11470.57186577493</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.752050007909983e-08</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1895.709493056404</v>
+        <v>514.4281827006686</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.000000000000456e-08</v>
+        <v>1.837908019610132e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.829831926004313</v>
+        <v>0.9895306829696342</v>
       </c>
     </row>
     <row r="22">
@@ -3560,7 +3409,7 @@
         <v>1303.231</v>
       </c>
       <c r="C22" t="n">
-        <v>1669.245099415437</v>
+        <v>544.8624189438492</v>
       </c>
       <c r="D22" t="n">
         <v>3.94348e-07</v>
@@ -3593,16 +3442,13 @@
         <v>-10139.89883350505</v>
       </c>
       <c r="Y22" t="n">
-        <v>5.821268237732372e-09</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1878.08991469867</v>
+        <v>509.1484949518529</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.000000000000031e-08</v>
+        <v>1.710717408491257e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.8302774363535452</v>
+        <v>0.9908388858677301</v>
       </c>
     </row>
   </sheetData>
@@ -3759,7 +3605,7 @@
         <v>1799.67</v>
       </c>
       <c r="C2" t="n">
-        <v>2147.285807801437</v>
+        <v>10612.4879358509</v>
       </c>
       <c r="D2" t="n">
         <v>3.26362e-07</v>
@@ -3792,10 +3638,7 @@
         <v>-17035.16492583882</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.43552925947184e-09</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2414.184672349003</v>
+        <v>-8140.970060020469</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000019e-08</v>
@@ -3812,7 +3655,7 @@
         <v>1651.82</v>
       </c>
       <c r="C3" t="n">
-        <v>1975.397389433182</v>
+        <v>12226.08253015791</v>
       </c>
       <c r="D3" t="n">
         <v>3.50995e-07</v>
@@ -3845,10 +3688,7 @@
         <v>-19903.46052767711</v>
       </c>
       <c r="Y3" t="n">
-        <v>9.229892964243688e-10</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2269.65944353937</v>
+        <v>-9958.98459192603</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000001121e-08</v>
@@ -3865,7 +3705,7 @@
         <v>1596.015</v>
       </c>
       <c r="C4" t="n">
-        <v>1926.838235194174</v>
+        <v>12367.85700210333</v>
       </c>
       <c r="D4" t="n">
         <v>3.5845e-07</v>
@@ -3898,10 +3738,7 @@
         <v>-20017.32349947653</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.958771555508287e-09</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2220.428780864845</v>
+        <v>-10160.78749969416</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000001104e-08</v>
@@ -3918,7 +3755,7 @@
         <v>1579</v>
       </c>
       <c r="C5" t="n">
-        <v>1904.022547217711</v>
+        <v>12528.67233455231</v>
       </c>
       <c r="D5" t="n">
         <v>3.62271e-07</v>
@@ -3951,10 +3788,7 @@
         <v>-22291.09534960582</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.072475311902202e-10</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2190.12682626144</v>
+        <v>-10354.78380099854</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000001934e-08</v>
@@ -3971,7 +3805,7 @@
         <v>1557.156</v>
       </c>
       <c r="C6" t="n">
-        <v>1881.769254769199</v>
+        <v>12837.68157580996</v>
       </c>
       <c r="D6" t="n">
         <v>3.65422e-07</v>
@@ -4004,10 +3838,7 @@
         <v>-22726.89571323263</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.243939984793676e-12</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2161.898799835519</v>
+        <v>-10693.6078107268</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000042e-08</v>
@@ -4024,7 +3855,7 @@
         <v>1527.902</v>
       </c>
       <c r="C7" t="n">
-        <v>1858.17083633283</v>
+        <v>13853.32289683177</v>
       </c>
       <c r="D7" t="n">
         <v>3.68586e-07</v>
@@ -4057,10 +3888,7 @@
         <v>-21966.10306427179</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.783910471788046e-10</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2134.599167013088</v>
+        <v>-11744.18404673886</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000097e-08</v>
@@ -4077,7 +3905,7 @@
         <v>1510.324</v>
       </c>
       <c r="C8" t="n">
-        <v>1841.912975942348</v>
+        <v>13584.3590268569</v>
       </c>
       <c r="D8" t="n">
         <v>3.71476e-07</v>
@@ -4110,10 +3938,7 @@
         <v>-23546.80736587457</v>
       </c>
       <c r="Y8" t="n">
-        <v>8.963737035817436e-11</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2108.106949011164</v>
+        <v>-11497.93338369478</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000196e-08</v>
@@ -4130,7 +3955,7 @@
         <v>1487.341</v>
       </c>
       <c r="C9" t="n">
-        <v>1820.229816884357</v>
+        <v>13708.9722290201</v>
       </c>
       <c r="D9" t="n">
         <v>3.74348e-07</v>
@@ -4163,10 +3988,7 @@
         <v>-22713.01822669869</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.981859031213007e-10</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2082.409191383807</v>
+        <v>-11647.10761644751</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000013e-08</v>
@@ -4183,7 +4005,7 @@
         <v>1474.733</v>
       </c>
       <c r="C10" t="n">
-        <v>1802.781229795612</v>
+        <v>14045.83623210755</v>
       </c>
       <c r="D10" t="n">
         <v>3.77123e-07</v>
@@ -4216,10 +4038,7 @@
         <v>-24584.77447526265</v>
       </c>
       <c r="Y10" t="n">
-        <v>5.474393743273697e-09</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2058.209139504361</v>
+        <v>-12010.52797097124</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000467e-08</v>
@@ -4236,7 +4055,7 @@
         <v>1457.247</v>
       </c>
       <c r="C11" t="n">
-        <v>1785.688415451813</v>
+        <v>14093.86282982815</v>
       </c>
       <c r="D11" t="n">
         <v>3.7933e-07</v>
@@ -4269,10 +4088,7 @@
         <v>-24296.18936322996</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.011318450530509e-10</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2034.459712771494</v>
+        <v>-12078.07215142767</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000037e-08</v>
@@ -4435,7 +4251,7 @@
         <v>1097.688</v>
       </c>
       <c r="C2" t="n">
-        <v>1523.270593476137</v>
+        <v>7972.64172056715</v>
       </c>
       <c r="D2" t="n">
         <v>4.23414e-07</v>
@@ -4468,10 +4284,7 @@
         <v>-14794.51045243109</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.195289892865387e-12</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1628.089489807075</v>
+        <v>-6170.543867500534</v>
       </c>
       <c r="AA2" t="n">
         <v>1e-08</v>
@@ -4488,7 +4301,7 @@
         <v>1022.422</v>
       </c>
       <c r="C3" t="n">
-        <v>1430.556168926691</v>
+        <v>8678.183004822797</v>
       </c>
       <c r="D3" t="n">
         <v>4.3275e-07</v>
@@ -4521,10 +4334,7 @@
         <v>-15334.95902045895</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.365301058043345e-11</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1566.524190175706</v>
+        <v>-6975.648782019831</v>
       </c>
       <c r="AA3" t="n">
         <v>1e-08</v>
@@ -4541,7 +4351,7 @@
         <v>995.0419999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>1398.245285654846</v>
+        <v>8665.804038409187</v>
       </c>
       <c r="D4" t="n">
         <v>4.35951e-07</v>
@@ -4574,10 +4384,7 @@
         <v>-15152.5633894038</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.535576153115226e-09</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1536.346467996142</v>
+        <v>-6996.951955180723</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000383e-08</v>
@@ -4594,7 +4401,7 @@
         <v>972.7489999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>1376.137489740064</v>
+        <v>8817.412816779011</v>
       </c>
       <c r="D5" t="n">
         <v>4.38116e-07</v>
@@ -4627,10 +4434,7 @@
         <v>-15206.82816016236</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.434136425764144e-13</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1507.939512535982</v>
+        <v>-7177.327405388364</v>
       </c>
       <c r="AA5" t="n">
         <v>1e-08</v>
@@ -4647,7 +4451,7 @@
         <v>953.058</v>
       </c>
       <c r="C6" t="n">
-        <v>1358.440868475107</v>
+        <v>8919.338374374254</v>
       </c>
       <c r="D6" t="n">
         <v>4.40232e-07</v>
@@ -4680,10 +4484,7 @@
         <v>-16132.01103357115</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.277163233124847e-09</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1481.633125818683</v>
+        <v>-7305.422243473682</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000002174e-08</v>
@@ -4700,7 +4501,7 @@
         <v>937.2249999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>1340.204541359324</v>
+        <v>9503.439099854586</v>
       </c>
       <c r="D7" t="n">
         <v>4.42322e-07</v>
@@ -4733,10 +4534,7 @@
         <v>-16828.88792932818</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.443577533704001e-08</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1459.276569040487</v>
+        <v>-7921.780518790572</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000001083e-08</v>
@@ -4753,7 +4551,7 @@
         <v>917.6209999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>1321.502497689098</v>
+        <v>9289.319121085295</v>
       </c>
       <c r="D8" t="n">
         <v>4.44305e-07</v>
@@ -4786,10 +4584,7 @@
         <v>-15859.37896803688</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.650962941173963e-10</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1438.460456695073</v>
+        <v>-7723.109121222881</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000239e-08</v>
@@ -4806,7 +4601,7 @@
         <v>903.425</v>
       </c>
       <c r="C9" t="n">
-        <v>1285.113884230718</v>
+        <v>9127.499026239509</v>
       </c>
       <c r="D9" t="n">
         <v>4.45998e-07</v>
@@ -4839,10 +4634,7 @@
         <v>-15374.36538035429</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.625280022033863e-08</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1413.222041036442</v>
+        <v>-7576.028558740737</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000001981e-08</v>
@@ -4859,7 +4651,7 @@
         <v>869.933</v>
       </c>
       <c r="C10" t="n">
-        <v>1265.622653800745</v>
+        <v>9724.631355215935</v>
       </c>
       <c r="D10" t="n">
         <v>4.50525e-07</v>
@@ -4892,10 +4684,7 @@
         <v>-15795.45562874301</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.362036821396672e-08</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1372.236703505263</v>
+        <v>-8224.702733439888</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000002207e-08</v>
@@ -4912,7 +4701,7 @@
         <v>850.2719999999999</v>
       </c>
       <c r="C11" t="n">
-        <v>1246.823010844561</v>
+        <v>9514.756700890215</v>
       </c>
       <c r="D11" t="n">
         <v>4.52218e-07</v>
@@ -4945,10 +4734,7 @@
         <v>-14297.14802215251</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.397444398910247e-10</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1354.01641079458</v>
+        <v>-8027.540247250638</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000186e-08</v>
@@ -4965,7 +4751,7 @@
         <v>836.0520000000001</v>
       </c>
       <c r="C12" t="n">
-        <v>1231.539165158899</v>
+        <v>9402.004724499035</v>
       </c>
       <c r="D12" t="n">
         <v>4.53792e-07</v>
@@ -4998,10 +4784,7 @@
         <v>-14220.3889639639</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.646039073902291</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1374.412059626735</v>
+        <v>-7928.497477108938</v>
       </c>
       <c r="AA12" t="n">
         <v>1.11296106566074e-08</v>
@@ -5018,7 +4801,7 @@
         <v>825.3199999999999</v>
       </c>
       <c r="C13" t="n">
-        <v>1217.824533050761</v>
+        <v>781.0427386656635</v>
       </c>
       <c r="D13" t="n">
         <v>4.55112e-07</v>
@@ -5051,16 +4834,13 @@
         <v>-14372.85713044984</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.044162985223539e-08</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1319.653545226634</v>
+        <v>85.7719635671917</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.00000000000037e-08</v>
+        <v>2.690184298522866e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.8383400912304341</v>
+        <v>0.901992311262204</v>
       </c>
     </row>
     <row r="14">
@@ -5071,7 +4851,7 @@
         <v>815.347</v>
       </c>
       <c r="C14" t="n">
-        <v>1205.432775690289</v>
+        <v>777.5714512425378</v>
       </c>
       <c r="D14" t="n">
         <v>4.56581e-07</v>
@@ -5104,16 +4884,13 @@
         <v>-14752.00982808087</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.955972353526669e-09</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1303.037974414169</v>
+        <v>81.83159636218082</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.000000000000008e-08</v>
+        <v>2.728266812858015e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.8388012164334024</v>
+        <v>0.9016270970989637</v>
       </c>
     </row>
     <row r="15">
@@ -5124,7 +4901,7 @@
         <v>803.2450000000001</v>
       </c>
       <c r="C15" t="n">
-        <v>1189.515827218494</v>
+        <v>773.1987644889214</v>
       </c>
       <c r="D15" t="n">
         <v>4.58282e-07</v>
@@ -5157,16 +4934,13 @@
         <v>-14282.7519702549</v>
       </c>
       <c r="Y15" t="n">
-        <v>6.946933965987063e-09</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1286.607047277894</v>
+        <v>78.63686674050332</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.000000000000044e-08</v>
+        <v>2.773295451314589e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.8393101945971007</v>
+        <v>0.9012690421086761</v>
       </c>
     </row>
     <row r="16">
@@ -5177,7 +4951,7 @@
         <v>789.414</v>
       </c>
       <c r="C16" t="n">
-        <v>1175.355302685921</v>
+        <v>763.7455521523082</v>
       </c>
       <c r="D16" t="n">
         <v>4.59592e-07</v>
@@ -5210,16 +4984,13 @@
         <v>-14163.21347150649</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.317777510507496e-12</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1270.552012661203</v>
+        <v>80.55388922225154</v>
       </c>
       <c r="AA16" t="n">
-        <v>1e-08</v>
+        <v>2.920438266562302e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.8397868574760489</v>
+        <v>0.8980775972435887</v>
       </c>
     </row>
     <row r="17">
@@ -5230,7 +5001,7 @@
         <v>772.1279999999999</v>
       </c>
       <c r="C17" t="n">
-        <v>1158.208669292641</v>
+        <v>772.1279999999999</v>
       </c>
       <c r="D17" t="n">
         <v>4.61087e-07</v>
@@ -5262,11 +5033,10 @@
       <c r="X17" t="n">
         <v>-12979.62958242628</v>
       </c>
-      <c r="Y17" t="n">
-        <v>3.773369718771121e-11</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1254.713551795002</v>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA17" t="n">
         <v>1e-08</v>
@@ -5283,7 +5053,7 @@
         <v>771.028</v>
       </c>
       <c r="C18" t="n">
-        <v>1154.607872273115</v>
+        <v>823.5795486867321</v>
       </c>
       <c r="D18" t="n">
         <v>4.62663e-07</v>
@@ -5316,16 +5086,13 @@
         <v>-15118.41544456057</v>
       </c>
       <c r="Y18" t="n">
-        <v>6.718298736843242e-09</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1238.755925526981</v>
+        <v>11.73327881081974</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.000000000000173e-08</v>
+        <v>3.164515897137034e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.8407914392213998</v>
+        <v>0.8820146434796517</v>
       </c>
     </row>
     <row r="19">
@@ -5336,7 +5103,7 @@
         <v>759.961</v>
       </c>
       <c r="C19" t="n">
-        <v>1138.080696627848</v>
+        <v>786.0247606595846</v>
       </c>
       <c r="D19" t="n">
         <v>4.64176e-07</v>
@@ -5369,16 +5136,13 @@
         <v>-14985.98171521551</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.396165538541654e-08</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1223.036752604663</v>
+        <v>35.79875440499733</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.00000000000009e-08</v>
+        <v>2.942162515480501e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.8412945433784456</v>
+        <v>0.8896750528501884</v>
       </c>
     </row>
     <row r="20">
@@ -5389,7 +5153,7 @@
         <v>741.038</v>
       </c>
       <c r="C20" t="n">
-        <v>1120.827389988081</v>
+        <v>823.1776091038588</v>
       </c>
       <c r="D20" t="n">
         <v>4.65548e-07</v>
@@ -5422,16 +5186,13 @@
         <v>-13152.69576382672</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.631463280094322e-10</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1207.145201132615</v>
+        <v>2.894934376799968</v>
       </c>
       <c r="AA20" t="n">
-        <v>1e-08</v>
+        <v>3.439685280116165e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.8418198223054431</v>
+        <v>0.8763585161717188</v>
       </c>
     </row>
     <row r="21">
@@ -5442,7 +5203,7 @@
         <v>730.3839999999999</v>
       </c>
       <c r="C21" t="n">
-        <v>1109.715556344335</v>
+        <v>812.4904304540778</v>
       </c>
       <c r="D21" t="n">
         <v>4.66994e-07</v>
@@ -5475,16 +5236,13 @@
         <v>-13556.25032917496</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.07358855129548e-11</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1191.151566546085</v>
+        <v>3.029828155550603</v>
       </c>
       <c r="AA21" t="n">
-        <v>1e-08</v>
+        <v>3.653357508622406e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.842349213806347</v>
+        <v>0.8713160627692039</v>
       </c>
     </row>
     <row r="22">
@@ -5495,7 +5253,7 @@
         <v>721.009</v>
       </c>
       <c r="C22" t="n">
-        <v>1093.464197620228</v>
+        <v>798.742829116511</v>
       </c>
       <c r="D22" t="n">
         <v>4.68552e-07</v>
@@ -5528,16 +5286,13 @@
         <v>-13463.88744921737</v>
       </c>
       <c r="Y22" t="n">
-        <v>9.705506530223433e-12</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1175.537807625076</v>
+        <v>7.532495860784441</v>
       </c>
       <c r="AA22" t="n">
-        <v>1e-08</v>
+        <v>3.522538321476825e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.842883274437631</v>
+        <v>0.8757745657796111</v>
       </c>
     </row>
   </sheetData>
@@ -5694,7 +5449,7 @@
         <v>1103.268</v>
       </c>
       <c r="C2" t="n">
-        <v>1502.779276547776</v>
+        <v>7780.03199151676</v>
       </c>
       <c r="D2" t="n">
         <v>4.24516e-07</v>
@@ -5727,10 +5482,7 @@
         <v>-12557.0569811854</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.857120419133815e-10</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1643.215844494769</v>
+        <v>-5962.399296223821</v>
       </c>
       <c r="AA2" t="n">
         <v>1e-08</v>
@@ -5747,7 +5499,7 @@
         <v>1060.644</v>
       </c>
       <c r="C3" t="n">
-        <v>1450.018808845394</v>
+        <v>7955.019574358761</v>
       </c>
       <c r="D3" t="n">
         <v>4.3251e-07</v>
@@ -5780,10 +5532,7 @@
         <v>-14015.6778187673</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.578574811151836e-12</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1598.382999802017</v>
+        <v>-6202.42642439019</v>
       </c>
       <c r="AA3" t="n">
         <v>1e-08</v>
@@ -5800,7 +5549,7 @@
         <v>1033.375</v>
       </c>
       <c r="C4" t="n">
-        <v>1423.464630649422</v>
+        <v>8205.355171440331</v>
       </c>
       <c r="D4" t="n">
         <v>4.35569e-07</v>
@@ -5833,10 +5582,7 @@
         <v>-14183.87339017491</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.569572412145782e-11</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1570.636705029124</v>
+        <v>-6488.504633804387</v>
       </c>
       <c r="AA4" t="n">
         <v>1e-08</v>
@@ -5853,7 +5599,7 @@
         <v>1009.235</v>
       </c>
       <c r="C5" t="n">
-        <v>1402.918049986543</v>
+        <v>8119.375801209856</v>
       </c>
       <c r="D5" t="n">
         <v>4.3794e-07</v>
@@ -5886,10 +5632,7 @@
         <v>-14387.35384990727</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.241585259746103e-12</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1544.736492937587</v>
+        <v>-6425.252352894384</v>
       </c>
       <c r="AA5" t="n">
         <v>1e-08</v>
@@ -5906,7 +5649,7 @@
         <v>987.1590000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>1377.575235031508</v>
+        <v>8114.082656299215</v>
       </c>
       <c r="D6" t="n">
         <v>4.40335e-07</v>
@@ -5939,10 +5682,7 @@
         <v>-14038.85517380458</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.750223480252316e-11</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1518.661451730663</v>
+        <v>-6442.902786142334</v>
       </c>
       <c r="AA6" t="n">
         <v>1e-08</v>
@@ -5959,7 +5699,7 @@
         <v>971.6859999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>1363.630012511125</v>
+        <v>8628.147451069326</v>
       </c>
       <c r="D7" t="n">
         <v>4.44043e-07</v>
@@ -5992,10 +5732,7 @@
         <v>-16069.93145612055</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.996394218619561e-09</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1489.075362164951</v>
+        <v>-6997.280054321456</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000147e-08</v>
@@ -6012,7 +5749,7 @@
         <v>942.199</v>
       </c>
       <c r="C8" t="n">
-        <v>1351.233919406838</v>
+        <v>8597.963988961346</v>
       </c>
       <c r="D8" t="n">
         <v>4.46692e-07</v>
@@ -6045,10 +5782,7 @@
         <v>-14829.49186189311</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.202655218792861e-10</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1464.84296172248</v>
+        <v>-6989.623997646881</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000054e-08</v>
@@ -6065,7 +5799,7 @@
         <v>923.4749999999999</v>
       </c>
       <c r="C9" t="n">
-        <v>1320.093377382473</v>
+        <v>8488.054012640825</v>
       </c>
       <c r="D9" t="n">
         <v>4.49304e-07</v>
@@ -6098,10 +5832,7 @@
         <v>-14851.65772171988</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.533504427906842e-10</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1441.857485825023</v>
+        <v>-6899.409278840539</v>
       </c>
       <c r="AA9" t="n">
         <v>1e-08</v>
@@ -6118,7 +5849,7 @@
         <v>905.785</v>
       </c>
       <c r="C10" t="n">
-        <v>1301.633756100767</v>
+        <v>8586.435248281012</v>
       </c>
       <c r="D10" t="n">
         <v>4.5171e-07</v>
@@ -6151,10 +5882,7 @@
         <v>-14844.99680820529</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.344228692442649e-09</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1419.028734077478</v>
+        <v>-7020.568347506062</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000001497e-08</v>
@@ -6171,7 +5899,7 @@
         <v>884.502</v>
       </c>
       <c r="C11" t="n">
-        <v>1281.948187934509</v>
+        <v>8743.282853476869</v>
       </c>
       <c r="D11" t="n">
         <v>4.54192e-07</v>
@@ -6204,10 +5932,7 @@
         <v>-14297.77010131324</v>
       </c>
       <c r="Y11" t="n">
-        <v>8.206331235602397e-10</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1396.888355884578</v>
+        <v>-7201.444473833661</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000713e-08</v>
@@ -6370,7 +6095,7 @@
         <v>1030.872</v>
       </c>
       <c r="C2" t="n">
-        <v>1507.215422820027</v>
+        <v>8083.331527191399</v>
       </c>
       <c r="D2" t="n">
         <v>4.37132e-07</v>
@@ -6403,10 +6128,7 @@
         <v>-15220.49099597104</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.720515138620531e-10</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1561.134085333618</v>
+        <v>-6367.642151548744</v>
       </c>
       <c r="AA2" t="n">
         <v>1e-08</v>
@@ -6423,7 +6145,7 @@
         <v>1006.711</v>
       </c>
       <c r="C3" t="n">
-        <v>1408.661345283361</v>
+        <v>8413.714707592158</v>
       </c>
       <c r="D3" t="n">
         <v>4.39257e-07</v>
@@ -6456,10 +6178,7 @@
         <v>-15759.77187096125</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.405020186175405e-11</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1551.139027118607</v>
+        <v>-6737.089025940097</v>
       </c>
       <c r="AA3" t="n">
         <v>1e-08</v>
@@ -6476,7 +6195,7 @@
         <v>976.9299999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>1385.183531593908</v>
+        <v>8847.557045087671</v>
       </c>
       <c r="D4" t="n">
         <v>4.42755e-07</v>
@@ -6509,10 +6228,7 @@
         <v>-15743.34464358955</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.849068832980438e-12</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1518.087734658738</v>
+        <v>-7214.314561198685</v>
       </c>
       <c r="AA4" t="n">
         <v>1e-08</v>
@@ -6529,7 +6245,7 @@
         <v>961.5530000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>1396.011596236439</v>
+        <v>8799.956686001628</v>
       </c>
       <c r="D5" t="n">
         <v>4.44808e-07</v>
@@ -6562,10 +6278,7 @@
         <v>-16705.190842766</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.972725382163073e-08</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1475.56739157723</v>
+        <v>-7187.541287650714</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000082e-08</v>
@@ -6582,7 +6295,7 @@
         <v>924.0379999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>1329.448200224221</v>
+        <v>9053.119067149444</v>
       </c>
       <c r="D6" t="n">
         <v>4.49283e-07</v>
@@ -6615,10 +6328,7 @@
         <v>-15810.28106044284</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.432665748083905e-08</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1448.98698330561</v>
+        <v>-7484.347453441758</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000002293e-08</v>
@@ -6635,7 +6345,7 @@
         <v>900.8800000000001</v>
       </c>
       <c r="C7" t="n">
-        <v>1309.863724958478</v>
+        <v>8705.529616483916</v>
       </c>
       <c r="D7" t="n">
         <v>4.51206e-07</v>
@@ -6668,10 +6378,7 @@
         <v>-14598.38951733558</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.669064314104212e-10</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1427.972103037568</v>
+        <v>-7147.48189853769</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000391e-08</v>
@@ -6688,7 +6395,7 @@
         <v>884.3800000000001</v>
       </c>
       <c r="C8" t="n">
-        <v>1291.406171382699</v>
+        <v>8982.811668968658</v>
       </c>
       <c r="D8" t="n">
         <v>4.53291e-07</v>
@@ -6721,10 +6428,7 @@
         <v>-14273.13733194418</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.033836778576327e-10</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1407.744060034204</v>
+        <v>-7449.709075695032</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000033e-08</v>
@@ -6741,7 +6445,7 @@
         <v>873.403</v>
       </c>
       <c r="C9" t="n">
-        <v>1278.194412869387</v>
+        <v>873.403</v>
       </c>
       <c r="D9" t="n">
         <v>4.55235e-07</v>
@@ -6773,11 +6477,10 @@
       <c r="X9" t="n">
         <v>-14724.14165709195</v>
       </c>
-      <c r="Y9" t="n">
-        <v>9.654838727229941e-10</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1388.279453831081</v>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000043e-08</v>
@@ -6794,7 +6497,7 @@
         <v>858.8789999999999</v>
       </c>
       <c r="C10" t="n">
-        <v>1256.600404026334</v>
+        <v>825.9713359832623</v>
       </c>
       <c r="D10" t="n">
         <v>4.57109e-07</v>
@@ -6827,16 +6530,13 @@
         <v>-14923.19798881167</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.148303916280517e-14</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1369.4863788943</v>
+        <v>74.48390177047469</v>
       </c>
       <c r="AA10" t="n">
-        <v>1e-08</v>
+        <v>2.800136132186734e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8357672395960193</v>
+        <v>0.8958720947403104</v>
       </c>
     </row>
     <row r="11">
@@ -6847,7 +6547,7 @@
         <v>841.515</v>
       </c>
       <c r="C11" t="n">
-        <v>1242.971667753642</v>
+        <v>812.5450537176379</v>
       </c>
       <c r="D11" t="n">
         <v>4.59292e-07</v>
@@ -6880,16 +6580,13 @@
         <v>-14624.64625254544</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.927648706203283e-11</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1348.577299168596</v>
+        <v>78.02694983348364</v>
       </c>
       <c r="AA11" t="n">
-        <v>1e-08</v>
+        <v>2.927189651007752e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.836339673968898</v>
+        <v>0.8936255616921976</v>
       </c>
     </row>
     <row r="12">
@@ -6900,7 +6597,7 @@
         <v>830.0150000000001</v>
       </c>
       <c r="C12" t="n">
-        <v>1228.233549895886</v>
+        <v>806.9781859060406</v>
       </c>
       <c r="D12" t="n">
         <v>4.61286e-07</v>
@@ -6933,16 +6630,13 @@
         <v>-14455.31715333279</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.257795657508232e-08</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1329.114153146811</v>
+        <v>74.2232218991925</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.000000000000044e-08</v>
+        <v>2.98356605075556e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.8368885419044735</v>
+        <v>0.8924654392818593</v>
       </c>
     </row>
     <row r="13">
@@ -6953,7 +6647,7 @@
         <v>814.2909999999999</v>
       </c>
       <c r="C13" t="n">
-        <v>1213.866011765583</v>
+        <v>881.885569199306</v>
       </c>
       <c r="D13" t="n">
         <v>4.63177e-07</v>
@@ -6986,16 +6680,13 @@
         <v>-14379.48901530511</v>
       </c>
       <c r="Y13" t="n">
-        <v>3.881021092753764e-09</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1310.494918396676</v>
+        <v>0.6063717843562653</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.000000000000032e-08</v>
+        <v>3.610780907462872e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.8374412808543498</v>
+        <v>0.8663073915615941</v>
       </c>
     </row>
     <row r="14">
@@ -7006,7 +6697,7 @@
         <v>801.577</v>
       </c>
       <c r="C14" t="n">
-        <v>1195.827250747904</v>
+        <v>861.7947248186757</v>
       </c>
       <c r="D14" t="n">
         <v>4.64722e-07</v>
@@ -7039,16 +6730,13 @@
         <v>-13745.31108476702</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.975839838410178e-08</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1293.970002298678</v>
+        <v>10.4298854438024</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.000000000000244e-08</v>
+        <v>3.327412805977434e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.8379153493642926</v>
+        <v>0.8748320996894928</v>
       </c>
     </row>
     <row r="15">
@@ -7059,7 +6747,7 @@
         <v>789.8200000000001</v>
       </c>
       <c r="C15" t="n">
-        <v>1183.398634711001</v>
+        <v>858.6022200503701</v>
       </c>
       <c r="D15" t="n">
         <v>4.66419e-07</v>
@@ -7092,16 +6780,13 @@
         <v>-14063.41627469487</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.029298790741381e-12</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1277.592410583077</v>
+        <v>7.37885656781325</v>
       </c>
       <c r="AA15" t="n">
-        <v>1e-08</v>
+        <v>3.497872573769488e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.8384121433308739</v>
+        <v>0.8700127575060208</v>
       </c>
     </row>
     <row r="16">
@@ -7112,7 +6797,7 @@
         <v>779.105</v>
       </c>
       <c r="C16" t="n">
-        <v>1171.12945782568</v>
+        <v>848.2863383445941</v>
       </c>
       <c r="D16" t="n">
         <v>4.68247e-07</v>
@@ -7145,16 +6830,13 @@
         <v>-13981.30618522348</v>
       </c>
       <c r="Y16" t="n">
-        <v>4.162083300514258e-10</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1261.494779866881</v>
+        <v>6.907173086745002</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.000000000000015e-08</v>
+        <v>3.533519517370238e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.8389165976775568</v>
+        <v>0.8706679394434075</v>
       </c>
     </row>
     <row r="17">
@@ -7165,7 +6847,7 @@
         <v>767.2379999999999</v>
       </c>
       <c r="C17" t="n">
-        <v>1158.436186574346</v>
+        <v>839.935437138969</v>
       </c>
       <c r="D17" t="n">
         <v>4.69891e-07</v>
@@ -7198,16 +6880,13 @@
         <v>-13817.13317467756</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.684064584578977e-08</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1246.467035942742</v>
+        <v>7.435466512382845</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.000000000000001e-08</v>
+        <v>3.584347853638317e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.8393764144437562</v>
+        <v>0.8701890166474052</v>
       </c>
     </row>
     <row r="18">
@@ -7218,7 +6897,7 @@
         <v>754.0160000000001</v>
       </c>
       <c r="C18" t="n">
-        <v>1141.150140988081</v>
+        <v>813.7995993528853</v>
       </c>
       <c r="D18" t="n">
         <v>4.70976e-07</v>
@@ -7251,16 +6930,13 @@
         <v>-13435.46996480902</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.119223745646828e-08</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1231.861757013885</v>
+        <v>23.19922688414381</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.000000000000048e-08</v>
+        <v>3.418641107513763e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.8398377001424042</v>
+        <v>0.8771431145963593</v>
       </c>
     </row>
     <row r="19">
@@ -7271,7 +6947,7 @@
         <v>739.6190000000001</v>
       </c>
       <c r="C19" t="n">
-        <v>1127.370888081084</v>
+        <v>806.7762103629418</v>
       </c>
       <c r="D19" t="n">
         <v>4.72749e-07</v>
@@ -7304,16 +6980,13 @@
         <v>-12450.89787332109</v>
       </c>
       <c r="Y19" t="n">
-        <v>8.147913167944852e-09</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1215.763524037895</v>
+        <v>20.23754720620306</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.000000000000141e-08</v>
+        <v>3.158268975441655e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.8403785040264899</v>
+        <v>0.8836270787617484</v>
       </c>
     </row>
     <row r="20">
@@ -7324,7 +6997,7 @@
         <v>729.491</v>
       </c>
       <c r="C20" t="n">
-        <v>1108.440848540964</v>
+        <v>729.491</v>
       </c>
       <c r="D20" t="n">
         <v>4.7425e-07</v>
@@ -7356,11 +7029,10 @@
       <c r="X20" t="n">
         <v>-12505.15815299472</v>
       </c>
-      <c r="Y20" t="n">
-        <v>3.575284539399535e-08</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1190.827821894881</v>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000781e-08</v>
@@ -7377,7 +7049,7 @@
         <v>715.3940000000001</v>
       </c>
       <c r="C21" t="n">
-        <v>1075.965097882781</v>
+        <v>800.3046572440321</v>
       </c>
       <c r="D21" t="n">
         <v>4.76944e-07</v>
@@ -7410,16 +7082,13 @@
         <v>-13102.68398428272</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.091914501195043e-08</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1168.959373694144</v>
+        <v>1.704264675671798</v>
       </c>
       <c r="AA21" t="n">
-        <v>1e-08</v>
+        <v>3.366762714642678e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.8424216063489984</v>
+        <v>0.8760169443173123</v>
       </c>
     </row>
     <row r="22">
@@ -7430,7 +7099,7 @@
         <v>682.413</v>
       </c>
       <c r="C22" t="n">
-        <v>1054.336552539145</v>
+        <v>789.83987800077</v>
       </c>
       <c r="D22" t="n">
         <v>4.80279e-07</v>
@@ -7463,16 +7132,13 @@
         <v>-11653.612686609</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.694152859371714e-08</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1137.195400226974</v>
+        <v>3.186220336460718</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.000000000000003e-08</v>
+        <v>3.906915977150668e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.8433912690254576</v>
+        <v>0.8683342418114384</v>
       </c>
     </row>
   </sheetData>
@@ -7629,7 +7295,7 @@
         <v>1285.113</v>
       </c>
       <c r="C2" t="n">
-        <v>1746.288290084989</v>
+        <v>7012.812562368542</v>
       </c>
       <c r="D2" t="n">
         <v>3.91163e-07</v>
@@ -7662,10 +7328,7 @@
         <v>-13281.79072917973</v>
       </c>
       <c r="Y2" t="n">
-        <v>9.200561400212982e-09</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1830.049929466298</v>
+        <v>-4960.74289289407</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000006e-08</v>
@@ -7682,7 +7345,7 @@
         <v>1127.67</v>
       </c>
       <c r="C3" t="n">
-        <v>1542.132214923713</v>
+        <v>7863.973662711359</v>
       </c>
       <c r="D3" t="n">
         <v>4.20174e-07</v>
@@ -7715,10 +7378,7 @@
         <v>-15851.70328379813</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.065936168913495e-09</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1689.575864067239</v>
+        <v>-6025.777740008856</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000004021e-08</v>
@@ -7735,7 +7395,7 @@
         <v>1072.181</v>
       </c>
       <c r="C4" t="n">
-        <v>1484.611337762111</v>
+        <v>8055.001686266009</v>
       </c>
       <c r="D4" t="n">
         <v>4.27276e-07</v>
@@ -7768,10 +7428,7 @@
         <v>-15655.10664406893</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.86677482297048e-10</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1641.579977125335</v>
+        <v>-6278.567737146794</v>
       </c>
       <c r="AA4" t="n">
         <v>1e-08</v>
@@ -7788,7 +7445,7 @@
         <v>1038.584</v>
       </c>
       <c r="C5" t="n">
-        <v>1454.026771458737</v>
+        <v>7950.706719524713</v>
       </c>
       <c r="D5" t="n">
         <v>4.314e-07</v>
@@ -7821,10 +7478,7 @@
         <v>-15220.94529272925</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.561498959134325e-12</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1608.530501502305</v>
+        <v>-6206.948464235841</v>
       </c>
       <c r="AA5" t="n">
         <v>1e-08</v>
@@ -7841,7 +7495,7 @@
         <v>1011.139</v>
       </c>
       <c r="C6" t="n">
-        <v>1431.678880070765</v>
+        <v>8200.906231744941</v>
       </c>
       <c r="D6" t="n">
         <v>4.34637e-07</v>
@@ -7874,10 +7528,7 @@
         <v>-15517.04222311667</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.353083679553433e-11</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1578.911717433993</v>
+        <v>-6492.091491623785</v>
       </c>
       <c r="AA6" t="n">
         <v>1e-08</v>
@@ -7894,7 +7545,7 @@
         <v>988.9290000000001</v>
       </c>
       <c r="C7" t="n">
-        <v>1405.52891378237</v>
+        <v>8534.689920098344</v>
       </c>
       <c r="D7" t="n">
         <v>4.37929e-07</v>
@@ -7927,10 +7578,7 @@
         <v>-15534.4546766757</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.581603528249857e-09</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1550.379064830883</v>
+        <v>-6860.876774721608</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000048e-08</v>
@@ -7947,7 +7595,7 @@
         <v>967.7239999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>1387.247335842548</v>
+        <v>8540.760427409927</v>
       </c>
       <c r="D8" t="n">
         <v>4.41101e-07</v>
@@ -7980,10 +7628,7 @@
         <v>-15673.25322399462</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.857311217561788e-08</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1522.112183208116</v>
+        <v>-6893.264505851108</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000331e-08</v>
@@ -8000,7 +7645,7 @@
         <v>947.5649999999999</v>
       </c>
       <c r="C9" t="n">
-        <v>1369.530998141567</v>
+        <v>8637.066197955164</v>
       </c>
       <c r="D9" t="n">
         <v>4.44239e-07</v>
@@ -8033,10 +7678,7 @@
         <v>-16328.19756850009</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.978407653209302e-08</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1495.690982409313</v>
+        <v>-7016.820795038913</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000003297e-08</v>
@@ -8053,7 +7695,7 @@
         <v>917.337</v>
       </c>
       <c r="C10" t="n">
-        <v>1344.448213564349</v>
+        <v>870.4053468660322</v>
       </c>
       <c r="D10" t="n">
         <v>4.4712e-07</v>
@@ -8086,16 +7728,13 @@
         <v>-14216.45014198157</v>
       </c>
       <c r="Y10" t="n">
-        <v>8.491653452779986e-10</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1470.951771926578</v>
+        <v>91.25685968907226</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.000000000000552e-08</v>
+        <v>2.846421594116214e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8311487213264482</v>
+        <v>0.8906494703558865</v>
       </c>
     </row>
     <row r="11">
@@ -8106,7 +7745,7 @@
         <v>899.665</v>
       </c>
       <c r="C11" t="n">
-        <v>1327.25603136718</v>
+        <v>870.6693811882104</v>
       </c>
       <c r="D11" t="n">
         <v>4.49771e-07</v>
@@ -8139,16 +7778,13 @@
         <v>-14604.09283335973</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.621049876732005e-10</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1447.456958989253</v>
+        <v>80.36824036456105</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.000000000000025e-08</v>
+        <v>2.855014146559465e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8315389482098392</v>
+        <v>0.8868434711521324</v>
       </c>
     </row>
   </sheetData>
@@ -8305,7 +7941,7 @@
         <v>1025.941</v>
       </c>
       <c r="C2" t="n">
-        <v>1482.916591821896</v>
+        <v>7473.530381372105</v>
       </c>
       <c r="D2" t="n">
         <v>4.31391e-07</v>
@@ -8338,10 +7974,7 @@
         <v>-14025.88224767315</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.27196624550196e-11</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1578.690383320698</v>
+        <v>-5712.802630441682</v>
       </c>
       <c r="AA2" t="n">
         <v>1e-08</v>
@@ -8358,7 +7991,7 @@
         <v>958.264</v>
       </c>
       <c r="C3" t="n">
-        <v>1386.574651067633</v>
+        <v>8249.652363376092</v>
       </c>
       <c r="D3" t="n">
         <v>4.40301e-07</v>
@@ -8391,10 +8024,7 @@
         <v>-14704.94776391744</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.08838873926891e-12</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1517.532787080726</v>
+        <v>-6590.193464454948</v>
       </c>
       <c r="AA3" t="n">
         <v>1e-08</v>
@@ -8411,7 +8041,7 @@
         <v>939.049</v>
       </c>
       <c r="C4" t="n">
-        <v>1364.961173030417</v>
+        <v>8569.632209609326</v>
       </c>
       <c r="D4" t="n">
         <v>4.42917e-07</v>
@@ -8444,10 +8074,7 @@
         <v>-15295.2724659305</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.342138618469332e-10</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1493.052936686385</v>
+        <v>-6943.853237771757</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000031e-08</v>
@@ -8464,7 +8091,7 @@
         <v>921.4680000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>1349.457558432359</v>
+        <v>8739.731053769639</v>
       </c>
       <c r="D5" t="n">
         <v>4.4482e-07</v>
@@ -8497,10 +8124,7 @@
         <v>-15427.87373519644</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.862011069255058e-08</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1473.692805584746</v>
+        <v>-7136.210608627715</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000003143e-08</v>
@@ -8517,7 +8141,7 @@
         <v>905.664</v>
       </c>
       <c r="C6" t="n">
-        <v>1334.719866641705</v>
+        <v>8671.094498125718</v>
       </c>
       <c r="D6" t="n">
         <v>4.464e-07</v>
@@ -8550,10 +8174,7 @@
         <v>-15479.41308114051</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.888687977710606e-09</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1455.06074743676</v>
+        <v>-7082.835224094306</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000148e-08</v>
@@ -8570,7 +8191,7 @@
         <v>889.5640000000001</v>
       </c>
       <c r="C7" t="n">
-        <v>1318.262209091663</v>
+        <v>8926.265355059668</v>
       </c>
       <c r="D7" t="n">
         <v>4.48057e-07</v>
@@ -8603,10 +8224,7 @@
         <v>-14655.40463624706</v>
       </c>
       <c r="Y7" t="n">
-        <v>7.729415954565923e-11</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1437.008184830983</v>
+        <v>-7359.299623065686</v>
       </c>
       <c r="AA7" t="n">
         <v>1e-08</v>
@@ -8623,7 +8241,7 @@
         <v>880.3820000000001</v>
       </c>
       <c r="C8" t="n">
-        <v>1308.658129521323</v>
+        <v>9112.118580385935</v>
       </c>
       <c r="D8" t="n">
         <v>4.49997e-07</v>
@@ -8656,10 +8274,7 @@
         <v>-16151.19265390456</v>
       </c>
       <c r="Y8" t="n">
-        <v>8.419406680258176e-14</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1419.177120355056</v>
+        <v>-7565.846542844743</v>
       </c>
       <c r="AA8" t="n">
         <v>1e-08</v>
@@ -8676,7 +8291,7 @@
         <v>861.3890000000001</v>
       </c>
       <c r="C9" t="n">
-        <v>1288.547915456701</v>
+        <v>8958.15851542227</v>
       </c>
       <c r="D9" t="n">
         <v>4.51829e-07</v>
@@ -8709,10 +8324,7 @@
         <v>-14092.42771567705</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.525030701132558e-11</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1401.265498985481</v>
+        <v>-7425.33841867995</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000001317e-08</v>
@@ -8729,7 +8341,7 @@
         <v>849.6870000000001</v>
       </c>
       <c r="C10" t="n">
-        <v>1277.674637191294</v>
+        <v>9129.756195785649</v>
       </c>
       <c r="D10" t="n">
         <v>4.53622e-07</v>
@@ -8762,10 +8374,7 @@
         <v>-14710.90490501782</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.782729252109054e-11</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1384.601825518677</v>
+        <v>-7616.115179348824</v>
       </c>
       <c r="AA10" t="n">
         <v>1e-08</v>
@@ -8782,7 +8391,7 @@
         <v>835.6020000000001</v>
       </c>
       <c r="C11" t="n">
-        <v>1263.974557229638</v>
+        <v>882.6012169203203</v>
       </c>
       <c r="D11" t="n">
         <v>4.55476e-07</v>
@@ -8815,16 +8424,13 @@
         <v>-14504.05841288523</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.91677281693671e-08</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1368.390390971445</v>
+        <v>37.60125940054108</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.000000000000034e-08</v>
+        <v>3.153086056093672e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8329994601735757</v>
+        <v>0.8769322680583219</v>
       </c>
     </row>
     <row r="12">
@@ -8835,7 +8441,7 @@
         <v>826.7269999999999</v>
       </c>
       <c r="C12" t="n">
-        <v>1249.268957051645</v>
+        <v>884.489071080503</v>
       </c>
       <c r="D12" t="n">
         <v>4.57073e-07</v>
@@ -8868,16 +8474,13 @@
         <v>-14552.66473296584</v>
       </c>
       <c r="Y12" t="n">
-        <v>3.180452003584913e-09</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1352.357036463741</v>
+        <v>28.92544154762107</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.000000000000003e-08</v>
+        <v>3.218347700306213e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.8334056593467165</v>
+        <v>0.8747738759353856</v>
       </c>
     </row>
     <row r="13">
@@ -8888,7 +8491,7 @@
         <v>815.9640000000001</v>
       </c>
       <c r="C13" t="n">
-        <v>1241.031162769922</v>
+        <v>914.0595928738231</v>
       </c>
       <c r="D13" t="n">
         <v>4.58828e-07</v>
@@ -8921,16 +8524,13 @@
         <v>-15045.93913038232</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.275423215382914e-09</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1336.665934289909</v>
+        <v>4.929423661169432</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.000000000000078e-08</v>
+        <v>3.837633874090611e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.8338248196596109</v>
+        <v>0.860578610978156</v>
       </c>
     </row>
     <row r="14">
@@ -8941,7 +8541,7 @@
         <v>799.6709999999999</v>
       </c>
       <c r="C14" t="n">
-        <v>1222.187665998255</v>
+        <v>909.6396231643075</v>
       </c>
       <c r="D14" t="n">
         <v>4.60394e-07</v>
@@ -8974,16 +8574,13 @@
         <v>-13777.00809800909</v>
       </c>
       <c r="Y14" t="n">
-        <v>6.322043780405196e-09</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1321.064042952145</v>
+        <v>2.911258873928954</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.000000000000171e-08</v>
+        <v>3.996743276789856e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.8342537658259238</v>
+        <v>0.8574573789628768</v>
       </c>
     </row>
     <row r="15">
@@ -8994,7 +8591,7 @@
         <v>787.1419999999999</v>
       </c>
       <c r="C15" t="n">
-        <v>1210.613011028484</v>
+        <v>903.5170434057248</v>
       </c>
       <c r="D15" t="n">
         <v>4.6214e-07</v>
@@ -9027,16 +8624,13 @@
         <v>-13556.95033914214</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.624561494765244e-10</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1305.248307885294</v>
+        <v>2.163249839935515</v>
       </c>
       <c r="AA15" t="n">
-        <v>1e-08</v>
+        <v>4.188539316196344e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.8346901559036031</v>
+        <v>0.8544447367747638</v>
       </c>
     </row>
     <row r="16">
@@ -9047,7 +8641,7 @@
         <v>778.432</v>
       </c>
       <c r="C16" t="n">
-        <v>1198.676164732769</v>
+        <v>878.6204492944057</v>
       </c>
       <c r="D16" t="n">
         <v>4.63978e-07</v>
@@ -9080,16 +8674,13 @@
         <v>-13791.09269012721</v>
       </c>
       <c r="Y16" t="n">
-        <v>7.108295698050464e-11</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1289.512726259253</v>
+        <v>9.542088425179006</v>
       </c>
       <c r="AA16" t="n">
-        <v>1e-08</v>
+        <v>3.627646359635247e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.8351238211759799</v>
+        <v>0.8645508891176983</v>
       </c>
     </row>
     <row r="17">
@@ -9100,7 +8691,7 @@
         <v>759.7130000000001</v>
       </c>
       <c r="C17" t="n">
-        <v>1179.421343705392</v>
+        <v>759.7130000000001</v>
       </c>
       <c r="D17" t="n">
         <v>4.65652e-07</v>
@@ -9132,11 +8723,10 @@
       <c r="X17" t="n">
         <v>-12114.95481458074</v>
       </c>
-      <c r="Y17" t="n">
-        <v>1.384184944204951e-09</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1273.785316868221</v>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA17" t="n">
         <v>1e-08</v>
@@ -9153,7 +8743,7 @@
         <v>753.1580000000001</v>
       </c>
       <c r="C18" t="n">
-        <v>1172.078035414172</v>
+        <v>886.7751524061712</v>
       </c>
       <c r="D18" t="n">
         <v>4.67156e-07</v>
@@ -9186,16 +8776,13 @@
         <v>-13244.15151782749</v>
       </c>
       <c r="Y18" t="n">
-        <v>7.980224748905889e-12</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1257.905590422531</v>
+        <v>1.376926676964889</v>
       </c>
       <c r="AA18" t="n">
-        <v>1e-08</v>
+        <v>5.116994519796936e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.8359988410809432</v>
+        <v>0.8407802036300678</v>
       </c>
     </row>
     <row r="19">
@@ -9206,7 +8793,7 @@
         <v>743.519</v>
       </c>
       <c r="C19" t="n">
-        <v>1159.9168653835</v>
+        <v>850.0908975155612</v>
       </c>
       <c r="D19" t="n">
         <v>4.69099e-07</v>
@@ -9239,16 +8826,13 @@
         <v>-13431.36814650586</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.919678243613795e-09</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1241.799825405904</v>
+        <v>11.83597795627372</v>
       </c>
       <c r="AA19" t="n">
-        <v>1e-08</v>
+        <v>3.636911594485809e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.8364540256777742</v>
+        <v>0.8673749331154442</v>
       </c>
     </row>
     <row r="20">
@@ -9259,7 +8843,7 @@
         <v>733.282</v>
       </c>
       <c r="C20" t="n">
-        <v>1145.711573004148</v>
+        <v>862.4002081170687</v>
       </c>
       <c r="D20" t="n">
         <v>4.70661e-07</v>
@@ -9292,16 +8876,13 @@
         <v>-13563.15286952507</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.983169149554645e-08</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1225.882886725404</v>
+        <v>2.068982762601175</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.000000000000037e-08</v>
+        <v>4.35474369601298e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.8369004121880459</v>
+        <v>0.8540351162796319</v>
       </c>
     </row>
     <row r="21">
@@ -9312,7 +8893,7 @@
         <v>720.221</v>
       </c>
       <c r="C21" t="n">
-        <v>1131.732877875347</v>
+        <v>852.1091264334079</v>
       </c>
       <c r="D21" t="n">
         <v>4.72531e-07</v>
@@ -9345,16 +8926,13 @@
         <v>-13210.89265957081</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.655998173363553e-08</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1209.790388678459</v>
+        <v>2.909684817243276</v>
       </c>
       <c r="AA21" t="n">
-        <v>1e-08</v>
+        <v>4.294445273254542e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.8373681415220726</v>
+        <v>0.8558742606688994</v>
       </c>
     </row>
     <row r="22">
@@ -9365,7 +8943,7 @@
         <v>705.5419999999999</v>
       </c>
       <c r="C22" t="n">
-        <v>1113.601024614723</v>
+        <v>837.432538141545</v>
       </c>
       <c r="D22" t="n">
         <v>4.74299e-07</v>
@@ -9398,16 +8976,13 @@
         <v>-12189.99184383551</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.334879530913401e-08</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1193.504918833813</v>
+        <v>5.118433314428422</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.000000000000018e-08</v>
+        <v>4.012537528048679e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.8378569494704342</v>
+        <v>0.8617676547417008</v>
       </c>
     </row>
   </sheetData>
@@ -9564,7 +9139,7 @@
         <v>888.883</v>
       </c>
       <c r="C2" t="n">
-        <v>1418.961381800347</v>
+        <v>7972.502796765885</v>
       </c>
       <c r="D2" t="n">
         <v>4.51846e-07</v>
@@ -9597,10 +9172,7 @@
         <v>-12737.63958463638</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.869656676034459e-08</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1391.609393157072</v>
+        <v>-6355.604984787474</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000982e-08</v>
@@ -9617,7 +9189,7 @@
         <v>764.0119999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>1224.275610306775</v>
+        <v>9106.351942287885</v>
       </c>
       <c r="D3" t="n">
         <v>4.66674e-07</v>
@@ -9650,10 +9222,7 @@
         <v>-13245.03810169215</v>
       </c>
       <c r="Y3" t="n">
-        <v>8.108928582058926e-10</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1295.417361774248</v>
+        <v>-7656.674349108917</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000003e-08</v>
@@ -9670,7 +9239,7 @@
         <v>738.019</v>
       </c>
       <c r="C4" t="n">
-        <v>1189.286982893059</v>
+        <v>9430.754241480476</v>
       </c>
       <c r="D4" t="n">
         <v>4.6716e-07</v>
@@ -9703,10 +9272,7 @@
         <v>-14172.60819647558</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.900937840576138e-11</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1266.111630016187</v>
+        <v>-8020.843164838061</v>
       </c>
       <c r="AA4" t="n">
         <v>1e-08</v>
@@ -9723,7 +9289,7 @@
         <v>720.3130000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>1173.38174357279</v>
+        <v>9685.276646510047</v>
       </c>
       <c r="D5" t="n">
         <v>4.67022e-07</v>
@@ -9756,10 +9322,7 @@
         <v>-14182.59212932005</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.346681399974671e-08</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1245.857993000636</v>
+        <v>-8299.171922250989</v>
       </c>
       <c r="AA5" t="n">
         <v>1e-08</v>
@@ -9776,7 +9339,7 @@
         <v>703.7619999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>1156.89564038517</v>
+        <v>9529.987906380444</v>
       </c>
       <c r="D6" t="n">
         <v>4.67225e-07</v>
@@ -9809,10 +9372,7 @@
         <v>-14216.79492881361</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.292420589213277e-12</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1226.774437129283</v>
+        <v>-8157.385739708934</v>
       </c>
       <c r="AA6" t="n">
         <v>1e-08</v>
@@ -9829,7 +9389,7 @@
         <v>691.2249999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>1142.653270691916</v>
+        <v>874.0306423447184</v>
       </c>
       <c r="D7" t="n">
         <v>4.68074e-07</v>
@@ -9862,16 +9422,13 @@
         <v>-14753.17619692637</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.494730951868302e-12</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1208.181963510594</v>
+        <v>2.425158582538614</v>
       </c>
       <c r="AA7" t="n">
-        <v>1e-08</v>
+        <v>4.722142415739674e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.833340525675825</v>
+        <v>0.8450322136387921</v>
       </c>
     </row>
     <row r="8">
@@ -9882,7 +9439,7 @@
         <v>670.2239999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>1122.390572507551</v>
+        <v>719.9522187917521</v>
       </c>
       <c r="D8" t="n">
         <v>4.69062e-07</v>
@@ -9915,16 +9472,13 @@
         <v>-12697.97441281812</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.539227863482646e-09</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1190.016728613844</v>
+        <v>136.2149910788679</v>
       </c>
       <c r="AA8" t="n">
-        <v>1e-08</v>
+        <v>4.389554019214903e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8337176306061557</v>
+        <v>0.8752003915879041</v>
       </c>
     </row>
     <row r="9">
@@ -9935,7 +9489,7 @@
         <v>655.4949999999999</v>
       </c>
       <c r="C9" t="n">
-        <v>1103.755808274577</v>
+        <v>707.2257912659417</v>
       </c>
       <c r="D9" t="n">
         <v>4.70189e-07</v>
@@ -9968,16 +9522,13 @@
         <v>-12339.30102183179</v>
       </c>
       <c r="Y9" t="n">
-        <v>7.123585102941405e-12</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1171.80634583206</v>
+        <v>136.7104834880252</v>
       </c>
       <c r="AA9" t="n">
-        <v>1e-08</v>
+        <v>4.503218017594847e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8341304710465119</v>
+        <v>0.8734834301347211</v>
       </c>
     </row>
     <row r="10">
@@ -9988,7 +9539,7 @@
         <v>643.347</v>
       </c>
       <c r="C10" t="n">
-        <v>1094.317038281651</v>
+        <v>706.5775739837936</v>
       </c>
       <c r="D10" t="n">
         <v>4.71574e-07</v>
@@ -10021,16 +9572,13 @@
         <v>-13073.63139279546</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.078463945277714e-10</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1154.342603242539</v>
+        <v>128.2415206381582</v>
       </c>
       <c r="AA10" t="n">
-        <v>1e-08</v>
+        <v>4.447396987027969e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8346108953997701</v>
+        <v>0.873820651578104</v>
       </c>
     </row>
     <row r="11">
@@ -10041,7 +9589,7 @@
         <v>632.314</v>
       </c>
       <c r="C11" t="n">
-        <v>1077.469719916296</v>
+        <v>708.2862760434356</v>
       </c>
       <c r="D11" t="n">
         <v>4.72768e-07</v>
@@ -10074,16 +9622,13 @@
         <v>-12978.06331141998</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.149259456054139e-12</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1139.994134631766</v>
+        <v>121.7228390069424</v>
       </c>
       <c r="AA11" t="n">
-        <v>1e-08</v>
+        <v>4.536074736117106e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8350318826856246</v>
+        <v>0.8724724838677635</v>
       </c>
     </row>
   </sheetData>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 36.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 36.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -589,18 +589,6 @@
       <c r="G2" t="n">
         <v>-50.825</v>
       </c>
-      <c r="H2" t="n">
-        <v/>
-      </c>
-      <c r="I2" t="n">
-        <v/>
-      </c>
-      <c r="J2" t="n">
-        <v/>
-      </c>
-      <c r="K2" t="n">
-        <v/>
-      </c>
       <c r="L2" t="n">
         <v>23.50819051819527</v>
       </c>
@@ -645,18 +633,6 @@
       <c r="G3" t="n">
         <v>-52.548</v>
       </c>
-      <c r="H3" t="n">
-        <v/>
-      </c>
-      <c r="I3" t="n">
-        <v/>
-      </c>
-      <c r="J3" t="n">
-        <v/>
-      </c>
-      <c r="K3" t="n">
-        <v/>
-      </c>
       <c r="L3" t="n">
         <v>25.38407689878018</v>
       </c>
@@ -701,18 +677,6 @@
       <c r="G4" t="n">
         <v>-53.344</v>
       </c>
-      <c r="H4" t="n">
-        <v/>
-      </c>
-      <c r="I4" t="n">
-        <v/>
-      </c>
-      <c r="J4" t="n">
-        <v/>
-      </c>
-      <c r="K4" t="n">
-        <v/>
-      </c>
       <c r="L4" t="n">
         <v>26.44943764494086</v>
       </c>
@@ -757,18 +721,6 @@
       <c r="G5" t="n">
         <v>-53.944</v>
       </c>
-      <c r="H5" t="n">
-        <v/>
-      </c>
-      <c r="I5" t="n">
-        <v/>
-      </c>
-      <c r="J5" t="n">
-        <v/>
-      </c>
-      <c r="K5" t="n">
-        <v/>
-      </c>
       <c r="L5" t="n">
         <v>25.12163405170091</v>
       </c>
@@ -813,18 +765,6 @@
       <c r="G6" t="n">
         <v>-54.467</v>
       </c>
-      <c r="H6" t="n">
-        <v/>
-      </c>
-      <c r="I6" t="n">
-        <v/>
-      </c>
-      <c r="J6" t="n">
-        <v/>
-      </c>
-      <c r="K6" t="n">
-        <v/>
-      </c>
       <c r="L6" t="n">
         <v>20.37922166693785</v>
       </c>
@@ -869,18 +809,6 @@
       <c r="G7" t="n">
         <v>-55.02</v>
       </c>
-      <c r="H7" t="n">
-        <v/>
-      </c>
-      <c r="I7" t="n">
-        <v/>
-      </c>
-      <c r="J7" t="n">
-        <v/>
-      </c>
-      <c r="K7" t="n">
-        <v/>
-      </c>
       <c r="L7" t="n">
         <v>19.09617276326737</v>
       </c>
@@ -925,18 +853,6 @@
       <c r="G8" t="n">
         <v>-55.467</v>
       </c>
-      <c r="H8" t="n">
-        <v/>
-      </c>
-      <c r="I8" t="n">
-        <v/>
-      </c>
-      <c r="J8" t="n">
-        <v/>
-      </c>
-      <c r="K8" t="n">
-        <v/>
-      </c>
       <c r="L8" t="n">
         <v>18.57042870385614</v>
       </c>
@@ -981,18 +897,6 @@
       <c r="G9" t="n">
         <v>-55.902</v>
       </c>
-      <c r="H9" t="n">
-        <v/>
-      </c>
-      <c r="I9" t="n">
-        <v/>
-      </c>
-      <c r="J9" t="n">
-        <v/>
-      </c>
-      <c r="K9" t="n">
-        <v/>
-      </c>
       <c r="L9" t="n">
         <v>17.67260199782607</v>
       </c>
@@ -1037,18 +941,6 @@
       <c r="G10" t="n">
         <v>-56.329</v>
       </c>
-      <c r="H10" t="n">
-        <v/>
-      </c>
-      <c r="I10" t="n">
-        <v/>
-      </c>
-      <c r="J10" t="n">
-        <v/>
-      </c>
-      <c r="K10" t="n">
-        <v/>
-      </c>
       <c r="L10" t="n">
         <v>16.70472601548688</v>
       </c>
@@ -1124,6 +1016,566 @@
         <v>1.00000000000002e-08</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.8265402066269282</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1930.794</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2261.076629314057</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3.21875e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-50.825</v>
+      </c>
+      <c r="H12" t="n">
+        <v/>
+      </c>
+      <c r="I12" t="n">
+        <v/>
+      </c>
+      <c r="J12" t="n">
+        <v/>
+      </c>
+      <c r="K12" t="n">
+        <v/>
+      </c>
+      <c r="L12" t="n">
+        <v>23.50819051819527</v>
+      </c>
+      <c r="M12" t="n">
+        <v>85.64734640804066</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>13.13808114540886</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-30005.75286025774</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>22.86099674476418</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.000000000000104e-08</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.8220353692950022</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1830.712</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.9481653661654221</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2140.765211010589</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.94679020748626</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3.33289e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-52.548</v>
+      </c>
+      <c r="H13" t="n">
+        <v/>
+      </c>
+      <c r="I13" t="n">
+        <v/>
+      </c>
+      <c r="J13" t="n">
+        <v/>
+      </c>
+      <c r="K13" t="n">
+        <v/>
+      </c>
+      <c r="L13" t="n">
+        <v>25.38407689878018</v>
+      </c>
+      <c r="M13" t="n">
+        <v>85.77810386746992</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>13.54653027123325</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-29591.61726137361</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>22.172719613548</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.000000000000025e-08</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8230149902873902</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1796.852</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.9306285393470253</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2107.731307966744</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.9321803961178293</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3.37632e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-53.344</v>
+      </c>
+      <c r="H14" t="n">
+        <v/>
+      </c>
+      <c r="I14" t="n">
+        <v/>
+      </c>
+      <c r="J14" t="n">
+        <v/>
+      </c>
+      <c r="K14" t="n">
+        <v/>
+      </c>
+      <c r="L14" t="n">
+        <v>26.44943764494086</v>
+      </c>
+      <c r="M14" t="n">
+        <v>85.95154901116902</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>14.12895821703982</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-30378.4553114298</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>22.68818819544549</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.00000000000067e-08</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.823396817960149</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1764.29</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.9137639748207215</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2080.764500004039</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.9202538618230206</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3.41131e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-53.944</v>
+      </c>
+      <c r="H15" t="n">
+        <v/>
+      </c>
+      <c r="I15" t="n">
+        <v/>
+      </c>
+      <c r="J15" t="n">
+        <v/>
+      </c>
+      <c r="K15" t="n">
+        <v/>
+      </c>
+      <c r="L15" t="n">
+        <v>25.12163405170091</v>
+      </c>
+      <c r="M15" t="n">
+        <v>85.9639341652811</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>14.17245905177188</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-30022.53268889376</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>19.6920210568419</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.000000000000014e-08</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.8238277432532697</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1729.522</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.8957568751508447</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2053.812041726064</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.9083336739229086</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3.44068e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-54.467</v>
+      </c>
+      <c r="H16" t="n">
+        <v/>
+      </c>
+      <c r="I16" t="n">
+        <v/>
+      </c>
+      <c r="J16" t="n">
+        <v/>
+      </c>
+      <c r="K16" t="n">
+        <v/>
+      </c>
+      <c r="L16" t="n">
+        <v>20.37922166693785</v>
+      </c>
+      <c r="M16" t="n">
+        <v>85.5311086830211</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>12.79501822728133</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-26648.46776713715</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>20.22867302172472</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.000000000000059e-08</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.8241800051206308</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1701.958</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.88148088299425</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2025.987073465001</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.8960276034871161</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3.47512e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-55.02</v>
+      </c>
+      <c r="H17" t="n">
+        <v/>
+      </c>
+      <c r="I17" t="n">
+        <v/>
+      </c>
+      <c r="J17" t="n">
+        <v/>
+      </c>
+      <c r="K17" t="n">
+        <v/>
+      </c>
+      <c r="L17" t="n">
+        <v>19.09617276326737</v>
+      </c>
+      <c r="M17" t="n">
+        <v>85.55717016970785</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>12.87037773732172</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-26433.47969658138</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>20.29080719582248</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.000000000013293e-08</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.8246520731325662</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1683.699</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.8720241517220377</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2004.233320498379</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.886406632360091</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3.50007e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-55.467</v>
+      </c>
+      <c r="H18" t="n">
+        <v/>
+      </c>
+      <c r="I18" t="n">
+        <v/>
+      </c>
+      <c r="J18" t="n">
+        <v/>
+      </c>
+      <c r="K18" t="n">
+        <v/>
+      </c>
+      <c r="L18" t="n">
+        <v>18.57042870385614</v>
+      </c>
+      <c r="M18" t="n">
+        <v>85.55650137490484</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>12.86843281824995</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-26106.72336765886</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>18.08754074163039</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.00000000000003e-08</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.8250918689372405</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1659.309</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.8593920428590519</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1981.177476920511</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.8762097892814635</v>
+      </c>
+      <c r="F19" t="n">
+        <v>3.52865e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-55.902</v>
+      </c>
+      <c r="H19" t="n">
+        <v/>
+      </c>
+      <c r="I19" t="n">
+        <v/>
+      </c>
+      <c r="J19" t="n">
+        <v/>
+      </c>
+      <c r="K19" t="n">
+        <v/>
+      </c>
+      <c r="L19" t="n">
+        <v>17.67260199782607</v>
+      </c>
+      <c r="M19" t="n">
+        <v>85.53386345187783</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>12.80294244357264</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-25655.12322408354</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>18.39648124032101</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.00000000000045e-08</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.8255544971559319</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1636.784</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.8477258578595128</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1960.492029889886</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.8670612948154001</v>
+      </c>
+      <c r="F20" t="n">
+        <v>3.55368e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-56.329</v>
+      </c>
+      <c r="H20" t="n">
+        <v/>
+      </c>
+      <c r="I20" t="n">
+        <v/>
+      </c>
+      <c r="J20" t="n">
+        <v/>
+      </c>
+      <c r="K20" t="n">
+        <v/>
+      </c>
+      <c r="L20" t="n">
+        <v>16.70472601548688</v>
+      </c>
+      <c r="M20" t="n">
+        <v>85.50959463695597</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>12.7334658991018</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-25182.41937332417</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>15.83757943480896</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.8260728795718459</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1609.728</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.8337129698973583</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1939.937064818133</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.8579705082382157</v>
+      </c>
+      <c r="F21" t="n">
+        <v>3.57908e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-56.714</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.03138138138137649</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.5012278308321236</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.968312757201658</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.384741144414158</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>85.10441995810237</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>11.67507802581874</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-22770.76496777428</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>15.39331823365171</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.00000000000002e-08</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.8265402066269282</v>
       </c>
     </row>
@@ -1138,7 +1590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2456,6 +2908,1182 @@
         <v>1.000000000000021e-08</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.8342102281061093</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1354.546</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1767.115735168486</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>3.50084e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-61.977</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.1772397094430852</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.7795572916666338</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.421179302045696</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1.777639344262239</v>
+      </c>
+      <c r="L23" t="n">
+        <v>17.85262538132501</v>
+      </c>
+      <c r="M23" t="n">
+        <v>84.15726188596206</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>9.772308143420897</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-17015.43293009196</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-15.01094047980166</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8267167429692154</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1244.023</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9184058717828705</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1619.527139486395</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9164805152572425</v>
+      </c>
+      <c r="F24" t="n">
+        <v>3.64831e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-63.364</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.3508177570093708</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.388055130168467</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.053706111833499</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.490704070407043</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>84.82174617823858</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>11.03454892679072</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-17987.86788757323</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>6.523834422509594</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8273802921156419</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1205.615</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.890050983872087</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1580.363247282171</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.8943179078938428</v>
+      </c>
+      <c r="F25" t="n">
+        <v>3.68465e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-63.85</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.5441696113074458</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.3812307692307739</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.394678217821834</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.101371951219499</v>
+      </c>
+      <c r="L25" t="n">
+        <v>14.33007810820176</v>
+      </c>
+      <c r="M25" t="n">
+        <v>84.64552725877967</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>10.66937634727152</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-16970.61181723978</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>9.282541853445423</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8276142146253896</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1179.377</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.8706806561017493</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1560.513042931444</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.8830847985079237</v>
+      </c>
+      <c r="F26" t="n">
+        <v>3.70409e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-64.23099999999999</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.02038043478261347</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.209090909090921</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.8908616187989684</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1.450120870265968</v>
+      </c>
+      <c r="L26" t="n">
+        <v>14.88228165027338</v>
+      </c>
+      <c r="M26" t="n">
+        <v>84.40234898269946</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>10.2030961158081</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-15954.47778077594</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>8.093026877455713</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.827788539465369</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1158.48</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.8552533468778469</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1548.160988878757</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.8760948465727665</v>
+      </c>
+      <c r="F27" t="n">
+        <v>3.71536e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-64.538</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.1767584097859319</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.3065708418891312</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.6573793103448126</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1.261358811040396</v>
+      </c>
+      <c r="L27" t="n">
+        <v>14.19285092928548</v>
+      </c>
+      <c r="M27" t="n">
+        <v>84.14928176602405</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>9.758886230328484</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-15063.35333011143</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>6.027871954138163</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.00000000000001e-08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8280178828800255</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1144.563</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.8449790557131319</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1532.940573166344</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.8674817062959292</v>
+      </c>
+      <c r="F28" t="n">
+        <v>3.72856e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-64.81999999999999</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.2288640595903332</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.4527363184080048</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.078364779874308</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1.56942148760332</v>
+      </c>
+      <c r="L28" t="n">
+        <v>13.64862167789395</v>
+      </c>
+      <c r="M28" t="n">
+        <v>84.41322827390229</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>10.22309178719359</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-15644.67735598397</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>4.591289611150387</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8282691527004641</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1123.976</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.8297806054574742</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1517.371025299292</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.858670994265476</v>
+      </c>
+      <c r="F29" t="n">
+        <v>3.74415e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-65.13500000000001</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.1970085470085128</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.1734999999999949</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.6999999999999998</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.300166666666741</v>
+      </c>
+      <c r="L29" t="n">
+        <v>13.4199996376029</v>
+      </c>
+      <c r="M29" t="n">
+        <v>84.14667144194296</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>9.754503793284201</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-14710.89724905403</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>2.747552621111026</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8285524028515685</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1105.091</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.8158386647629539</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1496.772305585621</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.8470143046080172</v>
+      </c>
+      <c r="F30" t="n">
+        <v>3.75922e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-65.443</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.1494522691705863</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.4786046511628182</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.325192307692328</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1.725596816976154</v>
+      </c>
+      <c r="L30" t="n">
+        <v>12.42720796277315</v>
+      </c>
+      <c r="M30" t="n">
+        <v>84.13055082820483</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>9.727525187412287</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-14498.22070462981</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>4.498486505227561</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.00000000000001e-08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8288695539065057</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1097.122</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.809955512769592</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1482.717669705111</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8390608720168182</v>
+      </c>
+      <c r="F31" t="n">
+        <v>3.77394e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-65.733</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.04395604395604338</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.6840236686390722</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.30755627009645</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1.507154213036602</v>
+      </c>
+      <c r="L31" t="n">
+        <v>9.895827623414803</v>
+      </c>
+      <c r="M31" t="n">
+        <v>84.35986172357947</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>10.12574288430962</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-14950.91672660913</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>2.535486991038965</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.829204368396678</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1076.179</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.7944942438278213</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1512.202465342167</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8557461377581957</v>
+      </c>
+      <c r="F32" t="n">
+        <v>3.7891e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-66.05800000000001</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.4490153172866617</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.4681069958848001</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.016145833333231</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1.804115853658517</v>
+      </c>
+      <c r="L32" t="n">
+        <v>10.19214685588772</v>
+      </c>
+      <c r="M32" t="n">
+        <v>83.96894711286227</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>9.465015658719462</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-13765.04988246847</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-23.99422234852591</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.00000000000012e-08</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.8295666008595675</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1065.261</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.7864339786171898</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1453.515175779782</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.82253535908965</v>
+      </c>
+      <c r="F33" t="n">
+        <v>3.80504e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-66.336</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.4557894736842675</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.199757281553413</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.129485396383898</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1.925560975609695</v>
+      </c>
+      <c r="L33" t="n">
+        <v>4.971492849267263</v>
+      </c>
+      <c r="M33" t="n">
+        <v>84.15566797095875</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>9.769624388721313</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-14076.70171652841</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-0.7188977649909702</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.000000000000875e-08</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.8299365425505235</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1048.456</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.7740276077741177</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1438.375561475393</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8139679438360331</v>
+      </c>
+      <c r="F34" t="n">
+        <v>3.81827e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-66.628</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.2451704545454759</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.8814732142856925</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.314577259475294</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1.671514543630914</v>
+      </c>
+      <c r="L34" t="n">
+        <v>2.749463182120563</v>
+      </c>
+      <c r="M34" t="n">
+        <v>83.97978427177917</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>9.482180294434437</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-13489.6073187469</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-1.098697697532884</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.000000000000727e-08</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.8303279715955958</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1030.135</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.7605020427508551</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1424.300223864997</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8060027962623493</v>
+      </c>
+      <c r="F35" t="n">
+        <v>3.83316e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-66.899</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.0808259587020501</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.4786666666667301</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.9040579710144514</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2.022670375521478</v>
+      </c>
+      <c r="L35" t="n">
+        <v>6.281280071470497</v>
+      </c>
+      <c r="M35" t="n">
+        <v>83.63784420144287</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>8.968673784275518</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-12575.63001602633</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>-2.650649784002667</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.000000000000242e-08</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.8307235729535724</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1016.373</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.7503421810702626</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1410.153126510934</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.7979970402880727</v>
+      </c>
+      <c r="F36" t="n">
+        <v>3.84765e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-67.218</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.1796721311475469</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.2934354485776941</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.5199213630406117</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1.355986696230574</v>
+      </c>
+      <c r="L36" t="n">
+        <v>3.283029918440783</v>
+      </c>
+      <c r="M36" t="n">
+        <v>83.29991164472642</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>8.5124809952092</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-11781.29576294632</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-3.627703107619254</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.000000000000402e-08</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.8311395019231349</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>999.289</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.7377298371557702</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1432.581672074162</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.8106892172161956</v>
+      </c>
+      <c r="F37" t="n">
+        <v>3.85963e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-67.48</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.04051767762398824</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.4305132751383817</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.560132086084758</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.452152241944754</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>83.14660460730367</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>8.320293886217215</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-11364.99916730823</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-24.80569509497946</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.000000000002781e-08</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.8315541560369971</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>990.212</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.7310286989146179</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1380.214819617891</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.7810551352972325</v>
+      </c>
+      <c r="F38" t="n">
+        <v>3.87442e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-67.748</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1.603937007874693</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.07665289256198038</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.8987261146498073</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1.570870113492997</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.3751499724847109</v>
+      </c>
+      <c r="M38" t="n">
+        <v>82.97218045826641</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>8.111783426305024</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-10949.68281148155</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-4.334661435312455</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.000000000005385e-08</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.8319803920677162</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>979.1770000000001</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.7228820578998425</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1367.321969294205</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.7737591500558035</v>
+      </c>
+      <c r="F39" t="n">
+        <v>3.88796e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-68.038</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.2303303303303584</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.9777292576418939</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.195612708018148</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2.132894736842174</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>82.62237828107673</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>7.723189704221721</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-10281.77806303802</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-6.180411898467014</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.669899940135306e-08</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.79501592205168</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>966.704</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.713673806574306</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1353.695557708511</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.7660480469772072</v>
+      </c>
+      <c r="F40" t="n">
+        <v>3.89977e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-68.301</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.6694835680751694</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.589969604863239</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.227838258164906</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1.699704433497526</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>82.2367987790237</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>7.335212255506595</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-9629.454571360633</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-7.311754207056424</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.8328563482705436</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>944.8869999999999</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.6975673029930323</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1339.594080035752</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.7580681069019101</v>
+      </c>
+      <c r="F41" t="n">
+        <v>3.91183e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-68.59</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.2893630337410727</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.6674130663856573</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.399912310493249</v>
+      </c>
+      <c r="K41" t="n">
+        <v>155.728650377143</v>
+      </c>
+      <c r="L41" t="n">
+        <v>6.500568358078487</v>
+      </c>
+      <c r="M41" t="n">
+        <v>81.75990489710814</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>6.905285885128736</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-8927.526278065347</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>-7.665914797873484</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.000000000000003e-08</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.833299599175079</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>932.79</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.6886366354483346</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1323.75521353549</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7491049891020723</v>
+      </c>
+      <c r="F42" t="n">
+        <v>3.92731e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-68.875</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.5140700093249601</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.5680966415857508</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.791614224706498</v>
+      </c>
+      <c r="K42" t="n">
+        <v>121.9464316596788</v>
+      </c>
+      <c r="L42" t="n">
+        <v>6.580861691306702</v>
+      </c>
+      <c r="M42" t="n">
+        <v>81.08546369845592</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>6.375283927555249</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-8109.955938307442</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-7.775695698362938</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.000000000001101e-08</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.833754606305494</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>922.5360000000001</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.6810665713825887</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1310.544362606973</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.7416290492608953</v>
+      </c>
+      <c r="F43" t="n">
+        <v>3.93865e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-69.149</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1.04195121951233</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1.609354838709598</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.302150537634419</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1.799421128798766</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>80.11546595980685</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>5.738887572902948</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-7160.385382407118</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>-9.203217045888891</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.000000000000021e-08</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.8342102281061093</v>
       </c>
     </row>
@@ -2470,7 +4098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2637,18 +4265,6 @@
       <c r="G2" t="n">
         <v>-53.004</v>
       </c>
-      <c r="H2" t="n">
-        <v/>
-      </c>
-      <c r="I2" t="n">
-        <v/>
-      </c>
-      <c r="J2" t="n">
-        <v/>
-      </c>
-      <c r="K2" t="n">
-        <v/>
-      </c>
       <c r="L2" t="n">
         <v>19.71343064952844</v>
       </c>
@@ -2805,18 +4421,6 @@
       <c r="G5" t="n">
         <v>-56.04</v>
       </c>
-      <c r="H5" t="n">
-        <v/>
-      </c>
-      <c r="I5" t="n">
-        <v/>
-      </c>
-      <c r="J5" t="n">
-        <v/>
-      </c>
-      <c r="K5" t="n">
-        <v/>
-      </c>
       <c r="L5" t="n">
         <v>19.61729010513972</v>
       </c>
@@ -2861,18 +4465,6 @@
       <c r="G6" t="n">
         <v>-56.484</v>
       </c>
-      <c r="H6" t="n">
-        <v/>
-      </c>
-      <c r="I6" t="n">
-        <v/>
-      </c>
-      <c r="J6" t="n">
-        <v/>
-      </c>
-      <c r="K6" t="n">
-        <v/>
-      </c>
       <c r="L6" t="n">
         <v>18.65952497497768</v>
       </c>
@@ -2973,18 +4565,6 @@
       <c r="G8" t="n">
         <v>-57.278</v>
       </c>
-      <c r="H8" t="n">
-        <v/>
-      </c>
-      <c r="I8" t="n">
-        <v/>
-      </c>
-      <c r="J8" t="n">
-        <v/>
-      </c>
-      <c r="K8" t="n">
-        <v/>
-      </c>
       <c r="L8" t="n">
         <v>15.63948427037806</v>
       </c>
@@ -3141,18 +4721,6 @@
       <c r="G11" t="n">
         <v>-58.296</v>
       </c>
-      <c r="H11" t="n">
-        <v/>
-      </c>
-      <c r="I11" t="n">
-        <v/>
-      </c>
-      <c r="J11" t="n">
-        <v/>
-      </c>
-      <c r="K11" t="n">
-        <v/>
-      </c>
       <c r="L11" t="n">
         <v>11.37329456554101</v>
       </c>
@@ -3197,18 +4765,6 @@
       <c r="G12" t="n">
         <v>-58.604</v>
       </c>
-      <c r="H12" t="n">
-        <v/>
-      </c>
-      <c r="I12" t="n">
-        <v/>
-      </c>
-      <c r="J12" t="n">
-        <v/>
-      </c>
-      <c r="K12" t="n">
-        <v/>
-      </c>
       <c r="L12" t="n">
         <v>7.841791312716895</v>
       </c>
@@ -3253,18 +4809,6 @@
       <c r="G13" t="n">
         <v>-58.922</v>
       </c>
-      <c r="H13" t="n">
-        <v/>
-      </c>
-      <c r="I13" t="n">
-        <v/>
-      </c>
-      <c r="J13" t="n">
-        <v/>
-      </c>
-      <c r="K13" t="n">
-        <v/>
-      </c>
       <c r="L13" t="n">
         <v>5.186029911891853</v>
       </c>
@@ -3365,18 +4909,6 @@
       <c r="G15" t="n">
         <v>-59.501</v>
       </c>
-      <c r="H15" t="n">
-        <v/>
-      </c>
-      <c r="I15" t="n">
-        <v/>
-      </c>
-      <c r="J15" t="n">
-        <v/>
-      </c>
-      <c r="K15" t="n">
-        <v/>
-      </c>
       <c r="L15" t="n">
         <v>2.834550189885208</v>
       </c>
@@ -3788,6 +5320,1182 @@
         <v>1.000000000000031e-08</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.8302774363535452</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1723.042</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2048.304598662674</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>3.42798e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-53.004</v>
+      </c>
+      <c r="H23" t="n">
+        <v/>
+      </c>
+      <c r="I23" t="n">
+        <v/>
+      </c>
+      <c r="J23" t="n">
+        <v/>
+      </c>
+      <c r="K23" t="n">
+        <v/>
+      </c>
+      <c r="L23" t="n">
+        <v>19.71343064952844</v>
+      </c>
+      <c r="M23" t="n">
+        <v>85.43829387511607</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>12.53361438801531</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-26214.44258555676</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>14.78148863714205</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.000000000003183e-08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8225065740333724</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1630.375</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9462189546163122</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1959.806927238805</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9567946722954934</v>
+      </c>
+      <c r="F24" t="n">
+        <v>3.54276e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-54.831</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.1477453580901716</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.5744803695150319</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.663030303030276</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.14095878889816</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>85.3846080067192</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>12.38720283166858</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-24758.82138059601</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>22.42946918417488</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8229630447503807</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1602.884</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.9302640330299551</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1931.752933011086</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.94309846996014</v>
+      </c>
+      <c r="F25" t="n">
+        <v>3.57814e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-55.537</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.16572164948454</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.8999999999999132</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.43159509202457</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.099876644736819</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>85.37456612357062</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>12.3601932199479</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-24325.7259433379</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>22.58107830742051</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.000000000000043e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8233357022393375</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1584.398</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.9195353334393472</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1910.089900850244</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9325223905162008</v>
+      </c>
+      <c r="F26" t="n">
+        <v>3.6039e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-56.04</v>
+      </c>
+      <c r="H26" t="n">
+        <v/>
+      </c>
+      <c r="I26" t="n">
+        <v/>
+      </c>
+      <c r="J26" t="n">
+        <v/>
+      </c>
+      <c r="K26" t="n">
+        <v/>
+      </c>
+      <c r="L26" t="n">
+        <v>19.61729010513972</v>
+      </c>
+      <c r="M26" t="n">
+        <v>85.70559847180388</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>13.31697755772579</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-25977.77842972598</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>22.07505510770022</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.823675887328453</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1563.037</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.9071380732448773</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1887.240790361848</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9213672573864339</v>
+      </c>
+      <c r="F27" t="n">
+        <v>3.63083e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-56.484</v>
+      </c>
+      <c r="H27" t="n">
+        <v/>
+      </c>
+      <c r="I27" t="n">
+        <v/>
+      </c>
+      <c r="J27" t="n">
+        <v/>
+      </c>
+      <c r="K27" t="n">
+        <v/>
+      </c>
+      <c r="L27" t="n">
+        <v>18.65952497497768</v>
+      </c>
+      <c r="M27" t="n">
+        <v>85.63825527665279</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>13.11059185151038</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-25258.80810553961</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>22.30615019188292</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.000000000001834e-08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8239646086605117</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1540.405</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.8940031641712738</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1867.899570984162</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.9119247070009522</v>
+      </c>
+      <c r="F28" t="n">
+        <v>3.65282e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-56.898</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.080913348946136</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.528904847396861</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.964970645792476</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3.215358361774638</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>85.32604517599174</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>12.23131827771866</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-23245.16000230626</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>21.13048765264193</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8242499916326076</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1527.777</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.8866742656302051</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1853.240117267767</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.9047678350562394</v>
+      </c>
+      <c r="F29" t="n">
+        <v>3.67409e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-57.278</v>
+      </c>
+      <c r="H29" t="n">
+        <v/>
+      </c>
+      <c r="I29" t="n">
+        <v/>
+      </c>
+      <c r="J29" t="n">
+        <v/>
+      </c>
+      <c r="K29" t="n">
+        <v/>
+      </c>
+      <c r="L29" t="n">
+        <v>15.63948427037806</v>
+      </c>
+      <c r="M29" t="n">
+        <v>85.47432271066397</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>12.63381550331409</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-23804.86509309887</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>19.20038643319879</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.000000000000081e-08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8245862782282972</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1504.661</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.873258458006247</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1834.265492363511</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.89550425925963</v>
+      </c>
+      <c r="F30" t="n">
+        <v>3.69758e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-57.632</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.05148148148148767</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.8073550212163488</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.814019520851761</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.350581915846059</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>85.12585822455783</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>11.72667954547315</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-21804.10890993775</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>18.88254883238824</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.000000000001189e-08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8249583368294882</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1487.335</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.863202986346241</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1820.165018751714</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8886202862309098</v>
+      </c>
+      <c r="F31" t="n">
+        <v>3.71604e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-57.955</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.2517307692307522</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.619925742574302</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.028626692456536</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.556556986170798</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>85.03653081940523</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>11.51460381523546</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-21190.06294064082</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>17.07166583184346</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.8253120335653574</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1474.421</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.8557081022981448</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1801.698360796722</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8796047042871652</v>
+      </c>
+      <c r="F32" t="n">
+        <v>3.73813e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-58.296</v>
+      </c>
+      <c r="H32" t="n">
+        <v/>
+      </c>
+      <c r="I32" t="n">
+        <v/>
+      </c>
+      <c r="J32" t="n">
+        <v/>
+      </c>
+      <c r="K32" t="n">
+        <v/>
+      </c>
+      <c r="L32" t="n">
+        <v>11.37329456554101</v>
+      </c>
+      <c r="M32" t="n">
+        <v>85.26673206274738</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>12.07735981958195</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-22025.43501170534</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>16.8992864936198</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.8256951017135238</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1459.115</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.8468249758276351</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1788.516187658939</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.8731690534828904</v>
+      </c>
+      <c r="F33" t="n">
+        <v>3.76013e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-58.604</v>
+      </c>
+      <c r="H33" t="n">
+        <v/>
+      </c>
+      <c r="I33" t="n">
+        <v/>
+      </c>
+      <c r="J33" t="n">
+        <v/>
+      </c>
+      <c r="K33" t="n">
+        <v/>
+      </c>
+      <c r="L33" t="n">
+        <v>7.841791312716895</v>
+      </c>
+      <c r="M33" t="n">
+        <v>85.01765938439033</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>11.47077097471103</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-20698.13310447288</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>14.21596200186957</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.000000000000296e-08</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.8260742225357488</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1444.263</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.8382053368403091</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1773.777722722984</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8659736075782249</v>
+      </c>
+      <c r="F34" t="n">
+        <v>3.77787e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-58.922</v>
+      </c>
+      <c r="H34" t="n">
+        <v/>
+      </c>
+      <c r="I34" t="n">
+        <v/>
+      </c>
+      <c r="J34" t="n">
+        <v/>
+      </c>
+      <c r="K34" t="n">
+        <v/>
+      </c>
+      <c r="L34" t="n">
+        <v>5.186029911891853</v>
+      </c>
+      <c r="M34" t="n">
+        <v>84.75612030995326</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>10.89569460163166</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-19445.36752758491</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>13.16397104436635</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.8264435291272435</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1421.302</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.8248794863967331</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1761.537934012502</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8599980369924471</v>
+      </c>
+      <c r="F35" t="n">
+        <v>3.79782e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-59.199</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.1277108433734979</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.040674955595003</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.920330739299603</v>
+      </c>
+      <c r="K35" t="n">
+        <v>209.3868852459078</v>
+      </c>
+      <c r="L35" t="n">
+        <v>7.128377908996096</v>
+      </c>
+      <c r="M35" t="n">
+        <v>84.64922985880173</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>10.67680243749723</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-18845.87304426603</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>10.53608036316837</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.000000000000005e-08</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.8268357757718611</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1410.956</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.818874989698452</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1745.030183817164</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8519388107396157</v>
+      </c>
+      <c r="F36" t="n">
+        <v>3.81492e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-59.501</v>
+      </c>
+      <c r="H36" t="n">
+        <v/>
+      </c>
+      <c r="I36" t="n">
+        <v/>
+      </c>
+      <c r="J36" t="n">
+        <v/>
+      </c>
+      <c r="K36" t="n">
+        <v/>
+      </c>
+      <c r="L36" t="n">
+        <v>2.834550189885208</v>
+      </c>
+      <c r="M36" t="n">
+        <v>84.5964145509308</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>10.5718338092747</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-18479.29582233515</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>10.04804241982436</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.000000000000436e-08</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.8272286976949332</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1388.711</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.8059646833913509</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1728.540086312317</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.8438882026827799</v>
+      </c>
+      <c r="F37" t="n">
+        <v>3.83809e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-59.847</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.2510101010100745</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.7450349650349404</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.847736976942892</v>
+      </c>
+      <c r="K37" t="n">
+        <v>526.3167910447532</v>
+      </c>
+      <c r="L37" t="n">
+        <v>7.739901477832682</v>
+      </c>
+      <c r="M37" t="n">
+        <v>83.8873259842145</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>9.337686704726467</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-16080.87588875104</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>8.924821047725914</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.000000000000143e-08</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.827645713622947</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1374.654</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.7978064376840495</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1714.972551873143</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.8372644151620999</v>
+      </c>
+      <c r="F38" t="n">
+        <v>3.85732e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-60.142</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.2927835051546179</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.346588693957132</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.769415807560104</v>
+      </c>
+      <c r="K38" t="n">
+        <v>669.3191943127331</v>
+      </c>
+      <c r="L38" t="n">
+        <v>7.911368909512697</v>
+      </c>
+      <c r="M38" t="n">
+        <v>83.84950143556108</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>9.27982204989377</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-15817.82457141673</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>7.678087237921545</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.000000000000003e-08</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.8281011956147474</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1359.802</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.7891867986967236</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1703.287545923993</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.8315596943130723</v>
+      </c>
+      <c r="F39" t="n">
+        <v>3.87449e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-60.412</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.2045614035087634</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.137337192474646</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2.151304347826123</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>8.168038353975263</v>
+      </c>
+      <c r="M39" t="n">
+        <v>83.03150958013086</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>8.181541091792829</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-13761.67120707656</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>6.325119294504361</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.000000000000507e-08</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.8285358283569312</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1348.519</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.7826384963338097</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1689.058568096029</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.8246129844158947</v>
+      </c>
+      <c r="F40" t="n">
+        <v>3.89213e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-60.687</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.5530120481928154</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.153514376996758</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.654231119199382</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>8.684304551254741</v>
+      </c>
+      <c r="M40" t="n">
+        <v>82.77435677241263</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>7.887424022376358</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-13120.67620608886</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>4.856193814334915</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.00000000000151e-08</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.8289594362779041</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1326.99</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.7701437341631836</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1678.613503759486</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.8195136137737731</v>
+      </c>
+      <c r="F41" t="n">
+        <v>3.90892e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-60.925</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.273921971252559</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.2238938053097252</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.246821392532797</v>
+      </c>
+      <c r="K41" t="n">
+        <v>273.0250950570233</v>
+      </c>
+      <c r="L41" t="n">
+        <v>6.754679243697739</v>
+      </c>
+      <c r="M41" t="n">
+        <v>82.73382390880052</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>7.842954344332018</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-12929.07100717827</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>2.471152404217491</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.000000000000195e-08</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.8294069796176506</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1313.218</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.7621508935940039</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1663.557091946988</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.8121629434572939</v>
+      </c>
+      <c r="F42" t="n">
+        <v>3.92624e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-61.223</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.1561624649859986</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.557309941520447</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.266279069767455</v>
+      </c>
+      <c r="K42" t="n">
+        <v>419.6310495627191</v>
+      </c>
+      <c r="L42" t="n">
+        <v>7.07559643093564</v>
+      </c>
+      <c r="M42" t="n">
+        <v>81.93453877658332</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>7.05685909151844</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-11470.57186577493</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>2.474893941090727</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.000000000000456e-08</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.829831926004313</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1303.231</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.7563547493328661</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1651.000215593288</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.8060325679448339</v>
+      </c>
+      <c r="F43" t="n">
+        <v>3.94348e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-61.501</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.07575757575757334</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.5641089108910526</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.468669527897076</v>
+      </c>
+      <c r="K43" t="n">
+        <v>667.2289351851733</v>
+      </c>
+      <c r="L43" t="n">
+        <v>7.108552881401914</v>
+      </c>
+      <c r="M43" t="n">
+        <v>81.02447070953967</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>6.33125126127253</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-10139.89883350505</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>1.158993790500062</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.000000000000031e-08</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.8302774363535452</v>
       </c>
     </row>
@@ -3802,7 +6510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3969,18 +6677,6 @@
       <c r="G2" t="n">
         <v>-48.614</v>
       </c>
-      <c r="H2" t="n">
-        <v/>
-      </c>
-      <c r="I2" t="n">
-        <v/>
-      </c>
-      <c r="J2" t="n">
-        <v/>
-      </c>
-      <c r="K2" t="n">
-        <v/>
-      </c>
       <c r="L2" t="n">
         <v>10.04293692076986</v>
       </c>
@@ -4025,18 +6721,6 @@
       <c r="G3" t="n">
         <v>-51.585</v>
       </c>
-      <c r="H3" t="n">
-        <v/>
-      </c>
-      <c r="I3" t="n">
-        <v/>
-      </c>
-      <c r="J3" t="n">
-        <v/>
-      </c>
-      <c r="K3" t="n">
-        <v/>
-      </c>
       <c r="L3" t="n">
         <v>13.23688585896683</v>
       </c>
@@ -4137,18 +6821,6 @@
       <c r="G5" t="n">
         <v>-53.561</v>
       </c>
-      <c r="H5" t="n">
-        <v/>
-      </c>
-      <c r="I5" t="n">
-        <v/>
-      </c>
-      <c r="J5" t="n">
-        <v/>
-      </c>
-      <c r="K5" t="n">
-        <v/>
-      </c>
       <c r="L5" t="n">
         <v>16.09407295805488</v>
       </c>
@@ -4193,18 +6865,6 @@
       <c r="G6" t="n">
         <v>-54.167</v>
       </c>
-      <c r="H6" t="n">
-        <v/>
-      </c>
-      <c r="I6" t="n">
-        <v/>
-      </c>
-      <c r="J6" t="n">
-        <v/>
-      </c>
-      <c r="K6" t="n">
-        <v/>
-      </c>
       <c r="L6" t="n">
         <v>16.96308812353972</v>
       </c>
@@ -4305,18 +6965,6 @@
       <c r="G8" t="n">
         <v>-55.183</v>
       </c>
-      <c r="H8" t="n">
-        <v/>
-      </c>
-      <c r="I8" t="n">
-        <v/>
-      </c>
-      <c r="J8" t="n">
-        <v/>
-      </c>
-      <c r="K8" t="n">
-        <v/>
-      </c>
       <c r="L8" t="n">
         <v>18.62414649420217</v>
       </c>
@@ -4417,18 +7065,6 @@
       <c r="G10" t="n">
         <v>-56.006</v>
       </c>
-      <c r="H10" t="n">
-        <v/>
-      </c>
-      <c r="I10" t="n">
-        <v/>
-      </c>
-      <c r="J10" t="n">
-        <v/>
-      </c>
-      <c r="K10" t="n">
-        <v/>
-      </c>
       <c r="L10" t="n">
         <v>20.1917131174878</v>
       </c>
@@ -4473,18 +7109,6 @@
       <c r="G11" t="n">
         <v>-56.336</v>
       </c>
-      <c r="H11" t="n">
-        <v/>
-      </c>
-      <c r="I11" t="n">
-        <v/>
-      </c>
-      <c r="J11" t="n">
-        <v/>
-      </c>
-      <c r="K11" t="n">
-        <v/>
-      </c>
       <c r="L11" t="n">
         <v>20.06663439230603</v>
       </c>
@@ -4504,6 +7128,566 @@
         <v>1.000000000000037e-08</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.8303127365707181</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1799.67</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2109.780841504336</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3.26362e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-48.614</v>
+      </c>
+      <c r="H12" t="n">
+        <v/>
+      </c>
+      <c r="I12" t="n">
+        <v/>
+      </c>
+      <c r="J12" t="n">
+        <v/>
+      </c>
+      <c r="K12" t="n">
+        <v/>
+      </c>
+      <c r="L12" t="n">
+        <v>10.04293692076986</v>
+      </c>
+      <c r="M12" t="n">
+        <v>82.87246204251296</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>7.997140332641517</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-17035.16492583882</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>6.305165326231872</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.000000000000019e-08</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.8266837363685654</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1651.82</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.9178460495535294</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1941.35736536491</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.9201701556739253</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3.50995e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-51.585</v>
+      </c>
+      <c r="H13" t="n">
+        <v/>
+      </c>
+      <c r="I13" t="n">
+        <v/>
+      </c>
+      <c r="J13" t="n">
+        <v/>
+      </c>
+      <c r="K13" t="n">
+        <v/>
+      </c>
+      <c r="L13" t="n">
+        <v>13.23688585896683</v>
+      </c>
+      <c r="M13" t="n">
+        <v>84.29810912628179</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>10.01536353342914</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-19903.46052767711</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>21.68685063077044</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.000000000001121e-08</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8273785291472333</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1596.015</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.8868375868909302</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1897.58059120979</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.899420714170842</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3.5845e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-52.828</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.18052805280527</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.022495894909689</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.760033726812839</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.833603082851622</v>
+      </c>
+      <c r="L14" t="n">
+        <v>29.84174166225471</v>
+      </c>
+      <c r="M14" t="n">
+        <v>84.47525403802632</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>10.33859206957012</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-20017.32349947653</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>21.4251014599414</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.000000000001104e-08</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8276890499240875</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1579</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.8773830757861164</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1873.0384948476</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.8877881806491655</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3.62271e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-53.561</v>
+      </c>
+      <c r="H15" t="n">
+        <v/>
+      </c>
+      <c r="I15" t="n">
+        <v/>
+      </c>
+      <c r="J15" t="n">
+        <v/>
+      </c>
+      <c r="K15" t="n">
+        <v/>
+      </c>
+      <c r="L15" t="n">
+        <v>16.09407295805488</v>
+      </c>
+      <c r="M15" t="n">
+        <v>85.08080360645602</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>11.61875326434367</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-22291.09534960582</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>20.94084482415121</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.000000000001934e-08</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.8279820818544708</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1557.156</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.8652452949707446</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1850.13318667199</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.8769314567065601</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3.65422e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-54.167</v>
+      </c>
+      <c r="H16" t="n">
+        <v/>
+      </c>
+      <c r="I16" t="n">
+        <v/>
+      </c>
+      <c r="J16" t="n">
+        <v/>
+      </c>
+      <c r="K16" t="n">
+        <v/>
+      </c>
+      <c r="L16" t="n">
+        <v>16.96308812353972</v>
+      </c>
+      <c r="M16" t="n">
+        <v>85.23320703257785</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>11.9920302377218</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-22726.89571323263</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>20.79492570099592</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.000000000000042e-08</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.8282968464883121</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1527.902</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.848990092628093</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1829.641289723358</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.8672186483686002</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3.68586e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-54.696</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.2501901140684187</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.9626220362621808</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.058834951456245</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.845380434782664</v>
+      </c>
+      <c r="L17" t="n">
+        <v>43.90265856437524</v>
+      </c>
+      <c r="M17" t="n">
+        <v>85.13928882704994</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>11.75923810363861</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-21966.10306427179</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>19.53105388712913</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.000000000000097e-08</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.828662381842392</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1510.324</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.8392227463923942</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1811.644763329082</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.858688602953341</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3.71476e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-55.183</v>
+      </c>
+      <c r="H18" t="n">
+        <v/>
+      </c>
+      <c r="I18" t="n">
+        <v/>
+      </c>
+      <c r="J18" t="n">
+        <v/>
+      </c>
+      <c r="K18" t="n">
+        <v/>
+      </c>
+      <c r="L18" t="n">
+        <v>18.62414649420217</v>
+      </c>
+      <c r="M18" t="n">
+        <v>85.50323347619953</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>12.71537901578058</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-23546.80736587457</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>17.43637473852698</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.000000000000196e-08</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.8290488156660615</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1487.341</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.8264520717687132</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1792.230154839416</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.8494864109020458</v>
+      </c>
+      <c r="F19" t="n">
+        <v>3.74348e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-55.595</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.09807460890493576</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.927534246575372</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.711515664690904</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.044092219020165</v>
+      </c>
+      <c r="L19" t="n">
+        <v>54.98396604574329</v>
+      </c>
+      <c r="M19" t="n">
+        <v>85.40079520789749</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>12.43098924070793</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-22713.01822669869</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>16.39458482639441</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.000000000000013e-08</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.8294575281000326</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1474.733</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.8194463429406504</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1772.151212762702</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.8399693361036997</v>
+      </c>
+      <c r="F20" t="n">
+        <v>3.77123e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-56.006</v>
+      </c>
+      <c r="H20" t="n">
+        <v/>
+      </c>
+      <c r="I20" t="n">
+        <v/>
+      </c>
+      <c r="J20" t="n">
+        <v/>
+      </c>
+      <c r="K20" t="n">
+        <v/>
+      </c>
+      <c r="L20" t="n">
+        <v>20.1917131174878</v>
+      </c>
+      <c r="M20" t="n">
+        <v>85.7844482803424</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>13.56699175309253</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-24584.77447526265</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>16.3365626140818</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.000000000000467e-08</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.8298920214506248</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1457.247</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.8097301171881512</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1756.363274543375</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.8324861236729386</v>
+      </c>
+      <c r="F21" t="n">
+        <v>3.7933e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-56.336</v>
+      </c>
+      <c r="H21" t="n">
+        <v/>
+      </c>
+      <c r="I21" t="n">
+        <v/>
+      </c>
+      <c r="J21" t="n">
+        <v/>
+      </c>
+      <c r="K21" t="n">
+        <v/>
+      </c>
+      <c r="L21" t="n">
+        <v>20.06663439230603</v>
+      </c>
+      <c r="M21" t="n">
+        <v>85.78032281468909</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>13.55367965450652</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-24296.18936322996</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>14.23502707910302</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.000000000000037e-08</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.8303127365707181</v>
       </c>
     </row>
@@ -4518,7 +7702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5836,6 +9020,1182 @@
         <v>1e-08</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.842883274437631</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1097.688</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1497.669202872253</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>4.23414e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-58.246</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.8875949367089176</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.9277419354838548</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.503529411764728</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.451873767258388</v>
+      </c>
+      <c r="L23" t="n">
+        <v>19.95946851888533</v>
+      </c>
+      <c r="M23" t="n">
+        <v>84.29157986772481</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>10.00383198900444</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-14794.51045243109</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-19.55799498900126</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8321077831733287</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1022.422</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9314322466857613</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1415.471196895312</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9451160471088668</v>
+      </c>
+      <c r="F24" t="n">
+        <v>4.3275e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-60.751</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.2821522309711143</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.416560509554228</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.760196905766502</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1.742947903430725</v>
+      </c>
+      <c r="L24" t="n">
+        <v>19.36522839351223</v>
+      </c>
+      <c r="M24" t="n">
+        <v>84.76359292678485</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>10.91133041405952</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-15334.95902045895</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-7.403509762901535</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8324967839821114</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>995.0419999999999</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.9064889112388946</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1381.9012024263</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9227012211882759</v>
+      </c>
+      <c r="F25" t="n">
+        <v>4.35951e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-61.788</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2.261971830985526</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.3104308390022535</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.7678657074341251</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1.212359550561808</v>
+      </c>
+      <c r="L25" t="n">
+        <v>18.47272800731751</v>
+      </c>
+      <c r="M25" t="n">
+        <v>84.81592564277415</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>11.02209187924315</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-15152.5633894038</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-2.79294239746082</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.000000000000383e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8329038413179529</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>972.7489999999999</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.8861798616728978</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1363.335588154215</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9103048827735718</v>
+      </c>
+      <c r="F26" t="n">
+        <v>4.38116e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-62.488</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.1949999999999439</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.5015037593984536</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.471428571428488</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.217322834645704</v>
+      </c>
+      <c r="L26" t="n">
+        <v>19.09993825200998</v>
+      </c>
+      <c r="M26" t="n">
+        <v>84.92344506142399</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>11.25680105724169</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-15206.82816016236</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-5.999455489552702</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8334844306000366</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>953.058</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.868241248879463</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1339.96721225882</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.8947017203057992</v>
+      </c>
+      <c r="F27" t="n">
+        <v>4.40232e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-63.058</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.7859154929577603</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.127598566308095</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.085694249649361</v>
+      </c>
+      <c r="L27" t="n">
+        <v>23.22126879201184</v>
+      </c>
+      <c r="M27" t="n">
+        <v>85.28020782147409</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>12.11199977031418</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-16132.01103357115</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-6.636942514395741</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.000000000002174e-08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8340083973848813</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>937.2249999999999</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.8538172959893885</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1318.762749148907</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.8805434114688101</v>
+      </c>
+      <c r="F28" t="n">
+        <v>4.42322e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-63.542</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.2932114882507049</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.8414698162729236</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.474242424242364</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.627355623100359</v>
+      </c>
+      <c r="L28" t="n">
+        <v>29.57202562288776</v>
+      </c>
+      <c r="M28" t="n">
+        <v>85.52805428366283</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>12.78624350064413</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-16828.88792932818</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-5.830822084520833</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.000000000001083e-08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8344343892557708</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>917.6209999999999</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.8359579406898862</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1302.331628218055</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.8695722831987349</v>
+      </c>
+      <c r="F29" t="n">
+        <v>4.44305e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-63.966</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.1460526315789201</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.4932862190812675</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.752820512820413</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1.621997874601445</v>
+      </c>
+      <c r="L29" t="n">
+        <v>23.85590927826167</v>
+      </c>
+      <c r="M29" t="n">
+        <v>85.33464182375577</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>12.25395659070184</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-15859.37896803688</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-6.941050053107006</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.000000000000239e-08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8348737990609221</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>903.425</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.823025304093695</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1281.349838354392</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.8555626542209713</v>
+      </c>
+      <c r="F30" t="n">
+        <v>4.45998e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-64.34699999999999</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.156037151702802</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.08296146044625062</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.45431578947368</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.195102040816012</v>
+      </c>
+      <c r="L30" t="n">
+        <v>20.9688700112818</v>
+      </c>
+      <c r="M30" t="n">
+        <v>85.25920610367623</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>12.05809956257537</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-15374.36538035429</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>3.583675613715968</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.000000000001981e-08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8359678274860433</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>869.933</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.7925139019466368</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1245.050904235925</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8313257038658116</v>
+      </c>
+      <c r="F31" t="n">
+        <v>4.50525e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-65.081</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.6262376237623983</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.8122186495177489</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.386295503211945</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1.670728793309423</v>
+      </c>
+      <c r="L31" t="n">
+        <v>24.99286650874291</v>
+      </c>
+      <c r="M31" t="n">
+        <v>85.51287642381136</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>12.74281711611629</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-15795.45562874301</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-5.676683017542359</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.000000000002207e-08</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.836941258026506</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>850.2719999999999</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.7746026193235235</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1229.173943793777</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8207245908752396</v>
+      </c>
+      <c r="F32" t="n">
+        <v>4.52218e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-65.41500000000001</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.2400327381973486</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.4854925414063918</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.58730002659417</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.550248110077668</v>
+      </c>
+      <c r="L32" t="n">
+        <v>47.0744364867566</v>
+      </c>
+      <c r="M32" t="n">
+        <v>85.13160294092722</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>11.74058399299445</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-14297.14802215251</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-5.824419741763336</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.000000000000186e-08</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.8373959246190945</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>836.0520000000001</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.7616481185910751</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1214.322982752668</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.8108085419823154</v>
+      </c>
+      <c r="F33" t="n">
+        <v>4.53792e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-65.751</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.1261221828733325</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.5013407862531229</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.519097170651178</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.815182623530424</v>
+      </c>
+      <c r="L33" t="n">
+        <v>44.18815138896286</v>
+      </c>
+      <c r="M33" t="n">
+        <v>85.16390910288288</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>11.81939121911365</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-14220.3889639639</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-5.999618658641566</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.11296106566074e-08</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.8301202655219043</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>825.3199999999999</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.7518712056613536</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1251.307708451269</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8355033982480852</v>
+      </c>
+      <c r="F34" t="n">
+        <v>4.55112e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-66.081</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.08728489781672054</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.9125130736155846</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.88783189296646</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.852161434378508</v>
+      </c>
+      <c r="L34" t="n">
+        <v>47.41960431019216</v>
+      </c>
+      <c r="M34" t="n">
+        <v>85.27032811850945</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>12.08658435245719</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-14372.85713044984</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-36.68219311720679</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.00000000000037e-08</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.8383400912304341</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>815.347</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.7427857460407692</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1236.470209255468</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.82559633788566</v>
+      </c>
+      <c r="F35" t="n">
+        <v>4.56581e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-66.371</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.3328671328671466</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.5071078431372531</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.10395604395602</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2.194921875000048</v>
+      </c>
+      <c r="L35" t="n">
+        <v>21.96787808658928</v>
+      </c>
+      <c r="M35" t="n">
+        <v>85.43648124167997</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>12.52861492137982</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-14752.00982808087</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>-36.39669031959875</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.000000000000008e-08</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.8388012164334024</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>803.2450000000001</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.7317607553330273</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1171.131702189083</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.7819695430359846</v>
+      </c>
+      <c r="F36" t="n">
+        <v>4.58282e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-66.672</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.1378811086042951</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.6977622439447728</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.709449109781569</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.753867862908704</v>
+      </c>
+      <c r="L36" t="n">
+        <v>42.19845363341759</v>
+      </c>
+      <c r="M36" t="n">
+        <v>85.35199058660156</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>12.29989707922384</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-14282.7519702549</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-5.84835100489147</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.000000000000044e-08</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.8393101945971007</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>789.414</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.7191606358090823</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1155.317234678082</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.7714101568373019</v>
+      </c>
+      <c r="F37" t="n">
+        <v>4.59592e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-66.971</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.2982800888684479</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.8429199155084094</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.792057239721545</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.611013103612479</v>
+      </c>
+      <c r="L37" t="n">
+        <v>41.76446205969599</v>
+      </c>
+      <c r="M37" t="n">
+        <v>85.36703815480016</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>12.34002189431738</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-14163.21347150649</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-4.65242714549629</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.8397868574760489</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>772.1279999999999</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.703412991669764</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1140.943067828761</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.7618124654233672</v>
+      </c>
+      <c r="F38" t="n">
+        <v>4.61087e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-67.261</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.04966584997506734</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.2213307910433163</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.975105197437993</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1.712809522370996</v>
+      </c>
+      <c r="L38" t="n">
+        <v>25.72104463456168</v>
+      </c>
+      <c r="M38" t="n">
+        <v>85.02808390379695</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>11.49494306050369</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-12979.62958242628</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-4.159634048516864</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.8402883893917831</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>771.028</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.7024108854246379</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1129.640760913212</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.7542658677542206</v>
+      </c>
+      <c r="F39" t="n">
+        <v>4.62663e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-67.56399999999999</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.6528089887640606</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.7471153846154235</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.418402777777863</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2.160793465577637</v>
+      </c>
+      <c r="L39" t="n">
+        <v>24.98987117065673</v>
+      </c>
+      <c r="M39" t="n">
+        <v>85.74503766977601</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>13.44087383798877</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-15118.41544456057</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-5.753585301465932</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.000000000000173e-08</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.8407914392213998</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>759.961</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.6923287855929917</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1114.430761127326</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.7441100871875133</v>
+      </c>
+      <c r="F40" t="n">
+        <v>4.64176e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-67.84399999999999</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1.392337164750732</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.3510729613734014</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.21411935953422</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2.001702610669688</v>
+      </c>
+      <c r="L40" t="n">
+        <v>24.89573249037776</v>
+      </c>
+      <c r="M40" t="n">
+        <v>85.7597954527312</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>13.48782614974743</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-14985.98171521551</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-4.301482193057495</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.00000000000009e-08</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.8412945433784456</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>741.038</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.6750898251597903</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1099.682306939375</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.7342624825498095</v>
+      </c>
+      <c r="F41" t="n">
+        <v>4.65548e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-68.121</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.3704297909920484</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.5717856008035495</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.004194206607812</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2.444802431856331</v>
+      </c>
+      <c r="L41" t="n">
+        <v>28.45831503359108</v>
+      </c>
+      <c r="M41" t="n">
+        <v>85.26109577660421</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>12.06292983031289</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-13152.69576382672</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>-3.763151348321571</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.8418198223054431</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>730.3839999999999</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.6653839706729051</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1085.591085155139</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7248537147409959</v>
+      </c>
+      <c r="F42" t="n">
+        <v>4.66994e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-68.43300000000001</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.3572397520006366</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.080586108610235</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.90478664853881</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.853529042604027</v>
+      </c>
+      <c r="L42" t="n">
+        <v>10.90406168021083</v>
+      </c>
+      <c r="M42" t="n">
+        <v>85.44933411728937</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>12.56415055985919</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-13556.25032917496</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-3.528623992015696</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.842349213806347</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>721.009</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.6568432924473985</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1072.263141061181</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.7159545906430994</v>
+      </c>
+      <c r="F43" t="n">
+        <v>4.68552e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-68.718</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.4457353332360831</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.7378880632915988</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.774215108682587</v>
+      </c>
+      <c r="K43" t="n">
+        <v>3.124725781107508</v>
+      </c>
+      <c r="L43" t="n">
+        <v>2.399510270709893</v>
+      </c>
+      <c r="M43" t="n">
+        <v>85.47404457713796</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>12.63303587865937</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-13463.88744921737</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>-3.447658904141463</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.842883274437631</v>
       </c>
     </row>
@@ -5850,7 +10210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6552,6 +10912,566 @@
         <v>1.000000000000713e-08</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.8359167128145656</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1103.268</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1484.470603677986</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>4.24516e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-56.793</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.4389021479714156</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.730769230769181</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.281444759206768</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.575904486251795</v>
+      </c>
+      <c r="L12" t="n">
+        <v>13.38475750765249</v>
+      </c>
+      <c r="M12" t="n">
+        <v>83.29187978546906</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>8.502195143941647</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-12557.0569811854</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-3.385301328636388</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.8329929119116914</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1060.644</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.9613656881192965</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1433.725139029858</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.9658157834029188</v>
+      </c>
+      <c r="F13" t="n">
+        <v>4.3251e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-58.699</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.6029032258065347</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4.145999999999344</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.814307004471065</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.915798045602605</v>
+      </c>
+      <c r="L13" t="n">
+        <v>17.05408389641397</v>
+      </c>
+      <c r="M13" t="n">
+        <v>84.15644170843692</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>9.77092698713358</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-14015.6778187673</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.7976312391873535</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8332372655986989</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1033.375</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.9366491187997839</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1408.894823824665</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.9490890694190428</v>
+      </c>
+      <c r="F14" t="n">
+        <v>4.35569e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-59.731</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.009859154929575547</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.3017716535433421</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.645244956772156</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.497611630321974</v>
+      </c>
+      <c r="L14" t="n">
+        <v>16.47358831974366</v>
+      </c>
+      <c r="M14" t="n">
+        <v>84.33490526499038</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>10.08084580072607</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-14183.87339017491</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.8028595961676501</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8334817869172857</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1009.235</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.9147686690813113</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1388.977497344874</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.9356719452062473</v>
+      </c>
+      <c r="F15" t="n">
+        <v>4.3794e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-60.5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.1333333333333077</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.584943181818164</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.125121951219435</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.781469298245574</v>
+      </c>
+      <c r="L15" t="n">
+        <v>17.50734696948017</v>
+      </c>
+      <c r="M15" t="n">
+        <v>84.50140570356353</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>10.38806846242153</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-14387.35384990727</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-0.7914516850244127</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.833799035812953</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>987.1590000000001</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.8947590250057104</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1366.486245582226</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.9205209198461477</v>
+      </c>
+      <c r="F16" t="n">
+        <v>4.40335e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-61.103</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.1234042553191611</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.01333333333333857</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.6645454545454504</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1.842955326460339</v>
+      </c>
+      <c r="L16" t="n">
+        <v>16.13921346509225</v>
+      </c>
+      <c r="M16" t="n">
+        <v>84.46374403670583</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>10.3169639507533</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-14038.85517380458</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.156693708779926</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.8342937424826312</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>971.6859999999999</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.8807343274707504</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1341.021506084798</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.9033668317595697</v>
+      </c>
+      <c r="F17" t="n">
+        <v>4.44043e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-61.73</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.818380062305196</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.7654676258993085</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.606504065040689</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.369515839808762</v>
+      </c>
+      <c r="L17" t="n">
+        <v>30.91630218200714</v>
+      </c>
+      <c r="M17" t="n">
+        <v>85.2113548665366</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>11.93705273448915</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-16069.93145612055</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-1.035281496752305</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.000000000000147e-08</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.8347660144063926</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>942.199</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.8540073672036168</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1338.333314415586</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.9015559561096563</v>
+      </c>
+      <c r="F18" t="n">
+        <v>4.46692e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-62.253</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.9744360902253231</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.280726256983201</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.121014492753639</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.736442516269007</v>
+      </c>
+      <c r="L18" t="n">
+        <v>19.69227215590608</v>
+      </c>
+      <c r="M18" t="n">
+        <v>84.91994308826736</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>11.24900032585141</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-14829.49186189311</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-14.77622543613768</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.000000000000054e-08</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.8350573690958482</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>923.4749999999999</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.8370359695015172</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1299.927874327808</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.8756844838200583</v>
+      </c>
+      <c r="F19" t="n">
+        <v>4.49304e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-62.734</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.6155172413792549</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.8594654788418399</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.40054794520522</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.444965104685971</v>
+      </c>
+      <c r="L19" t="n">
+        <v>20.45718987837393</v>
+      </c>
+      <c r="M19" t="n">
+        <v>85.00364251023134</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>11.43842763082429</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-14851.65772171988</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-3.924889600233314</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.8350383188528258</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>905.785</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.8210017874170192</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1280.151589668429</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.8623623711353205</v>
+      </c>
+      <c r="F20" t="n">
+        <v>4.5171e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-63.161</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.067944250871142</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.4464527027027063</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.241337386018242</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1.956617647058906</v>
+      </c>
+      <c r="L20" t="n">
+        <v>21.18666575845444</v>
+      </c>
+      <c r="M20" t="n">
+        <v>85.07494422047473</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>11.60486211880897</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-14844.99680820529</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-4.203297367555592</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.000000000001497e-08</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.8354669955290038</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>884.502</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.8017109170210682</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1261.813890802021</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.8500093485689099</v>
+      </c>
+      <c r="F21" t="n">
+        <v>4.54192e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-63.571</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.7470852017936435</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.3737896494157039</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.894354838709672</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1.286217457886645</v>
+      </c>
+      <c r="L21" t="n">
+        <v>18.67590530554978</v>
+      </c>
+      <c r="M21" t="n">
+        <v>84.97518770845778</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>11.37332294569194</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-14297.77010131324</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-4.81952807710627</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.000000000000713e-08</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.8359167128145656</v>
       </c>
     </row>
@@ -6566,7 +11486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7884,6 +12804,1182 @@
         <v>1.000000000000003e-08</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.8433912690254576</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1030.872</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1450.90482612377</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>4.37132e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-59.585</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.239095744680856</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.980515759312291</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.334017595307888</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.363323262840057</v>
+      </c>
+      <c r="L23" t="n">
+        <v>23.82595615524672</v>
+      </c>
+      <c r="M23" t="n">
+        <v>84.69957835180981</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>10.77881024896596</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-15220.49099597104</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-54.3119300782173</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8325931877394172</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1006.711</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9765625606282836</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1385.627504421491</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.955009232496198</v>
+      </c>
+      <c r="F24" t="n">
+        <v>4.39257e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-61.209</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.425882352941161</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.8982339955849531</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1.696547619047595</v>
+      </c>
+      <c r="L24" t="n">
+        <v>20.91324940953918</v>
+      </c>
+      <c r="M24" t="n">
+        <v>84.96440355693494</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>11.34884054817086</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-15759.77187096125</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-2.184150067233873</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8320871781901723</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>976.9299999999999</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.9476734259927516</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1365.958051384683</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9414525520836327</v>
+      </c>
+      <c r="F25" t="n">
+        <v>4.42755e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-62.137</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.04719101123595645</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.6905999999999675</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.9785123966941569</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.087645348837366</v>
+      </c>
+      <c r="L25" t="n">
+        <v>22.60308904714875</v>
+      </c>
+      <c r="M25" t="n">
+        <v>85.06970479274403</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>11.59246863346858</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-15743.34464358955</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-8.552571496712972</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.832484552392343</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>961.5530000000001</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.9327569281152268</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1334.310874213983</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9196405237542157</v>
+      </c>
+      <c r="F26" t="n">
+        <v>4.44808e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-62.644</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.527188940092435</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.8564154786151337</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.858105646630206</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.51448551448552</v>
+      </c>
+      <c r="L26" t="n">
+        <v>28.13137864428654</v>
+      </c>
+      <c r="M26" t="n">
+        <v>85.41196432998279</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>12.46138149116811</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-16705.190842766</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-13.98596630929978</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.000000000000082e-08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8335082663071087</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>924.0379999999999</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.8963654071504511</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1309.70572375147</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9026820368710698</v>
+      </c>
+      <c r="F27" t="n">
+        <v>4.49283e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-63.4</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.2080952380952536</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.518644067796547</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.7889929742388265</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1.975459317585316</v>
+      </c>
+      <c r="L27" t="n">
+        <v>23.20274917771795</v>
+      </c>
+      <c r="M27" t="n">
+        <v>85.29685877639768</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>12.15507523593054</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-15810.28106044284</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-10.11581567355347</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.000000000002293e-08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8338717127474594</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>900.8800000000001</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.8739009304743945</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1292.149500437876</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.890581847391035</v>
+      </c>
+      <c r="F28" t="n">
+        <v>4.51206e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-63.796</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.2292207792207749</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.1060000000000045</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.7062271062271</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1.083333333333269</v>
+      </c>
+      <c r="L28" t="n">
+        <v>19.89093419738325</v>
+      </c>
+      <c r="M28" t="n">
+        <v>84.99323427216088</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>11.41452792862191</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-14598.38951733558</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-10.26904699464922</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.000000000000391e-08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8343117487425564</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>884.3800000000001</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.8578950635966445</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1274.718995964014</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.8785683064888181</v>
+      </c>
+      <c r="F29" t="n">
+        <v>4.53291e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-64.19499999999999</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.1110903837185272</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.6501104785506829</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.090462591821676</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.615754127975166</v>
+      </c>
+      <c r="L29" t="n">
+        <v>42.99223780040595</v>
+      </c>
+      <c r="M29" t="n">
+        <v>84.95593288638126</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>11.32968348111185</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-14273.13733194418</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-10.22505815694774</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.000000000000033e-08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8347827323162988</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>873.403</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.8472467968865194</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1257.031186278434</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.866377424380558</v>
+      </c>
+      <c r="F30" t="n">
+        <v>4.55235e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-64.556</v>
+      </c>
+      <c r="H30" t="n">
+        <v>41.84999999956538</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.03312883435580984</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.084412470023971</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1.272423025435136</v>
+      </c>
+      <c r="L30" t="n">
+        <v>20.12970626298159</v>
+      </c>
+      <c r="M30" t="n">
+        <v>85.1665127896344</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>11.82578838154075</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-14724.14165709195</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-9.875793257105784</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.000000000000043e-08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8352437186803376</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>858.8789999999999</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.833157753823947</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1284.729159261568</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8854675621238672</v>
+      </c>
+      <c r="F31" t="n">
+        <v>4.57109e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-64.892</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.5553097345132646</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.292178770949652</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.83633217993051</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1.306085753803526</v>
+      </c>
+      <c r="L31" t="n">
+        <v>21.02973245681488</v>
+      </c>
+      <c r="M31" t="n">
+        <v>85.2853650046402</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>12.12530877963914</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-14923.19798881167</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-35.168648027681</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.8357672395960193</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>841.515</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.8163137615533257</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1225.393717312579</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8445720871894367</v>
+      </c>
+      <c r="F32" t="n">
+        <v>4.59292e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-65.282</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.8298113207547476</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.1738341968911918</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.6802180685358307</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1.36928895612703</v>
+      </c>
+      <c r="L32" t="n">
+        <v>20.43210742181096</v>
+      </c>
+      <c r="M32" t="n">
+        <v>85.26118134802077</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>12.06314865376089</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-14624.64625254544</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-10.41703027321614</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.836339673968898</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>830.0150000000001</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.805158157365803</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1208.328794273321</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.8328105141820267</v>
+      </c>
+      <c r="F33" t="n">
+        <v>4.61286e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-65.65000000000001</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.8781818181818274</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.9632218844984357</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.9481481481481612</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1.549621785173983</v>
+      </c>
+      <c r="L33" t="n">
+        <v>20.67610247526614</v>
+      </c>
+      <c r="M33" t="n">
+        <v>85.27067498680989</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>12.0874748724692</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-14455.31715333279</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-10.91738616057864</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.000000000000044e-08</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.8368885419044735</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>814.2909999999999</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.789905051257576</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1192.695052902398</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8220353474795418</v>
+      </c>
+      <c r="F34" t="n">
+        <v>4.63177e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-65.985</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.6273927392739019</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.6871052631578985</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.31825192802073</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.491134020618358</v>
+      </c>
+      <c r="L34" t="n">
+        <v>20.64423150311537</v>
+      </c>
+      <c r="M34" t="n">
+        <v>85.30855357734916</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>12.18551167942328</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-14379.48901530511</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-11.45534060728357</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.000000000000032e-08</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.8374412808543498</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>801.577</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.7775718032888661</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1176.978732024048</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8112032649091523</v>
+      </c>
+      <c r="F35" t="n">
+        <v>4.64722e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-66.291</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.06221042471042554</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.9053924219027367</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.802517307076914</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2.732774568555258</v>
+      </c>
+      <c r="L35" t="n">
+        <v>28.47249060432522</v>
+      </c>
+      <c r="M35" t="n">
+        <v>85.16346003264717</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>11.81828856485341</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-13745.31108476702</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>-10.18273444671445</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.000000000000244e-08</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.8379153493642926</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>789.8200000000001</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.7661668955990656</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1161.357287611102</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8004365735785567</v>
+      </c>
+      <c r="F36" t="n">
+        <v>4.66419e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-66.623</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.363636363636083</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.975603217158205</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.9120614035087621</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1.887393526405316</v>
+      </c>
+      <c r="L36" t="n">
+        <v>19.98301213925421</v>
+      </c>
+      <c r="M36" t="n">
+        <v>85.3217718766406</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>12.22009591001306</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-14063.41627469487</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-9.146284512329203</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.8384121433308739</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>779.105</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.7557727826539085</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1149.825167230343</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.7924883469456849</v>
+      </c>
+      <c r="F37" t="n">
+        <v>4.68247e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-66.90600000000001</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.7519999999999284</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.8403225806453644</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.6641237113402442</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1.98424242424255</v>
+      </c>
+      <c r="L37" t="n">
+        <v>20.36897692555258</v>
+      </c>
+      <c r="M37" t="n">
+        <v>85.34911493268234</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>12.29225854315993</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-13981.30618522348</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-10.71133662982697</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.000000000000015e-08</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.8389165976775568</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>767.2379999999999</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.7442611691849229</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1136.974643194984</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.7836314434438261</v>
+      </c>
+      <c r="F38" t="n">
+        <v>4.69891e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-67.21599999999999</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1.345238095237668</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.7062068965517407</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.503960396039302</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2.06439522998302</v>
+      </c>
+      <c r="L38" t="n">
+        <v>19.93755735879732</v>
+      </c>
+      <c r="M38" t="n">
+        <v>85.35152114097437</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>12.29864945710096</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-13817.13317467756</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-11.00312094313131</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.8393764144437562</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>754.0160000000001</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.731435134526886</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1120.339674316383</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.7721662056287159</v>
+      </c>
+      <c r="F39" t="n">
+        <v>4.70976e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-67.452</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.07493603070524234</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.868964219963118</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.643585122944768</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2.78240037620215</v>
+      </c>
+      <c r="L39" t="n">
+        <v>6.088107995850057</v>
+      </c>
+      <c r="M39" t="n">
+        <v>85.27729633485104</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>12.1044989798793</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-13435.46996480902</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-8.060806893597032</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.000000000000048e-08</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.8398377001424042</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>739.6190000000001</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.7174692881366456</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1108.999939890632</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.7643505762217571</v>
+      </c>
+      <c r="F40" t="n">
+        <v>4.72749e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-67.76300000000001</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.2278271944468502</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.477131128716333</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.626405353728462</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2.314555442044038</v>
+      </c>
+      <c r="L40" t="n">
+        <v>17.87258339835366</v>
+      </c>
+      <c r="M40" t="n">
+        <v>84.98131933645425</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>11.38728988891936</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-12450.89787332109</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-9.37992217969304</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.000000000000141e-08</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.8403785040264899</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>729.491</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.707644596031321</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1155.220940035276</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.7962072489079509</v>
+      </c>
+      <c r="F41" t="n">
+        <v>4.7425e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-68.051</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.1821360558120402</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1.032047320135243</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.525146576019675</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2.31600785040188</v>
+      </c>
+      <c r="L41" t="n">
+        <v>16.34433479455846</v>
+      </c>
+      <c r="M41" t="n">
+        <v>85.06418096498804</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>11.57943084299711</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-12505.15815299472</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>-51.38777726025626</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.000000000000781e-08</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.8413357784211097</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>715.3940000000001</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.6939697654024942</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1058.269129448036</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7293856291561878</v>
+      </c>
+      <c r="F42" t="n">
+        <v>4.76944e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-68.502</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.7413897280966428</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.4712296983758784</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.341602067183499</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.054945054945096</v>
+      </c>
+      <c r="L42" t="n">
+        <v>18.04630672300943</v>
+      </c>
+      <c r="M42" t="n">
+        <v>85.36916721598409</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>12.34572011487032</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-13102.68398428272</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>7.659762865930816</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.8424216063489984</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>682.413</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.6619764626452168</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1037.090696914563</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.7147889222239674</v>
+      </c>
+      <c r="F43" t="n">
+        <v>4.80279e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-69.06699999999999</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.3217473287241148</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.8247663237173271</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.921941640963257</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2.463549019585859</v>
+      </c>
+      <c r="L43" t="n">
+        <v>17.27696044348651</v>
+      </c>
+      <c r="M43" t="n">
+        <v>84.96948788281516</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>11.36037004230211</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-11653.612686609</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>-4.328940600104147</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.000000000000003e-08</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.8433912690254576</v>
       </c>
     </row>
@@ -7898,7 +13994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8600,6 +14696,566 @@
         <v>1.000000000000025e-08</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.8315389482098392</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1285.113</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1703.352852834605</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3.91163e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-53.475</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.7454545454545591</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.6358048780487715</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.818844221105524</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.424547548535715</v>
+      </c>
+      <c r="L12" t="n">
+        <v>16.31668625146886</v>
+      </c>
+      <c r="M12" t="n">
+        <v>82.81292236651709</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>7.930198535607936</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-13281.79072917973</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-27.36200052830145</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.000000000000006e-08</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.8284031854164853</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1127.67</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.8774870381048205</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1512.709613576152</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.8880776587533245</v>
+      </c>
+      <c r="F13" t="n">
+        <v>4.20174e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-57.547</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.270408163265389</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.355570469798548</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.840672782874595</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.766314199395766</v>
+      </c>
+      <c r="L13" t="n">
+        <v>30.69924737290529</v>
+      </c>
+      <c r="M13" t="n">
+        <v>84.50869731979265</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>10.40194724253539</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-15851.70328379813</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-1.228567599195912</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.000000000004021e-08</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8289223470162235</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1072.181</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.8343087339401284</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1462.618052295378</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.8586700341396606</v>
+      </c>
+      <c r="F14" t="n">
+        <v>4.27276e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-59.203</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.4534954407294752</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.7906921241050239</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.317207334273595</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.670312499999969</v>
+      </c>
+      <c r="L14" t="n">
+        <v>20.97188886248135</v>
+      </c>
+      <c r="M14" t="n">
+        <v>84.63548831530643</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>10.64929324606391</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-15655.10664406893</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.622086914171973</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8291880611169845</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1038.584</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.8081655076246214</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1435.196802512886</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.8425716375350699</v>
+      </c>
+      <c r="F15" t="n">
+        <v>4.314e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-60.2</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.05317220543806224</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.5406746031746239</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.059033078880185</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.871480144404231</v>
+      </c>
+      <c r="L15" t="n">
+        <v>19.28513144261598</v>
+      </c>
+      <c r="M15" t="n">
+        <v>84.60891718908613</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>10.59649711416417</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-15220.94529272925</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.3655264240599081</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.8294413702267376</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1011.139</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.7868094089780433</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1412.254538884987</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.8291027525710885</v>
+      </c>
+      <c r="F16" t="n">
+        <v>4.34637e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-60.958</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.2520000000000011</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.5253554502370354</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.662051282051197</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1.523755186722007</v>
+      </c>
+      <c r="L16" t="n">
+        <v>20.14885447202583</v>
+      </c>
+      <c r="M16" t="n">
+        <v>84.80183513301951</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>10.99205071730707</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-15517.04222311667</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-1.423747831272863</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.829710660250638</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>988.9290000000001</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.769526882071849</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1383.488043435705</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.8122145926097447</v>
+      </c>
+      <c r="F17" t="n">
+        <v>4.37929e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-61.586</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.1382352941176513</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.453649635036595</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.140368509212706</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.48141086749289</v>
+      </c>
+      <c r="L17" t="n">
+        <v>20.76489733801327</v>
+      </c>
+      <c r="M17" t="n">
+        <v>84.89752450767745</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>11.19931540573011</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-15534.4546766757</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.424879387193187</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.000000000000048e-08</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.8300354402130599</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>967.7239999999999</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.7530263875628058</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1368.332189969414</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.8033169332427675</v>
+      </c>
+      <c r="F18" t="n">
+        <v>4.41101e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-62.13</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.6645569620253631</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.9781645569619466</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.408559498955994</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.974384236453142</v>
+      </c>
+      <c r="L18" t="n">
+        <v>21.65651067143481</v>
+      </c>
+      <c r="M18" t="n">
+        <v>85.02603763945039</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>11.49019026745334</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-15673.25322399462</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-4.909487468848965</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.000000000000331e-08</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.8303925869631766</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>947.5649999999999</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.7373398292601507</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1344.958437778587</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.7895947310860449</v>
+      </c>
+      <c r="F19" t="n">
+        <v>4.44239e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-62.642</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.9382550335569928</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.183053691275155</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.404393939394043</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.166814551907726</v>
+      </c>
+      <c r="L19" t="n">
+        <v>27.5688320828623</v>
+      </c>
+      <c r="M19" t="n">
+        <v>85.29281186330189</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>12.14457803722284</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-16328.19756850009</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-4.991952366889791</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.000000000003297e-08</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.8307646042557969</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>917.337</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.7138181622938995</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1368.754075746922</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.8035646128570094</v>
+      </c>
+      <c r="F20" t="n">
+        <v>4.4712e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-63.094</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.8490322491451618</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.513431283803345</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.555102795831937</v>
+      </c>
+      <c r="L20" t="n">
+        <v>40.17568204186471</v>
+      </c>
+      <c r="M20" t="n">
+        <v>84.71981144865391</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>10.82034959652196</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-14216.45014198157</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-32.19194108301599</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.000000000000552e-08</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.8311487213264482</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>899.665</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.7000668423710601</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1346.932780672665</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.7907538232205916</v>
+      </c>
+      <c r="F21" t="n">
+        <v>4.49771e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-63.513</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.05945945945945714</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.7222627737226754</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.6947619047619104</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1.969176882661902</v>
+      </c>
+      <c r="L21" t="n">
+        <v>19.08251706481992</v>
+      </c>
+      <c r="M21" t="n">
+        <v>84.92702167297365</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>11.26477913511042</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-14604.09283335973</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-31.77550190223599</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.000000000000025e-08</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.8315389482098392</v>
       </c>
     </row>
@@ -8614,7 +15270,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9932,6 +16588,1182 @@
         <v>1.000000000000018e-08</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.8378569494704342</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1025.941</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1458.259168614275</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>4.31391e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-59.531</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.3729542302357828</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.01237410071943078</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.01242484969938</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1.681694915254219</v>
+      </c>
+      <c r="L23" t="n">
+        <v>16.84482306421697</v>
+      </c>
+      <c r="M23" t="n">
+        <v>84.17884112240792</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>9.808786325496181</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-14025.88224767315</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-24.10108999745114</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8300167163308894</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>958.264</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9340342183419904</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1366.571199102498</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9371250519213917</v>
+      </c>
+      <c r="F24" t="n">
+        <v>4.40301e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-61.818</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.6607287449392242</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.6020080321285322</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.043583535108876</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1.208421052631563</v>
+      </c>
+      <c r="L24" t="n">
+        <v>17.89853968774645</v>
+      </c>
+      <c r="M24" t="n">
+        <v>84.71783366981693</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>10.81627514523796</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-14704.94776391744</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-6.75025623272245</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8303059415707552</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>939.049</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.9153050711493156</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1342.949789443266</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9209266900885779</v>
+      </c>
+      <c r="F25" t="n">
+        <v>4.42917e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-62.535</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.0803468208092456</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.3881453154875469</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.8029023746701648</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.501080246913556</v>
+      </c>
+      <c r="L25" t="n">
+        <v>21.71478279751009</v>
+      </c>
+      <c r="M25" t="n">
+        <v>84.99731831245673</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>11.42389399695365</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-15295.2724659305</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-6.22833573357866</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.000000000000031e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8304992596469074</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>921.4680000000001</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.8981686081363354</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1328.342019612693</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9109094241971837</v>
+      </c>
+      <c r="F26" t="n">
+        <v>4.4482e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-62.977</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.4779005524862077</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.7511383537652727</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.320843672456632</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1.952305825242832</v>
+      </c>
+      <c r="L26" t="n">
+        <v>22.05487035432486</v>
+      </c>
+      <c r="M26" t="n">
+        <v>85.10076522835156</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>11.66632610415554</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-15427.87373519644</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-7.954005026388359</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.000000000003143e-08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8307662655285678</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>905.664</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.8827642135366458</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1312.997527421006</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9003869515654712</v>
+      </c>
+      <c r="F27" t="n">
+        <v>4.464e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-63.37</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.2385026737967876</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.794736842105481</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.683693045563587</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.339237057220706</v>
+      </c>
+      <c r="L27" t="n">
+        <v>22.66860832030125</v>
+      </c>
+      <c r="M27" t="n">
+        <v>85.17445459739281</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>11.84534365146112</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-15479.41308114051</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-8.420100334998438</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.000000000000148e-08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.831079933509654</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>889.5640000000001</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.8670713033205614</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1299.466354084852</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.8911079608158284</v>
+      </c>
+      <c r="F28" t="n">
+        <v>4.48057e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-63.711</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.3026011560693581</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.014900662251685</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.462889518413593</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1.653756260433965</v>
+      </c>
+      <c r="L28" t="n">
+        <v>19.63312384001986</v>
+      </c>
+      <c r="M28" t="n">
+        <v>84.97736917416218</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>11.37828810445258</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-14655.40463624706</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-9.762411025412803</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8314204096666354</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>880.3820000000001</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.8581214709227919</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1283.853064178501</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.8804011603770646</v>
+      </c>
+      <c r="F29" t="n">
+        <v>4.49997e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-64.059</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.9942652329749699</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.7861367837338074</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.65007363770251</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.082857142857144</v>
+      </c>
+      <c r="L29" t="n">
+        <v>28.86037771684565</v>
+      </c>
+      <c r="M29" t="n">
+        <v>85.46998644276681</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>12.62167155502846</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-16151.19265390456</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-9.646127287735339</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8318144207924617</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>861.3890000000001</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.8396087104424135</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1270.15165945778</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.8710054335984417</v>
+      </c>
+      <c r="F30" t="n">
+        <v>4.51829e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-64.401</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.1920378057503442</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.833853234528754</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.238893268107457</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.481245105043041</v>
+      </c>
+      <c r="L30" t="n">
+        <v>42.78520824174625</v>
+      </c>
+      <c r="M30" t="n">
+        <v>84.91003985232454</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>11.22699856954115</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-14092.42771567705</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-10.90175971386248</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.000000000001317e-08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8322144141010407</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>849.6870000000001</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.8282025964456047</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1314.975370373608</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.9017432557089122</v>
+      </c>
+      <c r="F31" t="n">
+        <v>4.53622e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-64.711</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.4387559808613274</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.2831481481481596</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.068999999999959</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1.635197368421106</v>
+      </c>
+      <c r="L31" t="n">
+        <v>20.16213179664474</v>
+      </c>
+      <c r="M31" t="n">
+        <v>85.16621755379342</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>11.82506265236012</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-14710.90490501782</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-47.38415916447627</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.8325963459740516</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>835.6020000000001</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.8144737367938313</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1244.553892422858</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8534517863553072</v>
+      </c>
+      <c r="F32" t="n">
+        <v>4.55476e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-65.02</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.2861471861471886</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.4825737265415453</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.772870662460241</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1.442966360856256</v>
+      </c>
+      <c r="L32" t="n">
+        <v>20.47736623949968</v>
+      </c>
+      <c r="M32" t="n">
+        <v>85.15250549842341</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>11.79145375214653</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-14504.05841288523</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-12.80006624480347</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.000000000000034e-08</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.8329994601735757</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>826.7269999999999</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.8058231418765794</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1228.223621976987</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.8422533171138015</v>
+      </c>
+      <c r="F33" t="n">
+        <v>4.57073e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-65.31399999999999</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.09839572192512704</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.286227544910314</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.09407744874719</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.014917127071719</v>
+      </c>
+      <c r="L33" t="n">
+        <v>20.25625930435349</v>
+      </c>
+      <c r="M33" t="n">
+        <v>85.2212811840911</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>11.9619640130516</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-14552.66473296584</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-11.22181173115177</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.000000000000003e-08</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.8334056593467165</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>815.9640000000001</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.7953322851898891</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1285.129302470806</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8812763397140251</v>
+      </c>
+      <c r="F34" t="n">
+        <v>4.58828e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-65.62</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.181249999999945</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.9119842829076278</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.323005565862668</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.130316091953885</v>
+      </c>
+      <c r="L34" t="n">
+        <v>23.24862057931246</v>
+      </c>
+      <c r="M34" t="n">
+        <v>85.41877434052572</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>12.47998475007076</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-15045.93913038232</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-55.04649914485083</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.000000000000078e-08</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.8338248196596109</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>799.6709999999999</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.7794512549941955</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1203.93493876787</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8255973730046361</v>
+      </c>
+      <c r="F35" t="n">
+        <v>4.60394e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-65.905</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.3720095693780042</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.122155777190177</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.659365397298413</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2.766965838000641</v>
+      </c>
+      <c r="L35" t="n">
+        <v>32.65969620253188</v>
+      </c>
+      <c r="M35" t="n">
+        <v>85.07401703520414</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>11.60266701426827</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-13777.00809800909</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>-12.76695398982486</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.000000000000171e-08</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.8342537658259238</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>787.1419999999999</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.7672390517583368</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1192.189117949273</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8175426862442857</v>
+      </c>
+      <c r="F36" t="n">
+        <v>4.6214e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-66.20099999999999</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.67687704723382</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.6032434399715112</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.472247455703861</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.78376754829137</v>
+      </c>
+      <c r="L36" t="n">
+        <v>25.4240100242232</v>
+      </c>
+      <c r="M36" t="n">
+        <v>85.05343488771216</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>11.55415029024188</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-13556.95033914214</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-14.22555459172236</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.8346901559036031</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>778.432</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.7587492848029272</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1178.85704744535</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.8084002300946065</v>
+      </c>
+      <c r="F37" t="n">
+        <v>4.63978e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-66.502</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.8430693069305298</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.8702127659573708</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1.801005025125543</v>
+      </c>
+      <c r="L37" t="n">
+        <v>19.67539403564603</v>
+      </c>
+      <c r="M37" t="n">
+        <v>85.18410989860938</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>11.86920475533394</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-13791.09269012721</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-14.19134460834653</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.8351238211759799</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>759.7130000000001</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.7405035962106983</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1163.762185914474</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.7980489414788663</v>
+      </c>
+      <c r="F38" t="n">
+        <v>4.65652e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-66.773</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.4712657712658155</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.7040077021100273</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.6063234903741286</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1.954908715377978</v>
+      </c>
+      <c r="L38" t="n">
+        <v>19.51201810419492</v>
+      </c>
+      <c r="M38" t="n">
+        <v>84.62129534688206</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>10.62102748036397</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-12114.95481458074</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-13.07111331733745</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.8355662219531531</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>753.1580000000001</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.7341143399084353</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1154.185290834239</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.7914815937217903</v>
+      </c>
+      <c r="F39" t="n">
+        <v>4.67156e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-67.05</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.6880705894974548</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.7912295884234384</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.570389473952497</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2.892066472090487</v>
+      </c>
+      <c r="L39" t="n">
+        <v>7.467353394552998</v>
+      </c>
+      <c r="M39" t="n">
+        <v>85.1099176869902</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>11.68826792808816</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-13244.15151782749</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-15.94911931922627</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.8359988410809432</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>743.519</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.7247190627921098</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1139.90253555826</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.7816872062882096</v>
+      </c>
+      <c r="F40" t="n">
+        <v>4.69099e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-67.354</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1.206024096385668</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.2457420924574034</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.9860406091370371</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1.900176056337989</v>
+      </c>
+      <c r="L40" t="n">
+        <v>18.40174427863388</v>
+      </c>
+      <c r="M40" t="n">
+        <v>85.22997130373646</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>11.98385782316719</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-13431.36814650586</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-15.52335261794383</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.8364540256777742</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>733.282</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.7147409061534727</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1126.941872296442</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.7727994423428377</v>
+      </c>
+      <c r="F41" t="n">
+        <v>4.70661e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-67.621</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.726046511628043</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.9042857142856076</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.9712830957229582</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2.497441860464951</v>
+      </c>
+      <c r="L41" t="n">
+        <v>19.17480637916633</v>
+      </c>
+      <c r="M41" t="n">
+        <v>85.32974306621261</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>12.24104606733497</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-13563.15286952507</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>-15.80795251322502</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.000000000000037e-08</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.8369004121880459</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>720.221</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.7020101545800392</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1112.130786068523</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7626427524027409</v>
+      </c>
+      <c r="F42" t="n">
+        <v>4.72531e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-67.929</v>
+      </c>
+      <c r="H42" t="n">
+        <v>6.089583333335669</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.5324808184143263</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.507808564231701</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.675921908893697</v>
+      </c>
+      <c r="L42" t="n">
+        <v>18.05679882031519</v>
+      </c>
+      <c r="M42" t="n">
+        <v>85.26851256380095</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>12.08192537796969</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-13210.89265957081</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-15.01468738046265</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.8373681415220726</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>705.5419999999999</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.6877023142656351</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1098.621903499401</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.7533790475278668</v>
+      </c>
+      <c r="F43" t="n">
+        <v>4.74299e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-68.20099999999999</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.2973384788081177</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.7345885745662486</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.673662794417919</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2.357975477350953</v>
+      </c>
+      <c r="L43" t="n">
+        <v>10.89948957310489</v>
+      </c>
+      <c r="M43" t="n">
+        <v>84.95704401492692</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>11.33219272521159</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-12189.99184383551</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>-15.3003012725485</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.000000000000018e-08</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.8378569494704342</v>
       </c>
     </row>
@@ -9946,7 +17778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10651,6 +18483,566 @@
         <v>0.8350318826856246</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>888.883</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1379.348012490791</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>4.51846e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-60.94</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.7376404494381527</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.6620915032679756</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.02399425287359</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.566666666666626</v>
+      </c>
+      <c r="L12" t="n">
+        <v>15.59733288311291</v>
+      </c>
+      <c r="M12" t="n">
+        <v>84.18378291574035</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>9.817178039847603</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-12737.63958463638</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-70.29711685387645</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.000000000000982e-08</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.8319789203211562</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>764.0119999999999</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.8595191943146623</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1208.83228379352</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.8763794726543606</v>
+      </c>
+      <c r="F13" t="n">
+        <v>4.66674e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-64.833</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.05116809277189791</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.4741520002765883</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.213726047648821</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.202898614834687</v>
+      </c>
+      <c r="L13" t="n">
+        <v>29.05123986674472</v>
+      </c>
+      <c r="M13" t="n">
+        <v>84.93799595836562</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>11.28932882962558</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-13245.03810169215</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-29.57584267053085</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.000000000000003e-08</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8323125432047137</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>738.019</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.8302768755843007</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1175.286319905606</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.852059312996221</v>
+      </c>
+      <c r="F14" t="n">
+        <v>4.6716e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-66.04000000000001</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.4224094649249371</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.7330957864454616</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.970781877833805</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.743928954267056</v>
+      </c>
+      <c r="L14" t="n">
+        <v>49.99083641701312</v>
+      </c>
+      <c r="M14" t="n">
+        <v>85.37416272287376</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>12.35911063946338</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-14172.60819647558</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-26.24447141704729</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8324771989517259</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>720.3130000000001</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.8103574936183953</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1167.538921071044</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.8464426022282314</v>
+      </c>
+      <c r="F15" t="n">
+        <v>4.67022e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-66.717</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.5130701296414133</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.8541903661457602</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.721826030128872</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.824414084164798</v>
+      </c>
+      <c r="L15" t="n">
+        <v>54.13847522499942</v>
+      </c>
+      <c r="M15" t="n">
+        <v>85.45124352320212</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>12.56944678295664</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-14182.59212932005</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-33.29788446911789</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.8326966992689748</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>703.7619999999999</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.791737495260906</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1154.827105124661</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.8372267873423066</v>
+      </c>
+      <c r="F16" t="n">
+        <v>4.67225e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-67.209</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.4725976581180024</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.075625970623147</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.10372332135491</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.825157797240739</v>
+      </c>
+      <c r="L16" t="n">
+        <v>54.94102559160388</v>
+      </c>
+      <c r="M16" t="n">
+        <v>85.52715115959077</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>12.78365128250039</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-14216.79492881361</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-35.95404866241518</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.8329860328488268</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>691.2249999999999</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.7776332768204588</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1196.961086529712</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.8677730896702931</v>
+      </c>
+      <c r="F17" t="n">
+        <v>4.68074e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-67.607</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.6179954441912824</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.8672097759674261</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.8335302806499133</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.670938897168394</v>
+      </c>
+      <c r="L17" t="n">
+        <v>24.07162065564544</v>
+      </c>
+      <c r="M17" t="n">
+        <v>85.74056446904169</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>13.42670635771172</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-14753.17619692637</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-73.90044548663536</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.833340525675825</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>670.2239999999999</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.7540069952963437</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1183.335302112138</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.8578946657379829</v>
+      </c>
+      <c r="F18" t="n">
+        <v>4.69062e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-67.997</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.1649680511182404</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.7280163425118001</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.042557025115498</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.656671067791302</v>
+      </c>
+      <c r="L18" t="n">
+        <v>24.01456330974726</v>
+      </c>
+      <c r="M18" t="n">
+        <v>85.16273897873488</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>11.81651850477065</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-12697.97441281812</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-75.52395684962164</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.8337176306061557</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>655.4949999999999</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.7374367605185382</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1169.563527737911</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.8479104019774842</v>
+      </c>
+      <c r="F19" t="n">
+        <v>4.70189e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-68.35599999999999</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.03890393440158307</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.1340777434343667</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.148836712913629</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.622559957075926</v>
+      </c>
+      <c r="L19" t="n">
+        <v>21.59716346479664</v>
+      </c>
+      <c r="M19" t="n">
+        <v>85.10010118566932</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>11.66473733014953</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-12339.30102183179</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-77.34740370335032</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.8341304710465119</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>643.347</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.7237701699773761</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1092.394586128003</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.791964447141505</v>
+      </c>
+      <c r="F20" t="n">
+        <v>4.71574e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-68.681</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.161245193329616</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.5857733146096377</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.283249964747706</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.13487202009813</v>
+      </c>
+      <c r="L20" t="n">
+        <v>29.97583159916922</v>
+      </c>
+      <c r="M20" t="n">
+        <v>85.42325054749543</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>12.49224272620482</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-13073.63139279546</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-37.20358665538674</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.8346108953997701</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>632.314</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.7113579627465031</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1075.650376403187</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.779825226601665</v>
+      </c>
+      <c r="F21" t="n">
+        <v>4.72768e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-68.98099999999999</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.4504338876803785</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.6973292985284389</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.214186034513914</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1.965843712635973</v>
+      </c>
+      <c r="L21" t="n">
+        <v>29.69119835096446</v>
+      </c>
+      <c r="M21" t="n">
+        <v>85.44698449543256</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>12.55763936947451</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-12978.06331141998</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-33.92634925564937</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.8350318826856246</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
